--- a/PENDING_APPROVAL_SHEET.xlsx
+++ b/PENDING_APPROVAL_SHEET.xlsx
@@ -742,8 +742,16 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr"/>
@@ -857,8 +865,16 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr"/>
@@ -980,8 +996,16 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
@@ -1091,8 +1115,16 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
@@ -1202,8 +1234,16 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
@@ -1327,8 +1367,16 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
@@ -1452,8 +1500,16 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
@@ -1577,8 +1633,16 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
@@ -1702,8 +1766,16 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="inlineStr"/>
@@ -1827,8 +1899,16 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr"/>
       <c r="AM11" t="inlineStr"/>
@@ -1940,8 +2020,16 @@
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
-      <c r="AJ12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr"/>
       <c r="AM12" t="inlineStr"/>
@@ -2051,8 +2139,16 @@
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="inlineStr"/>
       <c r="AM13" t="inlineStr"/>
@@ -2162,8 +2258,16 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="inlineStr"/>
       <c r="AM14" t="inlineStr"/>
@@ -2273,8 +2377,16 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr"/>
-      <c r="AJ15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="inlineStr"/>
       <c r="AM15" t="inlineStr"/>
@@ -2386,8 +2498,16 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr"/>
-      <c r="AJ16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK16" t="inlineStr"/>
       <c r="AL16" t="inlineStr"/>
       <c r="AM16" t="inlineStr"/>
@@ -2497,8 +2617,16 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
-      <c r="AJ17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="inlineStr"/>
       <c r="AM17" t="inlineStr"/>
@@ -2608,8 +2736,16 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
-      <c r="AJ18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="inlineStr"/>
       <c r="AM18" t="inlineStr"/>
@@ -2719,8 +2855,16 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr"/>
-      <c r="AJ19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK19" t="inlineStr"/>
       <c r="AL19" t="inlineStr"/>
       <c r="AM19" t="inlineStr"/>
@@ -2844,8 +2988,16 @@
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="inlineStr"/>
-      <c r="AJ20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK20" t="inlineStr"/>
       <c r="AL20" t="inlineStr"/>
       <c r="AM20" t="inlineStr"/>
@@ -2955,8 +3107,16 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr"/>
-      <c r="AJ21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="inlineStr"/>
       <c r="AM21" t="inlineStr"/>
@@ -3066,8 +3226,16 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr"/>
-      <c r="AI22" t="inlineStr"/>
-      <c r="AJ22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK22" t="inlineStr"/>
       <c r="AL22" t="inlineStr"/>
       <c r="AM22" t="inlineStr"/>
@@ -3177,8 +3345,16 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="inlineStr"/>
-      <c r="AJ23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK23" t="inlineStr"/>
       <c r="AL23" t="inlineStr"/>
       <c r="AM23" t="inlineStr"/>
@@ -3290,8 +3466,16 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="inlineStr"/>
-      <c r="AI24" t="inlineStr"/>
-      <c r="AJ24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK24" t="inlineStr"/>
       <c r="AL24" t="inlineStr"/>
       <c r="AM24" t="inlineStr"/>
@@ -3401,8 +3585,16 @@
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr"/>
-      <c r="AI25" t="inlineStr"/>
-      <c r="AJ25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK25" t="inlineStr"/>
       <c r="AL25" t="inlineStr"/>
       <c r="AM25" t="inlineStr"/>
@@ -3512,8 +3704,16 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr"/>
-      <c r="AI26" t="inlineStr"/>
-      <c r="AJ26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK26" t="inlineStr"/>
       <c r="AL26" t="inlineStr"/>
       <c r="AM26" t="inlineStr"/>
@@ -3637,8 +3837,16 @@
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr"/>
-      <c r="AI27" t="inlineStr"/>
-      <c r="AJ27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK27" t="inlineStr">
         <is>
           <t>HO</t>
@@ -3766,8 +3974,16 @@
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="inlineStr"/>
-      <c r="AI28" t="inlineStr"/>
-      <c r="AJ28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK28" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -3895,8 +4111,16 @@
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="inlineStr"/>
-      <c r="AI29" t="inlineStr"/>
-      <c r="AJ29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK29" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -4024,8 +4248,16 @@
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="inlineStr"/>
-      <c r="AI30" t="inlineStr"/>
-      <c r="AJ30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK30" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -4113,8 +4345,16 @@
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr"/>
-      <c r="AI31" t="inlineStr"/>
-      <c r="AJ31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK31" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -4242,8 +4482,16 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr"/>
-      <c r="AI32" t="inlineStr"/>
-      <c r="AJ32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK32" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -4371,8 +4619,16 @@
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr"/>
-      <c r="AI33" t="inlineStr"/>
-      <c r="AJ33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK33" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -4500,8 +4756,16 @@
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr"/>
-      <c r="AI34" t="inlineStr"/>
-      <c r="AJ34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK34" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -4629,8 +4893,16 @@
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="inlineStr"/>
-      <c r="AI35" t="inlineStr"/>
-      <c r="AJ35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK35" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -4758,8 +5030,16 @@
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="inlineStr"/>
-      <c r="AI36" t="inlineStr"/>
-      <c r="AJ36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK36" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -4887,8 +5167,16 @@
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="inlineStr"/>
-      <c r="AI37" t="inlineStr"/>
-      <c r="AJ37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK37" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -5016,8 +5304,16 @@
       <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="inlineStr"/>
-      <c r="AI38" t="inlineStr"/>
-      <c r="AJ38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK38" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -5135,8 +5431,16 @@
       <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="inlineStr"/>
       <c r="AH39" t="inlineStr"/>
-      <c r="AI39" t="inlineStr"/>
-      <c r="AJ39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK39" t="inlineStr">
         <is>
           <t>HO</t>
@@ -5264,8 +5568,16 @@
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="inlineStr"/>
       <c r="AH40" t="inlineStr"/>
-      <c r="AI40" t="inlineStr"/>
-      <c r="AJ40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK40" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -5389,8 +5701,16 @@
       <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="inlineStr"/>
-      <c r="AI41" t="inlineStr"/>
-      <c r="AJ41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK41" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -5504,8 +5824,16 @@
       <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="inlineStr"/>
       <c r="AH42" t="inlineStr"/>
-      <c r="AI42" t="inlineStr"/>
-      <c r="AJ42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK42" t="inlineStr"/>
       <c r="AL42" t="inlineStr"/>
       <c r="AM42" t="inlineStr"/>
@@ -5631,8 +5959,16 @@
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="inlineStr"/>
       <c r="AH43" t="inlineStr"/>
-      <c r="AI43" t="inlineStr"/>
-      <c r="AJ43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK43" t="inlineStr"/>
       <c r="AL43" t="inlineStr"/>
       <c r="AM43" t="inlineStr"/>
@@ -5722,8 +6058,16 @@
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="inlineStr"/>
-      <c r="AI44" t="inlineStr"/>
-      <c r="AJ44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK44" t="inlineStr"/>
       <c r="AL44" t="inlineStr"/>
       <c r="AM44" t="inlineStr"/>
@@ -5837,8 +6181,16 @@
       <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="inlineStr"/>
       <c r="AH45" t="inlineStr"/>
-      <c r="AI45" t="inlineStr"/>
-      <c r="AJ45" t="inlineStr"/>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK45" t="inlineStr"/>
       <c r="AL45" t="inlineStr"/>
       <c r="AM45" t="inlineStr"/>
@@ -5952,8 +6304,16 @@
       <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="inlineStr"/>
       <c r="AH46" t="inlineStr"/>
-      <c r="AI46" t="inlineStr"/>
-      <c r="AJ46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK46" t="inlineStr"/>
       <c r="AL46" t="inlineStr"/>
       <c r="AM46" t="inlineStr"/>
@@ -6067,8 +6427,16 @@
       <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="inlineStr"/>
       <c r="AH47" t="inlineStr"/>
-      <c r="AI47" t="inlineStr"/>
-      <c r="AJ47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK47" t="inlineStr"/>
       <c r="AL47" t="inlineStr"/>
       <c r="AM47" t="inlineStr"/>
@@ -6182,8 +6550,16 @@
       <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="inlineStr"/>
       <c r="AH48" t="inlineStr"/>
-      <c r="AI48" t="inlineStr"/>
-      <c r="AJ48" t="inlineStr"/>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK48" t="inlineStr"/>
       <c r="AL48" t="inlineStr"/>
       <c r="AM48" t="inlineStr"/>
@@ -6297,8 +6673,16 @@
       <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="inlineStr"/>
       <c r="AH49" t="inlineStr"/>
-      <c r="AI49" t="inlineStr"/>
-      <c r="AJ49" t="inlineStr"/>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK49" t="inlineStr"/>
       <c r="AL49" t="inlineStr"/>
       <c r="AM49" t="inlineStr"/>
@@ -6422,8 +6806,16 @@
       <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="inlineStr"/>
       <c r="AH50" t="inlineStr"/>
-      <c r="AI50" t="inlineStr"/>
-      <c r="AJ50" t="inlineStr"/>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK50" t="inlineStr">
         <is>
           <t>HO</t>
@@ -6551,8 +6943,16 @@
       <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="inlineStr"/>
       <c r="AH51" t="inlineStr"/>
-      <c r="AI51" t="inlineStr"/>
-      <c r="AJ51" t="inlineStr"/>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK51" t="inlineStr">
         <is>
           <t>HO</t>
@@ -6680,8 +7080,16 @@
       <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="inlineStr"/>
       <c r="AH52" t="inlineStr"/>
-      <c r="AI52" t="inlineStr"/>
-      <c r="AJ52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK52" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -6809,8 +7217,16 @@
       <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="inlineStr"/>
       <c r="AH53" t="inlineStr"/>
-      <c r="AI53" t="inlineStr"/>
-      <c r="AJ53" t="inlineStr"/>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK53" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -6938,8 +7354,16 @@
       <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="inlineStr"/>
       <c r="AH54" t="inlineStr"/>
-      <c r="AI54" t="inlineStr"/>
-      <c r="AJ54" t="inlineStr"/>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK54" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -7053,8 +7477,16 @@
       <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="inlineStr"/>
       <c r="AH55" t="inlineStr"/>
-      <c r="AI55" t="inlineStr"/>
-      <c r="AJ55" t="inlineStr"/>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK55" t="inlineStr"/>
       <c r="AL55" t="inlineStr"/>
       <c r="AM55" t="inlineStr"/>
@@ -7164,8 +7596,16 @@
       <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="inlineStr"/>
       <c r="AH56" t="inlineStr"/>
-      <c r="AI56" t="inlineStr"/>
-      <c r="AJ56" t="inlineStr"/>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK56" t="inlineStr"/>
       <c r="AL56" t="inlineStr"/>
       <c r="AM56" t="inlineStr"/>
@@ -7275,8 +7715,16 @@
       <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="inlineStr"/>
       <c r="AH57" t="inlineStr"/>
-      <c r="AI57" t="inlineStr"/>
-      <c r="AJ57" t="inlineStr"/>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK57" t="inlineStr"/>
       <c r="AL57" t="inlineStr"/>
       <c r="AM57" t="inlineStr"/>
@@ -7386,8 +7834,16 @@
       <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="inlineStr"/>
       <c r="AH58" t="inlineStr"/>
-      <c r="AI58" t="inlineStr"/>
-      <c r="AJ58" t="inlineStr"/>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK58" t="inlineStr"/>
       <c r="AL58" t="inlineStr"/>
       <c r="AM58" t="inlineStr"/>
@@ -7497,8 +7953,16 @@
       <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="inlineStr"/>
       <c r="AH59" t="inlineStr"/>
-      <c r="AI59" t="inlineStr"/>
-      <c r="AJ59" t="inlineStr"/>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK59" t="inlineStr"/>
       <c r="AL59" t="inlineStr"/>
       <c r="AM59" t="inlineStr"/>
@@ -7608,8 +8072,16 @@
       <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="inlineStr"/>
       <c r="AH60" t="inlineStr"/>
-      <c r="AI60" t="inlineStr"/>
-      <c r="AJ60" t="inlineStr"/>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK60" t="inlineStr"/>
       <c r="AL60" t="inlineStr"/>
       <c r="AM60" t="inlineStr"/>
@@ -7733,8 +8205,16 @@
       <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr"/>
-      <c r="AI61" t="inlineStr"/>
-      <c r="AJ61" t="inlineStr"/>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK61" t="inlineStr"/>
       <c r="AL61" t="inlineStr"/>
       <c r="AM61" t="inlineStr"/>
@@ -7846,8 +8326,16 @@
       <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr"/>
-      <c r="AI62" t="inlineStr"/>
-      <c r="AJ62" t="inlineStr"/>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK62" t="inlineStr"/>
       <c r="AL62" t="inlineStr"/>
       <c r="AM62" t="inlineStr"/>
@@ -7957,8 +8445,16 @@
       <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="inlineStr"/>
       <c r="AH63" t="inlineStr"/>
-      <c r="AI63" t="inlineStr"/>
-      <c r="AJ63" t="inlineStr"/>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK63" t="inlineStr"/>
       <c r="AL63" t="inlineStr"/>
       <c r="AM63" t="inlineStr"/>
@@ -8068,8 +8564,16 @@
       <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="inlineStr"/>
       <c r="AH64" t="inlineStr"/>
-      <c r="AI64" t="inlineStr"/>
-      <c r="AJ64" t="inlineStr"/>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK64" t="inlineStr"/>
       <c r="AL64" t="inlineStr"/>
       <c r="AM64" t="inlineStr"/>
@@ -8179,8 +8683,16 @@
       <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="inlineStr"/>
       <c r="AH65" t="inlineStr"/>
-      <c r="AI65" t="inlineStr"/>
-      <c r="AJ65" t="inlineStr"/>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK65" t="inlineStr"/>
       <c r="AL65" t="inlineStr"/>
       <c r="AM65" t="inlineStr"/>
@@ -8292,8 +8804,16 @@
       <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="inlineStr"/>
       <c r="AH66" t="inlineStr"/>
-      <c r="AI66" t="inlineStr"/>
-      <c r="AJ66" t="inlineStr"/>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK66" t="inlineStr"/>
       <c r="AL66" t="inlineStr"/>
       <c r="AM66" t="inlineStr"/>
@@ -8403,8 +8923,16 @@
       <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="inlineStr"/>
       <c r="AH67" t="inlineStr"/>
-      <c r="AI67" t="inlineStr"/>
-      <c r="AJ67" t="inlineStr"/>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK67" t="inlineStr"/>
       <c r="AL67" t="inlineStr"/>
       <c r="AM67" t="inlineStr"/>
@@ -8516,8 +9044,16 @@
       <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="inlineStr"/>
       <c r="AH68" t="inlineStr"/>
-      <c r="AI68" t="inlineStr"/>
-      <c r="AJ68" t="inlineStr"/>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK68" t="inlineStr"/>
       <c r="AL68" t="inlineStr"/>
       <c r="AM68" t="inlineStr"/>
@@ -8627,8 +9163,16 @@
       <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="inlineStr"/>
       <c r="AH69" t="inlineStr"/>
-      <c r="AI69" t="inlineStr"/>
-      <c r="AJ69" t="inlineStr"/>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK69" t="inlineStr"/>
       <c r="AL69" t="inlineStr"/>
       <c r="AM69" t="inlineStr"/>
@@ -8740,8 +9284,16 @@
       <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="inlineStr"/>
       <c r="AH70" t="inlineStr"/>
-      <c r="AI70" t="inlineStr"/>
-      <c r="AJ70" t="inlineStr"/>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK70" t="inlineStr"/>
       <c r="AL70" t="inlineStr"/>
       <c r="AM70" t="inlineStr"/>
@@ -8851,8 +9403,16 @@
       <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="inlineStr"/>
       <c r="AH71" t="inlineStr"/>
-      <c r="AI71" t="inlineStr"/>
-      <c r="AJ71" t="inlineStr"/>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK71" t="inlineStr"/>
       <c r="AL71" t="inlineStr"/>
       <c r="AM71" t="inlineStr"/>
@@ -8972,8 +9532,16 @@
       <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="inlineStr"/>
       <c r="AH72" t="inlineStr"/>
-      <c r="AI72" t="inlineStr"/>
-      <c r="AJ72" t="inlineStr"/>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK72" t="inlineStr"/>
       <c r="AL72" t="inlineStr"/>
       <c r="AM72" t="inlineStr"/>
@@ -9087,8 +9655,16 @@
       <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="inlineStr"/>
       <c r="AH73" t="inlineStr"/>
-      <c r="AI73" t="inlineStr"/>
-      <c r="AJ73" t="inlineStr"/>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK73" t="inlineStr"/>
       <c r="AL73" t="inlineStr"/>
       <c r="AM73" t="inlineStr"/>
@@ -9202,8 +9778,16 @@
       <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="inlineStr"/>
       <c r="AH74" t="inlineStr"/>
-      <c r="AI74" t="inlineStr"/>
-      <c r="AJ74" t="inlineStr"/>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK74" t="inlineStr"/>
       <c r="AL74" t="inlineStr"/>
       <c r="AM74" t="inlineStr"/>
@@ -9317,8 +9901,16 @@
       <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="inlineStr"/>
       <c r="AH75" t="inlineStr"/>
-      <c r="AI75" t="inlineStr"/>
-      <c r="AJ75" t="inlineStr"/>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK75" t="inlineStr"/>
       <c r="AL75" t="inlineStr"/>
       <c r="AM75" t="inlineStr"/>
@@ -9432,8 +10024,16 @@
       <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="inlineStr"/>
       <c r="AH76" t="inlineStr"/>
-      <c r="AI76" t="inlineStr"/>
-      <c r="AJ76" t="inlineStr"/>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK76" t="inlineStr"/>
       <c r="AL76" t="inlineStr"/>
       <c r="AM76" t="inlineStr"/>
@@ -9543,8 +10143,16 @@
       <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="inlineStr"/>
       <c r="AH77" t="inlineStr"/>
-      <c r="AI77" t="inlineStr"/>
-      <c r="AJ77" t="inlineStr"/>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK77" t="inlineStr"/>
       <c r="AL77" t="inlineStr"/>
       <c r="AM77" t="inlineStr"/>
@@ -9656,8 +10264,16 @@
       <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="inlineStr"/>
       <c r="AH78" t="inlineStr"/>
-      <c r="AI78" t="inlineStr"/>
-      <c r="AJ78" t="inlineStr"/>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK78" t="inlineStr"/>
       <c r="AL78" t="inlineStr"/>
       <c r="AM78" t="inlineStr"/>
@@ -9769,8 +10385,16 @@
       <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="inlineStr"/>
       <c r="AH79" t="inlineStr"/>
-      <c r="AI79" t="inlineStr"/>
-      <c r="AJ79" t="inlineStr"/>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK79" t="inlineStr"/>
       <c r="AL79" t="inlineStr"/>
       <c r="AM79" t="inlineStr"/>
@@ -9882,8 +10506,16 @@
       <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="inlineStr"/>
       <c r="AH80" t="inlineStr"/>
-      <c r="AI80" t="inlineStr"/>
-      <c r="AJ80" t="inlineStr"/>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK80" t="inlineStr"/>
       <c r="AL80" t="inlineStr"/>
       <c r="AM80" t="inlineStr"/>
@@ -9995,8 +10627,16 @@
       <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="inlineStr"/>
       <c r="AH81" t="inlineStr"/>
-      <c r="AI81" t="inlineStr"/>
-      <c r="AJ81" t="inlineStr"/>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK81" t="inlineStr"/>
       <c r="AL81" t="inlineStr"/>
       <c r="AM81" t="inlineStr"/>
@@ -10108,8 +10748,16 @@
       <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="inlineStr"/>
       <c r="AH82" t="inlineStr"/>
-      <c r="AI82" t="inlineStr"/>
-      <c r="AJ82" t="inlineStr"/>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK82" t="inlineStr"/>
       <c r="AL82" t="inlineStr"/>
       <c r="AM82" t="inlineStr"/>
@@ -10233,8 +10881,16 @@
       <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="inlineStr"/>
       <c r="AH83" t="inlineStr"/>
-      <c r="AI83" t="inlineStr"/>
-      <c r="AJ83" t="inlineStr"/>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK83" t="inlineStr"/>
       <c r="AL83" t="inlineStr"/>
       <c r="AM83" t="inlineStr"/>
@@ -10346,8 +11002,16 @@
       <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="inlineStr"/>
       <c r="AH84" t="inlineStr"/>
-      <c r="AI84" t="inlineStr"/>
-      <c r="AJ84" t="inlineStr"/>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK84" t="inlineStr"/>
       <c r="AL84" t="inlineStr"/>
       <c r="AM84" t="inlineStr"/>
@@ -10459,8 +11123,16 @@
       <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="inlineStr"/>
       <c r="AH85" t="inlineStr"/>
-      <c r="AI85" t="inlineStr"/>
-      <c r="AJ85" t="inlineStr"/>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK85" t="inlineStr"/>
       <c r="AL85" t="inlineStr"/>
       <c r="AM85" t="inlineStr"/>
@@ -10572,8 +11244,16 @@
       <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="inlineStr"/>
       <c r="AH86" t="inlineStr"/>
-      <c r="AI86" t="inlineStr"/>
-      <c r="AJ86" t="inlineStr"/>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK86" t="inlineStr"/>
       <c r="AL86" t="inlineStr"/>
       <c r="AM86" t="inlineStr"/>
@@ -10685,8 +11365,16 @@
       <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="inlineStr"/>
       <c r="AH87" t="inlineStr"/>
-      <c r="AI87" t="inlineStr"/>
-      <c r="AJ87" t="inlineStr"/>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK87" t="inlineStr"/>
       <c r="AL87" t="inlineStr"/>
       <c r="AM87" t="inlineStr"/>
@@ -10798,8 +11486,16 @@
       <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="inlineStr"/>
       <c r="AH88" t="inlineStr"/>
-      <c r="AI88" t="inlineStr"/>
-      <c r="AJ88" t="inlineStr"/>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK88" t="inlineStr"/>
       <c r="AL88" t="inlineStr"/>
       <c r="AM88" t="inlineStr"/>
@@ -10909,8 +11605,16 @@
       <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="inlineStr"/>
       <c r="AH89" t="inlineStr"/>
-      <c r="AI89" t="inlineStr"/>
-      <c r="AJ89" t="inlineStr"/>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK89" t="inlineStr"/>
       <c r="AL89" t="inlineStr"/>
       <c r="AM89" t="inlineStr"/>
@@ -11022,8 +11726,16 @@
       <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="inlineStr"/>
       <c r="AH90" t="inlineStr"/>
-      <c r="AI90" t="inlineStr"/>
-      <c r="AJ90" t="inlineStr"/>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK90" t="inlineStr"/>
       <c r="AL90" t="inlineStr"/>
       <c r="AM90" t="inlineStr"/>
@@ -11133,8 +11845,16 @@
       <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="inlineStr"/>
       <c r="AH91" t="inlineStr"/>
-      <c r="AI91" t="inlineStr"/>
-      <c r="AJ91" t="inlineStr"/>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK91" t="inlineStr"/>
       <c r="AL91" t="inlineStr"/>
       <c r="AM91" t="inlineStr"/>
@@ -11246,8 +11966,16 @@
       <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="inlineStr"/>
       <c r="AH92" t="inlineStr"/>
-      <c r="AI92" t="inlineStr"/>
-      <c r="AJ92" t="inlineStr"/>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK92" t="inlineStr"/>
       <c r="AL92" t="inlineStr"/>
       <c r="AM92" t="inlineStr"/>
@@ -11357,8 +12085,16 @@
       <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="inlineStr"/>
       <c r="AH93" t="inlineStr"/>
-      <c r="AI93" t="inlineStr"/>
-      <c r="AJ93" t="inlineStr"/>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK93" t="inlineStr"/>
       <c r="AL93" t="inlineStr"/>
       <c r="AM93" t="inlineStr"/>
@@ -11478,8 +12214,16 @@
       <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="inlineStr"/>
       <c r="AH94" t="inlineStr"/>
-      <c r="AI94" t="inlineStr"/>
-      <c r="AJ94" t="inlineStr"/>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK94" t="inlineStr"/>
       <c r="AL94" t="inlineStr"/>
       <c r="AM94" t="inlineStr"/>
@@ -11589,8 +12333,16 @@
       <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="inlineStr"/>
       <c r="AH95" t="inlineStr"/>
-      <c r="AI95" t="inlineStr"/>
-      <c r="AJ95" t="inlineStr"/>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK95" t="inlineStr"/>
       <c r="AL95" t="inlineStr"/>
       <c r="AM95" t="inlineStr"/>
@@ -11700,8 +12452,16 @@
       <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="inlineStr"/>
       <c r="AH96" t="inlineStr"/>
-      <c r="AI96" t="inlineStr"/>
-      <c r="AJ96" t="inlineStr"/>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK96" t="inlineStr"/>
       <c r="AL96" t="inlineStr"/>
       <c r="AM96" t="inlineStr"/>
@@ -11825,8 +12585,16 @@
       <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="inlineStr"/>
       <c r="AH97" t="inlineStr"/>
-      <c r="AI97" t="inlineStr"/>
-      <c r="AJ97" t="inlineStr"/>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK97" t="inlineStr"/>
       <c r="AL97" t="inlineStr"/>
       <c r="AM97" t="inlineStr"/>
@@ -11950,8 +12718,16 @@
       <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="inlineStr"/>
       <c r="AH98" t="inlineStr"/>
-      <c r="AI98" t="inlineStr"/>
-      <c r="AJ98" t="inlineStr"/>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK98" t="inlineStr"/>
       <c r="AL98" t="inlineStr"/>
       <c r="AM98" t="inlineStr"/>
@@ -12075,8 +12851,16 @@
       <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="inlineStr"/>
       <c r="AH99" t="inlineStr"/>
-      <c r="AI99" t="inlineStr"/>
-      <c r="AJ99" t="inlineStr"/>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK99" t="inlineStr"/>
       <c r="AL99" t="inlineStr"/>
       <c r="AM99" t="inlineStr"/>
@@ -12200,8 +12984,16 @@
       <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="inlineStr"/>
       <c r="AH100" t="inlineStr"/>
-      <c r="AI100" t="inlineStr"/>
-      <c r="AJ100" t="inlineStr"/>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK100" t="inlineStr"/>
       <c r="AL100" t="inlineStr"/>
       <c r="AM100" t="inlineStr"/>
@@ -12325,8 +13117,16 @@
       <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="inlineStr"/>
       <c r="AH101" t="inlineStr"/>
-      <c r="AI101" t="inlineStr"/>
-      <c r="AJ101" t="inlineStr"/>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK101" t="inlineStr">
         <is>
           <t>IOCL FEROKE</t>
@@ -12450,8 +13250,16 @@
       <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="inlineStr"/>
       <c r="AH102" t="inlineStr"/>
-      <c r="AI102" t="inlineStr"/>
-      <c r="AJ102" t="inlineStr"/>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK102" t="inlineStr">
         <is>
           <t>IOCL FEROKE</t>
@@ -12579,8 +13387,16 @@
       <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="inlineStr"/>
       <c r="AH103" t="inlineStr"/>
-      <c r="AI103" t="inlineStr"/>
-      <c r="AJ103" t="inlineStr"/>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK103" t="inlineStr">
         <is>
           <t>HO</t>
@@ -12708,8 +13524,16 @@
       <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="inlineStr"/>
       <c r="AH104" t="inlineStr"/>
-      <c r="AI104" t="inlineStr"/>
-      <c r="AJ104" t="inlineStr"/>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK104" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -12837,8 +13661,16 @@
       <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="inlineStr"/>
       <c r="AH105" t="inlineStr"/>
-      <c r="AI105" t="inlineStr"/>
-      <c r="AJ105" t="inlineStr"/>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK105" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -12966,8 +13798,16 @@
       <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="inlineStr"/>
       <c r="AH106" t="inlineStr"/>
-      <c r="AI106" t="inlineStr"/>
-      <c r="AJ106" t="inlineStr"/>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK106" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -13055,8 +13895,16 @@
       <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="inlineStr"/>
       <c r="AH107" t="inlineStr"/>
-      <c r="AI107" t="inlineStr"/>
-      <c r="AJ107" t="inlineStr"/>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK107" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -13184,8 +14032,16 @@
       <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="inlineStr"/>
       <c r="AH108" t="inlineStr"/>
-      <c r="AI108" t="inlineStr"/>
-      <c r="AJ108" t="inlineStr"/>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK108" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -13313,8 +14169,16 @@
       <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="inlineStr"/>
       <c r="AH109" t="inlineStr"/>
-      <c r="AI109" t="inlineStr"/>
-      <c r="AJ109" t="inlineStr"/>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK109" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -13442,8 +14306,16 @@
       <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="inlineStr"/>
       <c r="AH110" t="inlineStr"/>
-      <c r="AI110" t="inlineStr"/>
-      <c r="AJ110" t="inlineStr"/>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK110" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -13571,8 +14443,16 @@
       <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="inlineStr"/>
       <c r="AH111" t="inlineStr"/>
-      <c r="AI111" t="inlineStr"/>
-      <c r="AJ111" t="inlineStr"/>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK111" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -13700,8 +14580,16 @@
       <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="inlineStr"/>
       <c r="AH112" t="inlineStr"/>
-      <c r="AI112" t="inlineStr"/>
-      <c r="AJ112" t="inlineStr"/>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK112" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -13829,8 +14717,16 @@
       <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="inlineStr"/>
       <c r="AH113" t="inlineStr"/>
-      <c r="AI113" t="inlineStr"/>
-      <c r="AJ113" t="inlineStr"/>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK113" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -13958,8 +14854,16 @@
       <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="inlineStr"/>
       <c r="AH114" t="inlineStr"/>
-      <c r="AI114" t="inlineStr"/>
-      <c r="AJ114" t="inlineStr"/>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK114" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -14087,8 +14991,16 @@
       <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="inlineStr"/>
       <c r="AH115" t="inlineStr"/>
-      <c r="AI115" t="inlineStr"/>
-      <c r="AJ115" t="inlineStr"/>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK115" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -14212,8 +15124,16 @@
       <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="inlineStr"/>
       <c r="AH116" t="inlineStr"/>
-      <c r="AI116" t="inlineStr"/>
-      <c r="AJ116" t="inlineStr"/>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK116" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -14341,8 +15261,16 @@
       <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="inlineStr"/>
       <c r="AH117" t="inlineStr"/>
-      <c r="AI117" t="inlineStr"/>
-      <c r="AJ117" t="inlineStr"/>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK117" t="inlineStr">
         <is>
           <t>HO</t>
@@ -14470,8 +15398,16 @@
       <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="inlineStr"/>
       <c r="AH118" t="inlineStr"/>
-      <c r="AI118" t="inlineStr"/>
-      <c r="AJ118" t="inlineStr"/>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK118" t="inlineStr">
         <is>
           <t>HO</t>
@@ -14599,8 +15535,16 @@
       <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="inlineStr"/>
       <c r="AH119" t="inlineStr"/>
-      <c r="AI119" t="inlineStr"/>
-      <c r="AJ119" t="inlineStr"/>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK119" t="inlineStr">
         <is>
           <t>BELLARI</t>
@@ -14728,8 +15672,16 @@
       <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="inlineStr"/>
       <c r="AH120" t="inlineStr"/>
-      <c r="AI120" t="inlineStr"/>
-      <c r="AJ120" t="inlineStr"/>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK120" t="inlineStr">
         <is>
           <t>IOCL FEROKE</t>
@@ -14857,8 +15809,16 @@
       <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="inlineStr"/>
       <c r="AH121" t="inlineStr"/>
-      <c r="AI121" t="inlineStr"/>
-      <c r="AJ121" t="inlineStr"/>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK121" t="inlineStr">
         <is>
           <t>ONGC IPSHEM</t>
@@ -14986,8 +15946,16 @@
       <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="inlineStr"/>
       <c r="AH122" t="inlineStr"/>
-      <c r="AI122" t="inlineStr"/>
-      <c r="AJ122" t="inlineStr"/>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK122" t="inlineStr">
         <is>
           <t>ONGC IPSHEM</t>
@@ -15115,8 +16083,16 @@
       <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="inlineStr"/>
       <c r="AH123" t="inlineStr"/>
-      <c r="AI123" t="inlineStr"/>
-      <c r="AJ123" t="inlineStr"/>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK123" t="inlineStr">
         <is>
           <t>ONGC IPSHEM</t>
@@ -15244,8 +16220,16 @@
       <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="inlineStr"/>
       <c r="AH124" t="inlineStr"/>
-      <c r="AI124" t="inlineStr"/>
-      <c r="AJ124" t="inlineStr"/>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK124" t="inlineStr">
         <is>
           <t>ONGC IPSHEM</t>
@@ -15373,8 +16357,16 @@
       <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="inlineStr"/>
       <c r="AH125" t="inlineStr"/>
-      <c r="AI125" t="inlineStr"/>
-      <c r="AJ125" t="inlineStr"/>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK125" t="inlineStr">
         <is>
           <t>ONGC IPSHEM</t>
@@ -15502,8 +16494,16 @@
       <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="inlineStr"/>
       <c r="AH126" t="inlineStr"/>
-      <c r="AI126" t="inlineStr"/>
-      <c r="AJ126" t="inlineStr"/>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK126" t="inlineStr">
         <is>
           <t>ONGC IPSHEM</t>
@@ -15631,8 +16631,16 @@
       <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="inlineStr"/>
       <c r="AH127" t="inlineStr"/>
-      <c r="AI127" t="inlineStr"/>
-      <c r="AJ127" t="inlineStr"/>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK127" t="inlineStr">
         <is>
           <t>ONGC IPSHEM</t>
@@ -15760,8 +16768,16 @@
       <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="inlineStr"/>
       <c r="AH128" t="inlineStr"/>
-      <c r="AI128" t="inlineStr"/>
-      <c r="AJ128" t="inlineStr"/>
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK128" t="inlineStr">
         <is>
           <t>ONGC IPSHEM</t>
@@ -15889,8 +16905,16 @@
       <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="inlineStr"/>
       <c r="AH129" t="inlineStr"/>
-      <c r="AI129" t="inlineStr"/>
-      <c r="AJ129" t="inlineStr"/>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK129" t="inlineStr">
         <is>
           <t>ONGC IPSHEM</t>
@@ -16018,8 +17042,16 @@
       <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="inlineStr"/>
       <c r="AH130" t="inlineStr"/>
-      <c r="AI130" t="inlineStr"/>
-      <c r="AJ130" t="inlineStr"/>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK130" t="inlineStr">
         <is>
           <t>BELLARI</t>
@@ -16147,8 +17179,16 @@
       <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="inlineStr"/>
       <c r="AH131" t="inlineStr"/>
-      <c r="AI131" t="inlineStr"/>
-      <c r="AJ131" t="inlineStr"/>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK131" t="inlineStr">
         <is>
           <t>BELLARI</t>
@@ -16276,8 +17316,16 @@
       <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="inlineStr"/>
       <c r="AH132" t="inlineStr"/>
-      <c r="AI132" t="inlineStr"/>
-      <c r="AJ132" t="inlineStr"/>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK132" t="inlineStr">
         <is>
           <t>BELLARI</t>
@@ -16405,8 +17453,16 @@
       <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="inlineStr"/>
       <c r="AH133" t="inlineStr"/>
-      <c r="AI133" t="inlineStr"/>
-      <c r="AJ133" t="inlineStr"/>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK133" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -16534,8 +17590,16 @@
       <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="inlineStr"/>
       <c r="AH134" t="inlineStr"/>
-      <c r="AI134" t="inlineStr"/>
-      <c r="AJ134" t="inlineStr"/>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK134" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -16663,8 +17727,16 @@
       <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="inlineStr"/>
       <c r="AH135" t="inlineStr"/>
-      <c r="AI135" t="inlineStr"/>
-      <c r="AJ135" t="inlineStr"/>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK135" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -16792,8 +17864,16 @@
       <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="inlineStr"/>
       <c r="AH136" t="inlineStr"/>
-      <c r="AI136" t="inlineStr"/>
-      <c r="AJ136" t="inlineStr"/>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK136" t="inlineStr">
         <is>
           <t>BELLARI</t>
@@ -16921,8 +18001,16 @@
       <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="inlineStr"/>
       <c r="AH137" t="inlineStr"/>
-      <c r="AI137" t="inlineStr"/>
-      <c r="AJ137" t="inlineStr"/>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK137" t="inlineStr">
         <is>
           <t>BELLARI</t>
@@ -17050,8 +18138,16 @@
       <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="inlineStr"/>
       <c r="AH138" t="inlineStr"/>
-      <c r="AI138" t="inlineStr"/>
-      <c r="AJ138" t="inlineStr"/>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ138" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK138" t="inlineStr">
         <is>
           <t>BELLARI</t>
@@ -17179,8 +18275,16 @@
       <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="inlineStr"/>
       <c r="AH139" t="inlineStr"/>
-      <c r="AI139" t="inlineStr"/>
-      <c r="AJ139" t="inlineStr"/>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK139" t="inlineStr">
         <is>
           <t>BELLARI</t>
@@ -17308,8 +18412,16 @@
       <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="inlineStr"/>
       <c r="AH140" t="inlineStr"/>
-      <c r="AI140" t="inlineStr"/>
-      <c r="AJ140" t="inlineStr"/>
+      <c r="AI140" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK140" t="inlineStr">
         <is>
           <t>BELLARI</t>
@@ -17437,8 +18549,16 @@
       <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="inlineStr"/>
       <c r="AH141" t="inlineStr"/>
-      <c r="AI141" t="inlineStr"/>
-      <c r="AJ141" t="inlineStr"/>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK141" t="inlineStr"/>
       <c r="AL141" t="inlineStr"/>
       <c r="AM141" t="inlineStr"/>
@@ -17548,8 +18668,16 @@
       <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="inlineStr"/>
       <c r="AH142" t="inlineStr"/>
-      <c r="AI142" t="inlineStr"/>
-      <c r="AJ142" t="inlineStr"/>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK142" t="inlineStr"/>
       <c r="AL142" t="inlineStr"/>
       <c r="AM142" t="inlineStr"/>
@@ -17659,8 +18787,16 @@
       <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="inlineStr"/>
       <c r="AH143" t="inlineStr"/>
-      <c r="AI143" t="inlineStr"/>
-      <c r="AJ143" t="inlineStr"/>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK143" t="inlineStr"/>
       <c r="AL143" t="inlineStr"/>
       <c r="AM143" t="inlineStr"/>
@@ -17786,8 +18922,16 @@
       <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="inlineStr"/>
       <c r="AH144" t="inlineStr"/>
-      <c r="AI144" t="inlineStr"/>
-      <c r="AJ144" t="inlineStr"/>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK144" t="inlineStr"/>
       <c r="AL144" t="inlineStr"/>
       <c r="AM144" t="inlineStr"/>
@@ -17911,8 +19055,16 @@
       <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="inlineStr"/>
       <c r="AH145" t="inlineStr"/>
-      <c r="AI145" t="inlineStr"/>
-      <c r="AJ145" t="inlineStr"/>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK145" t="inlineStr"/>
       <c r="AL145" t="inlineStr"/>
       <c r="AM145" t="inlineStr"/>
@@ -18036,8 +19188,16 @@
       <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="inlineStr"/>
       <c r="AH146" t="inlineStr"/>
-      <c r="AI146" t="inlineStr"/>
-      <c r="AJ146" t="inlineStr"/>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK146" t="inlineStr">
         <is>
           <t>HO</t>
@@ -18165,8 +19325,16 @@
       <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="inlineStr"/>
       <c r="AH147" t="inlineStr"/>
-      <c r="AI147" t="inlineStr"/>
-      <c r="AJ147" t="inlineStr"/>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK147" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -18294,8 +19462,16 @@
       <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="inlineStr"/>
       <c r="AH148" t="inlineStr"/>
-      <c r="AI148" t="inlineStr"/>
-      <c r="AJ148" t="inlineStr"/>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK148" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -18423,8 +19599,16 @@
       <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="inlineStr"/>
       <c r="AH149" t="inlineStr"/>
-      <c r="AI149" t="inlineStr"/>
-      <c r="AJ149" t="inlineStr"/>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK149" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -18512,8 +19696,16 @@
       <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="inlineStr"/>
       <c r="AH150" t="inlineStr"/>
-      <c r="AI150" t="inlineStr"/>
-      <c r="AJ150" t="inlineStr"/>
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK150" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -18641,8 +19833,16 @@
       <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="inlineStr"/>
       <c r="AH151" t="inlineStr"/>
-      <c r="AI151" t="inlineStr"/>
-      <c r="AJ151" t="inlineStr"/>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK151" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -18770,8 +19970,16 @@
       <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="inlineStr"/>
       <c r="AH152" t="inlineStr"/>
-      <c r="AI152" t="inlineStr"/>
-      <c r="AJ152" t="inlineStr"/>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK152" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -18899,8 +20107,16 @@
       <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="inlineStr"/>
       <c r="AH153" t="inlineStr"/>
-      <c r="AI153" t="inlineStr"/>
-      <c r="AJ153" t="inlineStr"/>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK153" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -19028,8 +20244,16 @@
       <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="inlineStr"/>
       <c r="AH154" t="inlineStr"/>
-      <c r="AI154" t="inlineStr"/>
-      <c r="AJ154" t="inlineStr"/>
+      <c r="AI154" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ154" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK154" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -19157,8 +20381,16 @@
       <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="inlineStr"/>
       <c r="AH155" t="inlineStr"/>
-      <c r="AI155" t="inlineStr"/>
-      <c r="AJ155" t="inlineStr"/>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK155" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -19286,8 +20518,16 @@
       <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="inlineStr"/>
       <c r="AH156" t="inlineStr"/>
-      <c r="AI156" t="inlineStr"/>
-      <c r="AJ156" t="inlineStr"/>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK156" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -19415,8 +20655,16 @@
       <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="inlineStr"/>
       <c r="AH157" t="inlineStr"/>
-      <c r="AI157" t="inlineStr"/>
-      <c r="AJ157" t="inlineStr"/>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK157" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -19544,8 +20792,16 @@
       <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="inlineStr"/>
       <c r="AH158" t="inlineStr"/>
-      <c r="AI158" t="inlineStr"/>
-      <c r="AJ158" t="inlineStr"/>
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ158" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK158" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -19669,8 +20925,16 @@
       <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="inlineStr"/>
       <c r="AH159" t="inlineStr"/>
-      <c r="AI159" t="inlineStr"/>
-      <c r="AJ159" t="inlineStr"/>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK159" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -19784,8 +21048,16 @@
       <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="inlineStr"/>
       <c r="AH160" t="inlineStr"/>
-      <c r="AI160" t="inlineStr"/>
-      <c r="AJ160" t="inlineStr"/>
+      <c r="AI160" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ160" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK160" t="inlineStr"/>
       <c r="AL160" t="inlineStr"/>
       <c r="AM160" t="inlineStr"/>
@@ -19895,8 +21167,16 @@
       <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="inlineStr"/>
       <c r="AH161" t="inlineStr"/>
-      <c r="AI161" t="inlineStr"/>
-      <c r="AJ161" t="inlineStr"/>
+      <c r="AI161" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK161" t="inlineStr"/>
       <c r="AL161" t="inlineStr"/>
       <c r="AM161" t="inlineStr"/>
@@ -20008,8 +21288,16 @@
       <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="inlineStr"/>
       <c r="AH162" t="inlineStr"/>
-      <c r="AI162" t="inlineStr"/>
-      <c r="AJ162" t="inlineStr"/>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK162" t="inlineStr"/>
       <c r="AL162" t="inlineStr"/>
       <c r="AM162" t="inlineStr"/>
@@ -20119,8 +21407,16 @@
       <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="inlineStr"/>
       <c r="AH163" t="inlineStr"/>
-      <c r="AI163" t="inlineStr"/>
-      <c r="AJ163" t="inlineStr"/>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK163" t="inlineStr"/>
       <c r="AL163" t="inlineStr"/>
       <c r="AM163" t="inlineStr"/>
@@ -20242,8 +21538,16 @@
       <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="inlineStr"/>
       <c r="AH164" t="inlineStr"/>
-      <c r="AI164" t="inlineStr"/>
-      <c r="AJ164" t="inlineStr"/>
+      <c r="AI164" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK164" t="inlineStr"/>
       <c r="AL164" t="inlineStr"/>
       <c r="AM164" t="inlineStr"/>
@@ -20367,8 +21671,16 @@
       <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="inlineStr"/>
       <c r="AH165" t="inlineStr"/>
-      <c r="AI165" t="inlineStr"/>
-      <c r="AJ165" t="inlineStr"/>
+      <c r="AI165" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK165" t="inlineStr">
         <is>
           <t>KOLKATA</t>
@@ -20496,8 +21808,16 @@
       <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="inlineStr"/>
       <c r="AH166" t="inlineStr"/>
-      <c r="AI166" t="inlineStr"/>
-      <c r="AJ166" t="inlineStr"/>
+      <c r="AI166" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ166" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK166" t="inlineStr"/>
       <c r="AL166" t="inlineStr"/>
       <c r="AM166" t="inlineStr"/>
@@ -20621,8 +21941,16 @@
       <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="inlineStr"/>
       <c r="AH167" t="inlineStr"/>
-      <c r="AI167" t="inlineStr"/>
-      <c r="AJ167" t="inlineStr"/>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK167" t="inlineStr">
         <is>
           <t>BELLARI</t>
@@ -20750,8 +22078,16 @@
       <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="inlineStr"/>
       <c r="AH168" t="inlineStr"/>
-      <c r="AI168" t="inlineStr"/>
-      <c r="AJ168" t="inlineStr"/>
+      <c r="AI168" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ168" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK168" t="inlineStr"/>
       <c r="AL168" t="inlineStr"/>
       <c r="AM168" t="inlineStr"/>
@@ -20875,8 +22211,16 @@
       <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="inlineStr"/>
       <c r="AH169" t="inlineStr"/>
-      <c r="AI169" t="inlineStr"/>
-      <c r="AJ169" t="inlineStr"/>
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK169" t="inlineStr"/>
       <c r="AL169" t="inlineStr"/>
       <c r="AM169" t="inlineStr"/>
@@ -20986,8 +22330,16 @@
       <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="inlineStr"/>
       <c r="AH170" t="inlineStr"/>
-      <c r="AI170" t="inlineStr"/>
-      <c r="AJ170" t="inlineStr"/>
+      <c r="AI170" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK170" t="inlineStr"/>
       <c r="AL170" t="inlineStr"/>
       <c r="AM170" t="inlineStr"/>
@@ -21097,8 +22449,16 @@
       <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="inlineStr"/>
       <c r="AH171" t="inlineStr"/>
-      <c r="AI171" t="inlineStr"/>
-      <c r="AJ171" t="inlineStr"/>
+      <c r="AI171" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ171" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK171" t="inlineStr"/>
       <c r="AL171" t="inlineStr"/>
       <c r="AM171" t="inlineStr"/>
@@ -21208,8 +22568,16 @@
       <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="inlineStr"/>
       <c r="AH172" t="inlineStr"/>
-      <c r="AI172" t="inlineStr"/>
-      <c r="AJ172" t="inlineStr"/>
+      <c r="AI172" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ172" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK172" t="inlineStr"/>
       <c r="AL172" t="inlineStr"/>
       <c r="AM172" t="inlineStr"/>
@@ -21335,8 +22703,16 @@
       <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="inlineStr"/>
       <c r="AH173" t="inlineStr"/>
-      <c r="AI173" t="inlineStr"/>
-      <c r="AJ173" t="inlineStr"/>
+      <c r="AI173" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ173" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK173" t="inlineStr"/>
       <c r="AL173" t="inlineStr"/>
       <c r="AM173" t="inlineStr"/>
@@ -21450,8 +22826,16 @@
       <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="inlineStr"/>
       <c r="AH174" t="inlineStr"/>
-      <c r="AI174" t="inlineStr"/>
-      <c r="AJ174" t="inlineStr"/>
+      <c r="AI174" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ174" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK174" t="inlineStr"/>
       <c r="AL174" t="inlineStr"/>
       <c r="AM174" t="inlineStr"/>
@@ -21565,8 +22949,16 @@
       <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="inlineStr"/>
       <c r="AH175" t="inlineStr"/>
-      <c r="AI175" t="inlineStr"/>
-      <c r="AJ175" t="inlineStr"/>
+      <c r="AI175" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ175" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK175" t="inlineStr"/>
       <c r="AL175" t="inlineStr"/>
       <c r="AM175" t="inlineStr"/>
@@ -21680,8 +23072,16 @@
       <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="inlineStr"/>
       <c r="AH176" t="inlineStr"/>
-      <c r="AI176" t="inlineStr"/>
-      <c r="AJ176" t="inlineStr"/>
+      <c r="AI176" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ176" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK176" t="inlineStr"/>
       <c r="AL176" t="inlineStr"/>
       <c r="AM176" t="inlineStr"/>
@@ -21795,8 +23195,16 @@
       <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="inlineStr"/>
       <c r="AH177" t="inlineStr"/>
-      <c r="AI177" t="inlineStr"/>
-      <c r="AJ177" t="inlineStr"/>
+      <c r="AI177" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ177" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK177" t="inlineStr"/>
       <c r="AL177" t="inlineStr"/>
       <c r="AM177" t="inlineStr"/>
@@ -21910,8 +23318,16 @@
       <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="inlineStr"/>
       <c r="AH178" t="inlineStr"/>
-      <c r="AI178" t="inlineStr"/>
-      <c r="AJ178" t="inlineStr"/>
+      <c r="AI178" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ178" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK178" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -22029,8 +23445,16 @@
       <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="inlineStr"/>
       <c r="AH179" t="inlineStr"/>
-      <c r="AI179" t="inlineStr"/>
-      <c r="AJ179" t="inlineStr"/>
+      <c r="AI179" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ179" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
       <c r="AK179" t="inlineStr"/>
       <c r="AL179" t="inlineStr"/>
       <c r="AM179" t="inlineStr"/>
@@ -22144,8 +23568,16 @@
       <c r="AF180" t="inlineStr"/>
       <c r="AG180" t="inlineStr"/>
       <c r="AH180" t="inlineStr"/>
-      <c r="AI180" t="inlineStr"/>
-      <c r="AJ180" t="inlineStr"/>
+      <c r="AI180" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ180" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK180" t="inlineStr"/>
       <c r="AL180" t="inlineStr"/>
       <c r="AM180" t="inlineStr"/>
@@ -22259,8 +23691,16 @@
       <c r="AF181" t="inlineStr"/>
       <c r="AG181" t="inlineStr"/>
       <c r="AH181" t="inlineStr"/>
-      <c r="AI181" t="inlineStr"/>
-      <c r="AJ181" t="inlineStr"/>
+      <c r="AI181" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ181" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK181" t="inlineStr"/>
       <c r="AL181" t="inlineStr"/>
       <c r="AM181" t="inlineStr"/>
@@ -22374,8 +23814,16 @@
       <c r="AF182" t="inlineStr"/>
       <c r="AG182" t="inlineStr"/>
       <c r="AH182" t="inlineStr"/>
-      <c r="AI182" t="inlineStr"/>
-      <c r="AJ182" t="inlineStr"/>
+      <c r="AI182" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ182" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK182" t="inlineStr"/>
       <c r="AL182" t="inlineStr"/>
       <c r="AM182" t="inlineStr"/>
@@ -22489,8 +23937,16 @@
       <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="inlineStr"/>
       <c r="AH183" t="inlineStr"/>
-      <c r="AI183" t="inlineStr"/>
-      <c r="AJ183" t="inlineStr"/>
+      <c r="AI183" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ183" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK183" t="inlineStr"/>
       <c r="AL183" t="inlineStr"/>
       <c r="AM183" t="inlineStr"/>
@@ -22604,8 +24060,16 @@
       <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="inlineStr"/>
       <c r="AH184" t="inlineStr"/>
-      <c r="AI184" t="inlineStr"/>
-      <c r="AJ184" t="inlineStr"/>
+      <c r="AI184" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ184" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK184" t="inlineStr"/>
       <c r="AL184" t="inlineStr"/>
       <c r="AM184" t="inlineStr"/>
@@ -22719,8 +24183,16 @@
       <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="inlineStr"/>
       <c r="AH185" t="inlineStr"/>
-      <c r="AI185" t="inlineStr"/>
-      <c r="AJ185" t="inlineStr"/>
+      <c r="AI185" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ185" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK185" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -22850,8 +24322,16 @@
       <c r="AF186" t="inlineStr"/>
       <c r="AG186" t="inlineStr"/>
       <c r="AH186" t="inlineStr"/>
-      <c r="AI186" t="inlineStr"/>
-      <c r="AJ186" t="inlineStr"/>
+      <c r="AI186" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ186" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
       <c r="AK186" t="inlineStr"/>
       <c r="AL186" t="inlineStr"/>
       <c r="AM186" t="inlineStr"/>
@@ -22965,8 +24445,16 @@
       <c r="AF187" t="inlineStr"/>
       <c r="AG187" t="inlineStr"/>
       <c r="AH187" t="inlineStr"/>
-      <c r="AI187" t="inlineStr"/>
-      <c r="AJ187" t="inlineStr"/>
+      <c r="AI187" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ187" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
       <c r="AK187" t="inlineStr"/>
       <c r="AL187" t="inlineStr"/>
       <c r="AM187" t="inlineStr"/>
@@ -23080,8 +24568,16 @@
       <c r="AF188" t="inlineStr"/>
       <c r="AG188" t="inlineStr"/>
       <c r="AH188" t="inlineStr"/>
-      <c r="AI188" t="inlineStr"/>
-      <c r="AJ188" t="inlineStr"/>
+      <c r="AI188" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ188" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
       <c r="AK188" t="inlineStr"/>
       <c r="AL188" t="inlineStr"/>
       <c r="AM188" t="inlineStr"/>
@@ -23205,8 +24701,16 @@
       <c r="AF189" t="inlineStr"/>
       <c r="AG189" t="inlineStr"/>
       <c r="AH189" t="inlineStr"/>
-      <c r="AI189" t="inlineStr"/>
-      <c r="AJ189" t="inlineStr"/>
+      <c r="AI189" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ189" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK189" t="inlineStr"/>
       <c r="AL189" t="inlineStr"/>
       <c r="AM189" t="inlineStr"/>
@@ -23330,8 +24834,16 @@
       <c r="AF190" t="inlineStr"/>
       <c r="AG190" t="inlineStr"/>
       <c r="AH190" t="inlineStr"/>
-      <c r="AI190" t="inlineStr"/>
-      <c r="AJ190" t="inlineStr"/>
+      <c r="AI190" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ190" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK190" t="inlineStr">
         <is>
           <t>HO</t>
@@ -23459,8 +24971,16 @@
       <c r="AF191" t="inlineStr"/>
       <c r="AG191" t="inlineStr"/>
       <c r="AH191" t="inlineStr"/>
-      <c r="AI191" t="inlineStr"/>
-      <c r="AJ191" t="inlineStr"/>
+      <c r="AI191" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ191" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK191" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -23588,8 +25108,16 @@
       <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="inlineStr"/>
       <c r="AH192" t="inlineStr"/>
-      <c r="AI192" t="inlineStr"/>
-      <c r="AJ192" t="inlineStr"/>
+      <c r="AI192" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ192" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK192" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -23717,8 +25245,16 @@
       <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="inlineStr"/>
       <c r="AH193" t="inlineStr"/>
-      <c r="AI193" t="inlineStr"/>
-      <c r="AJ193" t="inlineStr"/>
+      <c r="AI193" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ193" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK193" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -23806,8 +25342,16 @@
       <c r="AF194" t="inlineStr"/>
       <c r="AG194" t="inlineStr"/>
       <c r="AH194" t="inlineStr"/>
-      <c r="AI194" t="inlineStr"/>
-      <c r="AJ194" t="inlineStr"/>
+      <c r="AI194" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ194" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK194" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -23935,8 +25479,16 @@
       <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="inlineStr"/>
       <c r="AH195" t="inlineStr"/>
-      <c r="AI195" t="inlineStr"/>
-      <c r="AJ195" t="inlineStr"/>
+      <c r="AI195" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ195" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK195" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -24064,8 +25616,16 @@
       <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="inlineStr"/>
       <c r="AH196" t="inlineStr"/>
-      <c r="AI196" t="inlineStr"/>
-      <c r="AJ196" t="inlineStr"/>
+      <c r="AI196" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ196" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK196" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -24193,8 +25753,16 @@
       <c r="AF197" t="inlineStr"/>
       <c r="AG197" t="inlineStr"/>
       <c r="AH197" t="inlineStr"/>
-      <c r="AI197" t="inlineStr"/>
-      <c r="AJ197" t="inlineStr"/>
+      <c r="AI197" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ197" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK197" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -24322,8 +25890,16 @@
       <c r="AF198" t="inlineStr"/>
       <c r="AG198" t="inlineStr"/>
       <c r="AH198" t="inlineStr"/>
-      <c r="AI198" t="inlineStr"/>
-      <c r="AJ198" t="inlineStr"/>
+      <c r="AI198" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ198" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK198" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -24451,8 +26027,16 @@
       <c r="AF199" t="inlineStr"/>
       <c r="AG199" t="inlineStr"/>
       <c r="AH199" t="inlineStr"/>
-      <c r="AI199" t="inlineStr"/>
-      <c r="AJ199" t="inlineStr"/>
+      <c r="AI199" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ199" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK199" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -24580,8 +26164,16 @@
       <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="inlineStr"/>
       <c r="AH200" t="inlineStr"/>
-      <c r="AI200" t="inlineStr"/>
-      <c r="AJ200" t="inlineStr"/>
+      <c r="AI200" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ200" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK200" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -24709,8 +26301,16 @@
       <c r="AF201" t="inlineStr"/>
       <c r="AG201" t="inlineStr"/>
       <c r="AH201" t="inlineStr"/>
-      <c r="AI201" t="inlineStr"/>
-      <c r="AJ201" t="inlineStr"/>
+      <c r="AI201" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ201" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK201" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -24838,8 +26438,16 @@
       <c r="AF202" t="inlineStr"/>
       <c r="AG202" t="inlineStr"/>
       <c r="AH202" t="inlineStr"/>
-      <c r="AI202" t="inlineStr"/>
-      <c r="AJ202" t="inlineStr"/>
+      <c r="AI202" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ202" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK202" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -24963,8 +26571,16 @@
       <c r="AF203" t="inlineStr"/>
       <c r="AG203" t="inlineStr"/>
       <c r="AH203" t="inlineStr"/>
-      <c r="AI203" t="inlineStr"/>
-      <c r="AJ203" t="inlineStr"/>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ203" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK203" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -25092,8 +26708,16 @@
       <c r="AF204" t="inlineStr"/>
       <c r="AG204" t="inlineStr"/>
       <c r="AH204" t="inlineStr"/>
-      <c r="AI204" t="inlineStr"/>
-      <c r="AJ204" t="inlineStr"/>
+      <c r="AI204" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ204" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK204" t="inlineStr"/>
       <c r="AL204" t="inlineStr"/>
       <c r="AM204" t="inlineStr"/>
@@ -25217,8 +26841,16 @@
       <c r="AF205" t="inlineStr"/>
       <c r="AG205" t="inlineStr"/>
       <c r="AH205" t="inlineStr"/>
-      <c r="AI205" t="inlineStr"/>
-      <c r="AJ205" t="inlineStr"/>
+      <c r="AI205" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ205" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK205" t="inlineStr">
         <is>
           <t>HO</t>
@@ -25334,8 +26966,16 @@
       <c r="AF206" t="inlineStr"/>
       <c r="AG206" t="inlineStr"/>
       <c r="AH206" t="inlineStr"/>
-      <c r="AI206" t="inlineStr"/>
-      <c r="AJ206" t="inlineStr"/>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ206" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK206" t="inlineStr"/>
       <c r="AL206" t="inlineStr"/>
       <c r="AM206" t="inlineStr"/>
@@ -25459,8 +27099,16 @@
       <c r="AF207" t="inlineStr"/>
       <c r="AG207" t="inlineStr"/>
       <c r="AH207" t="inlineStr"/>
-      <c r="AI207" t="inlineStr"/>
-      <c r="AJ207" t="inlineStr"/>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ207" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK207" t="inlineStr">
         <is>
           <t>BELLARI</t>
@@ -25588,8 +27236,16 @@
       <c r="AF208" t="inlineStr"/>
       <c r="AG208" t="inlineStr"/>
       <c r="AH208" t="inlineStr"/>
-      <c r="AI208" t="inlineStr"/>
-      <c r="AJ208" t="inlineStr"/>
+      <c r="AI208" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ208" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
       <c r="AK208" t="inlineStr">
         <is>
           <t>BELLARI</t>
@@ -25717,8 +27373,16 @@
       <c r="AF209" t="inlineStr"/>
       <c r="AG209" t="inlineStr"/>
       <c r="AH209" t="inlineStr"/>
-      <c r="AI209" t="inlineStr"/>
-      <c r="AJ209" t="inlineStr"/>
+      <c r="AI209" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ209" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
       <c r="AK209" t="inlineStr">
         <is>
           <t>HO</t>
@@ -25846,8 +27510,16 @@
       <c r="AF210" t="inlineStr"/>
       <c r="AG210" t="inlineStr"/>
       <c r="AH210" t="inlineStr"/>
-      <c r="AI210" t="inlineStr"/>
-      <c r="AJ210" t="inlineStr"/>
+      <c r="AI210" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ210" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
       <c r="AK210" t="inlineStr">
         <is>
           <t>BELLARI</t>
@@ -25975,8 +27647,16 @@
       <c r="AF211" t="inlineStr"/>
       <c r="AG211" t="inlineStr"/>
       <c r="AH211" t="inlineStr"/>
-      <c r="AI211" t="inlineStr"/>
-      <c r="AJ211" t="inlineStr"/>
+      <c r="AI211" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ211" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
       <c r="AK211" t="inlineStr">
         <is>
           <t>HO</t>
@@ -26104,8 +27784,16 @@
       <c r="AF212" t="inlineStr"/>
       <c r="AG212" t="inlineStr"/>
       <c r="AH212" t="inlineStr"/>
-      <c r="AI212" t="inlineStr"/>
-      <c r="AJ212" t="inlineStr"/>
+      <c r="AI212" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ212" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
       <c r="AK212" t="inlineStr"/>
       <c r="AL212" t="inlineStr"/>
       <c r="AM212" t="inlineStr"/>

--- a/PENDING_APPROVAL_SHEET.xlsx
+++ b/PENDING_APPROVAL_SHEET.xlsx
@@ -74483,16 +74483,8 @@
       <c r="AF595" t="inlineStr"/>
       <c r="AG595" t="inlineStr"/>
       <c r="AH595" t="inlineStr"/>
-      <c r="AI595" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ595" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
+      <c r="AI595" t="inlineStr"/>
+      <c r="AJ595" t="inlineStr"/>
       <c r="AK595" t="inlineStr">
         <is>
           <t>IOCL WILLINGTON</t>
@@ -74618,16 +74610,8 @@
       <c r="AF596" t="inlineStr"/>
       <c r="AG596" t="inlineStr"/>
       <c r="AH596" t="inlineStr"/>
-      <c r="AI596" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ596" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
+      <c r="AI596" t="inlineStr"/>
+      <c r="AJ596" t="inlineStr"/>
       <c r="AK596" t="inlineStr">
         <is>
           <t>IOCL WILLINGTON</t>
@@ -74753,16 +74737,8 @@
       <c r="AF597" t="inlineStr"/>
       <c r="AG597" t="inlineStr"/>
       <c r="AH597" t="inlineStr"/>
-      <c r="AI597" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ597" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
+      <c r="AI597" t="inlineStr"/>
+      <c r="AJ597" t="inlineStr"/>
       <c r="AK597" t="inlineStr">
         <is>
           <t>IOCL WILLINGTON</t>
@@ -74888,16 +74864,8 @@
       <c r="AF598" t="inlineStr"/>
       <c r="AG598" t="inlineStr"/>
       <c r="AH598" t="inlineStr"/>
-      <c r="AI598" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ598" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
+      <c r="AI598" t="inlineStr"/>
+      <c r="AJ598" t="inlineStr"/>
       <c r="AK598" t="inlineStr">
         <is>
           <t>IOCL WILLINGTON</t>
@@ -75150,16 +75118,8 @@
       <c r="AF600" t="inlineStr"/>
       <c r="AG600" t="inlineStr"/>
       <c r="AH600" t="inlineStr"/>
-      <c r="AI600" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ600" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
+      <c r="AI600" t="inlineStr"/>
+      <c r="AJ600" t="inlineStr"/>
       <c r="AK600" t="inlineStr">
         <is>
           <t>IOCL WILLINGTON</t>
@@ -75285,16 +75245,8 @@
       <c r="AF601" t="inlineStr"/>
       <c r="AG601" t="inlineStr"/>
       <c r="AH601" t="inlineStr"/>
-      <c r="AI601" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ601" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
+      <c r="AI601" t="inlineStr"/>
+      <c r="AJ601" t="inlineStr"/>
       <c r="AK601" t="inlineStr">
         <is>
           <t>IOCL WILLINGTON</t>
@@ -75420,16 +75372,8 @@
       <c r="AF602" t="inlineStr"/>
       <c r="AG602" t="inlineStr"/>
       <c r="AH602" t="inlineStr"/>
-      <c r="AI602" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ602" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
+      <c r="AI602" t="inlineStr"/>
+      <c r="AJ602" t="inlineStr"/>
       <c r="AK602" t="inlineStr">
         <is>
           <t>IOCL WILLINGTON</t>
@@ -75555,16 +75499,8 @@
       <c r="AF603" t="inlineStr"/>
       <c r="AG603" t="inlineStr"/>
       <c r="AH603" t="inlineStr"/>
-      <c r="AI603" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ603" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
+      <c r="AI603" t="inlineStr"/>
+      <c r="AJ603" t="inlineStr"/>
       <c r="AK603" t="inlineStr">
         <is>
           <t>IOCL WILLINGTON</t>
@@ -75690,16 +75626,8 @@
       <c r="AF604" t="inlineStr"/>
       <c r="AG604" t="inlineStr"/>
       <c r="AH604" t="inlineStr"/>
-      <c r="AI604" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ604" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
+      <c r="AI604" t="inlineStr"/>
+      <c r="AJ604" t="inlineStr"/>
       <c r="AK604" t="inlineStr">
         <is>
           <t>IOCL WILLINGTON</t>
@@ -75825,16 +75753,8 @@
       <c r="AF605" t="inlineStr"/>
       <c r="AG605" t="inlineStr"/>
       <c r="AH605" t="inlineStr"/>
-      <c r="AI605" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ605" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
+      <c r="AI605" t="inlineStr"/>
+      <c r="AJ605" t="inlineStr"/>
       <c r="AK605" t="inlineStr">
         <is>
           <t>IOCL WILLINGTON</t>
@@ -77562,16 +77482,8 @@
       <c r="AF618" t="inlineStr"/>
       <c r="AG618" t="inlineStr"/>
       <c r="AH618" t="inlineStr"/>
-      <c r="AI618" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ618" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
+      <c r="AI618" t="inlineStr"/>
+      <c r="AJ618" t="inlineStr"/>
       <c r="AK618" t="inlineStr">
         <is>
           <t>HO</t>
@@ -77699,16 +77611,8 @@
       <c r="AF619" t="inlineStr"/>
       <c r="AG619" t="inlineStr"/>
       <c r="AH619" t="inlineStr"/>
-      <c r="AI619" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ619" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
+      <c r="AI619" t="inlineStr"/>
+      <c r="AJ619" t="inlineStr"/>
       <c r="AK619" t="inlineStr">
         <is>
           <t>HO</t>
@@ -77834,16 +77738,8 @@
       <c r="AF620" t="inlineStr"/>
       <c r="AG620" t="inlineStr"/>
       <c r="AH620" t="inlineStr"/>
-      <c r="AI620" t="inlineStr">
-        <is>
-          <t>PAID</t>
-        </is>
-      </c>
-      <c r="AJ620" t="inlineStr">
-        <is>
-          <t>PAID</t>
-        </is>
-      </c>
+      <c r="AI620" t="inlineStr"/>
+      <c r="AJ620" t="inlineStr"/>
       <c r="AK620" t="inlineStr">
         <is>
           <t>BELLARI</t>
@@ -77969,16 +77865,8 @@
       <c r="AF621" t="inlineStr"/>
       <c r="AG621" t="inlineStr"/>
       <c r="AH621" t="inlineStr"/>
-      <c r="AI621" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ621" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
+      <c r="AI621" t="inlineStr"/>
+      <c r="AJ621" t="inlineStr"/>
       <c r="AK621" t="inlineStr">
         <is>
           <t>ONGC ELECTRICAL</t>
@@ -78239,16 +78127,8 @@
       <c r="AF623" t="inlineStr"/>
       <c r="AG623" t="inlineStr"/>
       <c r="AH623" t="inlineStr"/>
-      <c r="AI623" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ623" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
+      <c r="AI623" t="inlineStr"/>
+      <c r="AJ623" t="inlineStr"/>
       <c r="AK623" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -78505,16 +78385,8 @@
       <c r="AF625" t="inlineStr"/>
       <c r="AG625" t="inlineStr"/>
       <c r="AH625" t="inlineStr"/>
-      <c r="AI625" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ625" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
+      <c r="AI625" t="inlineStr"/>
+      <c r="AJ625" t="inlineStr"/>
       <c r="AK625" t="inlineStr">
         <is>
           <t>HO</t>

--- a/PENDING_APPROVAL_SHEET.xlsx
+++ b/PENDING_APPROVAL_SHEET.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO16"/>
+  <dimension ref="A1:AO69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>61518</v>
+        <v>20000</v>
       </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
@@ -756,8 +756,16 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr"/>
@@ -879,8 +887,16 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
       <c r="AK3" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -1006,8 +1022,16 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK4" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -1133,8 +1157,16 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
       <c r="AK5" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -1260,8 +1292,16 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK6" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -1387,8 +1427,16 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK7" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -1514,8 +1562,16 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK8" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -1641,8 +1697,16 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK9" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -1768,8 +1832,16 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK10" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -1895,8 +1967,16 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK11" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -2022,8 +2102,16 @@
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
-      <c r="AJ12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK12" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -2111,8 +2199,16 @@
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK13" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -2238,8 +2334,16 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK14" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -2365,8 +2469,16 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr"/>
-      <c r="AJ15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK15" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -2492,8 +2604,16 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr"/>
-      <c r="AJ16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK16" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -2504,6 +2624,6891 @@
       <c r="AN16" t="inlineStr"/>
       <c r="AO16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>WGG 02</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D17" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>f043477f-15db-42a4-b4a5-fa70405bb5ee</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>79930</v>
+      </c>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Pep consultancy pendiing payment RPA_ID : 072d33e629</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Cochin</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Payments@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>WGG 02</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D18" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>3750134c-0739-48e8-b0a1-03736d28d098</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>178620</v>
+      </c>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Transfer to cash ledger against invoice RPA_ID : c5a8562d0f</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Cochin</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Payments@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>WGG 02</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D19" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>c8fdd1ae-97e6-4c83-a1c4-19a5ccd0b80d</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>821260</v>
+      </c>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Transfer to cash ledger against invoice RPA_ID : 3f8a60c026</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Goa</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Payments@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>WGG 02</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D20" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>8d3d5259-7546-44c1-8eb6-f8b0b08dc8aa</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>159530</v>
+      </c>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Transfer to cash ledger against invoice RPA_ID : 3c4458a61c</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>Payments@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>WGE 233</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D21" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Muhammed anWer</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>45494666-6f8e-4033-ad54-b8c95e54033b</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>ACC-99980113126044</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>FDRL0001413</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>16857</v>
+      </c>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>FEB SALARY RPA_ID : bbd9e04d3e</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>WGE 220</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D22" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>ANDRIYA THOMAS</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>356fe78c-c5b5-4dec-a7e8-e94c59b2b477</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>ACC-0706101053789</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>CNRB0000706</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>14768</v>
+      </c>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>FEB SALARY RPA_ID : 000c912a9f</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>WGE 321</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D23" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VISHNU PRIYA </t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>21a272cc-52fe-42f0-a01d-8e32b5eaf10b</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>ACC-32818330206</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>SBIN0071100</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>27607</v>
+      </c>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>FULL &amp; FINAL SETTLEMENT/ FEB &amp; MARCH RPA_ID : 2894a65de5</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>WGE 202</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D24" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>DCR</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Janhavi Rajendra Patil</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>d32651c9-fec2-4707-bf79-4ed37e5dde9e</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>ACC-40356050651</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>SBIN0009832</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>25300</v>
+      </c>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>ROOM RENT FEB 10TH TO MAR 10TH RPA_ID : 7ce35e0234</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>MUMBAI</t>
+        </is>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>WGE 318</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D25" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>KURIAKOSE GEORGE</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>55e03390-452e-473b-be03-4127a50361e2</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>ACC-38067112026</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>SBIN0071006</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>9643</v>
+      </c>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Salary February 2026 RPA_ID : 8a271d717e</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>WGE 344</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D26" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAUTHAM KRISHNAN C G </t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>485b1085-bfe4-44b9-94f3-25bed0a2d2b4</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>ACC-20289798248</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>SBIN0010597</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>15000</v>
+      </c>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Salary February 2026 RPA_ID : 9e839ba707</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>WGE 346</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D27" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>DINESH KUMAR SUKUMARAN</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>d35846a6-6900-47db-9fcd-ef04e4e11adb</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>ACC-41138649192</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>SBIN0070433</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>11000</v>
+      </c>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Salary February 2026 RPA_ID : 34ae97798b</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>WGE 356</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D28" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>DINESH KUMAR ( QC)</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>c34d35d8-3671-4577-b688-9da8ac7c7f96</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>ACC-11260100728119</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>FDRL0001126</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>11000</v>
+      </c>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Salary February 2026 RPA_ID : 294e3e8a9f</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>WGE 206</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D29" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>RAHUL</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>ea4e334a-b924-4f42-b39a-73c63a1961bb</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>ACC-0754104000129480</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>IBKL0000754</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>1785</v>
+      </c>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Salary February 2026 RPA_ID : b3a8713771</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>WGE 195</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D30" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>SAYAN BATTACHARYA</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>f2510db1-aa4f-46e9-aa0b-0a9ee509cd93</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>ACC-14810110034736</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>UCBA0001481</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>20000</v>
+      </c>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Salary February 2026 RPA_ID : 877f741d94</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>KOLKATTA OFFICE</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>WGE 189</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D31" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>MUNNA GUPTA</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>04b49688-fc74-432e-b4c3-a48e109af4be</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>ACC-3421187013</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>CBIN0282509</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>23980</v>
+      </c>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Salary February 2026 RPA_ID : ed875b460e</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>GRSC KOLKATTA</t>
+        </is>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr"/>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>WGE 140</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D32" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>DCR</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Shamzusaman</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>430739ec-e17f-4edd-84da-e71535d8c6ba</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>ACC-37737516718</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>SBIN0003881</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>21035</v>
+      </c>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Salary February 2026 RPA_ID : 9343a23beb</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>GRSC KOLKATTA</t>
+        </is>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>WGE 296</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D33" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>ASWINRAJ  K</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>43b06e55-1c13-4c19-8daa-ba2ade1641dc</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>ACC-33106528754</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>SBIN0011925</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>5357</v>
+      </c>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Salary February 2026 RPA_ID : 0b001a09fa</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>GOA HUL</t>
+        </is>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>WGE 113</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D34" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>DCR</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>RIZWANUDHEEN</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>b6744435-8b6a-4624-8d18-bcb0cb8abfa4</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>ACC-67285944854</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>SBIN0070191</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>39842</v>
+      </c>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Salary February 2026 RPA_ID : 7b7869bfce</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>ST3 GOA</t>
+        </is>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="inlineStr"/>
+      <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>WGE 113</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D35" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>DCR</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>RIZWANUDHEEN</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>844217cc-6e00-4d05-b09d-d2a83f2e81f3</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>ACC-67285944854</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>SBIN0070191</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V35" t="n">
+        <v>10000</v>
+      </c>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>February 2026 Incentive RPA_ID : 92b9e43013</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>ST3 GOA</t>
+        </is>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL35" t="inlineStr"/>
+      <c r="AM35" t="inlineStr"/>
+      <c r="AN35" t="inlineStr"/>
+      <c r="AO35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>WGE 296</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D36" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>ASWINRAJ  K</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2dff1fc7-3a84-42f9-9ddf-3553cdb1fe73</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>ACC-33106528754</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>SBIN0011925</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V36" t="n">
+        <v>16964</v>
+      </c>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Salary February 2026 RPA_ID : 0e86310284</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>ST3 GOA</t>
+        </is>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL36" t="inlineStr"/>
+      <c r="AM36" t="inlineStr"/>
+      <c r="AN36" t="inlineStr"/>
+      <c r="AO36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>WGE 370</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D37" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>SOHEL ALI KHAN ( RUMJAN)</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>445a7615-a74d-4389-955e-f2de5db4f492</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>ACC-347701000009731</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>IOBA0003477</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V37" t="n">
+        <v>15946</v>
+      </c>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Salary February 2026 RPA_ID : a74d92d0c1</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>ST3 GOA</t>
+        </is>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="inlineStr"/>
+      <c r="AN37" t="inlineStr"/>
+      <c r="AO37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>WGE 369</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D38" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>JAVED AKTAR ( RUMJAN)</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>c02052df-5950-44b9-a233-f1728a48981a</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>ACC-00428100041338</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>BARB0BAGNAN</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V38" t="n">
+        <v>15946</v>
+      </c>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Salary February 2026 RPA_ID : 92535a0b70</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>ST3 GOA</t>
+        </is>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL38" t="inlineStr"/>
+      <c r="AM38" t="inlineStr"/>
+      <c r="AN38" t="inlineStr"/>
+      <c r="AO38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>WGE 420</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D39" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Riyajul Ali (RUMJAN)</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>32c1b89f-75a0-4c49-96bf-09b554131157</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>ACC-065110058620</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>IPOS0000001</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V39" t="n">
+        <v>15091</v>
+      </c>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Salary February 2026 RPA_ID : 0a9e85834b</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>ST3 GOA</t>
+        </is>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL39" t="inlineStr"/>
+      <c r="AM39" t="inlineStr"/>
+      <c r="AN39" t="inlineStr"/>
+      <c r="AO39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>WGE 422</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D40" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>SAHIL ALI KHAN (RUMJAN)</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>c27e26aa-d445-4eeb-b7d8-e304b22812f7</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>ACC-003521713823919</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>JIOP0000001</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V40" t="n">
+        <v>15784</v>
+      </c>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Salary February 2026 RPA_ID : 5f58afd6af</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>ST3 GOA</t>
+        </is>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL40" t="inlineStr"/>
+      <c r="AM40" t="inlineStr"/>
+      <c r="AN40" t="inlineStr"/>
+      <c r="AO40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>WGE 423</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D41" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>SAHIL SHA (RUMJAN)</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>eab4e5b2-026f-479e-a48e-ca76ff65f016</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>ACC-0692201700069932</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>PUNB0069220</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V41" t="n">
+        <v>17171</v>
+      </c>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Salary February 2026 RPA_ID : 6cf3801bc1</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>ST3 GOA</t>
+        </is>
+      </c>
+      <c r="Z41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL41" t="inlineStr"/>
+      <c r="AM41" t="inlineStr"/>
+      <c r="AN41" t="inlineStr"/>
+      <c r="AO41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>WGE 419</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D42" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Mosihur Rahaman Khan (RUMJAN)</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2b68c347-6b8a-4a70-a83c-85416be03460</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>ACC-003521713803568</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>JIOP0000001</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V42" t="n">
+        <v>14398</v>
+      </c>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Salary February 2026 RPA_ID : 21ee55faaa</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>ST3 GOA</t>
+        </is>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL42" t="inlineStr"/>
+      <c r="AM42" t="inlineStr"/>
+      <c r="AN42" t="inlineStr"/>
+      <c r="AO42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>WGE 421</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D43" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Jakir Khan (RUMJAN)</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>ffabbc9e-4a67-4366-a79e-0ac8cc87e68d</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>ACC-38416480530</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>SBIN0011387</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V43" t="n">
+        <v>13173</v>
+      </c>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Salary February 2026 RPA_ID : d1fc1885ae</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>ST3 GOA</t>
+        </is>
+      </c>
+      <c r="Z43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL43" t="inlineStr"/>
+      <c r="AM43" t="inlineStr"/>
+      <c r="AN43" t="inlineStr"/>
+      <c r="AO43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>WGE 435</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>b5d1f177-ba73-498c-b204-ebd8c990b681</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V44" t="n">
+        <v>15253</v>
+      </c>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Salary February 2026 RPA_ID : ab1643ca9c</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>ST3 GOA</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL44" t="inlineStr"/>
+      <c r="AM44" t="inlineStr"/>
+      <c r="AN44" t="inlineStr"/>
+      <c r="AO44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>WGE 418</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D45" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>SK Imran (RUMJAN)</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>b3a4ea3b-4885-4d88-9eca-7b6e49639a77</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>ACC-7384263440</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>AIRP0000001</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V45" t="n">
+        <v>17171</v>
+      </c>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Salary February 2026 RPA_ID : 8d5cca1ae1</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>ST3 GOA</t>
+        </is>
+      </c>
+      <c r="Z45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr"/>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL45" t="inlineStr"/>
+      <c r="AM45" t="inlineStr"/>
+      <c r="AN45" t="inlineStr"/>
+      <c r="AO45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>WGE 417</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D46" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>SK RAIHAN ALI ( RUMJAN)</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>8481aac0-bca2-4b10-bc92-30381aa09801</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>ACC-003521714278414</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>JIOP0000001</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V46" t="n">
+        <v>14559</v>
+      </c>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Salary February 2026 RPA_ID : 4b7266c788</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>ST3 GOA</t>
+        </is>
+      </c>
+      <c r="Z46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL46" t="inlineStr"/>
+      <c r="AM46" t="inlineStr"/>
+      <c r="AN46" t="inlineStr"/>
+      <c r="AO46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>WGE 196</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D47" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>NILESH ANANT DURBHATKAR</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>bf0b20e0-b711-47b9-9c70-2d613857a3e5</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>ACC-04930100017981</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>BARB0VASCOD</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V47" t="n">
+        <v>16000</v>
+      </c>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>The pending amount to be paid to Nilesh is ₹16,000 for August and September, as ₹8,000 per month is still unpaid. ( RUMJAN ROOM) RPA_ID : 46073aa5fa</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>ST3 GOA</t>
+        </is>
+      </c>
+      <c r="Z47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL47" t="inlineStr"/>
+      <c r="AM47" t="inlineStr"/>
+      <c r="AN47" t="inlineStr"/>
+      <c r="AO47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>WGE 342</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D48" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>PAUL OFFSHORE PVT</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2ddb007c-73f9-4e63-b5b8-a0490a6dc345</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>ACC-7806823928</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V48" t="n">
+        <v>267495</v>
+      </c>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>ONGC GOA JAN BILL LABOUR CHARGES - WELDER / FITTER/RIGGER AND FOOD ALLOWANCE RPA_ID : ba32fc0bde</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>ONGC GOA</t>
+        </is>
+      </c>
+      <c r="Z48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr"/>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr"/>
+      <c r="AM48" t="inlineStr"/>
+      <c r="AN48" t="inlineStr"/>
+      <c r="AO48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>WGE 192</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D49" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Hafis Bin Haris</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>991750ff-1321-428c-bab2-536fd8265c46</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>ACC-99980105201458</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>FDRL0001143</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V49" t="n">
+        <v>17020</v>
+      </c>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Salary December Rs.7423/- January 9597/- Full and Final Settlement RPA_ID : 960946da46</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>GOA HUL</t>
+        </is>
+      </c>
+      <c r="Z49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr"/>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL49" t="inlineStr"/>
+      <c r="AM49" t="inlineStr"/>
+      <c r="AN49" t="inlineStr"/>
+      <c r="AO49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>WGE 115</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D50" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Muhammad Shamil C</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>f0313af6-0669-4099-8a1a-cac212d17f68</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>ACC-11220100177873</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>FDRL0001122</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V50" t="n">
+        <v>9257</v>
+      </c>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Salary December Full and Final Settlement RPA_ID : fe57df9014</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>ST3 GOA</t>
+        </is>
+      </c>
+      <c r="Z50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr"/>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL50" t="inlineStr"/>
+      <c r="AM50" t="inlineStr"/>
+      <c r="AN50" t="inlineStr"/>
+      <c r="AO50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>WGE 112</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D51" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>ABHISHEK PEDNEKAR</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>a14ece95-49d1-46f1-9924-124e61d30cf9</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>ACC-06050100016920</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>BARB0MAPUCA</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V51" t="n">
+        <v>8936</v>
+      </c>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Salary January Full and Final Settlement RPA_ID : cfc23fd042</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>ST3 GOA</t>
+        </is>
+      </c>
+      <c r="Z51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr"/>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL51" t="inlineStr"/>
+      <c r="AM51" t="inlineStr"/>
+      <c r="AN51" t="inlineStr"/>
+      <c r="AO51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>WGE 104</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D52" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>BRAHMADATHAN</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>939d98b8-2e17-433c-9ed6-25a8d0292965</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>ACC-232001000010098</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>IOBA0002320</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V52" t="n">
+        <v>24379</v>
+      </c>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Salary November Full and Final settlement RPA_ID : 1f4599ae67</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>GOA HUL</t>
+        </is>
+      </c>
+      <c r="Z52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL52" t="inlineStr"/>
+      <c r="AM52" t="inlineStr"/>
+      <c r="AN52" t="inlineStr"/>
+      <c r="AO52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>WGE 428</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D53" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>c2fc57a9-2a27-422b-be5f-c65d4b6d7562</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V53" t="n">
+        <v>3000</v>
+      </c>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Aviator Repair RPA_ID : 9fb5aca796</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="Z53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="inlineStr"/>
+      <c r="AH53" t="inlineStr"/>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="AL53" t="inlineStr"/>
+      <c r="AM53" t="inlineStr"/>
+      <c r="AN53" t="inlineStr"/>
+      <c r="AO53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>WGE 428</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D54" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>NAIJAL driver</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>8f4e1df5-48a0-4db8-8960-c7ae96ff8c56</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>ACC-13962100139241</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>FDRL0001396</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V54" t="n">
+        <v>3000</v>
+      </c>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Aviator Repair RPA_ID : 416c24fb76</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="Z54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="inlineStr"/>
+      <c r="AH54" t="inlineStr"/>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="AL54" t="inlineStr"/>
+      <c r="AM54" t="inlineStr"/>
+      <c r="AN54" t="inlineStr"/>
+      <c r="AO54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>WGE 170</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D55" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>VEDANT</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>0df8789f-56a2-4e84-9f38-cfdf0933a273</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>ACC-2047172054</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>KKBK0001429</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V55" t="n">
+        <v>6451</v>
+      </c>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Material Shiftng 8 Days worked (December 5 days , January 3 Days) RPA_ID : 3088bde624</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>MDL</t>
+        </is>
+      </c>
+      <c r="Z55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="inlineStr"/>
+      <c r="AH55" t="inlineStr"/>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr"/>
+      <c r="AL55" t="inlineStr"/>
+      <c r="AM55" t="inlineStr"/>
+      <c r="AN55" t="inlineStr"/>
+      <c r="AO55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>WGE 195</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D56" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>SAYAN BATTACHARYA</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>17b498cb-7154-4787-be90-8be9a175b853</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>ACC-14810110034736</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>UCBA0001481</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V56" t="n">
+        <v>2412</v>
+      </c>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Office Expense Sheet attached RPA_ID : 08beb5ed2d</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>KOLKATTA</t>
+        </is>
+      </c>
+      <c r="Z56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="inlineStr"/>
+      <c r="AH56" t="inlineStr"/>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr"/>
+      <c r="AL56" t="inlineStr"/>
+      <c r="AM56" t="inlineStr"/>
+      <c r="AN56" t="inlineStr"/>
+      <c r="AO56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>WGE 197</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D57" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>NIZER RODRIGOUS</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>f40fed44-6737-4456-b3fe-f308180c7a6d</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>ACC-04930100017817</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>BARB0VASCOD</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V57" t="n">
+        <v>15000</v>
+      </c>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Room Rent  (Feb 12th to March 12th) RPA_ID : 48aa76f649</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>ST3 GOA</t>
+        </is>
+      </c>
+      <c r="Z57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="inlineStr"/>
+      <c r="AH57" t="inlineStr"/>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL57" t="inlineStr"/>
+      <c r="AM57" t="inlineStr"/>
+      <c r="AN57" t="inlineStr"/>
+      <c r="AO57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>WGE 203</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D58" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>DCR</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>MADUMITHA</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>47654d8c-27c7-4c79-9e19-bb4b72ce5774</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>ACC-10629442465</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>SBIN0002016</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V58" t="n">
+        <v>15000</v>
+      </c>
+      <c r="W58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Room Rent Kolkatta Office RPA_ID : 68d283734b</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>KOLKATTA</t>
+        </is>
+      </c>
+      <c r="Z58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="inlineStr"/>
+      <c r="AH58" t="inlineStr"/>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr"/>
+      <c r="AL58" t="inlineStr"/>
+      <c r="AM58" t="inlineStr"/>
+      <c r="AN58" t="inlineStr"/>
+      <c r="AO58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>WGE 56</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D59" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Akhil</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>9e779c26-63f3-4f56-b8d0-1a6b77ce40d8</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>ACC-852110110008274</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>BKID0008521</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V59" t="n">
+        <v>4800</v>
+      </c>
+      <c r="W59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>gardner - 05/03/2026 &amp; 07/03/2026 &amp; 09/03/2026 &amp; 10/03/2026 ( 1200 per day) RPA_ID : d329820ad4</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>IOCL FEROKE</t>
+        </is>
+      </c>
+      <c r="Z59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="inlineStr"/>
+      <c r="AH59" t="inlineStr"/>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>IOCL FEROKE</t>
+        </is>
+      </c>
+      <c r="AL59" t="inlineStr"/>
+      <c r="AM59" t="inlineStr"/>
+      <c r="AN59" t="inlineStr"/>
+      <c r="AO59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>WGE 197</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D60" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>NIZER RODRIGOUS</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>c7e3cccb-f5f5-49aa-9d16-7ca5ec178fa5</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>ACC-04930100017817</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>BARB0VASCOD</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V60" t="n">
+        <v>1100</v>
+      </c>
+      <c r="W60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Electricity Bill,Water Bill RPA_ID : 8996aebb15</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>GOA ST3</t>
+        </is>
+      </c>
+      <c r="Z60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="inlineStr"/>
+      <c r="AH60" t="inlineStr"/>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL60" t="inlineStr"/>
+      <c r="AM60" t="inlineStr"/>
+      <c r="AN60" t="inlineStr"/>
+      <c r="AO60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>WGG 02</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D61" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>4cc1d268-5e0c-4145-811b-b4bbdd325c23</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V61" t="n">
+        <v>15323</v>
+      </c>
+      <c r="W61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>GOA RPA_ID : c7819cf16a</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="Z61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
+      <c r="AH61" t="inlineStr"/>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL61" t="inlineStr"/>
+      <c r="AM61" t="inlineStr"/>
+      <c r="AN61" t="inlineStr"/>
+      <c r="AO61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>WGG 02</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D62" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>481b8090-a184-4fb1-9de9-ea1d34a898d8</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V62" t="n">
+        <v>1174</v>
+      </c>
+      <c r="W62" t="inlineStr"/>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Kolkatta RPA_ID : aee9ca63f1</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>Kolkatta</t>
+        </is>
+      </c>
+      <c r="Z62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="inlineStr"/>
+      <c r="AH62" t="inlineStr"/>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr"/>
+      <c r="AL62" t="inlineStr"/>
+      <c r="AM62" t="inlineStr"/>
+      <c r="AN62" t="inlineStr"/>
+      <c r="AO62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>WGG 02</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D63" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>217eddeb-f783-4029-8049-c1aa73344b6c</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V63" t="n">
+        <v>4103</v>
+      </c>
+      <c r="W63" t="inlineStr"/>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Willington RPA_ID : e982f19173</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>Willington</t>
+        </is>
+      </c>
+      <c r="Z63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="inlineStr"/>
+      <c r="AH63" t="inlineStr"/>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr"/>
+      <c r="AL63" t="inlineStr"/>
+      <c r="AM63" t="inlineStr"/>
+      <c r="AN63" t="inlineStr"/>
+      <c r="AO63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>WGG 02</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D64" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>c3603b1c-5cd6-478a-9af4-208f8eb7d205</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V64" t="n">
+        <v>6625</v>
+      </c>
+      <c r="W64" t="inlineStr"/>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>State office RPA_ID : 8fc71eaedc</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>KOCHI</t>
+        </is>
+      </c>
+      <c r="Z64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="inlineStr"/>
+      <c r="AH64" t="inlineStr"/>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr"/>
+      <c r="AL64" t="inlineStr"/>
+      <c r="AM64" t="inlineStr"/>
+      <c r="AN64" t="inlineStr"/>
+      <c r="AO64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>WGG 02</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D65" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>eec56ea3-d024-4c4b-bba9-353d80b61c85</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V65" t="n">
+        <v>25000</v>
+      </c>
+      <c r="W65" t="inlineStr"/>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Final Settlement Process RPA_ID : 69a33351c0</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>Kolkatta</t>
+        </is>
+      </c>
+      <c r="Z65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="inlineStr"/>
+      <c r="AH65" t="inlineStr"/>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr"/>
+      <c r="AL65" t="inlineStr"/>
+      <c r="AM65" t="inlineStr"/>
+      <c r="AN65" t="inlineStr"/>
+      <c r="AO65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>WGE 429</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D66" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>af11a212-43a6-4116-a861-616447f91d91</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V66" t="n">
+        <v>56</v>
+      </c>
+      <c r="W66" t="inlineStr"/>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>MILK RPA_ID : d8e5f75bfc</t>
+        </is>
+      </c>
+      <c r="Y66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>officeadmin@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="inlineStr"/>
+      <c r="AH66" t="inlineStr"/>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr"/>
+      <c r="AL66" t="inlineStr"/>
+      <c r="AM66" t="inlineStr"/>
+      <c r="AN66" t="inlineStr"/>
+      <c r="AO66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>WGE 429</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D67" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>19dddb8c-1ebe-4b39-ae2c-869522d784ce</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V67" t="n">
+        <v>326</v>
+      </c>
+      <c r="W67" t="inlineStr"/>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>LUNCH MD and Director RPA_ID : 939748ddda</t>
+        </is>
+      </c>
+      <c r="Y67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>officeadmin@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="inlineStr"/>
+      <c r="AH67" t="inlineStr"/>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr"/>
+      <c r="AL67" t="inlineStr"/>
+      <c r="AM67" t="inlineStr"/>
+      <c r="AN67" t="inlineStr"/>
+      <c r="AO67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>WGE 429</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D68" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>ac6c3530-8d38-4091-beae-8070464c8a30</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V68" t="n">
+        <v>468</v>
+      </c>
+      <c r="W68" t="inlineStr"/>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>blink it sugar, garbage bag and bru RPA_ID : b079ef54a6</t>
+        </is>
+      </c>
+      <c r="Y68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>officeadmin@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="inlineStr"/>
+      <c r="AH68" t="inlineStr"/>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr"/>
+      <c r="AL68" t="inlineStr"/>
+      <c r="AM68" t="inlineStr"/>
+      <c r="AN68" t="inlineStr"/>
+      <c r="AO68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>WGE 429</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>46329</v>
+      </c>
+      <c r="D69" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>71c23e37-a559-45a6-b8b0-38d512bea0e6</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V69" t="n">
+        <v>500</v>
+      </c>
+      <c r="W69" t="inlineStr"/>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Payment of stamp paper RPA_ID : 1bf17b4fb3</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>GAS BU SCHEDULE OF RATES MAHARASTRA BPCL</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>PAYMENT OF STAMP PAPER</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>executive.westerntender@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="inlineStr"/>
+      <c r="AH69" t="inlineStr"/>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr"/>
+      <c r="AL69" t="inlineStr"/>
+      <c r="AM69" t="inlineStr"/>
+      <c r="AN69" t="inlineStr"/>
+      <c r="AO69" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PENDING_APPROVAL_SHEET.xlsx
+++ b/PENDING_APPROVAL_SHEET.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO41"/>
+  <dimension ref="A1:AO33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -638,7 +638,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WGG 02</t>
+          <t>WGE 189</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>13-03-2026</t>
+          <t>17-03-2026</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -682,14 +682,26 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>MUNNA GUPTA</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>10b67a44-9010-4242-9437-2018cc75b52c</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>b5ea6847-295f-4515-a161-540fef2ca840</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>ACC-3421187013</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>CBIN0282509</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
@@ -702,16 +714,18 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>23980</v>
       </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0 RPA_ID : 8d331137f4</t>
-        </is>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
+          <t>Salary February 2026 RPA_ID : 09d7636913</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>GRSC KOLKATTA</t>
+        </is>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -733,19 +747,19 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>23980</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr"/>
@@ -757,7 +771,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WGE 01</t>
+          <t>WGG 02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -767,7 +781,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>17-03-2026</t>
+          <t>18-03-2026</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -801,26 +815,14 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>BENNY P A</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>cdce3678-6b83-43dc-a882-1d086b92e0a8</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>ACC-43152200012062</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>CNRB0014315</t>
-        </is>
-      </c>
+          <t>49eb6f14-9179-4e70-8f07-3889e22444d0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
@@ -833,27 +835,27 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>331732</v>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Payment of BG RPA_ID : e561583009</t>
+          <t>Transfer to cash ledger against invoice RPA_ID : 07b95eac79</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Development of New “A” site RO at Uthimoodu Junction to Mandiram Junction on SH 8 under Pathanamthitta RSA Re.Sy.No 559/2 of Ranni village, Ranni Taluk, Pathanamthitta District, Trivandrum Divisional Office under Kerala State office</t>
+          <t>Cochin</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>PAYMENT OF BG</t>
+          <t>PAYMENT</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>executive.westerntender@gmail.com</t>
+          <t>Payments@westernidc.com</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -875,12 +877,12 @@
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr"/>
@@ -892,7 +894,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WGE01</t>
+          <t>WGG 02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -902,7 +904,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>17-03-2026</t>
+          <t>18-03-2026</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -936,14 +938,10 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>ONLINE PAYMENTS</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>41905c38-a93b-40e0-9536-8d57171e4bd2</t>
+          <t>18ffaaff-c404-43f5-99d8-bf458d3a87d3</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -960,27 +958,27 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>79930</v>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Payment of BG RPA_ID : 6a807a9992</t>
+          <t>Pep consultancy pendiing payment RPA_ID : 597c1e041c</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Development of New “A” site RO at Uthimoodu Junction to Mandiram Junction on SH 8 under Pathanamthitta RSA Re.Sy.No 559/2 of Ranni village, Ranni Taluk, Pathanamthitta District, Trivandrum Divisional Office under Kerala State office</t>
+          <t>Cochin</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>PAYMENT OF BG</t>
+          <t>PAYMENT</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>executive.westerntender@gmail.com</t>
+          <t>midhuncraju12@gmail.com</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1029,7 +1027,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>17-03-2026</t>
+          <t>18-03-2026</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1066,7 +1064,7 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>171f98cc-9208-4c8c-babe-1f1e57add52b</t>
+          <t>d8f4c361-b186-48fe-b4d1-187cbbe0ae78</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -1083,12 +1081,12 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>400000</v>
+        <v>745000</v>
       </c>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Sakath amount RPA_ID : 3520588a23</t>
+          <t>Transfer to cash ledger against invoice RPA_ID : 9b4ce2fe88</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1103,7 +1101,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Payments@westernidc.com</t>
+          <t>midhuncraju12@gmail.com</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1125,12 +1123,12 @@
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr"/>
@@ -1152,7 +1150,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>17-03-2026</t>
+          <t>18-03-2026</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1189,7 +1187,7 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>58c36224-c95d-4bc0-923d-dc8ae1fe81ae</t>
+          <t>57e540d8-e92d-4a89-bb7d-7e68e087d58c</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -1206,17 +1204,17 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>47791</v>
+        <v>1175000</v>
       </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Transgfer to cashledger against receipt RPA_ID : 6d08c979e6</t>
+          <t>Transfer to cash ledger against invoice RPA_ID : 6dedbb2fa9</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Cochin</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1226,7 +1224,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Payments@westernidc.com</t>
+          <t>midhuncraju12@gmail.com</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1248,15 +1246,19 @@
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr"/>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
@@ -1265,7 +1267,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WGE 233</t>
+          <t>WGG 02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1275,7 +1277,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>17-03-2026</t>
+          <t>18-03-2026</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1309,26 +1311,14 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Muhammed anWer</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>f3f10817-8062-45fe-8496-c1a49772ee89</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>ACC-99980113126044</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>FDRL0001413</t>
-        </is>
-      </c>
+          <t>19e8af86-1a27-4d7e-89a7-34f19e28eeb3</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
@@ -1341,25 +1331,27 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>16857</v>
+        <v>15000</v>
       </c>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
-          <t>FEB SALARY RPA_ID : 949ac032ed</t>
+          <t>Transfer to cash ledger against invoice RPA_ID : a3ead5556a</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>HO</t>
-        </is>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>hrm@westernidc.com</t>
+          <t>midhuncraju12@gmail.com</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1381,19 +1373,15 @@
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>HO</t>
-        </is>
-      </c>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr"/>
@@ -1402,7 +1390,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WGE 202</t>
+          <t>WGG 02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1412,7 +1400,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>17-03-2026</t>
+          <t>18-03-2026</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1428,7 +1416,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>DCR</t>
+          <t>NEFT</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1446,26 +1434,14 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Janhavi Rajendra Patil</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>744b8a67-0392-4a50-8db4-0af5779b8e5a</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>ACC-40356050651</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>SBIN0009832</t>
-        </is>
-      </c>
+          <t>411bcf6e-9332-4070-bf51-f1835b3e221f</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
@@ -1478,25 +1454,27 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>25300</v>
+        <v>509</v>
       </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
-          <t>ROOM RENT FEB 10TH TO MAR 10TH RPA_ID : 33c8b92f21</t>
+          <t>Expense Reimbursement (Hishem sir Police Verification Payment made by Rose Ma'am) RPA_ID : 6f9048e91a</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>MUMBAI</t>
-        </is>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
+          <t>Cochin</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>hrm@westernidc.com</t>
+          <t>midhuncraju12@gmail.com</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1518,12 +1496,12 @@
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr"/>
@@ -1535,7 +1513,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WGE 318</t>
+          <t>WGG 02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1545,7 +1523,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>17-03-2026</t>
+          <t>18-03-2026</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1579,26 +1557,14 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>KURIAKOSE GEORGE</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>92f3eac1-f5f6-487c-987d-ce87e4c91af0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>ACC-38067112026</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>SBIN0071006</t>
-        </is>
-      </c>
+          <t>c924ecab-6c14-4929-9824-b363e55222e0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
@@ -1611,25 +1577,27 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>9643</v>
+        <v>7021</v>
       </c>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Salary February 2026 HALF SALARY PAID BALANCE TO BE PAID RPA_ID : c2e9934b6f</t>
+          <t>Trident Engineers Yard Rent (1 Phase electricity : Rs. 7021/- Due 20/03/2026) RPA_ID : 25fc2190d5</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>BELLARI</t>
-        </is>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
+          <t>IPSHEM</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>hrm@westernidc.com</t>
+          <t>midhuncraju12@gmail.com</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1651,19 +1619,15 @@
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>BELLARI</t>
-        </is>
-      </c>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="inlineStr"/>
@@ -1672,7 +1636,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WGE 344</t>
+          <t>WGG 02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1682,7 +1646,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>17-03-2026</t>
+          <t>18-03-2026</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1716,26 +1680,14 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GAUTHAM KRISHNAN C G </t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>7eb2aad4-4f8c-40f4-a713-8be9d2d8a120</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>ACC-20289798248</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>SBIN0010597</t>
-        </is>
-      </c>
+          <t>cb468725-c67b-4407-b1d0-166bf400cadc</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
@@ -1748,25 +1700,27 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>15000</v>
+        <v>34167</v>
       </c>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Salary February 2026 HALF SALARY PAID BALANCE TO BE PAID RPA_ID : ccf4b4faf0</t>
+          <t>Trident Engineers Yard Rent (3 Phase electricity : Rs. 34167/- Due 30/03/2026 (Previous bill not paid) RPA_ID : cb1ad76f3e</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>BELLARI</t>
-        </is>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
+          <t>IPSHEM</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>hrm@westernidc.com</t>
+          <t>midhuncraju12@gmail.com</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1796,11 +1750,7 @@
           <t>ACCEPTED</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>BELLARI</t>
-        </is>
-      </c>
+      <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr"/>
@@ -1809,7 +1759,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WGE 346</t>
+          <t>WGG 02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1819,7 +1769,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>17-03-2026</t>
+          <t>18-03-2026</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1853,26 +1803,14 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>DINESH KUMAR SUKUMARAN</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>43821507-5388-4ae9-989f-49efbc29e9db</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>ACC-41138649192</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>SBIN0070433</t>
-        </is>
-      </c>
+          <t>4770b06b-5259-4e12-9a08-13e5e810b39f</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
@@ -1885,25 +1823,27 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>54643</v>
+        <v>1598</v>
       </c>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Salary February 2026 RPA_ID : c2c8c4ca44</t>
+          <t>Trident Engineers (Water : Rs. 1598/- Due : 27/03/26) RPA_ID : 206464faf3</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>BELLARI</t>
-        </is>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
+          <t>IPSHEM</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>hrm@westernidc.com</t>
+          <t>midhuncraju12@gmail.com</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1925,19 +1865,15 @@
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>BELLARI</t>
-        </is>
-      </c>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr"/>
       <c r="AM11" t="inlineStr"/>
       <c r="AN11" t="inlineStr"/>
@@ -1946,7 +1882,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WGE 356</t>
+          <t>WGG 02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1956,7 +1892,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>17-03-2026</t>
+          <t>18-03-2026</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1990,26 +1926,14 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>DINESH KUMAR ( QC)</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>f3a7139d-9e88-4326-b90f-e1c5f4e249dc</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>ACC-11260100728119</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>FDRL0001126</t>
-        </is>
-      </c>
+          <t>227c95d6-9c8e-4b48-b0ad-3b02b2ef150a</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
@@ -2022,25 +1946,27 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>11000</v>
+        <v>1136</v>
       </c>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Salary February 2026 HALF SALARY PAID BALANCE TO BE PAID RPA_ID : 081d4980d2</t>
+          <t>Expense Reimbursement RPA_ID : e0e3b194df</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>BELLARI</t>
-        </is>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
+          <t>Cochin</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>hrm@westernidc.com</t>
+          <t>midhuncraju12@gmail.com</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -2062,19 +1988,15 @@
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>BELLARI</t>
-        </is>
-      </c>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr"/>
       <c r="AM12" t="inlineStr"/>
       <c r="AN12" t="inlineStr"/>
@@ -2083,7 +2005,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WGE 195</t>
+          <t>WGG 02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2093,7 +2015,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>17-03-2026</t>
+          <t>18-03-2026</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -2127,26 +2049,14 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>SAYAN BATTACHARYA</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>c8cfa3a7-42cb-4e79-b770-222b4f019bd8</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>ACC-14810110034736</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>UCBA0001481</t>
-        </is>
-      </c>
+          <t>2ba08a38-2ede-41d1-ba95-935b755a3fa0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
@@ -2159,25 +2069,27 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>41518</v>
+        <v>491</v>
       </c>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Salary February 2026 20000 PAID ON 13/03/2026 BALANCE TO BE PAID 41518 RPA_ID : 5c0cac8f09</t>
+          <t>Cheque to be given for bank cherges charges RPA_ID : 5036c9737d</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>KOLKATTA OFFICE</t>
-        </is>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
+          <t>Cochin</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>hrm@westernidc.com</t>
+          <t>midhuncraju12@gmail.com</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -2199,12 +2111,12 @@
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr"/>
@@ -2216,7 +2128,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WGE 189</t>
+          <t>WGG 02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2226,7 +2138,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>17-03-2026</t>
+          <t>18-03-2026</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -2260,26 +2172,14 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>MUNNA GUPTA</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>b5ea6847-295f-4515-a161-540fef2ca840</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>ACC-3421187013</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>CBIN0282509</t>
-        </is>
-      </c>
+          <t>24d1cde6-a742-4bbc-b9be-1f8a26d0ed41</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
@@ -2292,25 +2192,27 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>23980</v>
+        <v>130000</v>
       </c>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Salary February 2026 RPA_ID : 09d7636913</t>
+          <t>Zakkath fund RPA_ID : 64a790f015</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>GRSC KOLKATTA</t>
-        </is>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
+          <t>Cochin</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>hrm@westernidc.com</t>
+          <t>midhuncraju12@gmail.com</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -2330,8 +2232,16 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
       <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="inlineStr"/>
       <c r="AM14" t="inlineStr"/>
@@ -2341,7 +2251,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WGE 140</t>
+          <t>WGE 233</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2351,7 +2261,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>17-03-2026</t>
+          <t>18-03-2026</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -2367,7 +2277,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DCR</t>
+          <t>NEFT</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2387,22 +2297,22 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Shamzusaman</t>
+          <t>Muhammed anWer</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>5fe03c32-4cd9-4067-ad4b-855feb585177</t>
+          <t>124b9554-c227-44e7-bec8-ad74acee4b89</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>ACC-37737516718</t>
+          <t>ACC-99980113126044</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>SBIN0003881</t>
+          <t>FDRL0001413</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
@@ -2417,17 +2327,17 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>21035</v>
+        <v>16857</v>
       </c>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Salary February 2026 RPA_ID : edfdd0beb3</t>
+          <t>SALARY FOR THE MONTH OF FEBRUARY 2026 RPA_ID : 7abde59eeb</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>GRSC KOLKATTA</t>
+          <t>HO</t>
         </is>
       </c>
       <c r="Z15" t="n">
@@ -2435,7 +2345,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>hrm@westernidc.com</t>
+          <t>midhuncraju12@gmail.com</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2457,15 +2367,19 @@
       <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>ACCEPTED</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr"/>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
       <c r="AL15" t="inlineStr"/>
       <c r="AM15" t="inlineStr"/>
       <c r="AN15" t="inlineStr"/>
@@ -2474,7 +2388,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WGE 296</t>
+          <t>WGE 202</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2484,7 +2398,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>17-03-2026</t>
+          <t>18-03-2026</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -2500,7 +2414,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>NEFT</t>
+          <t>DCR</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2520,22 +2434,22 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>ASWINRAJ  K</t>
+          <t>Janhavi Rajendra Patil</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>f7ef9fdb-521a-47fe-94e9-1f879b4e0b17</t>
+          <t>ea339aeb-9490-4c27-a021-ed146b339814</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>ACC-33106528754</t>
+          <t>ACC-40356050651</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>SBIN0011925</t>
+          <t>SBIN0009832</t>
         </is>
       </c>
       <c r="O16" t="inlineStr"/>
@@ -2550,17 +2464,17 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>5357</v>
+        <v>25300</v>
       </c>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Salary February 2026 RPA_ID : 450e6c1177</t>
+          <t>ROOM RENT FEB 10TH TO MAR 10TH RPA_ID : 4b9d00efc0</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>GOA HUL</t>
+          <t>MUMBAI</t>
         </is>
       </c>
       <c r="Z16" t="n">
@@ -2568,7 +2482,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>hrm@westernidc.com</t>
+          <t>midhuncraju12@gmail.com</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2598,11 +2512,7 @@
           <t>ACCEPTED</t>
         </is>
       </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>GOA</t>
-        </is>
-      </c>
+      <c r="AK16" t="inlineStr"/>
       <c r="AL16" t="inlineStr"/>
       <c r="AM16" t="inlineStr"/>
       <c r="AN16" t="inlineStr"/>
@@ -2611,7 +2521,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>WGE 113</t>
+          <t>WGE 195</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2621,7 +2531,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>17-03-2026</t>
+          <t>18-03-2026</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -2637,7 +2547,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>DCR</t>
+          <t>NEFT</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2657,22 +2567,22 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>RIZWANUDHEEN</t>
+          <t>SAYAN BATTACHARYA</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>a6a64880-d884-4f66-af2b-c182c4dbe6c6</t>
+          <t>8c2c4536-3f5d-4932-ac99-fecdcde7dba6</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>ACC-67285944854</t>
+          <t>ACC-14810110034736</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>SBIN0070191</t>
+          <t>UCBA0001481</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
@@ -2687,17 +2597,17 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>10000</v>
+        <v>41518</v>
       </c>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
-          <t>February 2026 Incentive RPA_ID : 07fa1623b6</t>
+          <t>Salary February 2026 Rs.20000/- PAID ON 13/03/2026 BALANCE TO BE PAID Rs.41518/- RPA_ID : 7d8eace7ce</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>ST3 GOA</t>
+          <t>KOLKATTA OFFICE</t>
         </is>
       </c>
       <c r="Z17" t="n">
@@ -2705,7 +2615,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>hrm@westernidc.com</t>
+          <t>midhuncraju12@gmail.com</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -2735,11 +2645,7 @@
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>GOA</t>
-        </is>
-      </c>
+      <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="inlineStr"/>
       <c r="AM17" t="inlineStr"/>
       <c r="AN17" t="inlineStr"/>
@@ -2748,7 +2654,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>WGE 196</t>
+          <t>WGE 189</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2758,7 +2664,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>17-03-2026</t>
+          <t>18-03-2026</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2794,22 +2700,22 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>NILESH ANANT DURBHATKAR</t>
+          <t>MUNNA GUPTA</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>6de6ffe4-86a4-4db5-bfe7-bc14a5b5f1b9</t>
+          <t>6a2c6dbb-e5a5-4b53-88cb-be8ceefabb6f</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>ACC-04930100017981</t>
+          <t>ACC-3421187013</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>BARB0VASCOD</t>
+          <t>CBIN0282509</t>
         </is>
       </c>
       <c r="O18" t="inlineStr"/>
@@ -2824,25 +2730,27 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>16000</v>
+        <v>23980</v>
       </c>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
-          <t>The pending amount to be paid to Nilesh is ₹16,000 for August and September, as ₹8,000 per month is still unpaid. ( RUMJAN ROOM) RPA_ID : 28e6df0afb</t>
+          <t>SALARY FOR THE MONTH OF FEBRUARY 2026 RPA_ID : a896c65d37</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>ST3 GOA</t>
-        </is>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
+          <t>GRSC KOLKATTA</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>URGENT</t>
+        </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>hrm@westernidc.com</t>
+          <t>midhuncraju12@gmail.com</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2872,11 +2780,7 @@
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>GOA</t>
-        </is>
-      </c>
+      <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="inlineStr"/>
       <c r="AM18" t="inlineStr"/>
       <c r="AN18" t="inlineStr"/>
@@ -2885,7 +2789,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>WGE 342</t>
+          <t>WGE 113</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2895,7 +2799,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>17-03-2026</t>
+          <t>18-03-2026</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2911,7 +2815,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>NEFT</t>
+          <t>DCR</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2931,20 +2835,24 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>PAUL OFFSHORE PVT</t>
+          <t>RIZWANUDHEEN</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>e92c5ac0-5d85-40c9-804f-e1375dce3fdd</t>
+          <t>0c01e206-e077-4f84-905f-069ff1bbc334</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>ACC-7806823928</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>ACC-67285944854</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>SBIN0070191</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
@@ -2957,17 +2865,17 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>167495</v>
+        <v>10000</v>
       </c>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
-          <t>ONGC GOA JAN BILL LABOUR CHARGES - WELDER / FITTER/RIGGER AND FOOD ALLOWANCE 100,000 paid balance to paid RPA_ID : f568c01428</t>
+          <t>INCENTIVE FOR THE MONTH OF FEBRUARY 2026 RPA_ID : 280c4deaa3</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>ONGC GOA</t>
+          <t>ST3 GOA</t>
         </is>
       </c>
       <c r="Z19" t="n">
@@ -2975,7 +2883,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>hrm@westernidc.com</t>
+          <t>midhuncraju12@gmail.com</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -3018,7 +2926,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>WGE 192</t>
+          <t>WGE 196</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3028,7 +2936,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>17-03-2026</t>
+          <t>18-03-2026</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -3064,22 +2972,22 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Hafis Bin Haris</t>
+          <t>NILESH ANANT DURBHATKAR</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>cb53c480-a2f2-4bfd-b6ce-879afa2e8330</t>
+          <t>c5a9bd5a-c955-462e-9c5f-7d410080b5a4</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>ACC-99980105201458</t>
+          <t>ACC-04930100017981</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>FDRL0001143</t>
+          <t>BARB0VASCOD</t>
         </is>
       </c>
       <c r="O20" t="inlineStr"/>
@@ -3094,17 +3002,17 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>7423</v>
+        <v>16000</v>
       </c>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Salary December Rs.7423/- January 9597/- Full and Final Settlement RPA_ID : 619897ac87</t>
+          <t>The pending amount to be paid to Nilesh is ₹16,000 for August and September, as ₹8,000 per month is still unpaid. ( RUMJAN ROOM) RPA_ID : 28f6e90f0d</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>GOA HUL</t>
+          <t>ST3 GOA</t>
         </is>
       </c>
       <c r="Z20" t="n">
@@ -3112,7 +3020,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>hrm@westernidc.com</t>
+          <t>midhuncraju12@gmail.com</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -3134,12 +3042,12 @@
       <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>ACCEPTED</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>ACCEPTED</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -3155,7 +3063,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>WGE 115</t>
+          <t>WGE 342</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3165,7 +3073,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>17-03-2026</t>
+          <t>18-03-2026</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -3201,24 +3109,20 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Muhammad Shamil C</t>
+          <t>PAUL OFFSHORE PVT</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>08dd4076-dc7e-491b-bc01-b699b727629c</t>
+          <t>ed38e12e-7510-49f9-b1d7-a73fde45e7f9</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>ACC-11220100177873</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>FDRL0001122</t>
-        </is>
-      </c>
+          <t>ACC-7806823928</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
@@ -3231,17 +3135,17 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>9257</v>
+        <v>167495</v>
       </c>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Salary December Full and Final Settlement RPA_ID : 737fda2039</t>
+          <t>ONGC GOA JAN BILL LABOUR CHARGES - WELDER / FITTER/RIGGER AND FOOD ALLOWANCE RPA_ID : 16cd738907</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>ST3 GOA</t>
+          <t>ONGC GOA</t>
         </is>
       </c>
       <c r="Z21" t="n">
@@ -3249,7 +3153,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>hrm@westernidc.com</t>
+          <t>midhuncraju12@gmail.com</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -3292,7 +3196,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>WGE 112</t>
+          <t>WGE 192</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3302,7 +3206,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>17-03-2026</t>
+          <t>18-03-2026</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -3338,22 +3242,22 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>ABHISHEK PEDNEKAR</t>
+          <t>Hafis Bin Haris</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>c92ec88f-32d8-4799-8e47-e71a182c6ac7</t>
+          <t>362e0f5c-05f7-45c3-98b5-09761da5107d</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>ACC-06050100016920</t>
+          <t>ACC-99980105201458</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>BARB0MAPUCA</t>
+          <t>FDRL0001143</t>
         </is>
       </c>
       <c r="O22" t="inlineStr"/>
@@ -3368,17 +3272,17 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>8936</v>
+        <v>9597</v>
       </c>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Salary January Full and Final Settlement RPA_ID : 3b8fffd5f8</t>
+          <t>Salary- January 9597/- Full and Final Settlement RPA_ID : fcac69f5b5</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>ST3 GOA</t>
+          <t>GOA HUL</t>
         </is>
       </c>
       <c r="Z22" t="n">
@@ -3386,7 +3290,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>hrm@westernidc.com</t>
+          <t>midhuncraju12@gmail.com</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3408,12 +3312,12 @@
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -3429,7 +3333,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>WGE 104</t>
+          <t>WGE 115</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3439,7 +3343,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>17-03-2026</t>
+          <t>18-03-2026</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -3475,22 +3379,22 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>BRAHMADATHAN</t>
+          <t>Muhammad Shamil C</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>77454dcc-b56c-491e-b53b-b9e81c0181e7</t>
+          <t>404584ed-2576-43b8-ba2c-b1c126176af5</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>ACC-232001000010098</t>
+          <t>ACC-11220100177873</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>IOBA0002320</t>
+          <t>FDRL0001122</t>
         </is>
       </c>
       <c r="O23" t="inlineStr"/>
@@ -3505,17 +3409,17 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>24379</v>
+        <v>9257</v>
       </c>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Salary November Full and Final settlement RPA_ID : 15d0b7fb19</t>
+          <t>Salary December Full and Final Settlement RPA_ID : 2851178f14</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>GOA HUL</t>
+          <t>ST3 GOA</t>
         </is>
       </c>
       <c r="Z23" t="n">
@@ -3523,7 +3427,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>hrm@westernidc.com</t>
+          <t>midhuncraju12@gmail.com</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3545,12 +3449,12 @@
       <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -3566,7 +3470,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>WGE 170</t>
+          <t>WGE 112</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3576,7 +3480,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>17-03-2026</t>
+          <t>18-03-2026</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -3612,22 +3516,22 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>VEDANT</t>
+          <t>ABHISHEK PEDNEKAR</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>f4e45530-0b9c-4491-9744-1befa42bbcb8</t>
+          <t>96803c97-2dc0-4b6d-a061-a7576ec83bc4</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>ACC-2047172054</t>
+          <t>ACC-06050100016920</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>KKBK0001429</t>
+          <t>BARB0MAPUCA</t>
         </is>
       </c>
       <c r="O24" t="inlineStr"/>
@@ -3642,17 +3546,17 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>6451</v>
+        <v>8936</v>
       </c>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Material Shiftng 8 Days worked (December 5 days , January 3 Days) RPA_ID : a9ff4f8485</t>
+          <t>Salary January Full and Final Settlement RPA_ID : 8aa81913bf</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>MDL</t>
+          <t>ST3 GOA</t>
         </is>
       </c>
       <c r="Z24" t="n">
@@ -3660,7 +3564,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>hrm@westernidc.com</t>
+          <t>midhuncraju12@gmail.com</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -3682,15 +3586,19 @@
       <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr"/>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
       <c r="AL24" t="inlineStr"/>
       <c r="AM24" t="inlineStr"/>
       <c r="AN24" t="inlineStr"/>
@@ -3699,7 +3607,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>WGE 197</t>
+          <t>WGE 104</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3709,7 +3617,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>17-03-2026</t>
+          <t>18-03-2026</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -3745,22 +3653,22 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>NIZER RODRIGOUS</t>
+          <t>BRAHMADATHAN</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>6ccbc13e-1605-4b98-b576-58126d10f10a</t>
+          <t>522a85b0-5410-4ff9-8a58-5b491b591b08</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>ACC-04930100017817</t>
+          <t>ACC-232001000010098</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>BARB0VASCOD</t>
+          <t>IOBA0002320</t>
         </is>
       </c>
       <c r="O25" t="inlineStr"/>
@@ -3775,17 +3683,17 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>15000</v>
+        <v>24379</v>
       </c>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Room Rent  (Feb 12th to March 12th) RPA_ID : b8303c1e4e</t>
+          <t>Salary November Full and Final settlement RPA_ID : 9bec927d04</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>ST3 GOA</t>
+          <t>GOA HUL</t>
         </is>
       </c>
       <c r="Z25" t="n">
@@ -3793,7 +3701,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>hrm@westernidc.com</t>
+          <t>midhuncraju12@gmail.com</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -3815,12 +3723,12 @@
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -3836,7 +3744,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>WGE 203</t>
+          <t>WGE 170</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3846,7 +3754,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>17-03-2026</t>
+          <t>18-03-2026</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -3862,7 +3770,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>DCR</t>
+          <t>NEFT</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3882,22 +3790,22 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>MADUMITHA</t>
+          <t>VEDANT</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>edc5872b-1488-4a6c-a55f-f5e545563623</t>
+          <t>2236fd8d-5433-4bfc-945b-ff21a8101138</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>ACC-10629442465</t>
+          <t>ACC-2047172054</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>SBIN0002016</t>
+          <t>KKBK0001429</t>
         </is>
       </c>
       <c r="O26" t="inlineStr"/>
@@ -3912,17 +3820,17 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>15000</v>
+        <v>6451</v>
       </c>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Room Rent Kolkatta Office RPA_ID : 32b266481a</t>
+          <t>Material Shiftng 8 Days worked (December 5 days , January 3 Days) RPA_ID : c5f53a66e7</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>KOLKATTA</t>
+          <t>MDL</t>
         </is>
       </c>
       <c r="Z26" t="n">
@@ -3930,7 +3838,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>hrm@westernidc.com</t>
+          <t>midhuncraju12@gmail.com</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -3952,12 +3860,12 @@
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>ACCEPTED</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>ACCEPTED</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr"/>
@@ -3969,7 +3877,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>WGG 02</t>
+          <t>WGE 299</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3979,7 +3887,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>17-03-2026</t>
+          <t>18-03-2026</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -4013,14 +3921,26 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>ARJUN(ONGC) SUPERVISOR</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>71be5608-af49-44f0-9424-5a7826ab659f</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>95104621-27bb-4239-a5ea-edc0126c33a6</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>ACC-67329839060</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>SBIN0070076</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
@@ -4033,17 +3953,17 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>300000</v>
+        <v>4800</v>
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr">
         <is>
-          <t>August Arrear RPA_ID : 947c2479ad</t>
+          <t>Material Purchase for ongc jetty project room stay expenses to gujarat 16/03/2026 -17/03/2026-18/03/2026-19/03/2026 RPA_ID : 447ae09537</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>ONGC IPSHEM</t>
         </is>
       </c>
       <c r="Z27" t="n">
@@ -4051,7 +3971,7 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>hrm@westernidc.com</t>
+          <t>midhuncraju12@gmail.com</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -4073,15 +3993,19 @@
       <c r="AH27" t="inlineStr"/>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr"/>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>ONGC IPSHEM</t>
+        </is>
+      </c>
       <c r="AL27" t="inlineStr"/>
       <c r="AM27" t="inlineStr"/>
       <c r="AN27" t="inlineStr"/>
@@ -4090,7 +4014,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>WGE 130</t>
+          <t>WGG 02</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4100,7 +4024,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>17-03-2026</t>
+          <t>18-03-2026</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -4134,26 +4058,14 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Ranjith</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>61d3f2ef-2a9d-4020-a03f-64d60882f6cc</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>ACC-112201507178</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>ICIC0001122</t>
-        </is>
-      </c>
+          <t>9e2511bb-72d7-4ac8-b7d0-5343ef5848f6</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
@@ -4166,17 +4078,17 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>11310</v>
+        <v>4000</v>
       </c>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Electrical (As per instruction from Arun kumar Sir) RPA_ID : 0af9322df0</t>
+          <t>KOLKATA INSTALLLATION BALANCE AMOUNT TO BE PAID RPA_ID : c86c75e699</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>ONGC ELECTRICAL</t>
+          <t>KOLKATA</t>
         </is>
       </c>
       <c r="Z28" t="n">
@@ -4184,7 +4096,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>hrm@westernidc.com</t>
+          <t>midhuncraju12@gmail.com</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -4206,17 +4118,17 @@
       <c r="AH28" t="inlineStr"/>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>ACCEPTED</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>ACCEPTED</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>ONGC ELECTRICAL</t>
+          <t>KOLKATA</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr"/>
@@ -4227,7 +4139,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>WGE 299</t>
+          <t>WGE 206</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4237,7 +4149,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>17-03-2026</t>
+          <t>18-03-2026</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -4273,22 +4185,22 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>ARJUN(ONGC) SUPERVISOR</t>
+          <t>RAHUL</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>4abe57f1-9ddf-4372-a8db-8e19bc15297c</t>
+          <t>5cdee763-b2a8-4f06-a31a-7822125955ec</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>ACC-67329839060</t>
+          <t>ACC-0754104000129480</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>SBIN0070076</t>
+          <t>IBKL0000754</t>
         </is>
       </c>
       <c r="O29" t="inlineStr"/>
@@ -4303,17 +4215,17 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>4800</v>
+        <v>7500</v>
       </c>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr">
         <is>
-          <t>material purchase for ongc jetty project room stay expenses to gujarat 16/03/2026 -17/03/2026-18/03/2026-19/03/2026 RPA_ID : aa4253f6bd</t>
+          <t>SALARY ADVANCE MARCH 2026 RPA_ID : 4f9ca7b8d7</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>ONGC IPSHEM</t>
+          <t>BELLARI</t>
         </is>
       </c>
       <c r="Z29" t="n">
@@ -4321,7 +4233,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>hrm@westernidc.com</t>
+          <t>midhuncraju12@gmail.com</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -4343,17 +4255,17 @@
       <c r="AH29" t="inlineStr"/>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>ONGC IPSHEM</t>
+          <t>BELLARI</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr"/>
@@ -4364,7 +4276,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>WGE 299</t>
+          <t>WGE 87</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4374,7 +4286,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>17-03-2026</t>
+          <t>18-03-2026</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -4390,7 +4302,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>NEFT</t>
+          <t>DCR</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4410,22 +4322,22 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>ARJUN(ONGC) SUPERVISOR</t>
+          <t>Mary Ashna K P</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>45745010-cab5-4c50-8675-3c2758bbf1b7</t>
+          <t>1d6b1b15-06b5-4ab8-98e9-010dc469b19c</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>ACC-67329839060</t>
+          <t>ACC-67216866751</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>SBIN0070076</t>
+          <t>SBIN0070150</t>
         </is>
       </c>
       <c r="O30" t="inlineStr"/>
@@ -4440,17 +4352,17 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>320</v>
+        <v>5000</v>
       </c>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr">
         <is>
-          <t>TRAVEL EXPENSES 80*4 RPA_ID : b191fee65f</t>
+          <t>SALARY ADVANCE MARCH 2026 RPA_ID : fc2d312190</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>ONGC IPSHEM</t>
+          <t>HO</t>
         </is>
       </c>
       <c r="Z30" t="n">
@@ -4458,7 +4370,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>hrm@westernidc.com</t>
+          <t>midhuncraju12@gmail.com</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -4490,7 +4402,7 @@
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>ONGC IPSHEM</t>
+          <t>HO</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr"/>
@@ -4501,7 +4413,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>WGE 341</t>
+          <t>WGE 73</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4511,7 +4423,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>17-03-2026</t>
+          <t>18-03-2026</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -4527,7 +4439,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>NEFT</t>
+          <t>DCR</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4547,22 +4459,22 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>PRADEEP KUMAR K ( ROOM OWNER)</t>
+          <t>Nithin</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>202546cf-444c-4669-8089-cfbf290fa9d6</t>
+          <t>9dcddf16-321a-4fd4-9256-514f2b2397d4</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>ACC-570183114278</t>
+          <t>ACC-32555551936</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>SBIN 0070200</t>
+          <t>SBIN0001890</t>
         </is>
       </c>
       <c r="O31" t="inlineStr"/>
@@ -4577,17 +4489,17 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr">
         <is>
-          <t>CHELLARI ROOM RENT DUE DATE 16TH RPA_ID : 69630e64e1</t>
+          <t>Casual Engaged Elathoor (Leave Nishant &amp; Aswanth) 17.03.2026,18.03.2020 RPA_ID : 87005c0883</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>CHELLARI</t>
+          <t>ELATHOOR</t>
         </is>
       </c>
       <c r="Z31" t="n">
@@ -4595,7 +4507,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>hrm@westernidc.com</t>
+          <t>midhuncraju12@gmail.com</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -4627,7 +4539,7 @@
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>CHELLARI</t>
+          <t>HO</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr"/>
@@ -4638,7 +4550,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>WGE 01</t>
+          <t>WGE 10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4648,7 +4560,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>17-03-2026</t>
+          <t>18-03-2026</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -4664,7 +4576,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>NEFT</t>
+          <t>DCR</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4684,22 +4596,22 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>BENNY P A</t>
+          <t>KIRAN KUMAR K</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>84c4d6dd-9010-461b-9312-77f46cb359fb</t>
+          <t>432009f2-0842-4eb4-95fb-ee23df956013</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>ACC-43152200012062</t>
+          <t>ACC-30060475288</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>CNRB0014315</t>
+          <t>SBIN0009122</t>
         </is>
       </c>
       <c r="O32" t="inlineStr"/>
@@ -4714,17 +4626,17 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>5700</v>
+        <v>2000</v>
       </c>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr">
         <is>
-          <t>BENNY FEB EXPENSES ( NORMAL SAMPLE DELIVERY - 18*150 =2700/ GRASS CUTTING MACHINE 3000) RPA_ID : 5d9b976872</t>
+          <t>Casual Payment for leave compensate 05.03.2026 &amp; 06.03.2026 (Udayan &amp; Benny) RPA_ID : b98f37f723</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>IOCL WELLINGTON</t>
+          <t>IOCL Wilington</t>
         </is>
       </c>
       <c r="Z32" t="n">
@@ -4732,7 +4644,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>hrm@westernidc.com</t>
+          <t>midhuncraju12@gmail.com</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -4771,7 +4683,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>WGE01</t>
+          <t>WGG 02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4781,7 +4693,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>17-03-2026</t>
+          <t>18-03-2026</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -4815,14 +4727,10 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>ONLINE PAYMENTS</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>85758f51-a269-4fa2-a534-cc4525314c16</t>
+          <t>63122d13-e499-4642-a046-dbc1c2af073b</t>
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
@@ -4839,17 +4747,17 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>5700</v>
+        <v>300000</v>
       </c>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr">
         <is>
-          <t>BENNY FEB EXPENSES ( NORMAL SAMPLE DELIVERY - 18*150 =2700/ GRASS CUTTING MACHINE 3000) RPA_ID : 3a13e18e20</t>
+          <t>AUGUST PF ARREAR KOCHI AND KONGAN APPROXIMATE RPA_ID : 88cf69713d</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>IOCL WELLINGTON</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="Z33" t="n">
@@ -4857,7 +4765,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>hrm@westernidc.com</t>
+          <t>midhuncraju12@gmail.com</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -4893,1016 +4801,6 @@
       <c r="AN33" t="inlineStr"/>
       <c r="AO33" t="inlineStr"/>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>WGE 02</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>17-03-2026</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>DCR</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>SAFAL SOJAN</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>d3244fff-a4fb-42f5-b67a-48d0dfcd8fd6</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>ACC-67268241138</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>SBIN0070435</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V34" t="n">
-        <v>6000</v>
-      </c>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>HOSE SHIFITING  VECHICLE CHARGE RPA_ID : f0554a3339</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>IOCL WELLINGTON</t>
-        </is>
-      </c>
-      <c r="Z34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>hrm@westernidc.com</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="inlineStr"/>
-      <c r="AG34" t="inlineStr"/>
-      <c r="AH34" t="inlineStr"/>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr"/>
-      <c r="AL34" t="inlineStr"/>
-      <c r="AM34" t="inlineStr"/>
-      <c r="AN34" t="inlineStr"/>
-      <c r="AO34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>WGE 10</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>17-03-2026</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>DCR</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>KIRAN KUMAR K</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>cbe043ce-cf7f-4adb-a9c7-2d0810897e82</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>ACC-30060475288</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>SBIN0009122</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V35" t="n">
-        <v>2000</v>
-      </c>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>2 CASUAL PRESENT 17/03/2026 ( COMPANSATE FOR THE LEAVE ON 04/03/2026 (VINOD &amp; UDHAYAN) RPA_ID : 799aeb3f77</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>IOCL WELLINGTON</t>
-        </is>
-      </c>
-      <c r="Z35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>hrm@westernidc.com</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="inlineStr"/>
-      <c r="AG35" t="inlineStr"/>
-      <c r="AH35" t="inlineStr"/>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr"/>
-      <c r="AL35" t="inlineStr"/>
-      <c r="AM35" t="inlineStr"/>
-      <c r="AN35" t="inlineStr"/>
-      <c r="AO35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>WGG 02</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>17-03-2026</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>NEFT</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>d80d215d-84de-42dd-9712-efaabaa71083</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V36" t="n">
-        <v>18000</v>
-      </c>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>KOLKATA INSTALLLATION BALANCE AMOUNT TO BE PAID RPA_ID : f34397cc92</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>KOLKATA</t>
-        </is>
-      </c>
-      <c r="Z36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>hrm@westernidc.com</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="inlineStr"/>
-      <c r="AG36" t="inlineStr"/>
-      <c r="AH36" t="inlineStr"/>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>KOLKATA</t>
-        </is>
-      </c>
-      <c r="AL36" t="inlineStr"/>
-      <c r="AM36" t="inlineStr"/>
-      <c r="AN36" t="inlineStr"/>
-      <c r="AO36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>WGE 429</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>17-03-2026</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>NEFT</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>80be749c-cea3-4a17-a98c-61013d78e22e</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V37" t="n">
-        <v>500</v>
-      </c>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>Payment of stamp paper RPA_ID : ad10ffbc61</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>GAS BU SCHEDULE OF RATES MAHARASTRA BPCL</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>PAYMENT OF STAMP PAPER</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>executive.westerntender@gmail.com</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="inlineStr"/>
-      <c r="AG37" t="inlineStr"/>
-      <c r="AH37" t="inlineStr"/>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr"/>
-      <c r="AL37" t="inlineStr"/>
-      <c r="AM37" t="inlineStr"/>
-      <c r="AN37" t="inlineStr"/>
-      <c r="AO37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>WGG 02</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>17-03-2026</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>NEFT</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>cdcd724c-7f4e-499e-8f6b-9aa8e428a03d</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V38" t="n">
-        <v>79930</v>
-      </c>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>Pep consultancy pendiing payment RPA_ID : 36d37b1ac3</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>Cochin</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>PAYMENT</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>Payments@westernidc.com</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="inlineStr"/>
-      <c r="AG38" t="inlineStr"/>
-      <c r="AH38" t="inlineStr"/>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr"/>
-      <c r="AL38" t="inlineStr"/>
-      <c r="AM38" t="inlineStr"/>
-      <c r="AN38" t="inlineStr"/>
-      <c r="AO38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>WGG 02</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>17-03-2026</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>NEFT</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>fde679a2-9c8d-469a-8bae-d0f42dab782d</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V39" t="n">
-        <v>793000</v>
-      </c>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>Transfer to cash ledger against invoice RPA_ID : 9cb470118d</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>Cochin</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>PAYMENT</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>Payments@westernidc.com</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="inlineStr"/>
-      <c r="AG39" t="inlineStr"/>
-      <c r="AH39" t="inlineStr"/>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr"/>
-      <c r="AL39" t="inlineStr"/>
-      <c r="AM39" t="inlineStr"/>
-      <c r="AN39" t="inlineStr"/>
-      <c r="AO39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>WGG 02</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>17-03-2026</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>NEFT</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>fe7a0ab8-070e-4af8-b064-75bcecec5f91</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V40" t="n">
-        <v>1175000</v>
-      </c>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>Transfer to cash ledger against invoice RPA_ID : 6b5064d69e</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>Goa</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>PAYMENT</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>Payments@westernidc.com</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF40" t="inlineStr"/>
-      <c r="AG40" t="inlineStr"/>
-      <c r="AH40" t="inlineStr"/>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>GOA</t>
-        </is>
-      </c>
-      <c r="AL40" t="inlineStr"/>
-      <c r="AM40" t="inlineStr"/>
-      <c r="AN40" t="inlineStr"/>
-      <c r="AO40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>WGG 02</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>17-03-2026</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>NEFT</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>4911d27c-7b0f-4e35-a3e4-6f51558dae2a</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V41" t="n">
-        <v>15000</v>
-      </c>
-      <c r="W41" t="inlineStr"/>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>Transfer to cash ledger against invoice RPA_ID : b5615fa386</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>Mumbai</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>PAYMENT</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>Payments@westernidc.com</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF41" t="inlineStr"/>
-      <c r="AG41" t="inlineStr"/>
-      <c r="AH41" t="inlineStr"/>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr"/>
-      <c r="AL41" t="inlineStr"/>
-      <c r="AM41" t="inlineStr"/>
-      <c r="AN41" t="inlineStr"/>
-      <c r="AO41" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PENDING_APPROVAL_SHEET.xlsx
+++ b/PENDING_APPROVAL_SHEET.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO33"/>
+  <dimension ref="A1:AO31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -638,7 +638,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WGE 189</t>
+          <t>WGG 02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>17-03-2026</t>
+          <t>19-03-2026</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -682,26 +682,14 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>MUNNA GUPTA</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>b5ea6847-295f-4515-a161-540fef2ca840</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>ACC-3421187013</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>CBIN0282509</t>
-        </is>
-      </c>
+          <t>0b6b32f0-b66d-4ce6-b983-301989cfa5d7</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
@@ -714,25 +702,27 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>23980</v>
+        <v>79930</v>
       </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Salary February 2026 RPA_ID : 09d7636913</t>
+          <t>Pep consultancy pendiing payment RPA_ID : d02b620b35</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>GRSC KOLKATTA</t>
-        </is>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
+          <t>Cochin</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>hrm@westernidc.com</t>
+          <t>Payments@westernidc.com</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -747,19 +737,19 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>23980</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>ACCEPTED</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>ACCEPTED</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr"/>
@@ -781,7 +771,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>18-03-2026</t>
+          <t>19-03-2026</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -818,7 +808,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>49eb6f14-9179-4e70-8f07-3889e22444d0</t>
+          <t>49b38ca0-bf49-4d91-9cec-c3da77b22ae3</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -835,12 +825,12 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>331732</v>
+        <v>52938.88</v>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Transfer to cash ledger against invoice RPA_ID : 07b95eac79</t>
+          <t>Transfer to cash ledger against invoice elathur RPA_ID : ac3b216906</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -904,7 +894,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>18-03-2026</t>
+          <t>19-03-2026</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -941,7 +931,7 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>18ffaaff-c404-43f5-99d8-bf458d3a87d3</t>
+          <t>14f251fb-ee0c-4fef-ac43-f869a8867ad9</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -958,17 +948,17 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>79930</v>
+        <v>7021</v>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Pep consultancy pendiing payment RPA_ID : 597c1e041c</t>
+          <t>Trident Engineers Yard Rent (1 Phase electricity : Rs. 7021/- Due 20/03/2026) RPA_ID : f440d20079</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Cochin</t>
+          <t>IPSHEM</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -978,7 +968,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>midhuncraju12@gmail.com</t>
+          <t>Payments@westernidc.com</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1000,12 +990,12 @@
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr"/>
@@ -1027,7 +1017,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>18-03-2026</t>
+          <t>19-03-2026</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1064,7 +1054,7 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>d8f4c361-b186-48fe-b4d1-187cbbe0ae78</t>
+          <t>a247a994-c373-4924-82b2-0a1c5baaffe4</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -1081,17 +1071,17 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>745000</v>
+        <v>34167</v>
       </c>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Transfer to cash ledger against invoice RPA_ID : 9b4ce2fe88</t>
+          <t>Trident Engineers Yard Rent (3 Phase electricity : Rs. 34167/- Due 30/03/2026 (Previous bill not paid) RPA_ID : 7fe1541fa6</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Cochin</t>
+          <t>IPSHEM</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1101,7 +1091,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>midhuncraju12@gmail.com</t>
+          <t>Payments@westernidc.com</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1150,7 +1140,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>18-03-2026</t>
+          <t>19-03-2026</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1187,7 +1177,7 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>57e540d8-e92d-4a89-bb7d-7e68e087d58c</t>
+          <t>0c933cf5-322f-4c12-8127-cbe902c6f3db</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -1204,17 +1194,17 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>1175000</v>
+        <v>1598</v>
       </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Transfer to cash ledger against invoice RPA_ID : 6dedbb2fa9</t>
+          <t>Trident Engineers (Water : Rs. 1598/- Due : 27/03/26) RPA_ID : b2aba3ac84</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>IPSHEM</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1224,7 +1214,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>midhuncraju12@gmail.com</t>
+          <t>Payments@westernidc.com</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1254,11 +1244,7 @@
           <t>ACCEPTED</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>GOA</t>
-        </is>
-      </c>
+      <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
@@ -1277,7 +1263,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>18-03-2026</t>
+          <t>19-03-2026</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1314,7 +1300,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>19e8af86-1a27-4d7e-89a7-34f19e28eeb3</t>
+          <t>f40af4c4-3647-405e-a8d6-687c0a1238b4</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -1331,17 +1317,17 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>15000</v>
+        <v>24300</v>
       </c>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Transfer to cash ledger against invoice RPA_ID : a3ead5556a</t>
+          <t>School fees 8800, Tution 15500 ( Hijas sir Salary) RPA_ID : 6c1db80677</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Cochin</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1351,7 +1337,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>midhuncraju12@gmail.com</t>
+          <t>Payments@westernidc.com</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1400,7 +1386,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>18-03-2026</t>
+          <t>19-03-2026</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1437,7 +1423,7 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>411bcf6e-9332-4070-bf51-f1835b3e221f</t>
+          <t>5d677423-2741-4508-9397-d14cdbd38f43</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -1454,17 +1440,17 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>509</v>
+        <v>80</v>
       </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Expense Reimbursement (Hishem sir Police Verification Payment made by Rose Ma'am) RPA_ID : 6f9048e91a</t>
+          <t>Drinking Water - paid to Dinesh RPA_ID : eefc11ad6a</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Cochin</t>
+          <t>BELLARI</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1474,7 +1460,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>midhuncraju12@gmail.com</t>
+          <t>Payments@westernidc.com</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1504,7 +1490,11 @@
           <t>ACCEPTED</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
@@ -1523,7 +1513,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18-03-2026</t>
+          <t>19-03-2026</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1560,7 +1550,7 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>c924ecab-6c14-4929-9824-b363e55222e0</t>
+          <t>6729fa13-63b0-4510-b875-9fc54663dde0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1577,17 +1567,17 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>7021</v>
+        <v>600</v>
       </c>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Trident Engineers Yard Rent (1 Phase electricity : Rs. 7021/- Due 20/03/2026) RPA_ID : 25fc2190d5</t>
+          <t>NAIJIL -200 FOR STAMP PAPER AND 400 FOR AVIATOR PETEROL RPA_ID : 619e700ef8</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>IPSHEM</t>
+          <t>Cochin</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1597,7 +1587,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>midhuncraju12@gmail.com</t>
+          <t>Payments@westernidc.com</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1646,7 +1636,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>18-03-2026</t>
+          <t>19-03-2026</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1683,7 +1673,7 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>cb468725-c67b-4407-b1d0-166bf400cadc</t>
+          <t>8b12b5ec-7a48-42e2-a6f6-6cab0d1d618f</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1700,17 +1690,17 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>34167</v>
+        <v>600</v>
       </c>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Trident Engineers Yard Rent (3 Phase electricity : Rs. 34167/- Due 30/03/2026 (Previous bill not paid) RPA_ID : cb1ad76f3e</t>
+          <t>SARFARAS- STAMP PAPER RPA_ID : a6b8ce9577</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>IPSHEM</t>
+          <t>Cochin</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1720,7 +1710,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>midhuncraju12@gmail.com</t>
+          <t>Payments@westernidc.com</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1769,7 +1759,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>18-03-2026</t>
+          <t>19-03-2026</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1806,7 +1796,7 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>4770b06b-5259-4e12-9a08-13e5e810b39f</t>
+          <t>a4d54aea-e88c-4473-9307-74c81e72aa7e</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -1823,17 +1813,17 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>1598</v>
+        <v>70</v>
       </c>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Trident Engineers (Water : Rs. 1598/- Due : 27/03/26) RPA_ID : 206464faf3</t>
+          <t>FOOD EXPENSE PAID TO DINESH RPA_ID : ef0077fb87</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>IPSHEM</t>
+          <t>BELLARI</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1843,7 +1833,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>midhuncraju12@gmail.com</t>
+          <t>Payments@westernidc.com</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1873,7 +1863,11 @@
           <t>ACCEPTED</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
       <c r="AL11" t="inlineStr"/>
       <c r="AM11" t="inlineStr"/>
       <c r="AN11" t="inlineStr"/>
@@ -1892,7 +1886,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>18-03-2026</t>
+          <t>19-03-2026</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1929,7 +1923,7 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>227c95d6-9c8e-4b48-b0ad-3b02b2ef150a</t>
+          <t>70247de1-2f5d-4cf5-a353-dd6d28fe63ce</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -1946,12 +1940,12 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>1136</v>
+        <v>400</v>
       </c>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Expense Reimbursement RPA_ID : e0e3b194df</t>
+          <t>COURIER AND FUEL EXP (TIRUNELVELI BILL) RPA_ID : 62a753b060</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1966,7 +1960,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>midhuncraju12@gmail.com</t>
+          <t>Payments@westernidc.com</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -2015,7 +2009,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>18-03-2026</t>
+          <t>19-03-2026</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -2052,7 +2046,7 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2ba08a38-2ede-41d1-ba95-935b755a3fa0</t>
+          <t>396cfce1-b442-4342-a51f-ab8f272788f4</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -2069,17 +2063,17 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>491</v>
+        <v>504</v>
       </c>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Cheque to be given for bank cherges charges RPA_ID : 5036c9737d</t>
+          <t>GAS PURCHASE RPA_ID : 190c084198</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Cochin</t>
+          <t>BELLARI</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -2089,7 +2083,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>midhuncraju12@gmail.com</t>
+          <t>Payments@westernidc.com</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -2119,7 +2113,11 @@
           <t>ACCEPTED</t>
         </is>
       </c>
-      <c r="AK13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
       <c r="AL13" t="inlineStr"/>
       <c r="AM13" t="inlineStr"/>
       <c r="AN13" t="inlineStr"/>
@@ -2138,7 +2136,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>18-03-2026</t>
+          <t>19-03-2026</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -2175,7 +2173,7 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>24d1cde6-a742-4bbc-b9be-1f8a26d0ed41</t>
+          <t>a8912cbc-4a05-4178-8ef8-4dd6ff8432be</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -2192,17 +2190,17 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>130000</v>
+        <v>360</v>
       </c>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Zakkath fund RPA_ID : 64a790f015</t>
+          <t>CAN PURCHASE (ONLY 360 PAID 20 DISCOUNT) RPA_ID : e4566d4c69</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Cochin</t>
+          <t>BELLARI</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -2212,7 +2210,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>midhuncraju12@gmail.com</t>
+          <t>Payments@westernidc.com</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -2242,7 +2240,11 @@
           <t>ACCEPTED</t>
         </is>
       </c>
-      <c r="AK14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
       <c r="AL14" t="inlineStr"/>
       <c r="AM14" t="inlineStr"/>
       <c r="AN14" t="inlineStr"/>
@@ -2251,7 +2253,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WGE 233</t>
+          <t>WGG 02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2261,7 +2263,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>18-03-2026</t>
+          <t>19-03-2026</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -2295,26 +2297,14 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Muhammed anWer</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>124b9554-c227-44e7-bec8-ad74acee4b89</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>ACC-99980113126044</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>FDRL0001413</t>
-        </is>
-      </c>
+          <t>47ff5575-da66-43fa-a7a2-e6af17728a8e</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
@@ -2327,25 +2317,27 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>16857</v>
+        <v>200</v>
       </c>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
-          <t>SALARY FOR THE MONTH OF FEBRUARY 2026 RPA_ID : 7abde59eeb</t>
+          <t>PUNCHER REAPIR - PICK UP RPA_ID : e5d63497df</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>HO</t>
-        </is>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>midhuncraju12@gmail.com</t>
+          <t>Payments@westernidc.com</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2367,17 +2359,17 @@
       <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>HO</t>
+          <t>BELLARI</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr"/>
@@ -2388,7 +2380,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WGE 202</t>
+          <t>WGG 02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2398,7 +2390,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>18-03-2026</t>
+          <t>19-03-2026</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -2414,7 +2406,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>DCR</t>
+          <t>NEFT</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2432,26 +2424,14 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Janhavi Rajendra Patil</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>ea339aeb-9490-4c27-a021-ed146b339814</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>ACC-40356050651</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>SBIN0009832</t>
-        </is>
-      </c>
+          <t>76e58838-dddc-43e0-b8c9-f2760d7f2faf</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
@@ -2464,25 +2444,27 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>25300</v>
+        <v>320</v>
       </c>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
-          <t>ROOM RENT FEB 10TH TO MAR 10TH RPA_ID : 4b9d00efc0</t>
+          <t>MATERIAL PURCHASE RPA_ID : a0262b6a31</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>MUMBAI</t>
-        </is>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>midhuncraju12@gmail.com</t>
+          <t>Payments@westernidc.com</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2512,7 +2494,11 @@
           <t>ACCEPTED</t>
         </is>
       </c>
-      <c r="AK16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
       <c r="AL16" t="inlineStr"/>
       <c r="AM16" t="inlineStr"/>
       <c r="AN16" t="inlineStr"/>
@@ -2521,7 +2507,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>WGE 195</t>
+          <t>WGE 233</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2531,7 +2517,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>18-03-2026</t>
+          <t>19-03-2026</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -2567,22 +2553,22 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>SAYAN BATTACHARYA</t>
+          <t>Muhammed anWer</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>8c2c4536-3f5d-4932-ac99-fecdcde7dba6</t>
+          <t>028543ba-d97f-4bca-97ba-3faae973e460</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>ACC-14810110034736</t>
+          <t>ACC-99980113126044</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>UCBA0001481</t>
+          <t>FDRL0001413</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
@@ -2597,21 +2583,23 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>41518</v>
+        <v>16857</v>
       </c>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Salary February 2026 Rs.20000/- PAID ON 13/03/2026 BALANCE TO BE PAID Rs.41518/- RPA_ID : 7d8eace7ce</t>
+          <t>SALARY FOR THE MONTH OF FEBRUARY 2026 RPA_ID : cc134671f9</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>KOLKATTA OFFICE</t>
-        </is>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
@@ -2645,7 +2633,11 @@
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="AK17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
       <c r="AL17" t="inlineStr"/>
       <c r="AM17" t="inlineStr"/>
       <c r="AN17" t="inlineStr"/>
@@ -2654,7 +2646,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>WGE 189</t>
+          <t>WGE 195</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2664,7 +2656,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>18-03-2026</t>
+          <t>19-03-2026</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2700,22 +2692,22 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>MUNNA GUPTA</t>
+          <t>SAYAN BATTACHARYA</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>6a2c6dbb-e5a5-4b53-88cb-be8ceefabb6f</t>
+          <t>2c567703-0bec-4827-860e-708fd1e81236</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>ACC-3421187013</t>
+          <t>ACC-14810110034736</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>CBIN0282509</t>
+          <t>UCBA0001481</t>
         </is>
       </c>
       <c r="O18" t="inlineStr"/>
@@ -2730,23 +2722,21 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>23980</v>
+        <v>21518</v>
       </c>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
-          <t>SALARY FOR THE MONTH OF FEBRUARY 2026 RPA_ID : a896c65d37</t>
+          <t>Salary Feb 2026 Balance RPA_ID : 34a3d6a2cc</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>GRSC KOLKATTA</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>URGENT</t>
-        </is>
+          <t>KOLKATTA OFFICE</t>
+        </is>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
@@ -2799,7 +2789,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>18-03-2026</t>
+          <t>19-03-2026</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2840,7 +2830,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0c01e206-e077-4f84-905f-069ff1bbc334</t>
+          <t>9fa81cd1-12f7-4606-918c-b079dfe3e6eb</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2870,7 +2860,7 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
-          <t>INCENTIVE FOR THE MONTH OF FEBRUARY 2026 RPA_ID : 280c4deaa3</t>
+          <t>INCENTIVE FOR THE MONTH OF FEBRUARY 2026 RPA_ID : c7ffb2582a</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2878,8 +2868,10 @@
           <t>ST3 GOA</t>
         </is>
       </c>
-      <c r="Z19" t="n">
-        <v>0</v>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -2926,7 +2918,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>WGE 196</t>
+          <t>WGE 342</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2936,7 +2928,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>18-03-2026</t>
+          <t>19-03-2026</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2972,24 +2964,20 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>NILESH ANANT DURBHATKAR</t>
+          <t>PAUL OFFSHORE PVT</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>c5a9bd5a-c955-462e-9c5f-7d410080b5a4</t>
+          <t>66cb05f4-3291-4552-a228-4b2bc2670d95</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>ACC-04930100017981</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>BARB0VASCOD</t>
-        </is>
-      </c>
+          <t>ACC-7806823928</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
@@ -3002,17 +2990,17 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>16000</v>
+        <v>167495</v>
       </c>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr">
         <is>
-          <t>The pending amount to be paid to Nilesh is ₹16,000 for August and September, as ₹8,000 per month is still unpaid. ( RUMJAN ROOM) RPA_ID : 28f6e90f0d</t>
+          <t>ONGC GOA JAN BILL LABOUR CHARGES - WELDER / FITTER/RIGGER AND FOOD ALLOWANCE RPA_ID : dec7397961</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>ST3 GOA</t>
+          <t>ONGC GOA</t>
         </is>
       </c>
       <c r="Z20" t="n">
@@ -3063,7 +3051,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>WGE 342</t>
+          <t>WGE 192</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3073,7 +3061,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>18-03-2026</t>
+          <t>19-03-2026</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -3109,20 +3097,24 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>PAUL OFFSHORE PVT</t>
+          <t>Hafis Bin Haris</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>ed38e12e-7510-49f9-b1d7-a73fde45e7f9</t>
+          <t>fb7e6c3f-2f91-49f2-9965-9f0b73937942</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>ACC-7806823928</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>ACC-99980105201458</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>FDRL0001143</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
@@ -3135,17 +3127,17 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>167495</v>
+        <v>9597</v>
       </c>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr">
         <is>
-          <t>ONGC GOA JAN BILL LABOUR CHARGES - WELDER / FITTER/RIGGER AND FOOD ALLOWANCE RPA_ID : 16cd738907</t>
+          <t>Salary- January 9597/- Full and Final Settlement RPA_ID : 7fd866874a</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>ONGC GOA</t>
+          <t>GOA HUL</t>
         </is>
       </c>
       <c r="Z21" t="n">
@@ -3196,7 +3188,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>WGE 192</t>
+          <t>WGE 104</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3206,7 +3198,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>18-03-2026</t>
+          <t>19-03-2026</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -3242,22 +3234,22 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Hafis Bin Haris</t>
+          <t>BRAHMADATHAN</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>362e0f5c-05f7-45c3-98b5-09761da5107d</t>
+          <t>5c5c232b-6471-4fa9-86b6-f219c224c0c0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>ACC-99980105201458</t>
+          <t>ACC-232001000010098</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>FDRL0001143</t>
+          <t>IOBA0002320</t>
         </is>
       </c>
       <c r="O22" t="inlineStr"/>
@@ -3272,12 +3264,12 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>9597</v>
+        <v>14379</v>
       </c>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Salary- January 9597/- Full and Final Settlement RPA_ID : fcac69f5b5</t>
+          <t>Salary November Full and Final settlement RPA_ID : c9f97f1e58</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -3312,12 +3304,12 @@
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>ACCEPTED</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>ACCEPTED</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -3333,7 +3325,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>WGE 115</t>
+          <t>WGE 170</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3343,7 +3335,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>18-03-2026</t>
+          <t>19-03-2026</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -3379,22 +3371,22 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Muhammad Shamil C</t>
+          <t>VEDANT</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>404584ed-2576-43b8-ba2c-b1c126176af5</t>
+          <t>1949c42b-f7b6-4546-8481-eeefc449aa26</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>ACC-11220100177873</t>
+          <t>ACC-2047172054</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>FDRL0001122</t>
+          <t>KKBK0001429</t>
         </is>
       </c>
       <c r="O23" t="inlineStr"/>
@@ -3409,21 +3401,23 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>9257</v>
+        <v>6451</v>
       </c>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Salary December Full and Final Settlement RPA_ID : 2851178f14</t>
+          <t>Material Shiftng 8 Days worked (December 5 days , January 3 Days) RPA_ID : 6fd90881d8</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>ST3 GOA</t>
-        </is>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
+          <t>MDL</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
@@ -3449,19 +3443,15 @@
       <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>ACCEPTED</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>GOA</t>
-        </is>
-      </c>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr"/>
       <c r="AL23" t="inlineStr"/>
       <c r="AM23" t="inlineStr"/>
       <c r="AN23" t="inlineStr"/>
@@ -3470,7 +3460,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>WGE 112</t>
+          <t>WGG 02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3480,7 +3470,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>18-03-2026</t>
+          <t>19-03-2026</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -3514,26 +3504,14 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>ABHISHEK PEDNEKAR</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>96803c97-2dc0-4b6d-a061-a7576ec83bc4</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>ACC-06050100016920</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>BARB0MAPUCA</t>
-        </is>
-      </c>
+          <t>f32fcf89-22cf-45d5-8aaa-f465131dbb1a</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
@@ -3546,17 +3524,17 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>8936</v>
+        <v>25000</v>
       </c>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Salary January Full and Final Settlement RPA_ID : 8aa81913bf</t>
+          <t>Advance Payment RPA_ID : bdf455cfda</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>ST3 GOA</t>
+          <t>PAPPINASSERY</t>
         </is>
       </c>
       <c r="Z24" t="n">
@@ -3594,11 +3572,7 @@
           <t>ACCEPTED</t>
         </is>
       </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>GOA</t>
-        </is>
-      </c>
+      <c r="AK24" t="inlineStr"/>
       <c r="AL24" t="inlineStr"/>
       <c r="AM24" t="inlineStr"/>
       <c r="AN24" t="inlineStr"/>
@@ -3607,7 +3581,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>WGE 104</t>
+          <t>WGE 73</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3617,7 +3591,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>18-03-2026</t>
+          <t>19-03-2026</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -3633,7 +3607,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>NEFT</t>
+          <t>DCR</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3653,22 +3627,22 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>BRAHMADATHAN</t>
+          <t>Nithin</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>522a85b0-5410-4ff9-8a58-5b491b591b08</t>
+          <t>b52493a9-7b01-434c-acd8-24574ab5106c</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>ACC-232001000010098</t>
+          <t>ACC-32555551936</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>IOBA0002320</t>
+          <t>SBIN0001890</t>
         </is>
       </c>
       <c r="O25" t="inlineStr"/>
@@ -3683,17 +3657,17 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>24379</v>
+        <v>160</v>
       </c>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Salary November Full and Final settlement RPA_ID : 9bec927d04</t>
+          <t>Wage Register and Salary Slip Printing Charge RPA_ID : 5317f9847e</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>GOA HUL</t>
+          <t>Elathoor</t>
         </is>
       </c>
       <c r="Z25" t="n">
@@ -3733,7 +3707,7 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>GOA</t>
+          <t>HO</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr"/>
@@ -3744,7 +3718,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>WGE 170</t>
+          <t>WGE 340</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3754,7 +3728,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>18-03-2026</t>
+          <t>19-03-2026</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -3790,22 +3764,22 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>VEDANT</t>
+          <t>SAMAL KUMAR</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2236fd8d-5433-4bfc-945b-ff21a8101138</t>
+          <t>b35c601a-f865-4353-a40c-5a9c16266d15</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>ACC-2047172054</t>
+          <t>ACC-42854727464</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>KKBK0001429</t>
+          <t>SBIN0060181</t>
         </is>
       </c>
       <c r="O26" t="inlineStr"/>
@@ -3820,17 +3794,17 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>6451</v>
+        <v>15000</v>
       </c>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Material Shiftng 8 Days worked (December 5 days , January 3 Days) RPA_ID : c5f53a66e7</t>
+          <t>Advance Payment Kolkatta to Dhuma Expense RPA_ID : 84372acd11</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>MDL</t>
+          <t>HO</t>
         </is>
       </c>
       <c r="Z26" t="n">
@@ -3868,7 +3842,11 @@
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="AK26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
       <c r="AL26" t="inlineStr"/>
       <c r="AM26" t="inlineStr"/>
       <c r="AN26" t="inlineStr"/>
@@ -3877,7 +3855,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>WGE 299</t>
+          <t>WGE 56</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3887,7 +3865,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>18-03-2026</t>
+          <t>19-03-2026</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -3923,22 +3901,22 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>ARJUN(ONGC) SUPERVISOR</t>
+          <t>Akhil</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>95104621-27bb-4239-a5ea-edc0126c33a6</t>
+          <t>8f725397-c506-497f-b6c5-8c7d1c508260</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>ACC-67329839060</t>
+          <t>ACC-852110110008274</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>SBIN0070076</t>
+          <t>BKID0008521</t>
         </is>
       </c>
       <c r="O27" t="inlineStr"/>
@@ -3953,17 +3931,17 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>4800</v>
+        <v>850</v>
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Material Purchase for ongc jetty project room stay expenses to gujarat 16/03/2026 -17/03/2026-18/03/2026-19/03/2026 RPA_ID : 447ae09537</t>
+          <t>Night Wagon Expense RPA_ID : 651b643483</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>ONGC IPSHEM</t>
+          <t>IOCL FEROKE</t>
         </is>
       </c>
       <c r="Z27" t="n">
@@ -4003,7 +3981,7 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>ONGC IPSHEM</t>
+          <t>IOCL FEROKE</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr"/>
@@ -4014,7 +3992,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>WGG 02</t>
+          <t>WGE 306</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4024,7 +4002,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>18-03-2026</t>
+          <t>19-03-2026</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -4058,14 +4036,26 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>SABIN V V</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>9e2511bb-72d7-4ac8-b7d0-5343ef5848f6</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>dee80dfb-1221-4d57-a58c-c7370fe99be3</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>ACC-67274681749</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>SBIN0070812</t>
+        </is>
+      </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
@@ -4078,17 +4068,17 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>4000</v>
+        <v>6640</v>
       </c>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr">
         <is>
-          <t>KOLKATA INSTALLLATION BALANCE AMOUNT TO BE PAID RPA_ID : c86c75e699</t>
+          <t>Room Stay 18.03.2026 to 22.03.2026 , Food Expense 21,22.03.2026,Travel 15.03.2026 to 22.03.2026 RPA_ID : 7fdbc621fb</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>KOLKATA</t>
+          <t>C &amp; C Chennai</t>
         </is>
       </c>
       <c r="Z28" t="n">
@@ -4118,19 +4108,15 @@
       <c r="AH28" t="inlineStr"/>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>KOLKATA</t>
-        </is>
-      </c>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr"/>
       <c r="AL28" t="inlineStr"/>
       <c r="AM28" t="inlineStr"/>
       <c r="AN28" t="inlineStr"/>
@@ -4139,7 +4125,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>WGE 206</t>
+          <t>WGE 56</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4149,7 +4135,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>18-03-2026</t>
+          <t>19-03-2026</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -4185,22 +4171,22 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>RAHUL</t>
+          <t>Akhil</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>5cdee763-b2a8-4f06-a31a-7822125955ec</t>
+          <t>3e065b04-3ecb-43ed-8d0a-718c9b6824e2</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>ACC-0754104000129480</t>
+          <t>ACC-852110110008274</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>IBKL0000754</t>
+          <t>BKID0008521</t>
         </is>
       </c>
       <c r="O29" t="inlineStr"/>
@@ -4215,17 +4201,17 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>7500</v>
+        <v>1200</v>
       </c>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr">
         <is>
-          <t>SALARY ADVANCE MARCH 2026 RPA_ID : 4f9ca7b8d7</t>
+          <t>Gardner expense pending 11.03.2026 RPA_ID : 72b9f74124</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>BELLARI</t>
+          <t>IOCL FEROKE</t>
         </is>
       </c>
       <c r="Z29" t="n">
@@ -4265,7 +4251,7 @@
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>BELLARI</t>
+          <t>IOCL FEROKE</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr"/>
@@ -4276,7 +4262,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>WGE 87</t>
+          <t>WGE 10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4286,7 +4272,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>18-03-2026</t>
+          <t>19-03-2026</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -4322,22 +4308,22 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Mary Ashna K P</t>
+          <t>KIRAN KUMAR K</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1d6b1b15-06b5-4ab8-98e9-010dc469b19c</t>
+          <t>57cca2ba-0501-462e-a741-414d08288833</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>ACC-67216866751</t>
+          <t>ACC-30060475288</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>SBIN0070150</t>
+          <t>SBIN0009122</t>
         </is>
       </c>
       <c r="O30" t="inlineStr"/>
@@ -4352,17 +4338,17 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr">
         <is>
-          <t>SALARY ADVANCE MARCH 2026 RPA_ID : fc2d312190</t>
+          <t>Casual Payment Leave Compensate 06.03.2026,07.03.2026 (Udayan) RPA_ID : deff9b0dd9</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>HO</t>
+          <t>IOCL WELLINGDON</t>
         </is>
       </c>
       <c r="Z30" t="n">
@@ -4400,11 +4386,7 @@
           <t>ACCEPTED</t>
         </is>
       </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>HO</t>
-        </is>
-      </c>
+      <c r="AK30" t="inlineStr"/>
       <c r="AL30" t="inlineStr"/>
       <c r="AM30" t="inlineStr"/>
       <c r="AN30" t="inlineStr"/>
@@ -4413,7 +4395,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>WGE 73</t>
+          <t>WGG 02</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4423,7 +4405,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>18-03-2026</t>
+          <t>19-03-2026</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -4439,7 +4421,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>DCR</t>
+          <t>NEFT</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4457,26 +4439,14 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Nithin</t>
-        </is>
-      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>9dcddf16-321a-4fd4-9256-514f2b2397d4</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>ACC-32555551936</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>SBIN0001890</t>
-        </is>
-      </c>
+          <t>f1341a7b-0b23-4f4a-b657-ece85bc395b3</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
@@ -4489,17 +4459,17 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>2000</v>
+        <v>300000</v>
       </c>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Casual Engaged Elathoor (Leave Nishant &amp; Aswanth) 17.03.2026,18.03.2020 RPA_ID : 87005c0883</t>
+          <t>AUGUST PF ARREAR KOCHI AND KONGAN APPROXIMATE RPA_ID : 1295f4fdcc</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>ELATHOOR</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="Z31" t="n">
@@ -4529,278 +4499,20 @@
       <c r="AH31" t="inlineStr"/>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>ACCEPTED</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>HO</t>
-        </is>
-      </c>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr"/>
       <c r="AL31" t="inlineStr"/>
       <c r="AM31" t="inlineStr"/>
       <c r="AN31" t="inlineStr"/>
       <c r="AO31" t="inlineStr"/>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>WGE 10</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>18-03-2026</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>DCR</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>KIRAN KUMAR K</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>432009f2-0842-4eb4-95fb-ee23df956013</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>ACC-30060475288</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>SBIN0009122</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V32" t="n">
-        <v>2000</v>
-      </c>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>Casual Payment for leave compensate 05.03.2026 &amp; 06.03.2026 (Udayan &amp; Benny) RPA_ID : b98f37f723</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>IOCL Wilington</t>
-        </is>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>midhuncraju12@gmail.com</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="inlineStr"/>
-      <c r="AG32" t="inlineStr"/>
-      <c r="AH32" t="inlineStr"/>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr"/>
-      <c r="AL32" t="inlineStr"/>
-      <c r="AM32" t="inlineStr"/>
-      <c r="AN32" t="inlineStr"/>
-      <c r="AO32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>WGG 02</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>18-03-2026</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>NEFT</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>63122d13-e499-4642-a046-dbc1c2af073b</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V33" t="n">
-        <v>300000</v>
-      </c>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>AUGUST PF ARREAR KOCHI AND KONGAN APPROXIMATE RPA_ID : 88cf69713d</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>Kochi</t>
-        </is>
-      </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>midhuncraju12@gmail.com</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="inlineStr"/>
-      <c r="AG33" t="inlineStr"/>
-      <c r="AH33" t="inlineStr"/>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr"/>
-      <c r="AL33" t="inlineStr"/>
-      <c r="AM33" t="inlineStr"/>
-      <c r="AN33" t="inlineStr"/>
-      <c r="AO33" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PENDING_APPROVAL_SHEET.xlsx
+++ b/PENDING_APPROVAL_SHEET.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO16"/>
+  <dimension ref="A1:AO36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -638,7 +638,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WGP008</t>
+          <t>WGG 02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20-03-2026</t>
+          <t>21-03-2026</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -664,7 +664,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DCR</t>
+          <t>NEFT</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -682,26 +682,14 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>GAYATHRI ELECTRICALS</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>a2a70115-8ba6-4d91-a05f-93aafba7cd26</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>ACC-39177475703</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>SBIN0000512</t>
-        </is>
-      </c>
+          <t>8eb0ffb7-935a-4cbd-bb02-21ad4f9a9432</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
@@ -714,27 +702,27 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>430870</v>
+        <v>79930</v>
       </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Being material purchase (50000 paid on 20-03-2026 remaining pending) RPA_ID : 589b0439a1</t>
+          <t>Pep consultancy pendiing payment RPA_ID : 4101b2afc2</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>ONGC Electrical</t>
+          <t>Cochin</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>SITE EXPENSES</t>
+          <t>PAYMENT</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>midhuncraju12@gmail.com</t>
+          <t>Payments@westernidc.com</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -764,11 +752,7 @@
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>ONGC ELECTRICAL</t>
-        </is>
-      </c>
+      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
@@ -777,7 +761,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WGP057</t>
+          <t>WGG 02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -787,7 +771,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20-03-2026</t>
+          <t>21-03-2026</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -803,7 +787,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DCR</t>
+          <t>NEFT</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -821,26 +805,14 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>SURANA MARKETING</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>7c7efe89-089e-41b2-a399-95e04debc96a</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>ACC-4211805706</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>KKBK0008655</t>
-        </is>
-      </c>
+          <t>b4554160-44f4-47e4-a073-be51a443ce9c</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
@@ -853,27 +825,27 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>410433</v>
+        <v>219454</v>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Being purchase electrical consumable  ( 50000 paid on 20-03-2026 balance amount remaining) RPA_ID : 65763a743c</t>
+          <t>Transfer to cash ledger GOA  (PAID ) RPA_ID : 3463cf8c74</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>BPCL PKD</t>
+          <t>Cochin</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>SITE EXPENSES</t>
+          <t>PAYMENT</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>midhuncraju12@gmail.com</t>
+          <t>Payments@westernidc.com</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -912,7 +884,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WGP133</t>
+          <t>WGG 02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -922,7 +894,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20-03-2026</t>
+          <t>21-03-2026</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -938,7 +910,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DCR</t>
+          <t>NEFT</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -956,26 +928,14 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>GAURAV ELECTRICALS</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>8cec0dcd-2fd6-46ec-a8a1-44d8d5828e52</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>ACC-15960500004640</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>BARB0INDVAT</t>
-        </is>
-      </c>
+          <t>32a01d2b-be99-49d6-80b0-ec0eb6af09f8</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
@@ -988,27 +948,27 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>383100</v>
+        <v>1222258.14</v>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Being balance payment(500000 paid on 20-03-2026 remaining pending) RPA_ID : 1c79784954</t>
+          <t>GST SAHAY LOAN RETURN  (PAID) RPA_ID : 891cb44c2b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>ONGC Electrical</t>
+          <t>Cochin</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>SITE EXPENSES</t>
+          <t>PAYMENT</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>midhuncraju12@gmail.com</t>
+          <t>Payments@westernidc.com</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1038,11 +998,7 @@
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>ONGC ELECTRICAL</t>
-        </is>
-      </c>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
@@ -1061,7 +1017,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20-03-2026</t>
+          <t>21-03-2026</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1098,7 +1054,7 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>8622b11a-ee90-439c-9b10-8c47f67a5051</t>
+          <t>68a5bad7-c905-4315-94df-de668ad17d35</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -1115,28 +1071,27 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>20780</v>
+        <v>13637</v>
       </c>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Being Supply of  Personal protective Equipment’s &amp; Electrical Items (A/C NO:-50200049560664 :-HDFC0000072)  
-VERY URGENT  (20,000 paid on 20-03-2026 balance amount remaining RPA_ID : 02610ea68f</t>
+          <t>EID FOOD EXPENSE  ( PAID ) RPA_ID : 98c29213c3</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>GOA-HULL PROJECT</t>
+          <t>Cochin</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>SITE EXPENSES</t>
+          <t>PAYMENT</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>midhuncraju12@gmail.com</t>
+          <t>Payments@westernidc.com</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1166,11 +1121,7 @@
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>GOA</t>
-        </is>
-      </c>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
@@ -1189,7 +1140,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20-03-2026</t>
+          <t>21-03-2026</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1226,7 +1177,7 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>8d468de5-ef7f-41a9-9101-cfcd6682580b</t>
+          <t>f8e0b973-8c7d-4f4a-a54d-49c4df0d9f6c</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -1243,27 +1194,27 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>76700</v>
+        <v>200000</v>
       </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Being rental service for crane(A/C NO:-01692560001256 IFSC :-HDFC0000169) RPA_ID : 76869037ab</t>
+          <t>INVESTMENT RETURN RPA_ID : fc9dc40d1c</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>ONGC JETTY</t>
+          <t>Cochin</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>SITE EXPENSES</t>
+          <t>PAYMENT</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>midhuncraju12@gmail.com</t>
+          <t>Payments@westernidc.com</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1285,12 +1236,12 @@
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr"/>
@@ -1312,7 +1263,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20-03-2026</t>
+          <t>21-03-2026</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1349,7 +1300,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>67e192c1-645f-40f0-84b2-6c8a389a034b</t>
+          <t>3c3b798d-976a-4eb1-8c5f-db1b4ff47c23</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -1366,27 +1317,27 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>46575</v>
+        <v>25000</v>
       </c>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Being GSTR1 - Return amount RPA_ID : b95d9f393d</t>
+          <t>LOAN REPAYMENT RPA_ID : 67390d4c8c</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>ONGC JETTY</t>
+          <t>Cochin</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>SITE EXPENSES</t>
+          <t>PAYMENT</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>midhuncraju12@gmail.com</t>
+          <t>Payments@westernidc.com</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1408,12 +1359,12 @@
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr"/>
@@ -1425,7 +1376,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WGG 02</t>
+          <t>WGE 233</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1435,7 +1386,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>20-03-2026</t>
+          <t>21-03-2026</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1469,14 +1420,26 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Muhammed anWer</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>e72e968c-1673-4ff1-acad-d16d586497e1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>96c73ba1-5f1a-49d8-a5f8-efa724b94776</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>ACC-99980113126044</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>FDRL0001413</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
@@ -1489,22 +1452,22 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>24741</v>
+        <v>16857</v>
       </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Plesae return the GSTR1  amount to the vendor RPA_ID : e33ce6e4bd</t>
+          <t>SALARY FOR THE MONTH OF FEBRUARY 2026 RPA_ID : 0cd5650c0f</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>BPCL BALLARI</t>
+          <t>HO</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>SITE EXPENSES</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1539,7 +1502,11 @@
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
@@ -1548,7 +1515,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WGG 02</t>
+          <t>WGE 195</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1558,7 +1525,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20-03-2026</t>
+          <t>21-03-2026</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1592,14 +1559,26 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>SAYAN BATTACHARYA</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>e385bca9-cb9f-4d9c-a328-52256d74e844</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>edc72a82-56a9-4dfa-a4dc-93e1caff1e80</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ACC-14810110034736</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>UCBA0001481</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
@@ -1612,22 +1591,22 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>12000</v>
+        <v>21518</v>
       </c>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Being renovation work for Jelin sir flat (A/C NO:-5317366733 IFSC :-CBINO280963) RPA_ID : a60c2b0940</t>
+          <t>Salary Feb 2026 Balance RPA_ID : 08af33e4c2</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Maintenance(JELIN SIR</t>
+          <t>KOLKATTA OFFICE</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>MAINTENANCE</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1671,7 +1650,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WGG 02</t>
+          <t>WGE 113</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1681,7 +1660,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>20-03-2026</t>
+          <t>21-03-2026</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1697,7 +1676,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>NEFT</t>
+          <t>DCR</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1715,14 +1694,26 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>RIZWANUDHEEN</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>943f68d0-1c3d-46aa-b96f-2724369ad8cd</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>b7ee74df-ea8f-4121-bcbc-c7a75c66198a</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ACC-67285944854</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>SBIN0070191</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
@@ -1735,23 +1726,21 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>18500</v>
+        <v>10000</v>
       </c>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Being Payment for KSEB deposit, Labour charge,Power connection CD,Completion certificate RPA_ID : 4d7e673cdd</t>
+          <t>INCENTIVE FOR THE MONTH OF FEBRUARY 2026 RPA_ID : 287e9c3fda</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>IOCL Pappinisseri</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>SITE EXPENSES</t>
-        </is>
+          <t>ST3 GOA</t>
+        </is>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1785,7 +1774,11 @@
           <t>ACCEPTED</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
       <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr"/>
@@ -1794,7 +1787,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WGG 02</t>
+          <t>WGE 342</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1804,7 +1797,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>20-03-2026</t>
+          <t>21-03-2026</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1838,13 +1831,21 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>PAUL OFFSHORE PVT</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>a82c4f91-a55e-4951-9837-37db5288c7ca</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>bebceca7-39a1-423a-8c8c-4af10163f4dc</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ACC-7806823928</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -1858,23 +1859,21 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>60000</v>
+        <v>50000</v>
       </c>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Being hot work channel welding work RPA_ID : 33bb5d0ec4</t>
+          <t>ONGC GOA JAN BILL LABOUR CHARGES - WELDER / FITTER/RIGGER AND FOOD ALLOWANCE RPA_ID : 266d7cc875</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>NGOP CHENNAI</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>SITE EXPENSES</t>
-        </is>
+          <t>ONGC GOA</t>
+        </is>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1908,7 +1907,11 @@
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
       <c r="AL11" t="inlineStr"/>
       <c r="AM11" t="inlineStr"/>
       <c r="AN11" t="inlineStr"/>
@@ -1917,7 +1920,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WGG 02</t>
+          <t>WGE 192</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1927,7 +1930,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>20-03-2026</t>
+          <t>21-03-2026</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1961,14 +1964,26 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Hafis Bin Haris</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>7f0610e6-610d-4fb1-a124-05005f3babdb</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>c890cad4-b45a-45eb-a497-40ddcb228bd6</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ACC-99980105201458</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>FDRL0001143</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
@@ -1981,23 +1996,21 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>149877.6</v>
+        <v>9597</v>
       </c>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Being rent for JCB ,Hydra,Braker and farrana crane( total 324877.6  ,90000 paid on 20-03-2026 balance amount remaining RPA_ID : dc6b495190</t>
+          <t>Salary- January 9597/- Full and Final Settlement RPA_ID : c15bd5aec2</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>BPCL BALLARI</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>SITE EXPENSES</t>
-        </is>
+          <t>GOA HUL</t>
+        </is>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -2031,7 +2044,11 @@
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
       <c r="AL12" t="inlineStr"/>
       <c r="AM12" t="inlineStr"/>
       <c r="AN12" t="inlineStr"/>
@@ -2040,7 +2057,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WGG 02</t>
+          <t>WGE 104</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2050,7 +2067,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>20-03-2026</t>
+          <t>21-03-2026</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -2084,14 +2101,26 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>BRAHMADATHAN</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>d535beaf-b00b-47d4-a095-45822bd6762f</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>c11d50ba-83c5-4e4e-8f6c-3b9e12ce8673</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ACC-232001000010098</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>IOBA0002320</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
@@ -2104,23 +2133,21 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>2964</v>
+        <v>14379</v>
       </c>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Being purchasing of stationery items  (A/C NO :- 05102530000015 ,IFSC :- HDFC0000510) RPA_ID : 32415ea4c8</t>
+          <t>Salary November Full and Final settlement RPA_ID : 29007481e3</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Head office</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>HEAD OFFICE</t>
-        </is>
+          <t>GOA HUL</t>
+        </is>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -2154,7 +2181,11 @@
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="AK13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
       <c r="AL13" t="inlineStr"/>
       <c r="AM13" t="inlineStr"/>
       <c r="AN13" t="inlineStr"/>
@@ -2163,7 +2194,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WGG 02</t>
+          <t>WGE 170</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2173,7 +2204,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>20-03-2026</t>
+          <t>21-03-2026</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -2207,14 +2238,26 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>VEDANT</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>9c879633-7ec2-4f55-8706-20a97bb1a48e</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>01728c9c-fc01-4603-9030-5f9e403ff122</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ACC-2047172054</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>KKBK0001429</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
@@ -2227,22 +2270,22 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>11155</v>
+        <v>6451</v>
       </c>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Being supply of shalimastic and tankmastic paint RPA_ID : 0b87f53c4c</t>
+          <t>Material Shiftng 8 Days worked (December 5 days , January 3 Days) RPA_ID : b540d17e29</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>IOCL Pappinisseri</t>
+          <t>MDL</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>SITE EXPENSES</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2269,12 +2312,12 @@
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>ACCEPTED</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>ACCEPTED</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr"/>
@@ -2286,7 +2329,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WGG 02</t>
+          <t>WGE 340</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2296,7 +2339,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>20-03-2026</t>
+          <t>21-03-2026</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -2330,14 +2373,26 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>SAMAL KUMAR</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>31c809b6-d354-4deb-a00e-bbc620a02da6</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>484cb28e-5bf3-4b43-bb9f-49ee04ba4f95</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>ACC-42854727464</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>SBIN0060181</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
@@ -2350,23 +2405,21 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>15600</v>
+        <v>15000</v>
       </c>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Being rennovation work for jelin sir flat pooja room (A/C NO:- 5317366733 ,IFSC :- CBINO280963) RPA_ID : 4df021f727</t>
+          <t>Advance Payment Kolkatta to Dhuma Expense RPA_ID : cef2965df5</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>Maintenance(JELIN SIR</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>MAINTENANCE</t>
-        </is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
@@ -2400,7 +2453,11 @@
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="AK15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
       <c r="AL15" t="inlineStr"/>
       <c r="AM15" t="inlineStr"/>
       <c r="AN15" t="inlineStr"/>
@@ -2409,7 +2466,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WGG 02</t>
+          <t>WGE 332</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2419,7 +2476,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>20-03-2026</t>
+          <t>21-03-2026</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -2453,14 +2510,26 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>CLEETUS PETER ( ONGC)</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>7ada6fa4-8397-4616-9bb0-b4202f67b2f8</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>e68a901e-e629-4bbd-b77a-65d77b001fa7</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>ACC-40062610000123</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>CNRB0014006</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
@@ -2473,23 +2542,21 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>4611</v>
+        <v>12800</v>
       </c>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Being 30 L diesel required for Excavtor and 20 L Diesel for JCB2 RPA_ID : f7e441152a</t>
+          <t>WEEKLY SALARY ( 14/03/2026 TO 20/03/2026) Sunday Workers 8 Days RPA_ID : ec2c536294</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>BPCL BALLARI</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>SITE EXPENSES</t>
-        </is>
+          <t>HUL GOA</t>
+        </is>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
@@ -2523,12 +2590,2718 @@
           <t>ACCEPTED</t>
         </is>
       </c>
-      <c r="AK16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
       <c r="AL16" t="inlineStr"/>
       <c r="AM16" t="inlineStr"/>
       <c r="AN16" t="inlineStr"/>
       <c r="AO16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>WGE 221</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>21-03-2026</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>GLADWIN JESTIN</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1e5b7965-d9d3-41ed-ac74-ef03d3f6c67c</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>ACC-609053000010959</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>SIBL0000609</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>8000</v>
+      </c>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>WEEKLY SALARY ( 14/03/2026 TO 20/03/2026) 5 days RPA_ID : d6f8cbbd8e</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>HUL GOA</t>
+        </is>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>midhuncraju12@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>WGE 416</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>21-03-2026</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>SREEJITH P R</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>12f4ff2b-1d00-4564-81bb-2977fa5069e1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>ACC-110020773907</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>7700</v>
+      </c>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>WEEKLY SALARY ( 14/03/2026 TO 20/03/2026) 5.5 days RPA_ID : 023f0f9d85</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>HUL GOA</t>
+        </is>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>midhuncraju12@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>WGE 298</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>21-03-2026</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>NAKUL(ONGC)</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>7f2b263d-29aa-4952-beb5-875f0be4050d</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>ACC-054801000019038</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>IOBA0000548</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>7700</v>
+      </c>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>WEEKLY SALARY ( 14/03/2026 TO 20/03/2026) 5.5 days RPA_ID : b9f9aa496c</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>HUL GOA</t>
+        </is>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>midhuncraju12@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>WGE 309</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>21-03-2026</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Harvin(ongc )</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>22ac805c-c28a-4e86-895c-e8900fffc571</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>ACC-20533170557</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>SBIN0007617</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>7200</v>
+      </c>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>WEEKLY SALARY ( 14/03/2026 TO 20/03/2026) 4.5 days RPA_ID : 21b1ae9364</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>HUL GOA</t>
+        </is>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>midhuncraju12@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>WGE 236</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>21-03-2026</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>vishnu P. G (ONGC )</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>6d58ad50-fc06-4c33-809e-a166b015e68e</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>ACC-40561101027837</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>KLGB0040561</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>3200</v>
+      </c>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>weekly salary (19/03/2026 to 20/03/2026) 2 days RPA_ID : ed9557ceaf</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>HUL GOA</t>
+        </is>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>midhuncraju12@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>WGE 285</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>21-03-2026</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Girajesh Komal Sharma</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>af682a53-dd3a-4bd5-8f0e-e1d195ba06c8</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>ACC-034210780342</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>IPOS0000001</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>WEEKLY SALARY ( 07/03/2026) one day salary per day 1000 RPA_ID : 299b545191</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>ONGC IPSHEM</t>
+        </is>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>midhuncraju12@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>ONGC IPSHEM</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>WGE 285</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>21-03-2026</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Girajesh Komal Sharma</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>d7f1708d-d491-4d3a-852e-542b9f0e8832</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>ACC-034210780342</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>IPOS0000001</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>WEEKLY SALARY ( 07/03/2026) per day 1000 one day salary / chottu vidha salary credited to girajesh account RPA_ID : 57c538321d</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>ONGC IPSHEM</t>
+        </is>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>midhuncraju12@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>ONGC IPSHEM</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>WGE 433</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>21-03-2026</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Pappu yadav</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>647840b8-0391-453f-8b4f-dba435dabe18</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>ACC-034719459058</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>SBIN0011193</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>1300</v>
+      </c>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>WEEKLY SALARY ( 07/03/2026) one day salary per day 1300 RPA_ID : e11f3661cd</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>ONGC IPSHEM</t>
+        </is>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>midhuncraju12@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>ONGC IPSHEM</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>WGE 405</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>21-03-2026</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>SANJAY</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>078dea23-c127-464f-a2e0-deb7277e3d98</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>ACC-7555267882</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>IDIB000B005</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>WEEKLY SALARY ( 07/03/2026) one day salary per day 1000 RPA_ID : a16d4c8dc3</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>ONGC IPSHEM</t>
+        </is>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>midhuncraju12@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>ONGC IPSHEM</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>WGE 406</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>21-03-2026</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>BIBEK</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>85681318-850c-432e-b646-eb0d30d69ff0</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>ACC-1628001700106918</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>PUNB0162800</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>4000</v>
+      </c>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>WEEKLY SALARY ( 02/03/2026 , 7/03/2026 to 11/03/2026) per day 1000 RPA_ID : 4ec6f2906b</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>ONGC IPSHEM</t>
+        </is>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>midhuncraju12@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>ONGC IPSHEM</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>WGE 334</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>21-03-2026</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>RAJU YADAV ( KHALASI)</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1d1bc5a7-cfd9-4512-acbe-8d11bd6b0238</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>ACC-7452654471</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>IDIB000B005</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>10500</v>
+      </c>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>WEEKLY SALARY ( 14/03/2026 TO 20/03/2026) per day 1500 7 days RPA_ID : e1302c143d</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>midhuncraju12@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>WGE 364</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>21-03-2026</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Manmohan Yadahv</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>7a3b3db3-2d74-4c3c-90f8-881b45235cd1</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>ACC-791510110002741</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>BKID0007915</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>7000</v>
+      </c>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>WEEKLY SALARY ( 14/03/2026 TO 20/03/2026) per day 1000 7 days RPA_ID : df2e5793a3</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>midhuncraju12@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>WGE 362</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>21-03-2026</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Ramjathan</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>9113b29f-3921-40f2-9f5e-2191111fe1a7</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>ACC-501051125288</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>NSPB0000002</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>7000</v>
+      </c>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>WEEKLY SALARY ( 14/03/2026 TO 20/03/2026) per day 1000 7 days RPA_ID : 3881f09802</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>midhuncraju12@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>WGE 363</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>21-03-2026</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Pramod Kumar</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>e22a6c95-b6e3-4e1e-9637-ffe85d135638</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>ACC-694402010010832</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>UBIN0569445</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>7000</v>
+      </c>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>WEEKLY SALARY ( 14/03/2026 TO 20/03/2026) per day 1000 7 days RPA_ID : 5e8a5a1d3b</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>midhuncraju12@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>WGE 333</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>21-03-2026</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>LAKHI CHAND SAHANI</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>31a33bb8-bca5-477c-a855-049f876a8cbf</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>ACC-041215193811</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>SBIN0008326</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>10500</v>
+      </c>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>WEEKLY SALARY ( 14/03/2026 TO 20/03/2026) per day 1500 7 days RPA_ID : 3ff9ed3358</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>midhuncraju12@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>WGE 299</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>21-03-2026</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>ARJUN(ONGC) SUPERVISOR</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>3953274c-7f17-4757-a1d9-5fe765e7d97b</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>ACC-67329839060</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>SBIN0070076</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>4800</v>
+      </c>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Material Purcahse Stay  (20 to 23rd) RPA_ID : aa72bb24db</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>ONGC IPSHEM</t>
+        </is>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>midhuncraju12@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>ONGC IPSHEM</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>WGE 347</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>21-03-2026</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>ABDUL GAFFUR( ROOM OWNER BELLARI)</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2d429307-d977-4da9-a1d7-cfe32a525ab8</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>ACC-618010100002509</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>UTIB0000618</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>25000</v>
+      </c>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Bellari Staff Room Rent (March 2026) Due date 21st RPA_ID : f0f66f355f</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>midhuncraju12@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>WGE 10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>21-03-2026</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>DCR</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>KIRAN KUMAR K</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>aa5e373b-1aee-4747-a651-d59f64329f5e</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>ACC-30060475288</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>SBIN0009122</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>2000</v>
+      </c>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Casual Payment (Leave 10.03.2206) Aneesh &amp; Safal) Leave Compensate RPA_ID : 3fe9379df0</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>IOCL Willington</t>
+        </is>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>midhuncraju12@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>IOCL WILLINGTON</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="inlineStr"/>
+      <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>WGG 02</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>21-03-2026</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>3fda35eb-6b76-4674-bc9f-1536e94a955a</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>0 RPA_ID : 997287ad3b</t>
+        </is>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>midhuncraju12@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr"/>
+      <c r="AL35" t="inlineStr"/>
+      <c r="AM35" t="inlineStr"/>
+      <c r="AN35" t="inlineStr"/>
+      <c r="AO35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>WGG 02</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>21-03-2026</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>5d8a3a06-a053-4443-a241-61f4e0e16785</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V36" t="n">
+        <v>300000</v>
+      </c>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>AUGUST PF ARREAR KOCHI AND KONGAN APPROXIMATE RPA_ID : 09b6c36ca3</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>midhuncraju12@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr"/>
+      <c r="AL36" t="inlineStr"/>
+      <c r="AM36" t="inlineStr"/>
+      <c r="AN36" t="inlineStr"/>
+      <c r="AO36" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PENDING_APPROVAL_SHEET.xlsx
+++ b/PENDING_APPROVAL_SHEET.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO18"/>
+  <dimension ref="A1:AO34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -638,7 +638,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WGE 23</t>
+          <t>WGE 323</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>23-03-2026</t>
+          <t>25-03-2026</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -664,7 +664,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DCR</t>
+          <t>NEFT</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -684,22 +684,22 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>KRISHNAPRIYA AS</t>
+          <t>VINITHA V NAIR</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>80acd119-c747-4897-ad1a-2ebeedafbec8</t>
+          <t>d7f3f372-5fe8-4ca8-86fa-bbfa73644d50</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>ACC-41607255741</t>
+          <t>ACC-22020100013715</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>SBIN0070141</t>
+          <t>FDRL0002202</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -714,25 +714,27 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>33565</v>
+        <v>2000</v>
       </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
-          <t>MEETING EXPENSES RPA_ID : 7c097b03d9</t>
+          <t>Daily Site Labour Charges-for 2 labours RPA_ID : 2679f83596</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>IOCL HK</t>
-        </is>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
+          <t>Construction of IOCL RO at Pappinissery</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>LABOUR CHARGES</t>
+        </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>midhuncraju12@gmail.com</t>
+          <t>executive.westerntender@gmail.com</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -754,12 +756,12 @@
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>ACCEPTED</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>ACCEPTED</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr"/>
@@ -771,68 +773,40 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WGP008</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
+          <t>WGE 454</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>23-03-2026</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>DCR</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
+          <t>25-03-2026</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>GAYATHRI ELECTRICALS</t>
+          <t>Nikesh Patil</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>f4fc1ca8-0370-406a-b987-ce6773f3c51e</t>
+          <t>9e5513e8-38f2-470c-a34b-57d3dd152b47</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>ACC-39177475703</t>
+          <t>ACC- 306001000000480</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>SBIN0000512</t>
+          <t>IOBA0003060</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
@@ -847,27 +821,29 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>430870</v>
+        <v>2250</v>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Being material purchase (50000 paid on 20-03-2026 remaining pending) RPA_ID : dd6c3be0ef</t>
+          <t>Rental details:
+• Activa 4G – rent paid up to 25th March.
+(26th March to 31st March - Rs 2700) RPA_ID : dc5a7121d4</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>ONGC Electrical</t>
+          <t>Rental charges for the bike hired for official/site work</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>SITE EXPENSES</t>
+          <t>RENTAL CHARGES</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>midhuncraju12@gmail.com</t>
+          <t>executive.westerntender@gmail.com</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -887,21 +863,9 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>ONGC ELECTRICAL</t>
-        </is>
-      </c>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr"/>
@@ -910,68 +874,40 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WGP057</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
+          <t>WGE 480</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>23-03-2026</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>DCR</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
+          <t>25-03-2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>SURANA MARKETING</t>
+          <t>GREYTHR</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>4320e91d-06b2-4ac1-8642-f5693c3d14b4</t>
+          <t>b89bf31a-eb33-4945-924f-f2ab06fcf3b2</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>ACC-4211805706</t>
+          <t>ACC-917020067527527</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>KKBK0008655</t>
+          <t>UTIB0003093</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -986,27 +922,25 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>410433</v>
+        <v>5171</v>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Being purchase electrical consumable  ( 50000 paid on 20-03-2026 balance amount remaining) RPA_ID : 87e8b89b48</t>
+          <t>HR SOFTWARE CHARGE GREYTHR RPA_ID : 7d6e2bb351</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>BPCL PKD</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>SITE EXPENSES</t>
-        </is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>midhuncraju12@gmail.com</t>
+          <t>hrm@westernidc.com</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1026,17 +960,13 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
@@ -1045,7 +975,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WGP133</t>
+          <t>WGE 342</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1055,7 +985,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>23-03-2026</t>
+          <t>25-03-2026</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1071,7 +1001,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DCR</t>
+          <t>NEFT</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1091,24 +1021,20 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>GAURAV ELECTRICALS</t>
+          <t>PAUL OFFSHORE PVT</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>d51bbb01-d941-4f48-97e0-d80e6bec9a6c</t>
+          <t>65006a06-3511-4c3a-95d4-c8d0b6b2daea</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>ACC-15960500004640</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>BARB0INDVAT</t>
-        </is>
-      </c>
+          <t>ACC-7806823928</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
@@ -1121,27 +1047,25 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>383100</v>
+        <v>117495</v>
       </c>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Being balance payment(500000 paid on 20-03-2026 remaining pending) RPA_ID : 66ca22005d</t>
+          <t>ONGC GOA JAN BILL LABOUR CHARGES - WELDER / FITTER/RIGGER AND FOOD ALLOWANCE Total Amount= 342495/- Paid Rs.75000/- , Paid Rs.100000/- Excel Attendnace Sheet already shared= 167495,paid Rs.50000/-21.03.2026 RPA_ID : 2872baced9</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>ONGC Electrical</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>SITE EXPENSES</t>
-        </is>
+          <t>ONGC GOA</t>
+        </is>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>midhuncraju12@gmail.com</t>
+          <t>hrm@westernidc.com</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1161,19 +1085,11 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>ONGC ELECTRICAL</t>
+          <t>GOA</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr"/>
@@ -1184,7 +1100,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WGG 02</t>
+          <t>WGE 192</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1194,7 +1110,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>23-03-2026</t>
+          <t>25-03-2026</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1228,14 +1144,26 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Hafis Bin Haris</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0ac3b4e7-c898-4c8c-bfdc-310007efc14c</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>2cc83306-cb14-4444-9475-21502303190d</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>ACC-99980105201458</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>FDRL0001143</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
@@ -1248,28 +1176,25 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>20780</v>
+        <v>9597</v>
       </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Being Supply of  Personal protective Equipment’s &amp; Electrical Items (A/C NO:-50200049560664 :-HDFC0000072)  
-VERY URGENT  (20,000 paid on 20-03-2026 balance amount remaining RPA_ID : 32788e724f</t>
+          <t>Salary- January 9597/- Full and Final Settlement Paid December 7423 , Balance 9597  Total = 17020 RPA_ID : 40dd7da88f</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>GOA-HULL PROJECT</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>SITE EXPENSES</t>
-        </is>
+          <t>GOA HUL</t>
+        </is>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>midhuncraju12@gmail.com</t>
+          <t>hrm@westernidc.com</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1289,16 +1214,8 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -1312,7 +1229,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WGG 02</t>
+          <t>WGE 104</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1322,7 +1239,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>23-03-2026</t>
+          <t>25-03-2026</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1356,14 +1273,26 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>BRAHMADATHAN</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>e15ae6fc-c695-46dd-a962-716701fa3f5f</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>8256608e-60e0-4564-b21a-2aa7ac68bf30</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ACC-232001000010098</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>IOBA0002320</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
@@ -1376,27 +1305,25 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>76700</v>
+        <v>14379</v>
       </c>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Being rental service for crane(A/C NO:-01692560001256 IFSC :-HDFC0000169) RPA_ID : c10b2ad4d0</t>
+          <t>Salary November Full and Final settlement Final Settlement Total 24379 , Rs.10000/- Paid  18.03.2026 Balance to be paid RPA_ID : 672d7ca2f1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>ONGC JETTY</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>SITE EXPENSES</t>
-        </is>
+          <t>GOA HUL</t>
+        </is>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>midhuncraju12@gmail.com</t>
+          <t>hrm@westernidc.com</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1416,17 +1343,13 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr"/>
@@ -1435,58 +1358,42 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WGG 02</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
+          <t>WGE 452</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>23-03-2026</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>NEFT</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>25-03-2026</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA REDDY</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>ebfa7c23-48e3-40a7-becb-da56a1b8d342</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>82606c50-1286-46ec-8658-69cc64a22e38</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>ACC- 79860100001270</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>BARB0VASCOD</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
@@ -1499,27 +1406,25 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>46575</v>
+        <v>15000</v>
       </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Being GSTR1 - Return amount RPA_ID : c335897201</t>
+          <t>Hishm sir baleno auto 4th jan 10th jan 7days=10500,Baleno auto 14th jan 29th jan 16days=24000,Swift manual 17th jan 19th jan 3days=3600,Sidharth Dezire 13th feb  to 14th 3days 2400,Sir swift auto 16thfeb 17thfeb 2days 3000 2nd 1500 =45000 (10000 paid) As per Advice from Admin Andriya - No documents provided Rs.10000/- paid,Rs.10000/- paid 18.03.2026,23.023.2026 10000/-paid RPA_ID : 4d857f3b95</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>ONGC JETTY</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>SITE EXPENSES</t>
-        </is>
+          <t>ONGC IPSHEM</t>
+        </is>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>midhuncraju12@gmail.com</t>
+          <t>hrm@westernidc.com</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1539,17 +1444,13 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>ONGC IPSHEM</t>
+        </is>
+      </c>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
@@ -1558,7 +1459,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WGG 02</t>
+          <t>WGE 170</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1568,7 +1469,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>23-03-2026</t>
+          <t>25-03-2026</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1602,14 +1503,26 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>VEDANT</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>719cb03c-6955-4d7a-ae3b-e27966c07256</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>318e5d94-e803-4e64-a37e-b3a7e817a8e9</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ACC-2047172054</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>KKBK0001429</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
@@ -1622,27 +1535,25 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>24741</v>
+        <v>6451</v>
       </c>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Plesae return the GSTR1  amount to the vendor RPA_ID : 2d9bb22b1e</t>
+          <t>Material Shiftng 8 Days worked (December 5 days , January 3 Days) Basic Pay is Rs.25000/- perday 806.45 RPA_ID : 1d208cc8b6</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>BPCL BALLARI</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>SITE EXPENSES</t>
-        </is>
+          <t>MDL</t>
+        </is>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>midhuncraju12@gmail.com</t>
+          <t>hrm@westernidc.com</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1662,16 +1573,8 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
@@ -1681,58 +1584,42 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WGG 02</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
+          <t>WGE 462</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>23-03-2026</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>NEFT</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>25-03-2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>PRANEET</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>cb0b5a1d-2830-4b23-83b5-ed796860a19d</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>349ef867-f418-4928-9e4c-8d931ee36829</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ACC-'095203100002750</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>SRCB0000095</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
@@ -1745,27 +1632,25 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>60000</v>
+        <v>5000</v>
       </c>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Being hot work channel welding work RPA_ID : da24a4dc65</t>
+          <t>Casual Payment 5 Nos @ 1000 ST3 GOA Deployed Local Casual Labours 25.04.2026 RPA_ID : e58b841a76</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>NGOP CHENNAI</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>SITE EXPENSES</t>
-        </is>
+          <t>ST3 GOA</t>
+        </is>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>midhuncraju12@gmail.com</t>
+          <t>hrm@westernidc.com</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1785,17 +1670,13 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
       <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr"/>
@@ -1804,7 +1685,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WGG 02</t>
+          <t>WGE 306</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1814,7 +1695,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>23-03-2026</t>
+          <t>25-03-2026</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1848,14 +1729,26 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>SABIN V V</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>eaecc58b-7ed4-4129-a56d-76bef62baa2f</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>8c38e6b2-570c-4035-935d-24b6a643aec6</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ACC-67274681749</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>SBIN0070812</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
@@ -1868,27 +1761,28 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>149877.6</v>
+        <v>3540</v>
       </c>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Being rent for JCB ,Hydra,Braker and farrana crane( total 324877.6  ,90000 paid on 20-03-2026 balance amount remaining RPA_ID : ee32d596fc</t>
+          <t>Room stay 23/03/2025 to 25/03/2025 3 Days Transportation Charge @ 80/-/ 1.Stay Expense @1100  5 days 5500/-
+2. Food Expense @250 2days 500/-
+3.Travel perday Rs.80/- 8 days 640/-
+Total Advance paid Rs. 15460/- RPA_ID : 2e1527ac0d</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>BPCL BALLARI</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>SITE EXPENSES</t>
-        </is>
+          <t>CHENNAI</t>
+        </is>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>midhuncraju12@gmail.com</t>
+          <t>hrm@westernidc.com</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1908,16 +1802,8 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr"/>
       <c r="AM11" t="inlineStr"/>
@@ -1927,7 +1813,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WGG 02</t>
+          <t>WGE 195</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1937,7 +1823,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>23-03-2026</t>
+          <t>25-03-2026</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1971,14 +1857,26 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>SAYAN BATTACHARYA</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>94630ae7-68ae-45f1-912b-166e1fd0818e</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>5a1a613b-f6db-4fd6-942f-37447a57ee05</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ACC-14810110034736</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>UCBA0001481</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
@@ -1991,28 +1889,25 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>22000</v>
+        <v>224</v>
       </c>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Being rental for two water pumps (26/02/26 to 12/03/26 =15 days X 600=9000, Pump (sub) (10 days X 600=6000)
-(13/02/26 to 18/03/26 =6 days X 600=3600, Pump (sub) (6 days X 600=3600) -(A/C NO:- 57025596625 IFSC :-SBIN0070202) RPA_ID : f799c09d00</t>
+          <t>Sun, 01 Mar, 2026 / travel Howrah, West Bengal 711101, India to Bhowanipore, Kolkata, West Bengal, India RPA_ID : 6c53f59e1d</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>IOCL Pappinasseri</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>SITE EXPENSES</t>
-        </is>
+          <t>DUMKA</t>
+        </is>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>midhuncraju12@gmail.com</t>
+          <t>hrm@westernidc.com</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -2032,16 +1927,8 @@
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr"/>
       <c r="AM12" t="inlineStr"/>
@@ -2051,7 +1938,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WGG 02</t>
+          <t>WGE 195</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2061,7 +1948,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>23-03-2026</t>
+          <t>25-03-2026</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -2095,14 +1982,26 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>SAYAN BATTACHARYA</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>02dca49a-d6aa-4350-8621-57c3c1723f4b</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>59733069-09fc-46de-9eff-5c7f851f4ee6</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ACC-14810110034736</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>UCBA0001481</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
@@ -2115,28 +2014,25 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>79178</v>
+        <v>224</v>
       </c>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
-          <t>GXY EPOXY MASTIC 6606 AL.GREY-20  AND EPOXY THINNER-20 (A/C NO:- 00592320003684 ,IFSC HDFC0000059)
-(PO NO:-WIDMC-PO-2025-26-176 (20-01-2026) RPA_ID : 059b927dc2</t>
+          <t>Sun, 08 Mar, 2026 / travel to Howrah, West Bengal 711101, India to Bhowanipore, Kolkata, West Bengal, India RPA_ID : 085e7c5d3c</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>ONGC GOA</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>SITE EXPENSES</t>
-        </is>
+          <t>DUMKA</t>
+        </is>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>midhuncraju12@gmail.com</t>
+          <t>hrm@westernidc.com</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -2156,21 +2052,9 @@
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>GOA</t>
-        </is>
-      </c>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="inlineStr"/>
       <c r="AM13" t="inlineStr"/>
       <c r="AN13" t="inlineStr"/>
@@ -2179,7 +2063,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WGG 02</t>
+          <t>WGE 195</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2189,7 +2073,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>23-03-2026</t>
+          <t>25-03-2026</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -2223,14 +2107,26 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>SAYAN BATTACHARYA</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>035d5eb5-5479-41dc-8c5f-7bb687134385</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>8f880215-f6ef-41aa-b1a5-041c8923081b</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ACC-14810110034736</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>UCBA0001481</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
@@ -2243,27 +2139,25 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>9000</v>
+        <v>199</v>
       </c>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Being supply of water for carryout pressure test (A/C NO :- 014302856762195001 ,IFSC :- CSBK0000143) RPA_ID : 8a041a4fb3</t>
+          <t>Wed, 11 Mar, 2026 / travel to Bhowanipore, Kolkata, West Bengal, India to Howrah, West Bengal, India RPA_ID : 5cbbf71546</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>IOCL Pappinasseri</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>SITE EXPENSES</t>
-        </is>
+          <t>DUMKA</t>
+        </is>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>midhuncraju12@gmail.com</t>
+          <t>hrm@westernidc.com</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -2283,16 +2177,8 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
       <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="inlineStr"/>
       <c r="AM14" t="inlineStr"/>
@@ -2302,7 +2188,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WGG 02</t>
+          <t>WGE 195</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2312,7 +2198,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>23-03-2026</t>
+          <t>25-03-2026</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -2346,14 +2232,26 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>SAYAN BATTACHARYA</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>196163c4-1657-4933-abad-b98762048246</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>2d667d7f-c9d1-4618-9d79-0362e10e1a67</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>ACC-14810110034736</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>UCBA0001481</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
@@ -2366,28 +2264,25 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>477153.72</v>
+        <v>256</v>
       </c>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Being rent for crane service in ONGC GOA (A/C NO:- 50200034984564 IFSC :- HDFC0000169) 
-Total bill amount 3513041.72 ,paid amount :- 3035888, balance remaining RPA_ID : b1cfb71824</t>
+          <t>Thu, 12 Mar, 2026/ travel to , Howrah, West Bengal 711101, India to Bhowanipore, Kolkata, West Bengal, India RPA_ID : 3b7c64cde8</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>ONGC GOA</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>SITE EXPENSES</t>
-        </is>
+          <t>DUMKA</t>
+        </is>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>midhuncraju12@gmail.com</t>
+          <t>hrm@westernidc.com</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2407,21 +2302,9 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>GOA</t>
-        </is>
-      </c>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="inlineStr"/>
       <c r="AM15" t="inlineStr"/>
       <c r="AN15" t="inlineStr"/>
@@ -2430,7 +2313,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WGG 02</t>
+          <t>WGE 195</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2440,7 +2323,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>23-03-2026</t>
+          <t>25-03-2026</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -2474,14 +2357,26 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>SAYAN BATTACHARYA</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>a312e3b9-953d-4d75-8dee-4c3a7ba885d4</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>49ed11b7-aa3c-45fd-ad7a-02068dc0e0d5</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>ACC-14810110034736</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>UCBA0001481</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
@@ -2494,27 +2389,25 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>25515</v>
+        <v>196</v>
       </c>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Being supply of 20mm aggregates( A/C NO:- 50200117806106 ,IFSC :- HDFC0001534) RPA_ID : e9fe0833c6</t>
+          <t>Wed, 18 Mar, 2026/travel to Behala, Kolkata, West Bengal, India to Bhowanipore, Kolkata, West Bengal, India RPA_ID : 5cfb945509</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>IOCL Pappinasseri</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>SITE EXPENSES</t>
-        </is>
+          <t>DUMKA</t>
+        </is>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>midhuncraju12@gmail.com</t>
+          <t>hrm@westernidc.com</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2534,16 +2427,8 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
       <c r="AK16" t="inlineStr"/>
       <c r="AL16" t="inlineStr"/>
       <c r="AM16" t="inlineStr"/>
@@ -2553,7 +2438,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>WGG 02</t>
+          <t>WGE 195</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2563,7 +2448,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>23-03-2026</t>
+          <t>25-03-2026</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -2597,14 +2482,26 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>SAYAN BATTACHARYA</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>a177aaf3-6783-4853-bdd2-e4d3a1297e76</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>9bf4f9ac-61f0-40c1-914a-7a977acc86e9</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>ACC-14810110034736</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>UCBA0001481</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
@@ -2617,27 +2514,25 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>8100</v>
+        <v>214</v>
       </c>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Being rental of grasscutting machine and petrol expenses (A/C NO:-  32555551936 ,IFSC :- SBIN0001890) RPA_ID : 4799f3742e</t>
+          <t>Mon, 23 Mar, 2026/ travel to Bhowanipore, Kolkata, West Bengal, India to Howrah, West Bengal, India RPA_ID : a9fe535782</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>HPCL ELATOOR</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>SITE EXPENSES</t>
-        </is>
+          <t>DUMKA</t>
+        </is>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>midhuncraju12@gmail.com</t>
+          <t>hrm@westernidc.com</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -2657,16 +2552,8 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
       <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="inlineStr"/>
       <c r="AM17" t="inlineStr"/>
@@ -2676,7 +2563,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>WGG 02</t>
+          <t>WGE 195</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2686,7 +2573,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>23-03-2026</t>
+          <t>25-03-2026</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2720,14 +2607,26 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>SAYAN BATTACHARYA</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>6623d2fb-55f0-4d25-af7d-fb39970e114e</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>0d958c8b-8b18-420d-8fb6-e22d523741e0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>ACC-14810110034736</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>UCBA0001481</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
@@ -2740,27 +2639,25 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>29500</v>
+        <v>222</v>
       </c>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Being purchasing of cement (A/C NO:- 39733680664 ,IFSC :- SBIN0070202 RPA_ID : 46b11c2c2c</t>
+          <t>Fri, 20 Mar, 2026 / travel to Bhowanipore, Kolkata, West Bengal, India to Howrah, West Bengal, India RPA_ID : 95a07065c5</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>IOCL Pappinasseri</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>SITE EXPENSES</t>
-        </is>
+          <t>DUMKA</t>
+        </is>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>midhuncraju12@gmail.com</t>
+          <t>hrm@westernidc.com</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2780,22 +2677,2058 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
       <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="inlineStr"/>
       <c r="AM18" t="inlineStr"/>
       <c r="AN18" t="inlineStr"/>
       <c r="AO18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>WGE 195</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>25-03-2026</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>SAYAN BATTACHARYA</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>9b220f18-b666-460b-86c2-267278708f44</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>ACC-14810110034736</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>UCBA0001481</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>400</v>
+      </c>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Food for inspector (VCS) for Bill submission ( dumka) RPA_ID : 5ddb08e6c2</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>DUMKA</t>
+        </is>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>WGE 195</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>25-03-2026</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>SAYAN BATTACHARYA</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>a451f63d-ca46-40c8-9958-6822a9edc6bc</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>ACC-14810110034736</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>UCBA0001481</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Car expenses( only diesel) from Asansol to Jamtara and back from asansol with inspection accompanied for bill submission RPA_ID : 4d77ce6f4f</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>DUMKA</t>
+        </is>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>WGE 195</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>25-03-2026</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>SAYAN BATTACHARYA</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>215cd75a-c290-4553-a2e2-4e1a873618db</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>ACC-14810110034736</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>UCBA0001481</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>168</v>
+      </c>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>train ticket for asanol to howrah for bill submission RPA_ID : 08872f17e6</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>DUMKA</t>
+        </is>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>WGE 132</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>25-03-2026</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>United India Insurance</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>8f6e8f3d-f01e-40d1-8a5c-e174289c4aa8</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>ACC-200999095210100100</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>INDB0000007</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>9500</v>
+      </c>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>shamzusaman &amp; munna workmen compensation charge  for 2 workers instruction from sayan sir RPA_ID : aa410d1dbc</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>GRSE KOLKATA</t>
+        </is>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>KOLKATA</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>WGE 344</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>25-03-2026</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAUTHAM KRISHNAN C G </t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>e6ab2a51-d403-4924-9225-211b57c55d87</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>ACC-20289798248</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>SBIN0010597</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>3350</v>
+      </c>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Being purcchase of gonny Bags (Old pending payment: 100 bags × ₹6 = ₹600
+New purchase: 500 bags × ₹5.5 = ₹2,750)
+(24-03-2026) RPA_ID : 44c4b3a17c</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>BPCL BALLARI</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>asstprocurement@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>WGE 56</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>25-03-2026</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Akhil</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>b658a24c-5f1e-4bfa-92cd-d2453760a726</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>ACC-852110110008274</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>BKID0008521</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>400</v>
+      </c>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Being payment for grasscutting,monthly waste removing and petorl expenses .   VERY URGENT (24-03-2026) RPA_ID : d1230bee3c</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>IOCL FEROKE</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>asstprocurement@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>IOCL FEROKE</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>WGE 306</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>25-03-2026</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>SABIN V V</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>e8910824-2d15-4f50-9dbf-df38e380f185</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>ACC-67274681749</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>SBIN0070812</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>799</v>
+      </c>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Being purchase of  Safety shoe (24-03-2026) RPA_ID : 55dbb7992c</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>NGOPV CHENNAI- COLD &amp; COOL ROOM</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>asstprocurement@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>COLD &amp; COOL ROOM</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>WGE 344</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>25-03-2026</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAUTHAM KRISHNAN C G </t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>caecb3a3-465d-4f7f-9b91-e905c532689c</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>ACC-20289798248</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>SBIN0010597</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>225</v>
+      </c>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Being Water for Trailer &amp; Food for Helper &amp; Trailer driver (25-03-2026) RPA_ID : 3f2506d792</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>BPCL BALLARI</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>asstprocurement@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>WGE 586</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>25-03-2026</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Reji Alias (Royal Engineering &amp; Constructions)</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>9b0548dd-6146-4511-bc31-799b19461de1</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>ACC-338802010103171</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>UBIN0533882</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>22000</v>
+      </c>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Being construction of Electric Room (25-03-2026) RPA_ID : ee4ba557f1</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>IOCL THIRUVANIYOOR</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>asstprocurement@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>WGE 587</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>25-03-2026</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>DCR</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>ALUVA BARRELS CORPORATION</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>232c4087-f922-4951-b2f2-4e714b534c3b</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>ACC-57027655116</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>SBIN0070368</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>2478</v>
+      </c>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Being Supply of Drums (25-03-2026)
+A/C NO: 57027655116, IFSC: SBIN0070368 RPA_ID : ad31da43ea</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>IOCL THIRUVANIYOOR</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>asstprocurement@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>WGE 591</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>25-03-2026</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>BINU MATHEW</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>54315035-5ea5-4090-93ba-d9d6365143eb</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>ACC-12230100213494</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>FDRL0001223</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>5300</v>
+      </c>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Being rental of crane for Unloading Tanks (25/03/2026)
+A/c No: 12230100213494, IFSC: FDRL0001223 RPA_ID : 8db3e666c7</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>IOCL THIRUVANIYOOR</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>asstprocurement@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>WGE 592</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>25-03-2026</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>FINE HARDWARE</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>3a92ff26-29f6-4123-bcda-8d0b5e2d66cf</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>ACC-3878002100002060</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>PUNB0387800</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>18900</v>
+      </c>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Being purchase of Coating mesh, Chicken Mesh &amp; GI strip (25/03/2026)
+A/C No: 3878002100002069, IFSC: PUNB0387800) RPA_ID : e53188448d</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>IOCL PAPPINISSERI</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>asstprocurement@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>WGE 588</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>25-03-2026</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Faisal K</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>dac867de-3ea9-4003-b3d5-b1357bbfe88f</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>ACC-11380100147266</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>FDRL0001138</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Being Rental of crane for Underground tank installation (25/03/2026)
+A/C NO: 11380100147266, IFSC: FDRL0001138) RPA_ID : fc4f457aa6</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>IOCL PAPPINISSERI</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>asstprocurement@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>WGE 589</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>25-03-2026</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>DAVIS K OUSEPH (MAR BASIL EARTH MOVERS)</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>7a5d7e03-07c4-4660-a52b-ea9de7620633</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>ACC-759053000005397</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>SIBL0000759</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>29800</v>
+      </c>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Being rental of JCB Hittachi, Tipper (25/03/2026)
+A/c No: 0759053000005397, IFSC: SIBL0000759 RPA_ID : 667501e5da</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>IOCL THIRUVANIYOOR</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>asstprocurement@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>WGE 590</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>25-03-2026</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>NABIL T P</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2c0c0555-edcf-4409-baa8-15d10049985a</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>ACC-50210029339189</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>BDBL0001867</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>20000</v>
+      </c>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Being generator rental at the Pappinissery site (25/03/2026)
+AC no : 50210029339189, Ifsc code :BDBL0001867 RPA_ID : a4c763c1ce</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>IOCL PAPPINISSERI</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>asstprocurement@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr"/>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>WGE 344</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>25-03-2026</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAUTHAM KRISHNAN C G </t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>68941cd4-8ff4-4c9b-8495-f0472e385b93</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>ACC-20289798248</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>SBIN0010597</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>600</v>
+      </c>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Being food expenses for Excavator operator (16/03/26 TO 21/03/2026) RPA_ID : 865c545d03</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>BPCL BALLARI</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>asstprocurement@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="inlineStr"/>
+      <c r="AK34" t="inlineStr"/>
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="inlineStr"/>
+      <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PENDING_APPROVAL_SHEET.xlsx
+++ b/PENDING_APPROVAL_SHEET.xlsx
@@ -754,16 +754,8 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr"/>
@@ -863,8 +855,16 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr"/>

--- a/PENDING_APPROVAL_SHEET.xlsx
+++ b/PENDING_APPROVAL_SHEET.xlsx
@@ -754,8 +754,16 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr"/>
@@ -857,12 +865,12 @@
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr"/>
@@ -960,8 +968,16 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK4" t="inlineStr">
         <is>
           <t>HO</t>
@@ -1085,8 +1101,16 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK5" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -1214,8 +1238,16 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK6" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -1343,8 +1375,16 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK7" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -1444,8 +1484,16 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK8" t="inlineStr">
         <is>
           <t>ONGC IPSHEM</t>
@@ -1573,8 +1621,16 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
@@ -1670,8 +1726,16 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
       <c r="AK10" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -1802,8 +1866,16 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr"/>
       <c r="AM11" t="inlineStr"/>
@@ -1927,8 +1999,16 @@
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
-      <c r="AJ12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr"/>
       <c r="AM12" t="inlineStr"/>
@@ -2052,8 +2132,16 @@
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="inlineStr"/>
       <c r="AM13" t="inlineStr"/>
@@ -2177,8 +2265,16 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="inlineStr"/>
       <c r="AM14" t="inlineStr"/>
@@ -2302,8 +2398,16 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr"/>
-      <c r="AJ15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="inlineStr"/>
       <c r="AM15" t="inlineStr"/>
@@ -2427,8 +2531,16 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr"/>
-      <c r="AJ16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK16" t="inlineStr"/>
       <c r="AL16" t="inlineStr"/>
       <c r="AM16" t="inlineStr"/>
@@ -2552,8 +2664,16 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
-      <c r="AJ17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="inlineStr"/>
       <c r="AM17" t="inlineStr"/>
@@ -2677,8 +2797,16 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
-      <c r="AJ18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="inlineStr"/>
       <c r="AM18" t="inlineStr"/>
@@ -2802,8 +2930,16 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr"/>
-      <c r="AJ19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK19" t="inlineStr"/>
       <c r="AL19" t="inlineStr"/>
       <c r="AM19" t="inlineStr"/>
@@ -2927,8 +3063,16 @@
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="inlineStr"/>
-      <c r="AJ20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK20" t="inlineStr"/>
       <c r="AL20" t="inlineStr"/>
       <c r="AM20" t="inlineStr"/>
@@ -3052,8 +3196,16 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr"/>
-      <c r="AJ21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="inlineStr"/>
       <c r="AM21" t="inlineStr"/>
@@ -3177,8 +3329,16 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr"/>
-      <c r="AI22" t="inlineStr"/>
-      <c r="AJ22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
       <c r="AK22" t="inlineStr">
         <is>
           <t>KOLKATA</t>
@@ -3310,8 +3470,16 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="inlineStr"/>
-      <c r="AJ23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK23" t="inlineStr"/>
       <c r="AL23" t="inlineStr"/>
       <c r="AM23" t="inlineStr"/>
@@ -3437,8 +3605,16 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="inlineStr"/>
-      <c r="AI24" t="inlineStr"/>
-      <c r="AJ24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
       <c r="AK24" t="inlineStr">
         <is>
           <t>IOCL FEROKE</t>
@@ -3699,8 +3875,16 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr"/>
-      <c r="AI26" t="inlineStr"/>
-      <c r="AJ26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
       <c r="AK26" t="inlineStr"/>
       <c r="AL26" t="inlineStr"/>
       <c r="AM26" t="inlineStr"/>
@@ -3826,8 +4010,16 @@
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr"/>
-      <c r="AI27" t="inlineStr"/>
-      <c r="AJ27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
       <c r="AK27" t="inlineStr"/>
       <c r="AL27" t="inlineStr"/>
       <c r="AM27" t="inlineStr"/>
@@ -3954,8 +4146,16 @@
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="inlineStr"/>
-      <c r="AI28" t="inlineStr"/>
-      <c r="AJ28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
       <c r="AK28" t="inlineStr"/>
       <c r="AL28" t="inlineStr"/>
       <c r="AM28" t="inlineStr"/>
@@ -4082,8 +4282,16 @@
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="inlineStr"/>
-      <c r="AI29" t="inlineStr"/>
-      <c r="AJ29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
       <c r="AK29" t="inlineStr"/>
       <c r="AL29" t="inlineStr"/>
       <c r="AM29" t="inlineStr"/>
@@ -4210,8 +4418,16 @@
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="inlineStr"/>
-      <c r="AI30" t="inlineStr"/>
-      <c r="AJ30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
       <c r="AK30" t="inlineStr"/>
       <c r="AL30" t="inlineStr"/>
       <c r="AM30" t="inlineStr"/>
@@ -4338,8 +4554,16 @@
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr"/>
-      <c r="AI31" t="inlineStr"/>
-      <c r="AJ31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
       <c r="AK31" t="inlineStr"/>
       <c r="AL31" t="inlineStr"/>
       <c r="AM31" t="inlineStr"/>
@@ -4466,8 +4690,16 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr"/>
-      <c r="AI32" t="inlineStr"/>
-      <c r="AJ32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
       <c r="AK32" t="inlineStr"/>
       <c r="AL32" t="inlineStr"/>
       <c r="AM32" t="inlineStr"/>
@@ -4594,8 +4826,16 @@
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr"/>
-      <c r="AI33" t="inlineStr"/>
-      <c r="AJ33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
       <c r="AK33" t="inlineStr"/>
       <c r="AL33" t="inlineStr"/>
       <c r="AM33" t="inlineStr"/>
@@ -4721,8 +4961,16 @@
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr"/>
-      <c r="AI34" t="inlineStr"/>
-      <c r="AJ34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK34" t="inlineStr"/>
       <c r="AL34" t="inlineStr"/>
       <c r="AM34" t="inlineStr"/>

--- a/PENDING_APPROVAL_SHEET.xlsx
+++ b/PENDING_APPROVAL_SHEET.xlsx
@@ -754,8 +754,16 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
       <c r="AK2" t="inlineStr">
         <is>
           <t>COLD &amp; COOL ROOM</t>

--- a/PENDING_APPROVAL_SHEET.xlsx
+++ b/PENDING_APPROVAL_SHEET.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO2"/>
+  <dimension ref="A1:AO29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -638,7 +638,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WGE 306</t>
+          <t>WGE 342</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>25-03-2026</t>
+          <t>26-03-2026</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -684,24 +684,20 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>SABIN V V</t>
+          <t>PAUL OFFSHORE PVT</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>e8910824-2d15-4f50-9dbf-df38e380f185</t>
+          <t>d75eb280-6fc7-46a8-8502-dccbdc27c26d</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>ACC-67274681749</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>SBIN0070812</t>
-        </is>
-      </c>
+          <t>ACC-7806823928</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
@@ -714,27 +710,25 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>799</v>
+        <v>117495</v>
       </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Being purchase of  Safety shoe (24-03-2026) RPA_ID : 55dbb7992c</t>
+          <t>ONGC GOA JAN BILL LABOUR CHARGES - WELDER / FITTER/RIGGER AND FOOD ALLOWANCE Total Amount= 342495/- Paid Rs.75000/- , Paid Rs.100000/- Excel Attendnace Sheet already shared= 167495,paid Rs.50000/-21.03.2026 RPA_ID : 231230f018</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>NGOPV CHENNAI- COLD &amp; COOL ROOM</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>SITE EXPENSES</t>
-        </is>
+          <t>ONGC GOA</t>
+        </is>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>asstprocurement@westernidc.com</t>
+          <t>hrm@westernidc.com</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -749,24 +743,24 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>799</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>ACCEPTED</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>ACCEPTED</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>COLD &amp; COOL ROOM</t>
+          <t>GOA</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr"/>
@@ -774,6 +768,3599 @@
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>WGE 192</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>26-03-2026</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Hafis Bin Haris</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>ef41f273-bc8f-4227-99e2-4ffa667ca6b8</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ACC-99980105201458</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>FDRL0001143</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>9597</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Salary- January 9597/- Full and Final Settlement Paid December 7423 , Balance 9597  Total = 17020 RPA_ID : 49d711b070</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>GOA HUL</t>
+        </is>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>WGE 104</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>26-03-2026</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>BRAHMADATHAN</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>36440d92-947d-4d6f-bd3d-fd89a9c14606</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ACC-232001000010098</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>IOBA0002320</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>14379</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Salary November Full and Final settlement Final Settlement Total 24379 , Rs.10000/- Paid  18.03.2026 Balance to be paid RPA_ID : d959278e3e</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>GOA HUL</t>
+        </is>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>WGE 452</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>26-03-2026</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA REDDY</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>1e80d2d2-9b98-48cc-99da-75a6b2bc40df</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>ACC- 79860100001270</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>BARB0VASCOD</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>15000</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Hishm sir baleno auto 4th jan 10th jan 7days=10500,Baleno auto 14th jan 29th jan 16days=24000,Swift manual 17th jan 19th jan 3days=3600,Sidharth Dezire 13th feb  to 14th 3days 2400,Sir swift auto 16thfeb 17thfeb 2days 3000 2nd 1500 =45000 (10000 paid) As per Advice from Admin Andriya - No documents provided Rs.10000/- paid,Rs.10000/- paid 18.03.2026,23.023.2026 10000/-paid RPA_ID : f261da1e4a</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>ONGC IPSHEM</t>
+        </is>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>ONGC IPSHEM</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>WGE 170</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>26-03-2026</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>VEDANT</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>1f48ba73-1868-4772-9abf-496e85a4bba2</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>ACC-2047172054</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>KKBK0001429</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>6451</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Material Shiftng 8 Days worked (December 5 days , January 3 Days) Basic Pay is Rs.25000/- perday 806.45 RPA_ID : 8e805badc2</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>MDL</t>
+        </is>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>WGE 462</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>26-03-2026</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>PRANEET</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>19bde9fc-14a8-4b8a-b3b2-a19890cbd87e</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ACC-'095203100002750</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>SRCB00000095</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>5000</v>
+      </c>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Casual Payment 5 Nos @ 1000 ST3 GOA Deployed Local Casual Labours 26.04.2026 RPA_ID : 8eac0b97b6</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>ST3 GOA</t>
+        </is>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>WGE 195</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>26-03-2026</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>SAYAN BATTACHARYA</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>505e49b6-a801-4bfd-9126-e68cff9de09e</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>ACC-14810110034736</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>UCBA0001481</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>224</v>
+      </c>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Sun, 01 Mar, 2026 / travel Howrah, West Bengal 711101, India to Bhowanipore, Kolkata, West Bengal, India RPA_ID : 021f953025</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>DUMKA</t>
+        </is>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>WGE 195</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>26-03-2026</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>SAYAN BATTACHARYA</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>026d5df8-ed4a-42b4-9285-822cf7a0887f</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ACC-14810110034736</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>UCBA0001481</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>224</v>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Sun, 08 Mar, 2026 / travel to Howrah, West Bengal 711101, India to Bhowanipore, Kolkata, West Bengal, India RPA_ID : b91288658f</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>DUMKA</t>
+        </is>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>WGE 195</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>26-03-2026</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>SAYAN BATTACHARYA</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>e889899a-4f8e-42bb-8a5f-5adc15edb837</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ACC-14810110034736</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>UCBA0001481</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>199</v>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Wed, 11 Mar, 2026 / travel to Bhowanipore, Kolkata, West Bengal, India to Howrah, West Bengal, India RPA_ID : 3a89bded6e</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>DUMKA</t>
+        </is>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>WGE 195</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>26-03-2026</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>SAYAN BATTACHARYA</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>f29b11e2-8bc4-4afe-9a4e-d16973fa0358</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ACC-14810110034736</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>UCBA0001481</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>256</v>
+      </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Thu, 12 Mar, 2026/ travel to , Howrah, West Bengal 711101, India to Bhowanipore, Kolkata, West Bengal, India RPA_ID : 9f4ad9bcdc</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>DUMKA</t>
+        </is>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>WGE 195</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>26-03-2026</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>SAYAN BATTACHARYA</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>bc2f0239-1cfa-4b79-88ac-25b72aa7c1a5</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ACC-14810110034736</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>UCBA0001481</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>196</v>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Wed, 18 Mar, 2026/travel to Behala, Kolkata, West Bengal, India to Bhowanipore, Kolkata, West Bengal, India RPA_ID : 6f6349e329</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>DUMKA</t>
+        </is>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>WGE 195</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>26-03-2026</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>SAYAN BATTACHARYA</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>72482b03-4829-424e-bbd4-e635d894b1c2</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ACC-14810110034736</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>UCBA0001481</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>214</v>
+      </c>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Mon, 23 Mar, 2026/ travel to Bhowanipore, Kolkata, West Bengal, India to Howrah, West Bengal, India RPA_ID : 377b6a8fe9</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>DUMKA</t>
+        </is>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>WGE 195</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>26-03-2026</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>SAYAN BATTACHARYA</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>58ed1edc-8cbc-4cd9-ba88-77e278d2a0e7</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ACC-14810110034736</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>UCBA0001481</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>222</v>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Fri, 20 Mar, 2026 / travel to Bhowanipore, Kolkata, West Bengal, India to Howrah, West Bengal, India RPA_ID : 5da98d81ae</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>DUMKA</t>
+        </is>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>WGE 195</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>26-03-2026</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>SAYAN BATTACHARYA</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>5d3f6a53-c3d1-4e81-aa48-7b67b7beeb6e</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>ACC-14810110034736</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>UCBA0001481</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>400</v>
+      </c>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Food for inspector (VCS) for Bill submission ( dumka) RPA_ID : 5a45f667eb</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>DUMKA</t>
+        </is>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>WGE 195</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>26-03-2026</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>SAYAN BATTACHARYA</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>c714ab46-bd7b-4cde-bd40-7b5dbf8b3b60</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>ACC-14810110034736</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>UCBA0001481</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Car expenses( only diesel) from Asansol to Jamtara and back from asansol with inspection accompanied for bill submission RPA_ID : b6c31887cd</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>DUMKA</t>
+        </is>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>WGE 195</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>26-03-2026</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>SAYAN BATTACHARYA</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1ef0abff-c779-437d-809e-7fe8b0687a6f</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>ACC-14810110034736</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>UCBA0001481</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>168</v>
+      </c>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>train ticket for asanol to howrah for bill submission RPA_ID : 0abff50fa5</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>DUMKA</t>
+        </is>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>WGE 195</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>26-03-2026</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>SAYAN BATTACHARYA</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>c2ef46a4-79b5-41fe-9563-3926cb433f8c</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>ACC-14810110034736</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>UCBA0001481</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>450</v>
+      </c>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>PRINTER REPAIR CHARGE FOR KOLKATA OFFICE RPA_ID : 5503789d2d</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>KOLKATA OFFICE</t>
+        </is>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>KOLKATA</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>WGE 593</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>26-03-2026</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ASHIQUE ALI P</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>d3b772db-65b3-408e-966a-97ece594d8dd</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>ACC-852116310000006</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>BKID0008521</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>1500</v>
+      </c>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>TRAVEL EXPENSES FOR KOCHI TO BELLARI ( PROJECT PLANNING COORDINATOR) 26/03/2026 RPA_ID : 7ebcf74e94</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>WGE 593</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>26-03-2026</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ASHIQUE ALI P</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>d1954046-76f7-4c95-8766-189ee53890de</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>ACC-852116310000006</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>BKID0008521</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>750</v>
+      </c>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>FOOD EXPENSES ( 27/03/2026 TO 31/03/2026 ) PER DAY 150 RPA_ID : d33f365719</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>WGE 73</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>26-03-2026</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>DCR</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Nithin</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>4253920a-de62-4358-afc2-93d27aaa9dc5</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>ACC-32555551936</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>SBIN0001890</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>CASUAL WAGE  25/03/2026 LEAVE NISHANTH( MEDICAL LEAVE ) &amp; ATHUL RAJ( MARRIAGE LEAVE) RPA_ID : 6a1da9c546</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>HPCL ELATHUR</t>
+        </is>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>HPCL ELATHUR</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>WGE 73</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>26-03-2026</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>DCR</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Nithin</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>c9cf54c7-0d83-42f4-aace-1209b558cec3</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>ACC-32555551936</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>SBIN0001890</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>CASUAL WAGE  26/03/2026 LEAVE NISHANTH &amp; ATHUL RAJ RPA_ID : 11a13a4f3d</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>HPCL ELATHUR</t>
+        </is>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>HPCL ELATHUR</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>WGE 594</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>26-03-2026</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>DCR</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ANIL KUMAR P P</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>3cad723e-8552-4c3c-a934-13cde12c11ee</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>ACC- 20075235595</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>SBIN0012877</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>11000</v>
+      </c>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>PAPPANASHERI ROOM RENT  FEBRUARY 2026 ( ADVANCE  DEPOSIT 11000) RPA_ID : b0b5085517</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>PAPPANASHERI</t>
+        </is>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>WGE 105</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>26-03-2026</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>DCR</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>RUMJAN ALI</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2bedafb7-bc38-488d-9cef-f96418433968</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>ACC-35361930366</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>SBIN0014087</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>5000</v>
+      </c>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>KOLKATA TO GOA 5 CARPENTERS FOR ONGC IPSHEM FOOD  EXPENSES  &amp; TRAVEL EXPENSES FOR 2 DAYS ( 5 WORKERS)   TOTAL 5000 APPROVED BY HISHAM SIR RPA_ID : ec8bfd64f2</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>ONGC IPSHEM</t>
+        </is>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>PAID</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>PAID</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>ONGC IPSHEM</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>WGE 306</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>26-03-2026</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>SABIN V V</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>69a9a5eb-93c4-45ac-81ee-34c6f27c02c8</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>ACC-67274681749</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>SBIN0070812</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>3300</v>
+      </c>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>L &amp; T CHENNAI  ROOM  STAY EXPENSES  ( 26/03/2026 TO 28/03/2026)  PER DAY 1100 / Room stay till 23/03/2026 has already been paid RPA_ID : b29f95944d</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>L &amp; T CHENNAI</t>
+        </is>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>WGE 323</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>26-03-2026</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>VINITHA V NAIR</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>dbd5e10a-67ca-4c80-8474-33eb4c103425</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>ACC-22020100013715</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>FDRL0002202</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>4000</v>
+      </c>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Daily Site Labour Charges-for 4 labours RPA_ID : ed8f362c50</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>Construction of IOCL RO at Pappinissery</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>LABOUR CHARGES</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>executive.westerntender@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> WGG 02</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>26-03-2026</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>39348140-ef38-4fbd-bddc-13235d55301f</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>79930</v>
+      </c>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Pep consultancy pendiing payment RPA_ID : 2b00207380</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>Cochin</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>Payments@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> WGG 02</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>26-03-2026</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>ff529cd2-01b5-491b-ae2f-c8908174cdf1</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>50000</v>
+      </c>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Payment as per the instraction of Sreekumar Sir RPA_ID : 43735a8e39</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>Cochin</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>Payments@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>WGE 597</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>26-03-2026</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Shree Krishna Steels &amp; Water Services</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>68393174-0d18-45cc-bf26-a55e000f3cd1</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>ACC-278705000855</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>ICIC0002787</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>73900</v>
+      </c>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Providing team for Survey of Damaged Vessel 
+Samudra Shiksha ONGC Training Vessel at Betul 
+Goa RPA_ID : 8f2ec28874</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>ONGC Jetty project</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>SURVEY</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>executive.westerntender@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PENDING_APPROVAL_SHEET.xlsx
+++ b/PENDING_APPROVAL_SHEET.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO29"/>
+  <dimension ref="A1:AO67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -638,7 +638,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WGE 342</t>
+          <t xml:space="preserve"> WGG 02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -682,21 +682,13 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>PAUL OFFSHORE PVT</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>d75eb280-6fc7-46a8-8502-dccbdc27c26d</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>ACC-7806823928</t>
-        </is>
-      </c>
+          <t>39348140-ef38-4fbd-bddc-13235d55301f</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -710,25 +702,27 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>117495</v>
+        <v>79930</v>
       </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
-          <t>ONGC GOA JAN BILL LABOUR CHARGES - WELDER / FITTER/RIGGER AND FOOD ALLOWANCE Total Amount= 342495/- Paid Rs.75000/- , Paid Rs.100000/- Excel Attendnace Sheet already shared= 167495,paid Rs.50000/-21.03.2026 RPA_ID : 231230f018</t>
+          <t>Pep consultancy pendiing payment RPA_ID : 2b00207380</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>ONGC GOA</t>
-        </is>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
+          <t>Cochin</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>hrm@westernidc.com</t>
+          <t>Payments@westernidc.com</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -743,26 +737,14 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>79930</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>GOA</t>
-        </is>
-      </c>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
@@ -771,7 +753,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WGE 192</t>
+          <t xml:space="preserve"> WGG 02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -815,26 +797,14 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Hafis Bin Haris</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>ef41f273-bc8f-4227-99e2-4ffa667ca6b8</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>ACC-99980105201458</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>FDRL0001143</t>
-        </is>
-      </c>
+          <t>ff529cd2-01b5-491b-ae2f-c8908174cdf1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
@@ -847,25 +817,27 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>9597</v>
+        <v>50000</v>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Salary- January 9597/- Full and Final Settlement Paid December 7423 , Balance 9597  Total = 17020 RPA_ID : 49d711b070</t>
+          <t>Payment as per the instraction of Sreekumar Sir RPA_ID : 43735a8e39</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>GOA HUL</t>
-        </is>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
+          <t>Cochin</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>hrm@westernidc.com</t>
+          <t>Payments@westernidc.com</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -880,26 +852,14 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>GOA</t>
-        </is>
-      </c>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr"/>
@@ -908,7 +868,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WGE 104</t>
+          <t>WGE 597</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -954,22 +914,22 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>BRAHMADATHAN</t>
+          <t>Shree Krishna Steels &amp; Water Services</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>36440d92-947d-4d6f-bd3d-fd89a9c14606</t>
+          <t>68393174-0d18-45cc-bf26-a55e000f3cd1</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>ACC-232001000010098</t>
+          <t>ACC-278705000855</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>IOBA0002320</t>
+          <t>ICIC0002787</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -984,25 +944,29 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>14379</v>
+        <v>73900</v>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Salary November Full and Final settlement Final Settlement Total 24379 , Rs.10000/- Paid  18.03.2026 Balance to be paid RPA_ID : d959278e3e</t>
+          <t>Providing team for Survey of Damaged Vessel 
+Samudra Shiksha ONGC Training Vessel at Betul 
+Goa RPA_ID : 8f2ec28874</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>GOA HUL</t>
-        </is>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
+          <t>ONGC Jetty project</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>SURVEY</t>
+        </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>hrm@westernidc.com</t>
+          <t>executive.westerntender@gmail.com</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1017,26 +981,14 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>73900</v>
       </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>GOA</t>
-        </is>
-      </c>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
@@ -1045,7 +997,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WGE 452</t>
+          <t>WGE 342</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1055,7 +1007,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>26-03-2026</t>
+          <t>27-03-2026</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1091,24 +1043,20 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>CHANDRAKALA REDDY</t>
+          <t>PAUL OFFSHORE PVT</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1e80d2d2-9b98-48cc-99da-75a6b2bc40df</t>
+          <t>01c2a523-2911-494f-aaa4-df83747405c3</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>ACC- 79860100001270</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>BARB0VASCOD</t>
-        </is>
-      </c>
+          <t>ACC-7806823928</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
@@ -1121,17 +1069,17 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>15000</v>
+        <v>117495</v>
       </c>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Hishm sir baleno auto 4th jan 10th jan 7days=10500,Baleno auto 14th jan 29th jan 16days=24000,Swift manual 17th jan 19th jan 3days=3600,Sidharth Dezire 13th feb  to 14th 3days 2400,Sir swift auto 16thfeb 17thfeb 2days 3000 2nd 1500 =45000 (10000 paid) As per Advice from Admin Andriya - No documents provided Rs.10000/- paid,Rs.10000/- paid 18.03.2026,23.023.2026 10000/-paid RPA_ID : f261da1e4a</t>
+          <t>ONGC GOA JAN BILL LABOUR CHARGES - WELDER / FITTER/RIGGER AND FOOD ALLOWANCE Total Amount= 342495/- Paid Rs.75000/- , Paid Rs.100000/- Excel Attendnace Sheet already shared= 167495,paid Rs.50000/-21.03.2026 RPA_ID : 903275d6b5</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>ONGC IPSHEM</t>
+          <t>ONGC GOA</t>
         </is>
       </c>
       <c r="Z5" t="n">
@@ -1159,19 +1107,11 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>ONGC IPSHEM</t>
+          <t>GOA</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr"/>
@@ -1182,7 +1122,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WGE 170</t>
+          <t>WGE 192</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1192,7 +1132,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26-03-2026</t>
+          <t>27-03-2026</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1228,22 +1168,22 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>VEDANT</t>
+          <t>Hafis Bin Haris</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1f48ba73-1868-4772-9abf-496e85a4bba2</t>
+          <t>bc38d485-3ee6-48d1-a661-44de4543d7f1</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>ACC-2047172054</t>
+          <t>ACC-99980105201458</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>KKBK0001429</t>
+          <t>FDRL0001143</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
@@ -1258,17 +1198,17 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>6451</v>
+        <v>9597</v>
       </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Material Shiftng 8 Days worked (December 5 days , January 3 Days) Basic Pay is Rs.25000/- perday 806.45 RPA_ID : 8e805badc2</t>
+          <t>Salary- January 9597/- Full and Final Settlement Paid December 7423 , Balance 9597  Total = 17020 RPA_ID : bf1fe2a429</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>MDL</t>
+          <t>GOA HUL</t>
         </is>
       </c>
       <c r="Z6" t="n">
@@ -1296,17 +1236,13 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
@@ -1315,7 +1251,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WGE 462</t>
+          <t>WGE 104</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1325,7 +1261,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>26-03-2026</t>
+          <t>27-03-2026</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1361,22 +1297,22 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>PRANEET</t>
+          <t>BRAHMADATHAN</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>19bde9fc-14a8-4b8a-b3b2-a19890cbd87e</t>
+          <t>85581fa4-aede-4d8d-9b08-8d1da3ec7f77</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>ACC-'095203100002750</t>
+          <t>ACC-232001000010098</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>SRCB00000095</t>
+          <t>IOBA0002320</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
@@ -1391,17 +1327,17 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>5000</v>
+        <v>14379</v>
       </c>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Casual Payment 5 Nos @ 1000 ST3 GOA Deployed Local Casual Labours 26.04.2026 RPA_ID : 8eac0b97b6</t>
+          <t>Salary November Full and Final settlement Final Settlement Total 24379 , Rs.10000/- Paid  18.03.2026 Balance to be paid RPA_ID : 55539696c4</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>ST3 GOA</t>
+          <t>GOA HUL</t>
         </is>
       </c>
       <c r="Z7" t="n">
@@ -1429,16 +1365,8 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -1452,7 +1380,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WGE 195</t>
+          <t>WGE 452</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1462,7 +1390,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>26-03-2026</t>
+          <t>27-03-2026</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1498,22 +1426,22 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>SAYAN BATTACHARYA</t>
+          <t>CHANDRAKALA REDDY</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>505e49b6-a801-4bfd-9126-e68cff9de09e</t>
+          <t>4db33d2a-db29-4655-8225-d6b0aa05bea0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>ACC-14810110034736</t>
+          <t>ACC- 79860100001270</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>UCBA0001481</t>
+          <t>BARB0VASCOD</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -1528,17 +1456,17 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>224</v>
+        <v>15000</v>
       </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Sun, 01 Mar, 2026 / travel Howrah, West Bengal 711101, India to Bhowanipore, Kolkata, West Bengal, India RPA_ID : 021f953025</t>
+          <t>Hishm sir baleno auto 4th jan 10th jan 7days=10500,Baleno auto 14th jan 29th jan 16days=24000,Swift manual 17th jan 19th jan 3days=3600,Sidharth Dezire 13th feb  to 14th 3days 2400,Sir swift auto 16thfeb 17thfeb 2days 3000 2nd 1500 =45000 (10000 paid) As per Advice from Admin Andriya - No documents provided Rs.10000/- paid,Rs.10000/- paid 18.03.2026,23.023.2026 10000/-paid RPA_ID : fac96b4e1c</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>DUMKA</t>
+          <t>ONGC IPSHEM</t>
         </is>
       </c>
       <c r="Z8" t="n">
@@ -1566,17 +1494,13 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>ONGC IPSHEM</t>
+        </is>
+      </c>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
@@ -1585,7 +1509,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WGE 195</t>
+          <t>WGE 170</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1595,7 +1519,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>26-03-2026</t>
+          <t>27-03-2026</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1631,22 +1555,22 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>SAYAN BATTACHARYA</t>
+          <t>VEDANT</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>026d5df8-ed4a-42b4-9285-822cf7a0887f</t>
+          <t>23d771db-6829-48d7-96e0-56f77e5ebb0a</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>ACC-14810110034736</t>
+          <t>ACC-2047172054</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>UCBA0001481</t>
+          <t>KKBK0001429</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -1661,17 +1585,17 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>224</v>
+        <v>6451</v>
       </c>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Sun, 08 Mar, 2026 / travel to Howrah, West Bengal 711101, India to Bhowanipore, Kolkata, West Bengal, India RPA_ID : b91288658f</t>
+          <t>Material Shiftng 8 Days worked (December 5 days , January 3 Days) Basic Pay is Rs.25000/- perday 806.45 RPA_ID : d29c72c93e</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>DUMKA</t>
+          <t>MDL</t>
         </is>
       </c>
       <c r="Z9" t="n">
@@ -1699,16 +1623,8 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
@@ -1718,7 +1634,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WGE 195</t>
+          <t>WGE 462</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1728,7 +1644,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>26-03-2026</t>
+          <t>27-03-2026</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1764,22 +1680,22 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>SAYAN BATTACHARYA</t>
+          <t>PRANEET</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>e889899a-4f8e-42bb-8a5f-5adc15edb837</t>
+          <t>c567b109-7c52-46e7-bdbd-ab5c8079a077</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>ACC-14810110034736</t>
+          <t>ACC-095203100002750</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>UCBA0001481</t>
+          <t>SRCB00000095</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -1794,17 +1710,17 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>199</v>
+        <v>5000</v>
       </c>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar, 2026 / travel to Bhowanipore, Kolkata, West Bengal, India to Howrah, West Bengal, India RPA_ID : 3a89bded6e</t>
+          <t>Casual Payment 5 Nos @ 1000 ST3 GOA Deployed Local Casual Labours 27.04.2026 RPA_ID : bebc93b73f</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>DUMKA</t>
+          <t>ST3 GOA</t>
         </is>
       </c>
       <c r="Z10" t="n">
@@ -1834,15 +1750,19 @@
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr"/>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
       <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr"/>
@@ -1851,7 +1771,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WGE 195</t>
+          <t>WGE 462</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1861,7 +1781,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>26-03-2026</t>
+          <t>27-03-2026</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1897,22 +1817,22 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>SAYAN BATTACHARYA</t>
+          <t>PRANEET</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>f29b11e2-8bc4-4afe-9a4e-d16973fa0358</t>
+          <t>fca1fb7d-4d31-44ff-907a-cbcb6f6df271</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>ACC-14810110034736</t>
+          <t>ACC-095203100002750</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>UCBA0001481</t>
+          <t>SRCB00000095</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -1927,17 +1847,17 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>256</v>
+        <v>5000</v>
       </c>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Thu, 12 Mar, 2026/ travel to , Howrah, West Bengal 711101, India to Bhowanipore, Kolkata, West Bengal, India RPA_ID : 9f4ad9bcdc</t>
+          <t>Casual Payment 5 Nos @ 1000 ST3 GOA Deployed Local Casual Labours 26.04.2026 RPA_ID : cd621ffdb2</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>DUMKA</t>
+          <t>ST3 GOA</t>
         </is>
       </c>
       <c r="Z11" t="n">
@@ -1967,15 +1887,19 @@
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr"/>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
       <c r="AL11" t="inlineStr"/>
       <c r="AM11" t="inlineStr"/>
       <c r="AN11" t="inlineStr"/>
@@ -1984,7 +1908,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WGE 195</t>
+          <t xml:space="preserve"> WGG 02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1994,7 +1918,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>26-03-2026</t>
+          <t>27-03-2026</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -2028,26 +1952,14 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>SAYAN BATTACHARYA</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>bc2f0239-1cfa-4b79-88ac-25b72aa7c1a5</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>ACC-14810110034736</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>UCBA0001481</t>
-        </is>
-      </c>
+          <t>ff7de8ef-594e-45b3-acc7-eacb3da08c66</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
@@ -2060,17 +1972,17 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>196</v>
+        <v>290000</v>
       </c>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar, 2026/travel to Behala, Kolkata, West Bengal, India to Bhowanipore, Kolkata, West Bengal, India RPA_ID : 6f6349e329</t>
+          <t>AUGUST PF ARREAR KOCHI AND KONGAN APPROXIMATE RPA_ID : 2508629473</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>DUMKA</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="Z12" t="n">
@@ -2098,16 +2010,8 @@
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr"/>
       <c r="AM12" t="inlineStr"/>
@@ -2127,7 +2031,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>26-03-2026</t>
+          <t>27-03-2026</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -2168,7 +2072,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>72482b03-4829-424e-bbd4-e635d894b1c2</t>
+          <t>23b5bf13-ce2a-4336-a4d6-08d7741a6702</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -2193,12 +2097,12 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Mon, 23 Mar, 2026/ travel to Bhowanipore, Kolkata, West Bengal, India to Howrah, West Bengal, India RPA_ID : 377b6a8fe9</t>
+          <t>Sun, 01 Mar, 2026 / travel Howrah, West Bengal 711101, India to Bhowanipore, Kolkata, West Bengal, India RPA_ID : 0a371d9b02</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2231,16 +2135,8 @@
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
       <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="inlineStr"/>
       <c r="AM13" t="inlineStr"/>
@@ -2260,7 +2156,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>26-03-2026</t>
+          <t>27-03-2026</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -2301,7 +2197,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>58ed1edc-8cbc-4cd9-ba88-77e278d2a0e7</t>
+          <t>6a834274-aad7-449b-8baa-80180b6b10c4</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -2326,12 +2222,12 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Fri, 20 Mar, 2026 / travel to Bhowanipore, Kolkata, West Bengal, India to Howrah, West Bengal, India RPA_ID : 5da98d81ae</t>
+          <t>Sun, 08 Mar, 2026 / travel to Howrah, West Bengal 711101, India to Bhowanipore, Kolkata, West Bengal, India RPA_ID : abb6395ee2</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2364,16 +2260,8 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
       <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="inlineStr"/>
       <c r="AM14" t="inlineStr"/>
@@ -2393,7 +2281,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>26-03-2026</t>
+          <t>27-03-2026</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -2434,7 +2322,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>5d3f6a53-c3d1-4e81-aa48-7b67b7beeb6e</t>
+          <t>fae9de6f-fb2d-4c03-9eca-81dd642dd63a</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2459,12 +2347,12 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>400</v>
+        <v>199</v>
       </c>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Food for inspector (VCS) for Bill submission ( dumka) RPA_ID : 5a45f667eb</t>
+          <t>Wed, 11 Mar, 2026 / travel to Bhowanipore, Kolkata, West Bengal, India to Howrah, West Bengal, India RPA_ID : 8d4d760a1b</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2497,16 +2385,8 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
       <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="inlineStr"/>
       <c r="AM15" t="inlineStr"/>
@@ -2526,7 +2406,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>26-03-2026</t>
+          <t>27-03-2026</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -2567,7 +2447,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>c714ab46-bd7b-4cde-bd40-7b5dbf8b3b60</t>
+          <t>cfdebe7e-aac8-4b69-9674-b4dbde999ed0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2592,12 +2472,12 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>1000</v>
+        <v>256</v>
       </c>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Car expenses( only diesel) from Asansol to Jamtara and back from asansol with inspection accompanied for bill submission RPA_ID : b6c31887cd</t>
+          <t>Thu, 12 Mar, 2026/ travel to , Howrah, West Bengal 711101, India to Bhowanipore, Kolkata, West Bengal, India RPA_ID : ab614533ca</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2630,16 +2510,8 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
       <c r="AK16" t="inlineStr"/>
       <c r="AL16" t="inlineStr"/>
       <c r="AM16" t="inlineStr"/>
@@ -2659,7 +2531,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>26-03-2026</t>
+          <t>27-03-2026</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -2700,7 +2572,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1ef0abff-c779-437d-809e-7fe8b0687a6f</t>
+          <t>a81fcf64-4e04-4f6f-a291-cdaacf67be01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2725,12 +2597,12 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>168</v>
+        <v>196</v>
       </c>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
-          <t>train ticket for asanol to howrah for bill submission RPA_ID : 0abff50fa5</t>
+          <t>Wed, 18 Mar, 2026/travel to Behala, Kolkata, West Bengal, India to Bhowanipore, Kolkata, West Bengal, India RPA_ID : 54f3e6eb6d</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2763,16 +2635,8 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
       <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="inlineStr"/>
       <c r="AM17" t="inlineStr"/>
@@ -2792,7 +2656,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>26-03-2026</t>
+          <t>27-03-2026</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2833,7 +2697,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>c2ef46a4-79b5-41fe-9563-3926cb433f8c</t>
+          <t>2bcb6df8-c94e-42b5-901e-37e90f5d520f</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2858,17 +2722,17 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>450</v>
+        <v>214</v>
       </c>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
-          <t>PRINTER REPAIR CHARGE FOR KOLKATA OFFICE RPA_ID : 5503789d2d</t>
+          <t>Mon, 23 Mar, 2026/ travel to Bhowanipore, Kolkata, West Bengal, India to Howrah, West Bengal, India RPA_ID : a852637597</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>KOLKATA OFFICE</t>
+          <t>DUMKA</t>
         </is>
       </c>
       <c r="Z18" t="n">
@@ -2896,21 +2760,9 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>KOLKATA</t>
-        </is>
-      </c>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="inlineStr"/>
       <c r="AM18" t="inlineStr"/>
       <c r="AN18" t="inlineStr"/>
@@ -2919,7 +2771,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>WGE 593</t>
+          <t>WGE 195</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2929,7 +2781,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>26-03-2026</t>
+          <t>27-03-2026</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2965,22 +2817,22 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>ASHIQUE ALI P</t>
+          <t>SAYAN BATTACHARYA</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>d3b772db-65b3-408e-966a-97ece594d8dd</t>
+          <t>4cda1365-1660-44ab-ae1a-f57fd40dc259</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>ACC-852116310000006</t>
+          <t>ACC-14810110034736</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>BKID0008521</t>
+          <t>UCBA0001481</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
@@ -2995,17 +2847,17 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>1500</v>
+        <v>222</v>
       </c>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
-          <t>TRAVEL EXPENSES FOR KOCHI TO BELLARI ( PROJECT PLANNING COORDINATOR) 26/03/2026 RPA_ID : 7ebcf74e94</t>
+          <t>Fri, 20 Mar, 2026 / travel to Bhowanipore, Kolkata, West Bengal, India to Howrah, West Bengal, India RPA_ID : 927b82968c</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>BELLARI</t>
+          <t>DUMKA</t>
         </is>
       </c>
       <c r="Z19" t="n">
@@ -3033,21 +2885,9 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>BELLARI</t>
-        </is>
-      </c>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
       <c r="AL19" t="inlineStr"/>
       <c r="AM19" t="inlineStr"/>
       <c r="AN19" t="inlineStr"/>
@@ -3056,7 +2896,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>WGE 593</t>
+          <t>WGE 195</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3066,7 +2906,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>26-03-2026</t>
+          <t>27-03-2026</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -3102,22 +2942,22 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>ASHIQUE ALI P</t>
+          <t>SAYAN BATTACHARYA</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>d1954046-76f7-4c95-8766-189ee53890de</t>
+          <t>8c7e4852-6bcb-4b8d-9491-d867f9de7ab2</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>ACC-852116310000006</t>
+          <t>ACC-14810110034736</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>BKID0008521</t>
+          <t>UCBA0001481</t>
         </is>
       </c>
       <c r="O20" t="inlineStr"/>
@@ -3132,17 +2972,17 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>750</v>
+        <v>400</v>
       </c>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr">
         <is>
-          <t>FOOD EXPENSES ( 27/03/2026 TO 31/03/2026 ) PER DAY 150 RPA_ID : d33f365719</t>
+          <t>Food for inspector (VCS) for Bill submission ( dumka) RPA_ID : 6ff8bcbaa9</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>BELLARI</t>
+          <t>DUMKA</t>
         </is>
       </c>
       <c r="Z20" t="n">
@@ -3170,21 +3010,9 @@
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>BELLARI</t>
-        </is>
-      </c>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
       <c r="AL20" t="inlineStr"/>
       <c r="AM20" t="inlineStr"/>
       <c r="AN20" t="inlineStr"/>
@@ -3193,7 +3021,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>WGE 73</t>
+          <t>WGE 195</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3203,7 +3031,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>26-03-2026</t>
+          <t>27-03-2026</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -3219,7 +3047,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DCR</t>
+          <t>NEFT</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3239,22 +3067,22 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Nithin</t>
+          <t>SAYAN BATTACHARYA</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>4253920a-de62-4358-afc2-93d27aaa9dc5</t>
+          <t>7983366b-e1e3-4ece-8bd8-fbd49a9d8afd</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>ACC-32555551936</t>
+          <t>ACC-14810110034736</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>SBIN0001890</t>
+          <t>UCBA0001481</t>
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
@@ -3274,12 +3102,12 @@
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr">
         <is>
-          <t>CASUAL WAGE  25/03/2026 LEAVE NISHANTH( MEDICAL LEAVE ) &amp; ATHUL RAJ( MARRIAGE LEAVE) RPA_ID : 6a1da9c546</t>
+          <t>Car expenses( only diesel) from Asansol to Jamtara and back from asansol with inspection accompanied for bill submission RPA_ID : af90e5fb2b</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>HPCL ELATHUR</t>
+          <t>DUMKA</t>
         </is>
       </c>
       <c r="Z21" t="n">
@@ -3307,21 +3135,9 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>HPCL ELATHUR</t>
-        </is>
-      </c>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="inlineStr"/>
       <c r="AM21" t="inlineStr"/>
       <c r="AN21" t="inlineStr"/>
@@ -3330,7 +3146,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>WGE 73</t>
+          <t>WGE 195</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3340,7 +3156,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>26-03-2026</t>
+          <t>27-03-2026</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -3356,7 +3172,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>DCR</t>
+          <t>NEFT</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3376,22 +3192,22 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Nithin</t>
+          <t>SAYAN BATTACHARYA</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>c9cf54c7-0d83-42f4-aace-1209b558cec3</t>
+          <t>1c114c1a-4e70-4543-95f2-a036830ca2bc</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>ACC-32555551936</t>
+          <t>ACC-14810110034736</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>SBIN0001890</t>
+          <t>UCBA0001481</t>
         </is>
       </c>
       <c r="O22" t="inlineStr"/>
@@ -3406,17 +3222,17 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>1000</v>
+        <v>168</v>
       </c>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr">
         <is>
-          <t>CASUAL WAGE  26/03/2026 LEAVE NISHANTH &amp; ATHUL RAJ RPA_ID : 11a13a4f3d</t>
+          <t>train ticket for asanol to howrah for bill submission RPA_ID : 2a18737879</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>HPCL ELATHUR</t>
+          <t>DUMKA</t>
         </is>
       </c>
       <c r="Z22" t="n">
@@ -3444,21 +3260,9 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr"/>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>HPCL ELATHUR</t>
-        </is>
-      </c>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
       <c r="AL22" t="inlineStr"/>
       <c r="AM22" t="inlineStr"/>
       <c r="AN22" t="inlineStr"/>
@@ -3467,7 +3271,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>WGE 594</t>
+          <t>WGE 195</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3477,7 +3281,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>26-03-2026</t>
+          <t>27-03-2026</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -3493,7 +3297,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DCR</t>
+          <t>NEFT</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3513,22 +3317,22 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>ANIL KUMAR P P</t>
+          <t>SAYAN BATTACHARYA</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>3cad723e-8552-4c3c-a934-13cde12c11ee</t>
+          <t>623b8105-4d5c-4c36-a3ef-75cba4e12a1c</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>ACC- 20075235595</t>
+          <t>ACC-14810110034736</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>SBIN0012877</t>
+          <t>UCBA0001481</t>
         </is>
       </c>
       <c r="O23" t="inlineStr"/>
@@ -3543,17 +3347,17 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>11000</v>
+        <v>450</v>
       </c>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr">
         <is>
-          <t>PAPPANASHERI ROOM RENT  FEBRUARY 2026 ( ADVANCE  DEPOSIT 11000) RPA_ID : b0b5085517</t>
+          <t>PRINTER REPAIR CHARGE FOR KOLKATA OFFICE RPA_ID : 38ac875587</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>PAPPANASHERI</t>
+          <t>KOLKATA OFFICE</t>
         </is>
       </c>
       <c r="Z23" t="n">
@@ -3581,17 +3385,13 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>KOLKATA</t>
+        </is>
+      </c>
       <c r="AL23" t="inlineStr"/>
       <c r="AM23" t="inlineStr"/>
       <c r="AN23" t="inlineStr"/>
@@ -3600,7 +3400,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>WGE 105</t>
+          <t>WGE 593</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3610,7 +3410,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>26-03-2026</t>
+          <t>27-03-2026</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -3626,7 +3426,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>DCR</t>
+          <t>NEFT</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3646,22 +3446,22 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>RUMJAN ALI</t>
+          <t>ASHIQUE ALI P</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2bedafb7-bc38-488d-9cef-f96418433968</t>
+          <t>56a9ea40-62f0-4208-822a-fe4b99bc9ce4</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>ACC-35361930366</t>
+          <t>ACC-852116310000006</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>SBIN0014087</t>
+          <t>BKID0008521</t>
         </is>
       </c>
       <c r="O24" t="inlineStr"/>
@@ -3676,17 +3476,17 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>5000</v>
+        <v>1500</v>
       </c>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr">
         <is>
-          <t>KOLKATA TO GOA 5 CARPENTERS FOR ONGC IPSHEM FOOD  EXPENSES  &amp; TRAVEL EXPENSES FOR 2 DAYS ( 5 WORKERS)   TOTAL 5000 APPROVED BY HISHAM SIR RPA_ID : ec8bfd64f2</t>
+          <t>TRAVEL EXPENSES FOR KOCHI TO BELLARI ( PROJECT PLANNING COORDINATOR) 26/03/2026 RPA_ID : ad47503d9d</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>ONGC IPSHEM</t>
+          <t>BELLARI</t>
         </is>
       </c>
       <c r="Z24" t="n">
@@ -3716,17 +3516,17 @@
       <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>PAID</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>PAID</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>ONGC IPSHEM</t>
+          <t>BELLARI</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr"/>
@@ -3737,7 +3537,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>WGE 306</t>
+          <t>WGE 593</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3747,7 +3547,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>26-03-2026</t>
+          <t>27-03-2026</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -3783,22 +3583,22 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>SABIN V V</t>
+          <t>ASHIQUE ALI P</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>69a9a5eb-93c4-45ac-81ee-34c6f27c02c8</t>
+          <t>d8801dd2-8690-43fa-9973-c8b43e3d1634</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>ACC-67274681749</t>
+          <t>ACC-852116310000006</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>SBIN0070812</t>
+          <t>BKID0008521</t>
         </is>
       </c>
       <c r="O25" t="inlineStr"/>
@@ -3813,17 +3613,17 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>3300</v>
+        <v>750</v>
       </c>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr">
         <is>
-          <t>L &amp; T CHENNAI  ROOM  STAY EXPENSES  ( 26/03/2026 TO 28/03/2026)  PER DAY 1100 / Room stay till 23/03/2026 has already been paid RPA_ID : b29f95944d</t>
+          <t>FOOD EXPENSES ( 27/03/2026 TO 31/03/2026 ) PER DAY 150 RPA_ID : e287c8edd9</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>L &amp; T CHENNAI</t>
+          <t>BELLARI</t>
         </is>
       </c>
       <c r="Z25" t="n">
@@ -3853,15 +3653,19 @@
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr"/>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
       <c r="AL25" t="inlineStr"/>
       <c r="AM25" t="inlineStr"/>
       <c r="AN25" t="inlineStr"/>
@@ -3870,7 +3674,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>WGE 323</t>
+          <t>WGE 73</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3880,7 +3684,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>26-03-2026</t>
+          <t>27-03-2026</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -3896,7 +3700,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>NEFT</t>
+          <t>DCR</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3916,22 +3720,22 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>VINITHA V NAIR</t>
+          <t>Nithin</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>dbd5e10a-67ca-4c80-8474-33eb4c103425</t>
+          <t>aa33b805-2ff3-48ef-924d-a6a4c5312be1</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>ACC-22020100013715</t>
+          <t>ACC-32555551936</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>FDRL0002202</t>
+          <t>SBIN0001890</t>
         </is>
       </c>
       <c r="O26" t="inlineStr"/>
@@ -3946,27 +3750,25 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>4000</v>
+        <v>1000</v>
       </c>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Daily Site Labour Charges-for 4 labours RPA_ID : ed8f362c50</t>
+          <t>CASUAL WAGE  25/03/2026 LEAVE NISHANTH( MEDICAL LEAVE ) &amp; ATHUL RAJ( MARRIAGE LEAVE) RPA_ID : a184b5949d</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>Construction of IOCL RO at Pappinissery</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>LABOUR CHARGES</t>
-        </is>
+          <t>HPCL ELATHUR</t>
+        </is>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>executive.westerntender@gmail.com</t>
+          <t>hrm@westernidc.com</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -3996,7 +3798,11 @@
           <t>ACCEPTED</t>
         </is>
       </c>
-      <c r="AK26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>HPCL ELATHUR</t>
+        </is>
+      </c>
       <c r="AL26" t="inlineStr"/>
       <c r="AM26" t="inlineStr"/>
       <c r="AN26" t="inlineStr"/>
@@ -4005,7 +3811,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WGG 02</t>
+          <t>WGE 73</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4015,7 +3821,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>26-03-2026</t>
+          <t>27-03-2026</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -4031,7 +3837,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>NEFT</t>
+          <t>DCR</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -4049,14 +3855,26 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Nithin</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>39348140-ef38-4fbd-bddc-13235d55301f</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>a3567c23-81a6-4979-8d75-09912815c2be</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>ACC-32555551936</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>SBIN0001890</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
@@ -4069,27 +3887,25 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>79930</v>
+        <v>1000</v>
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Pep consultancy pendiing payment RPA_ID : 2b00207380</t>
+          <t>CASUAL WAGE  26/03/2026 LEAVE NISHANTH &amp; ATHUL RAJ RPA_ID : f40d4082bd</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>Cochin</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>PAYMENT</t>
-        </is>
+          <t>HPCL ELATHUR</t>
+        </is>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>Payments@westernidc.com</t>
+          <t>hrm@westernidc.com</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -4109,9 +3925,21 @@
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr"/>
-      <c r="AI27" t="inlineStr"/>
-      <c r="AJ27" t="inlineStr"/>
-      <c r="AK27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>HPCL ELATHUR</t>
+        </is>
+      </c>
       <c r="AL27" t="inlineStr"/>
       <c r="AM27" t="inlineStr"/>
       <c r="AN27" t="inlineStr"/>
@@ -4120,7 +3948,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WGG 02</t>
+          <t>WGE 594</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4130,7 +3958,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>26-03-2026</t>
+          <t>27-03-2026</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -4146,7 +3974,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>NEFT</t>
+          <t>DCR</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -4164,14 +3992,26 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>ANIL KUMAR P P</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>ff529cd2-01b5-491b-ae2f-c8908174cdf1</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>9aed2b2e-4e60-43d4-b29a-925ca85c7ddc</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>ACC- 20075235595</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>SBIN0012877</t>
+        </is>
+      </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
@@ -4184,27 +4024,25 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>50000</v>
+        <v>11000</v>
       </c>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Payment as per the instraction of Sreekumar Sir RPA_ID : 43735a8e39</t>
+          <t>PAPPANASHERI ROOM RENT  FEBRUARY 2026 ( ADVANCE  DEPOSIT 11000) RPA_ID : 32fc90703b</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>Cochin</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>PAYMENT</t>
-        </is>
+          <t>PAPPANASHERI</t>
+        </is>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Payments@westernidc.com</t>
+          <t>hrm@westernidc.com</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -4235,7 +4073,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>WGE 597</t>
+          <t>WGE 306</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4245,7 +4083,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>26-03-2026</t>
+          <t>27-03-2026</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -4281,22 +4119,22 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Shree Krishna Steels &amp; Water Services</t>
+          <t>SABIN V V</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>68393174-0d18-45cc-bf26-a55e000f3cd1</t>
+          <t>4093ddb6-4436-4c8b-b2d4-3f61f2720e57</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>ACC-278705000855</t>
+          <t>ACC-67274681749</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>ICIC0002787</t>
+          <t>SBIN0070812</t>
         </is>
       </c>
       <c r="O29" t="inlineStr"/>
@@ -4311,29 +4149,25 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>73900</v>
+        <v>240</v>
       </c>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Providing team for Survey of Damaged Vessel 
-Samudra Shiksha ONGC Training Vessel at Betul 
-Goa RPA_ID : 8f2ec28874</t>
+          <t>TRAVEL EXPENSES ( 26/03/2026 TO 28/03/2026 ) PER DAY 80 /- / TRAVEL EXP TILL DATE 25/03/2026 IS PAID ALREADY RPA_ID : ff1c4810ec</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>ONGC Jetty project</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>SURVEY</t>
-        </is>
+          <t>L &amp; T CHENNAI</t>
+        </is>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>executive.westerntender@gmail.com</t>
+          <t>hrm@westernidc.com</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -4353,14 +4187,4853 @@
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="inlineStr"/>
-      <c r="AI29" t="inlineStr"/>
-      <c r="AJ29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
       <c r="AK29" t="inlineStr"/>
       <c r="AL29" t="inlineStr"/>
       <c r="AM29" t="inlineStr"/>
       <c r="AN29" t="inlineStr"/>
       <c r="AO29" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>WGE 306</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>SABIN V V</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>aeec2e47-3824-4c5e-b633-0fb24de2f6c0</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>ACC-67274681749</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>SBIN0070812</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>3300</v>
+      </c>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>L &amp; T CHENNAI  ROOM  STAY EXPENSES  ( 26/03/2026 TO 28/03/2026)  PER DAY 1100 / Room stay till 23/03/2026 has already been paid RPA_ID : 58e3151ea7</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>L &amp; T CHENNAI</t>
+        </is>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>WGE 299</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>ARJUN(ONGC) SUPERVISOR</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>c345f74b-6559-4b95-a812-519a1206a7c4</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>ACC-67329839060</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>SBIN0070076</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>4800</v>
+      </c>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>( MATRIAL PURCHASING ROOM STAY UP TO 23RD ALREADY PAID BALANCE TO BE PAID ( 24/03/2026 TO 27/03/2026) PER DAY 1200 RPA_ID : eb054552a2</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>ONGC IPSHEM</t>
+        </is>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>ONGC IPSHEM</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>WGE 93</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Sidharth</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>fead12f0-9f77-4c4a-b45f-56ca8435a65d</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>ACC-50100505122601</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>HDFC0004779</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>3500</v>
+      </c>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>sidharth &amp; Thameem ( new joinee ) Travel expenses Kochi to gsl goa 1500   &amp; food  expenses  (  27/03/2026 to 31/03/2026) perd day 200 sidharth  = 1000 / Thameem = 1000 RPA_ID : b0ced34d42</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>GSL HULL</t>
+        </is>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>WGE 132</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>United India Insurance</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>0c1d9d82-ff0e-4927-9eda-f0aa71ab33d0</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>ACC-200999095210100100</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>INDB0000007</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>7490</v>
+      </c>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Munna &amp; Shamsuzzaman( 2  workers )  workmen compensation  for grse kolkata for 6 month RPA_ID : d7539ca40e</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>GRSE KOLKATA</t>
+        </is>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>KOLKATA</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>WGE 601</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>BABI NAYAK ( CASUAL 1)</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>9faaffe6-df31-46d0-9439-6880295e23c2</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>ACC- 36885053323</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>24/03/2026  ( CASUAL WAGE )  LEAVE  ANEESH V A / SAFAL  PER DAY 1000 / delay in this payment request. At the time of the request, we had informed the supervisor that payment would be made only to the respective accounts.  So We received the account details only yesterday; hence, the email is being sent today. RPA_ID : 70878f5d60</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>IOCL WELLINGTON</t>
+        </is>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr"/>
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="inlineStr"/>
+      <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>WGE 602</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>SALMAN NAYAK ( CASUAL 2)</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>3e6b0c08-03b5-444c-a417-31de9ce15c76</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>ACC- 041010025016</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>24/03/2026  ( CASUAL WAGE )  LEAVE  ANEESH V A / SAFAL  PER DAY 1000 / delay in this payment request. At the time of the request, we had informed the supervisor that payment would be made only to the respective accounts.  So We received the account details only yesterday; hence, the email is being sent today. RPA_ID : 85ab5f8d16</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>IOCL WELLINGTON</t>
+        </is>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr"/>
+      <c r="AL35" t="inlineStr"/>
+      <c r="AM35" t="inlineStr"/>
+      <c r="AN35" t="inlineStr"/>
+      <c r="AO35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>WGE 603</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOHAMMED MANSOOR </t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>3a2ce0f5-53b2-4ab5-9e93-0a66041820f2</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>ACC-10880100006045</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V36" t="n">
+        <v>6060</v>
+      </c>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>This payment pertains to hotel expenses incurred during work at ONGC. Food was provided to five Rumjan team workers as well as other workers.
+The payment for these expenses has not yet been made. The attached document includes ₹4,070 towards the food expenses of the Rumjan team workers. It also covers the food expenses of other workers who were working at ONGC , In march  food had to be arranged due to the unavailability of gas and the workers being unable to cook at that time.
+ this amount is payable to the hotel. RPA_ID : 7e86f4a0d1</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>ONGC IPSHEM</t>
+        </is>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr"/>
+      <c r="AJ36" t="inlineStr"/>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>ONGC IPSHEM</t>
+        </is>
+      </c>
+      <c r="AL36" t="inlineStr"/>
+      <c r="AM36" t="inlineStr"/>
+      <c r="AN36" t="inlineStr"/>
+      <c r="AO36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>WGE 294</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>SHIBIN KUMAR</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>29d0a922-f68d-4e0f-b2f4-efc752b57675</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>ACC-30653126245</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>SBIN0005047</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V37" t="n">
+        <v>4482</v>
+      </c>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Reimbursement for L&amp;T Chennai and Palakkad site visit. An amount of ₹7,000 has already been paid, and the balance amount of ₹4,482 is pending for reimbursement.
+All relevant expense details are attached to this email RPA_ID : f53fed4e62</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>L &amp; T CHENNAI</t>
+        </is>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr"/>
+      <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="inlineStr"/>
+      <c r="AN37" t="inlineStr"/>
+      <c r="AO37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>WGE 169</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>ANJU MS</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>bc4ff6ad-56cf-4005-8670-fa902655f9ab</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>ACC-345002010013320</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>UBIN0534501</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V38" t="n">
+        <v>2928</v>
+      </c>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>The gas expenses for the Mumbai flat  transferred to Anju’s account, she will settle the payment RPA_ID : f91397ab8a</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>mumbai</t>
+        </is>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr"/>
+      <c r="AL38" t="inlineStr"/>
+      <c r="AM38" t="inlineStr"/>
+      <c r="AN38" t="inlineStr"/>
+      <c r="AO38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>WGE 220</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>ANDRIYA THOMAS</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>3811ed05-7769-4b45-b71c-1f0e1529107b</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>ACC-0706101053789</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>CNRB0000706</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V39" t="n">
+        <v>370</v>
+      </c>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Travel expense (morning) kadavantra to vadakekotta ,(Evening) vadakekotta to kadavantra -- auto petta to flat RPA_ID : b852bdeb92</t>
+        </is>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>REIMBURSEMENT</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>misexecutivewgc@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr"/>
+      <c r="AJ39" t="inlineStr"/>
+      <c r="AK39" t="inlineStr"/>
+      <c r="AL39" t="inlineStr"/>
+      <c r="AM39" t="inlineStr"/>
+      <c r="AN39" t="inlineStr"/>
+      <c r="AO39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>WGE 220</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>ANDRIYA THOMAS</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>211e1911-fc43-4837-b376-2072480111f9</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>ACC-0706101053789</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>CNRB0000706</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V40" t="n">
+        <v>669</v>
+      </c>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>smart marine RPA_ID : 753c08670f</t>
+        </is>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>REIMBURSEMENT</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>misexecutivewgc@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr"/>
+      <c r="AJ40" t="inlineStr"/>
+      <c r="AK40" t="inlineStr"/>
+      <c r="AL40" t="inlineStr"/>
+      <c r="AM40" t="inlineStr"/>
+      <c r="AN40" t="inlineStr"/>
+      <c r="AO40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>WGE 429</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>SAFNA</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>30d957c6-df99-434f-b7af-f16087a8aad5</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>ACC- 111001504967</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>ICIC0001110</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V41" t="n">
+        <v>1331</v>
+      </c>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Electrician work - front office and washrom RPA_ID : 50b90e0f94</t>
+        </is>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>REIMBURSEMENT</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>misexecutivewgc@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr"/>
+      <c r="AJ41" t="inlineStr"/>
+      <c r="AK41" t="inlineStr"/>
+      <c r="AL41" t="inlineStr"/>
+      <c r="AM41" t="inlineStr"/>
+      <c r="AN41" t="inlineStr"/>
+      <c r="AO41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>WGE 429</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>SAFNA</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>16808aa9-5ec5-4812-b90a-17868e3ee212</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>ACC- 111001504967</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>ICIC0001110</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V42" t="n">
+        <v>200</v>
+      </c>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Akshaya for tax renewal RPA_ID : 105f9f18fb</t>
+        </is>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>REIMBURSEMENT</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>misexecutivewgc@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr"/>
+      <c r="AJ42" t="inlineStr"/>
+      <c r="AK42" t="inlineStr"/>
+      <c r="AL42" t="inlineStr"/>
+      <c r="AM42" t="inlineStr"/>
+      <c r="AN42" t="inlineStr"/>
+      <c r="AO42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>WGE 429</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>SAFNA</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>7884dcd8-d051-4b7d-95b2-748f36e90869</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>ACC- 111001504967</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>ICIC0001110</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V43" t="n">
+        <v>267</v>
+      </c>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>GARBAGE FOR KITCHEN ( EXTRALARGE &amp; SMALL) RPA_ID : 4ad7f2d7a8</t>
+        </is>
+      </c>
+      <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>misexecutivewgc@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr"/>
+      <c r="AJ43" t="inlineStr"/>
+      <c r="AK43" t="inlineStr"/>
+      <c r="AL43" t="inlineStr"/>
+      <c r="AM43" t="inlineStr"/>
+      <c r="AN43" t="inlineStr"/>
+      <c r="AO43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> WGG 02</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>ed274e86-6352-4dcc-ab84-5798e842d0c4</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>0 RPA_ID : de534fb495</t>
+        </is>
+      </c>
+      <c r="Y44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>misexecutivewgc@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr"/>
+      <c r="AJ44" t="inlineStr"/>
+      <c r="AK44" t="inlineStr"/>
+      <c r="AL44" t="inlineStr"/>
+      <c r="AM44" t="inlineStr"/>
+      <c r="AN44" t="inlineStr"/>
+      <c r="AO44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>WGE 429</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>SAFNA</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>7deb5f3f-8fa6-4e40-a1bf-329364ff7a44</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>ACC- 111001504967</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>ICIC0001110</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V45" t="n">
+        <v>300</v>
+      </c>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>AVIATOR PETROL PAID BY SAFNA RPA_ID : bfd3e6292f</t>
+        </is>
+      </c>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>REIMBURSEMENT</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>misexecutivewgc@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr"/>
+      <c r="AI45" t="inlineStr"/>
+      <c r="AJ45" t="inlineStr"/>
+      <c r="AK45" t="inlineStr"/>
+      <c r="AL45" t="inlineStr"/>
+      <c r="AM45" t="inlineStr"/>
+      <c r="AN45" t="inlineStr"/>
+      <c r="AO45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>WGE 428</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>NAIJAL driver</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>7c58192c-c07b-4407-b496-b623efc120db</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>ACC-13962100139241</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>FDRL0001396</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V46" t="n">
+        <v>20</v>
+      </c>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>For air in car (tyre) RPA_ID : 42abfdf3ca</t>
+        </is>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>REIMBURSEMENT</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>misexecutivewgc@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr"/>
+      <c r="AJ46" t="inlineStr"/>
+      <c r="AK46" t="inlineStr"/>
+      <c r="AL46" t="inlineStr"/>
+      <c r="AM46" t="inlineStr"/>
+      <c r="AN46" t="inlineStr"/>
+      <c r="AO46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>WGE 428</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>NAIJAL driver</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>977eb545-f2f1-4531-9a20-b964ea13f2bb</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>ACC-13962100139241</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>FDRL0001396</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V47" t="n">
+        <v>90</v>
+      </c>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Stampaper 3190 total amount - shanu mam gives only 3100(90 rs paid by naijal RPA_ID : 250bea4667</t>
+        </is>
+      </c>
+      <c r="Y47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>REIMBURSEMENT</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>misexecutivewgc@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr"/>
+      <c r="AJ47" t="inlineStr"/>
+      <c r="AK47" t="inlineStr"/>
+      <c r="AL47" t="inlineStr"/>
+      <c r="AM47" t="inlineStr"/>
+      <c r="AN47" t="inlineStr"/>
+      <c r="AO47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>WGE 429</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>SAFNA</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>370d6a01-d160-4e93-8499-e12262fe7636</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>ACC- 111001504967</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>ICIC0001110</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V48" t="n">
+        <v>126</v>
+      </c>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>COFFEE POWDER (BRU instant coffee) 40g RPA_ID : 98670509a4</t>
+        </is>
+      </c>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>misexecutivewgc@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr"/>
+      <c r="AI48" t="inlineStr"/>
+      <c r="AJ48" t="inlineStr"/>
+      <c r="AK48" t="inlineStr"/>
+      <c r="AL48" t="inlineStr"/>
+      <c r="AM48" t="inlineStr"/>
+      <c r="AN48" t="inlineStr"/>
+      <c r="AO48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>WGE 322</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>MOHAMMED SARFARAS</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>81e9abaa-0aec-46c1-93fc-a605569f3e84</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>ACC-67373357798</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>SBIN0010116</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V49" t="n">
+        <v>4000</v>
+      </c>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>BREEZA PETROL RPA_ID : c586c5d319</t>
+        </is>
+      </c>
+      <c r="Y49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>misexecutivewgc@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr"/>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr"/>
+      <c r="AL49" t="inlineStr"/>
+      <c r="AM49" t="inlineStr"/>
+      <c r="AN49" t="inlineStr"/>
+      <c r="AO49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>WGE 90</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Roslin Neenu</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>966fe2f2-b498-4a34-9175-f9be7599dece</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>ACC-520291000298651</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>UBIN0919748</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V50" t="n">
+        <v>420</v>
+      </c>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>MILK (15 PACKET- 23-03-2026 to 27-03-2026 ) (Monday to Friday) RPA_ID : de24579c26</t>
+        </is>
+      </c>
+      <c r="Y50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>REIMBURSEMENT</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>misexecutivewgc@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr"/>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr"/>
+      <c r="AL50" t="inlineStr"/>
+      <c r="AM50" t="inlineStr"/>
+      <c r="AN50" t="inlineStr"/>
+      <c r="AO50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> WGG 02</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>b13af118-e687-40b7-9aff-bc2794939cd5</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V51" t="n">
+        <v>76700</v>
+      </c>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Being rental service for crane(A/C NO:-01692560001256 IFSC :-HDFC0000169) (19-03-2026) RPA_ID : 53fe49e5bc</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>ONGC JETTY</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>procexewestern@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr"/>
+      <c r="AI51" t="inlineStr"/>
+      <c r="AJ51" t="inlineStr"/>
+      <c r="AK51" t="inlineStr"/>
+      <c r="AL51" t="inlineStr"/>
+      <c r="AM51" t="inlineStr"/>
+      <c r="AN51" t="inlineStr"/>
+      <c r="AO51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> WGG 02</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>25c62775-477d-400d-80b9-03c72ca8b75f</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V52" t="n">
+        <v>93150</v>
+      </c>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Being GSTR1 - Return amount (19-03-2026) RPA_ID : 97e61d84d1</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>ONGC JETTY</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>procexewestern@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr"/>
+      <c r="AL52" t="inlineStr"/>
+      <c r="AM52" t="inlineStr"/>
+      <c r="AN52" t="inlineStr"/>
+      <c r="AO52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> WGG 02</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>559f626d-20f2-43cc-b8a2-f3d71cee045b</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V53" t="n">
+        <v>24741</v>
+      </c>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Plesae return the GSTR1  amount to the vendor (19-03-2026) RPA_ID : 8249315d27</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>BPCL BALLARI</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>procexewestern@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="inlineStr"/>
+      <c r="AH53" t="inlineStr"/>
+      <c r="AI53" t="inlineStr"/>
+      <c r="AJ53" t="inlineStr"/>
+      <c r="AK53" t="inlineStr"/>
+      <c r="AL53" t="inlineStr"/>
+      <c r="AM53" t="inlineStr"/>
+      <c r="AN53" t="inlineStr"/>
+      <c r="AO53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> WGG 02</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>592839e1-209b-4d24-b785-c82ada4fb9a9</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V54" t="n">
+        <v>60000</v>
+      </c>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Being hot work channel welding work (19-03-2026) RPA_ID : f7850f8c40</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>NGOP CHENNAI</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>procexewestern@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="inlineStr"/>
+      <c r="AH54" t="inlineStr"/>
+      <c r="AI54" t="inlineStr"/>
+      <c r="AJ54" t="inlineStr"/>
+      <c r="AK54" t="inlineStr"/>
+      <c r="AL54" t="inlineStr"/>
+      <c r="AM54" t="inlineStr"/>
+      <c r="AN54" t="inlineStr"/>
+      <c r="AO54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> WGG 02</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>b021f686-e6cb-43a0-87e6-c678989ebc1b</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V55" t="n">
+        <v>149877.6</v>
+      </c>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Being rent for JCB ,Hydra,Braker and farrana crane( total 324877.6  ,90000 paid on 20-03-2026 balance amount remaining (19-03-2026) RPA_ID : 01ab697598</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>BPCL BALLARI</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>procexewestern@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="inlineStr"/>
+      <c r="AH55" t="inlineStr"/>
+      <c r="AI55" t="inlineStr"/>
+      <c r="AJ55" t="inlineStr"/>
+      <c r="AK55" t="inlineStr"/>
+      <c r="AL55" t="inlineStr"/>
+      <c r="AM55" t="inlineStr"/>
+      <c r="AN55" t="inlineStr"/>
+      <c r="AO55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> WGG 02</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>44276cbb-68e1-416a-bf43-ff8499effeb8</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V56" t="n">
+        <v>22200</v>
+      </c>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Being rental for two water pumps (26/02/26 to 12/03/26 =15 days X 600=9000, Pump (sub) (10 days X 600=6000)
+(13/02/26 to 18/03/26 =6 days X 600=3600, Pump (sub) (6 days X 600=3600) -(A/C NO:- 57025596625 IFSC :-SBIN0070202)
+(21-03-2026) RPA_ID : 4361d81e9e</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>IOCL PAPPINISSERI</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>procexewestern@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="inlineStr"/>
+      <c r="AH56" t="inlineStr"/>
+      <c r="AI56" t="inlineStr"/>
+      <c r="AJ56" t="inlineStr"/>
+      <c r="AK56" t="inlineStr"/>
+      <c r="AL56" t="inlineStr"/>
+      <c r="AM56" t="inlineStr"/>
+      <c r="AN56" t="inlineStr"/>
+      <c r="AO56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> WGG 02</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>da37c663-88af-4b34-bf49-f285cc4ce06c</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V57" t="n">
+        <v>8100</v>
+      </c>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Being rental of grasscutting machine and petrol expenses (A/C NO:-  32555551936 ,IFSC :- SBIN0001890)
+(23-03-2026) RPA_ID : e2e574156f</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>HPCL ELATHOOR</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>procexewestern@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="inlineStr"/>
+      <c r="AH57" t="inlineStr"/>
+      <c r="AI57" t="inlineStr"/>
+      <c r="AJ57" t="inlineStr"/>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="AL57" t="inlineStr"/>
+      <c r="AM57" t="inlineStr"/>
+      <c r="AN57" t="inlineStr"/>
+      <c r="AO57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>WGE 598</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Tulujabhavani Earth Movers</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>0913e762-3179-4141-95ba-05a52b744c49</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>ACC-0537101034095</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>CNRB0000537</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V58" t="n">
+        <v>38000</v>
+      </c>
+      <c r="W58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Being rental of tractor and trolley  (A/C NO :- 0537101034095 IFSC :-CNRB0000537) RPA_ID : 1f14fc198b</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>BPCL BALLARI</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>procexewestern@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="inlineStr"/>
+      <c r="AH58" t="inlineStr"/>
+      <c r="AI58" t="inlineStr"/>
+      <c r="AJ58" t="inlineStr"/>
+      <c r="AK58" t="inlineStr"/>
+      <c r="AL58" t="inlineStr"/>
+      <c r="AM58" t="inlineStr"/>
+      <c r="AN58" t="inlineStr"/>
+      <c r="AO58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>WGE 599</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>KULAVENDRA (SKS MACHINERY )</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>4aaab65b-1b1c-40f9-b8e8-9a9aff8caad2</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>ACC-03490200000489</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>BARB0KRISHN</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V59" t="n">
+        <v>363850</v>
+      </c>
+      <c r="W59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Being purchasIng of ladder (03490200000489 IFSC :- BARB0KRISHN) 
+50 % ADVANCE ALREADY PROCESSED ,TOTAL AMOUNT 7,27,700) BALANCE AMOUNT REMAINING  VERY URGENT RPA_ID : ca8d2fe79a</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>ONGC IPSHEM</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>procexewestern@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="inlineStr"/>
+      <c r="AH59" t="inlineStr"/>
+      <c r="AI59" t="inlineStr"/>
+      <c r="AJ59" t="inlineStr"/>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>ONGC IPSHEM</t>
+        </is>
+      </c>
+      <c r="AL59" t="inlineStr"/>
+      <c r="AM59" t="inlineStr"/>
+      <c r="AN59" t="inlineStr"/>
+      <c r="AO59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>WGE 582</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>ST FRANCIS DE SALES PRESS</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>230fb38e-21dc-49ac-9a10-85b806621442</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>ACC-05102530000015</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>HDFC0000510</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V60" t="n">
+        <v>564</v>
+      </c>
+      <c r="W60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Being purchasing of luxor roller ball pen LX MAX 60,Register RLD ,Munix scissors  (A/C NO:- 05102530000015 ,IFSC :- HDFC0000510) RPA_ID : f8c24c0374</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>HEAD OFFICE -WESTERN</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>HO EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>procexewestern@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="inlineStr"/>
+      <c r="AH60" t="inlineStr"/>
+      <c r="AI60" t="inlineStr"/>
+      <c r="AJ60" t="inlineStr"/>
+      <c r="AK60" t="inlineStr"/>
+      <c r="AL60" t="inlineStr"/>
+      <c r="AM60" t="inlineStr"/>
+      <c r="AN60" t="inlineStr"/>
+      <c r="AO60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>WGE 469</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VISHNU HO </t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>bd036f85-1932-4d78-8a92-3096cd9847a7</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>ACC-20395308367</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>SBIN0017034</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V61" t="n">
+        <v>110</v>
+      </c>
+      <c r="W61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Fuel reimbursement (26/03/26) (A/C NO:- 20395308367 IFSC :-SBIN0017034) RPA_ID : 17b0038203</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>HEAD OFFICE -WESTERN</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>HO EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>procexewestern@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
+      <c r="AH61" t="inlineStr"/>
+      <c r="AI61" t="inlineStr"/>
+      <c r="AJ61" t="inlineStr"/>
+      <c r="AK61" t="inlineStr"/>
+      <c r="AL61" t="inlineStr"/>
+      <c r="AM61" t="inlineStr"/>
+      <c r="AN61" t="inlineStr"/>
+      <c r="AO61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>WGE 600</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>SHARUN EARTH MOVERS</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>002f22c8-52fb-4bb2-b823-d02b007c4beb</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>40422100006913</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>KLGB0040422</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V62" t="n">
+        <v>53960</v>
+      </c>
+      <c r="W62" t="inlineStr"/>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Being Rental charges for JCB (A/C NO ;- 40422100006913 ,IFSC KLGB0040422) ( From 1/03/26 to 19/03/26) RPA_ID : cfd04e7fc6</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>IOCL PAPPINISSERI</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>procexewestern@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="inlineStr"/>
+      <c r="AH62" t="inlineStr"/>
+      <c r="AI62" t="inlineStr"/>
+      <c r="AJ62" t="inlineStr"/>
+      <c r="AK62" t="inlineStr"/>
+      <c r="AL62" t="inlineStr"/>
+      <c r="AM62" t="inlineStr"/>
+      <c r="AN62" t="inlineStr"/>
+      <c r="AO62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>WGE 612</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>MUHAMMED SHAROOF AP</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>9fcb3320-9282-41f7-a08a-31ea0ae4247b</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>ACC-67309272344</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>SBIN0070191</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V63" t="n">
+        <v>525</v>
+      </c>
+      <c r="W63" t="inlineStr"/>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Being purchasing of IOCL Coverall (A/C NO :-  67309272344 IFSC :- SBIN0070191 RPA_ID : 47f948d924</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>IOCL FEROKE</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>procexewestern@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="inlineStr"/>
+      <c r="AH63" t="inlineStr"/>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>IOCL FEROKE</t>
+        </is>
+      </c>
+      <c r="AL63" t="inlineStr"/>
+      <c r="AM63" t="inlineStr"/>
+      <c r="AN63" t="inlineStr"/>
+      <c r="AO63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>WGE 57</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>DCR</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Sachin</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>b930d89a-9382-49ac-a482-dcc21428bc41</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>ACC-33079301093</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>SBIN0008268</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V64" t="n">
+        <v>400</v>
+      </c>
+      <c r="W64" t="inlineStr"/>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Being purchasing of petrol for grasscutting (A/C NO:-33079301093 
+IFSC:-SBIN0008268) (27/03/26) RPA_ID : b474ba69ec</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>IOCL FEROKE</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>procexewestern@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="inlineStr"/>
+      <c r="AH64" t="inlineStr"/>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>IOCL FEROKE</t>
+        </is>
+      </c>
+      <c r="AL64" t="inlineStr"/>
+      <c r="AM64" t="inlineStr"/>
+      <c r="AN64" t="inlineStr"/>
+      <c r="AO64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>WGE 256</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>JAYADEVAN A V (PUTHUVYPU</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>4c0fdb18-cb70-43e9-9993-c1cd1a2b2a85</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>ACC-343202010028724</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>UBIN0534323</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W65" t="inlineStr"/>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Being purchasing of petrol for grasscutting RPA_ID : a1e2fce675</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>IOCL PUTHUVYPE</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>procexewestern@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="inlineStr"/>
+      <c r="AH65" t="inlineStr"/>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr"/>
+      <c r="AL65" t="inlineStr"/>
+      <c r="AM65" t="inlineStr"/>
+      <c r="AN65" t="inlineStr"/>
+      <c r="AO65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>WGE 613</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>NEETHU SEBASTIAN</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>d1c2e33a-bad6-4894-be6d-e4601b455343</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>ACC-10500100195327</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>FDRL0001050</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V66" t="n">
+        <v>55250</v>
+      </c>
+      <c r="W66" t="inlineStr"/>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Being purchasing of bricks for thiruvaniyoor (A/C NO:-10500100195327
+IFSC :- FDRL0001050) RPA_ID : 90739635f4</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>IOCL THIRUVANIYOOR</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>procexewestern@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="inlineStr"/>
+      <c r="AH66" t="inlineStr"/>
+      <c r="AI66" t="inlineStr"/>
+      <c r="AJ66" t="inlineStr"/>
+      <c r="AK66" t="inlineStr"/>
+      <c r="AL66" t="inlineStr"/>
+      <c r="AM66" t="inlineStr"/>
+      <c r="AN66" t="inlineStr"/>
+      <c r="AO66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>WGE 624</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>ADANS ELECTRIACLS</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>bed3b8fd-56ba-4418-8741-e723c75659ca</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>ACC-857930150000001</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>BKID0008579</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V67" t="n">
+        <v>2400</v>
+      </c>
+      <c r="W67" t="inlineStr"/>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Being purchaisng of table fan (A/C NO:- 857930150000001 IFSC BKID0008579) RPA_ID : c77346aff7</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>IOCL THIRUVANIYOOR</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>procexewestern@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="inlineStr"/>
+      <c r="AH67" t="inlineStr"/>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr"/>
+      <c r="AL67" t="inlineStr"/>
+      <c r="AM67" t="inlineStr"/>
+      <c r="AN67" t="inlineStr"/>
+      <c r="AO67" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PENDING_APPROVAL_SHEET.xlsx
+++ b/PENDING_APPROVAL_SHEET.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO127"/>
+  <dimension ref="A1:AO92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5333,7 +5333,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WGG 02</t>
+          <t>WGE 342</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5377,13 +5377,21 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>PAUL OFFSHORE PVT</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>ef5187e9-647d-42e0-8599-3673b66c5a15</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr"/>
+          <t>afdeb99c-3b4b-42ea-8b39-0deab9716950</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>ACC-7806823928</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
@@ -5397,27 +5405,25 @@
         </is>
       </c>
       <c r="V40" t="n">
-        <v>79930</v>
+        <v>117495</v>
       </c>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Pep consultancy pendiing payment RPA_ID : f678c1f5ed</t>
+          <t>ONGC GOA JAN BILL LABOUR CHARGES - WELDER / FITTER/RIGGER AND FOOD ALLOWANCE Total Amount= 342495/- Paid Rs.75000/- , Paid Rs.100000/- Excel Attendnace Sheet already shared= 167495,paid Rs.50000/-21.03.2026 RPA_ID : fbea9a2956</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>Cochin</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>PAYMENT</t>
-        </is>
+          <t>ONGC GOA</t>
+        </is>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>Payments@westernidc.com</t>
+          <t>hrm@westernidc.com</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
@@ -5432,22 +5438,18 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>79930</v>
+        <v>117495</v>
       </c>
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="inlineStr"/>
       <c r="AH40" t="inlineStr"/>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr"/>
+      <c r="AJ40" t="inlineStr"/>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
       <c r="AL40" t="inlineStr"/>
       <c r="AM40" t="inlineStr"/>
       <c r="AN40" t="inlineStr"/>
@@ -5456,7 +5458,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WGG 02</t>
+          <t>WGE 192</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5500,14 +5502,26 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Hafis Bin Haris</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2ea5eb17-cd10-4c49-a972-01e30efebdf6</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>d8af6b7d-cae0-4883-8a02-0840cc1ee88a</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>ACC-99980105201458</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>FDRL0001143</t>
+        </is>
+      </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
@@ -5520,27 +5534,25 @@
         </is>
       </c>
       <c r="V41" t="n">
-        <v>50000</v>
+        <v>9597</v>
       </c>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Payment as per the instraction of Sreekumar Sir RPA_ID : 9f36b48186</t>
+          <t>Salary- January 9597/- Full and Final Settlement Paid December 7423 , Balance 9597  Total = 17020 RPA_ID : eb64028b9b</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>Cochin</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>PAYMENT</t>
-        </is>
+          <t>GOA HUL</t>
+        </is>
+      </c>
+      <c r="Z41" t="n">
+        <v>0</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>Payments@westernidc.com</t>
+          <t>hrm@westernidc.com</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
@@ -5555,22 +5567,18 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>50000</v>
+        <v>9597</v>
       </c>
       <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="inlineStr"/>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr"/>
+      <c r="AJ41" t="inlineStr"/>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
       <c r="AL41" t="inlineStr"/>
       <c r="AM41" t="inlineStr"/>
       <c r="AN41" t="inlineStr"/>
@@ -5579,7 +5587,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>WGE 342</t>
+          <t>WGE 104</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5625,20 +5633,24 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>PAUL OFFSHORE PVT</t>
+          <t>BRAHMADATHAN</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>afdeb99c-3b4b-42ea-8b39-0deab9716950</t>
+          <t>bdfe4e9e-1446-4b5f-bfae-3f3abe459e9a</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>ACC-7806823928</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+          <t>ACC-232001000010098</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>IOBA0002320</t>
+        </is>
+      </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
@@ -5651,17 +5663,17 @@
         </is>
       </c>
       <c r="V42" t="n">
-        <v>117495</v>
+        <v>14379</v>
       </c>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr">
         <is>
-          <t>ONGC GOA JAN BILL LABOUR CHARGES - WELDER / FITTER/RIGGER AND FOOD ALLOWANCE Total Amount= 342495/- Paid Rs.75000/- , Paid Rs.100000/- Excel Attendnace Sheet already shared= 167495,paid Rs.50000/-21.03.2026 RPA_ID : fbea9a2956</t>
+          <t>Salary November Full and Final settlement Final Settlement Total 24379 , Rs.10000/- Paid  18.03.2026 Balance to be paid RPA_ID : 3fe24bf065</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>ONGC GOA</t>
+          <t>GOA HUL</t>
         </is>
       </c>
       <c r="Z42" t="n">
@@ -5684,7 +5696,7 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>117495</v>
+        <v>14379</v>
       </c>
       <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="inlineStr"/>
@@ -5704,7 +5716,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>WGE 192</t>
+          <t>WGE 452</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5750,22 +5762,22 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Hafis Bin Haris</t>
+          <t>CHANDRAKALA REDDY</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>d8af6b7d-cae0-4883-8a02-0840cc1ee88a</t>
+          <t>8a65056d-c489-4435-af85-8ae50db4bc27</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>ACC-99980105201458</t>
+          <t>ACC- 79860100001270</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>FDRL0001143</t>
+          <t>BARB0VASCOD</t>
         </is>
       </c>
       <c r="O43" t="inlineStr"/>
@@ -5780,17 +5792,17 @@
         </is>
       </c>
       <c r="V43" t="n">
-        <v>9597</v>
+        <v>15000</v>
       </c>
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Salary- January 9597/- Full and Final Settlement Paid December 7423 , Balance 9597  Total = 17020 RPA_ID : eb64028b9b</t>
+          <t>Hishm sir baleno auto 4th jan 10th jan 7days=10500,Baleno auto 14th jan 29th jan 16days=24000,Swift manual 17th jan 19th jan 3days=3600,Sidharth Dezire 13th feb  to 14th 3days 2400,Sir swift auto 16thfeb 17thfeb 2days 3000 2nd 1500 =45000 (10000 paid) As per Advice from Admin Andriya - No documents provided Rs.10000/- paid,Rs.10000/- paid 18.03.2026,23.023.2026 10000/-paid RPA_ID : acf13c58da</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>GOA HUL</t>
+          <t>ONGC IPSHEM</t>
         </is>
       </c>
       <c r="Z43" t="n">
@@ -5813,7 +5825,7 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>9597</v>
+        <v>15000</v>
       </c>
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="inlineStr"/>
@@ -5822,7 +5834,7 @@
       <c r="AJ43" t="inlineStr"/>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>GOA</t>
+          <t>ONGC IPSHEM</t>
         </is>
       </c>
       <c r="AL43" t="inlineStr"/>
@@ -5833,7 +5845,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>WGE 104</t>
+          <t>WGE 170</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5879,22 +5891,22 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>BRAHMADATHAN</t>
+          <t>VEDANT</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>bdfe4e9e-1446-4b5f-bfae-3f3abe459e9a</t>
+          <t>bd187585-f62d-4e4a-b6aa-cf94b4dca9ff</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>ACC-232001000010098</t>
+          <t>ACC-2047172054</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>IOBA0002320</t>
+          <t>KKBK0001429</t>
         </is>
       </c>
       <c r="O44" t="inlineStr"/>
@@ -5909,17 +5921,17 @@
         </is>
       </c>
       <c r="V44" t="n">
-        <v>14379</v>
+        <v>6451</v>
       </c>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Salary November Full and Final settlement Final Settlement Total 24379 , Rs.10000/- Paid  18.03.2026 Balance to be paid RPA_ID : 3fe24bf065</t>
+          <t>Material Shiftng 8 Days worked (December 5 days , January 3 Days) Basic Pay is Rs.25000/- perday 806.45 RPA_ID : f40e3af64d</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>GOA HUL</t>
+          <t>MDL</t>
         </is>
       </c>
       <c r="Z44" t="n">
@@ -5942,18 +5954,14 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>14379</v>
+        <v>6451</v>
       </c>
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="inlineStr"/>
       <c r="AI44" t="inlineStr"/>
       <c r="AJ44" t="inlineStr"/>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>GOA</t>
-        </is>
-      </c>
+      <c r="AK44" t="inlineStr"/>
       <c r="AL44" t="inlineStr"/>
       <c r="AM44" t="inlineStr"/>
       <c r="AN44" t="inlineStr"/>
@@ -5962,7 +5970,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>WGE 452</t>
+          <t>WGE 195</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6008,22 +6016,22 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>CHANDRAKALA REDDY</t>
+          <t>SAYAN BATTACHARYA</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>8a65056d-c489-4435-af85-8ae50db4bc27</t>
+          <t>b37a4aa4-b4d4-4fa5-9095-f0cdd5a7fcf9</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>ACC- 79860100001270</t>
+          <t>ACC-14810110034736</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>BARB0VASCOD</t>
+          <t>UCBA0001481</t>
         </is>
       </c>
       <c r="O45" t="inlineStr"/>
@@ -6038,17 +6046,17 @@
         </is>
       </c>
       <c r="V45" t="n">
-        <v>15000</v>
+        <v>224</v>
       </c>
       <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Hishm sir baleno auto 4th jan 10th jan 7days=10500,Baleno auto 14th jan 29th jan 16days=24000,Swift manual 17th jan 19th jan 3days=3600,Sidharth Dezire 13th feb  to 14th 3days 2400,Sir swift auto 16thfeb 17thfeb 2days 3000 2nd 1500 =45000 (10000 paid) As per Advice from Admin Andriya - No documents provided Rs.10000/- paid,Rs.10000/- paid 18.03.2026,23.023.2026 10000/-paid RPA_ID : acf13c58da</t>
+          <t>Sun, 01 Mar, 2026 / travel Howrah, West Bengal 711101, India to Bhowanipore, Kolkata, West Bengal, India RPA_ID : 323af1739e</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>ONGC IPSHEM</t>
+          <t>DUMKA</t>
         </is>
       </c>
       <c r="Z45" t="n">
@@ -6071,18 +6079,14 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>15000</v>
+        <v>224</v>
       </c>
       <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="inlineStr"/>
       <c r="AH45" t="inlineStr"/>
       <c r="AI45" t="inlineStr"/>
       <c r="AJ45" t="inlineStr"/>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>ONGC IPSHEM</t>
-        </is>
-      </c>
+      <c r="AK45" t="inlineStr"/>
       <c r="AL45" t="inlineStr"/>
       <c r="AM45" t="inlineStr"/>
       <c r="AN45" t="inlineStr"/>
@@ -6091,7 +6095,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>WGE 170</t>
+          <t>WGE 195</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6137,22 +6141,22 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>VEDANT</t>
+          <t>SAYAN BATTACHARYA</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>bd187585-f62d-4e4a-b6aa-cf94b4dca9ff</t>
+          <t>c579aabc-9c06-4a3d-8eb3-814ebe138051</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>ACC-2047172054</t>
+          <t>ACC-14810110034736</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>KKBK0001429</t>
+          <t>UCBA0001481</t>
         </is>
       </c>
       <c r="O46" t="inlineStr"/>
@@ -6167,17 +6171,17 @@
         </is>
       </c>
       <c r="V46" t="n">
-        <v>6451</v>
+        <v>224</v>
       </c>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Material Shiftng 8 Days worked (December 5 days , January 3 Days) Basic Pay is Rs.25000/- perday 806.45 RPA_ID : f40e3af64d</t>
+          <t>Sun, 08 Mar, 2026 / travel to Howrah, West Bengal 711101, India to Bhowanipore, Kolkata, West Bengal, India RPA_ID : 27f8ae4e0c</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>MDL</t>
+          <t>DUMKA</t>
         </is>
       </c>
       <c r="Z46" t="n">
@@ -6200,7 +6204,7 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>6451</v>
+        <v>224</v>
       </c>
       <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="inlineStr"/>
@@ -6267,7 +6271,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>b37a4aa4-b4d4-4fa5-9095-f0cdd5a7fcf9</t>
+          <t>35863971-eb17-447e-854c-f7415d29d894</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -6292,12 +6296,12 @@
         </is>
       </c>
       <c r="V47" t="n">
-        <v>224</v>
+        <v>199</v>
       </c>
       <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Sun, 01 Mar, 2026 / travel Howrah, West Bengal 711101, India to Bhowanipore, Kolkata, West Bengal, India RPA_ID : 323af1739e</t>
+          <t>Wed, 11 Mar, 2026 / travel to Bhowanipore, Kolkata, West Bengal, India to Howrah, West Bengal, India RPA_ID : 792b2470e5</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -6325,7 +6329,7 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>224</v>
+        <v>199</v>
       </c>
       <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="inlineStr"/>
@@ -6392,7 +6396,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>c579aabc-9c06-4a3d-8eb3-814ebe138051</t>
+          <t>eaaa18da-1fed-465c-8530-57c49883c163</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -6417,12 +6421,12 @@
         </is>
       </c>
       <c r="V48" t="n">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Sun, 08 Mar, 2026 / travel to Howrah, West Bengal 711101, India to Bhowanipore, Kolkata, West Bengal, India RPA_ID : 27f8ae4e0c</t>
+          <t>Thu, 12 Mar, 2026/ travel to , Howrah, West Bengal 711101, India to Bhowanipore, Kolkata, West Bengal, India RPA_ID : 7ebb6a8a5f</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -6450,7 +6454,7 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="inlineStr"/>
@@ -6517,7 +6521,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>35863971-eb17-447e-854c-f7415d29d894</t>
+          <t>795c5066-d259-460f-be14-c120b26995d1</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -6542,12 +6546,12 @@
         </is>
       </c>
       <c r="V49" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Wed, 11 Mar, 2026 / travel to Bhowanipore, Kolkata, West Bengal, India to Howrah, West Bengal, India RPA_ID : 792b2470e5</t>
+          <t>Wed, 18 Mar, 2026/travel to Behala, Kolkata, West Bengal, India to Bhowanipore, Kolkata, West Bengal, India RPA_ID : 25efd76bf5</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -6575,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="inlineStr"/>
@@ -6642,7 +6646,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>eaaa18da-1fed-465c-8530-57c49883c163</t>
+          <t>670469a9-d43c-4c1f-8f57-b929b7f816b8</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -6667,12 +6671,12 @@
         </is>
       </c>
       <c r="V50" t="n">
-        <v>256</v>
+        <v>214</v>
       </c>
       <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Thu, 12 Mar, 2026/ travel to , Howrah, West Bengal 711101, India to Bhowanipore, Kolkata, West Bengal, India RPA_ID : 7ebb6a8a5f</t>
+          <t>Mon, 23 Mar, 2026/ travel to Bhowanipore, Kolkata, West Bengal, India to Howrah, West Bengal, India RPA_ID : 67b0d1e5d3</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -6700,7 +6704,7 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>256</v>
+        <v>214</v>
       </c>
       <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="inlineStr"/>
@@ -6767,7 +6771,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>795c5066-d259-460f-be14-c120b26995d1</t>
+          <t>d41cc2c3-13d9-4f2d-818e-420d8708c599</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -6792,12 +6796,12 @@
         </is>
       </c>
       <c r="V51" t="n">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Wed, 18 Mar, 2026/travel to Behala, Kolkata, West Bengal, India to Bhowanipore, Kolkata, West Bengal, India RPA_ID : 25efd76bf5</t>
+          <t>Fri, 20 Mar, 2026 / travel to Bhowanipore, Kolkata, West Bengal, India to Howrah, West Bengal, India RPA_ID : 8a79ec9b06</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
@@ -6825,7 +6829,7 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="inlineStr"/>
@@ -6892,7 +6896,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>670469a9-d43c-4c1f-8f57-b929b7f816b8</t>
+          <t>08943921-cc16-4b0a-8728-7f14e48cb4ba</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -6917,12 +6921,12 @@
         </is>
       </c>
       <c r="V52" t="n">
-        <v>214</v>
+        <v>400</v>
       </c>
       <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Mon, 23 Mar, 2026/ travel to Bhowanipore, Kolkata, West Bengal, India to Howrah, West Bengal, India RPA_ID : 67b0d1e5d3</t>
+          <t>Food for inspector (VCS) for Bill submission ( dumka) RPA_ID : 6076dce15d</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
@@ -6950,7 +6954,7 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>214</v>
+        <v>400</v>
       </c>
       <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="inlineStr"/>
@@ -7017,7 +7021,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>d41cc2c3-13d9-4f2d-818e-420d8708c599</t>
+          <t>45cba872-9a66-4532-8b8d-b66bb3c2d828</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -7042,12 +7046,12 @@
         </is>
       </c>
       <c r="V53" t="n">
-        <v>222</v>
+        <v>1000</v>
       </c>
       <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Fri, 20 Mar, 2026 / travel to Bhowanipore, Kolkata, West Bengal, India to Howrah, West Bengal, India RPA_ID : 8a79ec9b06</t>
+          <t>Car expenses( only diesel) from Asansol to Jamtara and back from asansol with inspection accompanied for bill submission RPA_ID : f4ae8dcecf</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
@@ -7075,7 +7079,7 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>222</v>
+        <v>1000</v>
       </c>
       <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="inlineStr"/>
@@ -7142,7 +7146,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>08943921-cc16-4b0a-8728-7f14e48cb4ba</t>
+          <t>36052954-fc86-4522-b9ed-ca3cae94610a</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -7167,12 +7171,12 @@
         </is>
       </c>
       <c r="V54" t="n">
-        <v>400</v>
+        <v>168</v>
       </c>
       <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Food for inspector (VCS) for Bill submission ( dumka) RPA_ID : 6076dce15d</t>
+          <t>train ticket for asanol to howrah for bill submission RPA_ID : a7449dd699</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
@@ -7200,7 +7204,7 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>400</v>
+        <v>168</v>
       </c>
       <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="inlineStr"/>
@@ -7267,7 +7271,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>45cba872-9a66-4532-8b8d-b66bb3c2d828</t>
+          <t>8cc63550-6ae0-4cd2-992f-b89135a3940c</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -7292,17 +7296,17 @@
         </is>
       </c>
       <c r="V55" t="n">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Car expenses( only diesel) from Asansol to Jamtara and back from asansol with inspection accompanied for bill submission RPA_ID : f4ae8dcecf</t>
+          <t>PRINTER REPAIR CHARGE FOR KOLKATA OFFICE RPA_ID : 9f82260217</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>DUMKA</t>
+          <t>KOLKATA OFFICE</t>
         </is>
       </c>
       <c r="Z55" t="n">
@@ -7325,14 +7329,18 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="inlineStr"/>
       <c r="AH55" t="inlineStr"/>
       <c r="AI55" t="inlineStr"/>
       <c r="AJ55" t="inlineStr"/>
-      <c r="AK55" t="inlineStr"/>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>KOLKATA</t>
+        </is>
+      </c>
       <c r="AL55" t="inlineStr"/>
       <c r="AM55" t="inlineStr"/>
       <c r="AN55" t="inlineStr"/>
@@ -7341,7 +7349,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>WGE 195</t>
+          <t>WGE 603</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7387,22 +7395,22 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>SAYAN BATTACHARYA</t>
+          <t xml:space="preserve">MOHAMMED MANSOOR </t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>36052954-fc86-4522-b9ed-ca3cae94610a</t>
+          <t>6dbe2287-1a7b-4d83-aa2f-b282509c47eb</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>ACC-14810110034736</t>
+          <t>ACC-10880100006045</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>UCBA0001481</t>
+          <t>BARB0CAVELO</t>
         </is>
       </c>
       <c r="O56" t="inlineStr"/>
@@ -7417,17 +7425,19 @@
         </is>
       </c>
       <c r="V56" t="n">
-        <v>168</v>
+        <v>6060</v>
       </c>
       <c r="W56" t="inlineStr"/>
       <c r="X56" t="inlineStr">
         <is>
-          <t>train ticket for asanol to howrah for bill submission RPA_ID : a7449dd699</t>
+          <t>This payment pertains to hotel expenses incurred during work at ONGC. Food was provided to five Rumjan team workers as well as other workers.
+The payment for these expenses has not yet been made. The attached document includes ₹4,070 towards the food expenses of the Rumjan team workers. It also covers the food expenses of other workers who were working at ONGC , In march  food had to be arranged due to the unavailability of gas and the workers being unable to cook at that time.
+ this amount is payable to the hotel. RPA_ID : a3e88170ea</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>DUMKA</t>
+          <t>ONGC IPSHEM</t>
         </is>
       </c>
       <c r="Z56" t="n">
@@ -7450,14 +7460,18 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>168</v>
+        <v>6060</v>
       </c>
       <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="inlineStr"/>
       <c r="AH56" t="inlineStr"/>
       <c r="AI56" t="inlineStr"/>
       <c r="AJ56" t="inlineStr"/>
-      <c r="AK56" t="inlineStr"/>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>ONGC IPSHEM</t>
+        </is>
+      </c>
       <c r="AL56" t="inlineStr"/>
       <c r="AM56" t="inlineStr"/>
       <c r="AN56" t="inlineStr"/>
@@ -7466,7 +7480,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>WGE 195</t>
+          <t>WGE 629</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7492,7 +7506,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>NEFT</t>
+          <t>DCR</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -7512,22 +7526,22 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>SAYAN BATTACHARYA</t>
+          <t>MR MOHAMMAD SHAKIL</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>8cc63550-6ae0-4cd2-992f-b89135a3940c</t>
+          <t>9dda6d9d-c078-46b8-855e-7755188066fe</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>ACC-14810110034736</t>
+          <t>ACC-000234001100249</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>UCBA0001481</t>
+          <t>IBKL01077BD</t>
         </is>
       </c>
       <c r="O57" t="inlineStr"/>
@@ -7542,17 +7556,17 @@
         </is>
       </c>
       <c r="V57" t="n">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="W57" t="inlineStr"/>
       <c r="X57" t="inlineStr">
         <is>
-          <t>PRINTER REPAIR CHARGE FOR KOLKATA OFFICE RPA_ID : 9f82260217</t>
+          <t>Food Expense (28/03/2026 to 31/03/2026) @ 150 New Joinee Grinder RPA_ID : 12e387c98e</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>KOLKATA OFFICE</t>
+          <t>Bellari</t>
         </is>
       </c>
       <c r="Z57" t="n">
@@ -7575,7 +7589,7 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="inlineStr"/>
@@ -7584,7 +7598,7 @@
       <c r="AJ57" t="inlineStr"/>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>KOLKATA</t>
+          <t>BELLARI</t>
         </is>
       </c>
       <c r="AL57" t="inlineStr"/>
@@ -7595,7 +7609,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>WGE 601</t>
+          <t>WGE 629</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -7641,22 +7655,22 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>BABI NAYAK ( CASUAL 1)</t>
+          <t>MR MOHAMMAD ABID</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>c6929600-e0e6-4b93-838c-d5ff7a357ed1</t>
+          <t>b3817574-8afc-40fd-8cf2-9fd5aff7d74e</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>ACC- 36885053323</t>
+          <t>ACC-38340700009010</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>SBIN0008873</t>
+          <t>PUNB0MBGB06</t>
         </is>
       </c>
       <c r="O58" t="inlineStr"/>
@@ -7671,17 +7685,17 @@
         </is>
       </c>
       <c r="V58" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="W58" t="inlineStr"/>
       <c r="X58" t="inlineStr">
         <is>
-          <t>24/03/2026  ( CASUAL WAGE )  LEAVE  ANEESH V A / SAFAL  PER DAY 1000 / delay in this payment request. At the time of the request, we had informed the supervisor that payment would be made only to the respective accounts.  So We received the account details only yesterday; hence, the email is being sent today. RPA_ID : 5a02be55eb</t>
+          <t>Food Expense (28/03/2026 to 31/03/2026) @ 150 New Joinee Grinder RPA_ID : 1b31a2867e</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>IOCL WELLINGTON</t>
+          <t>Bellari</t>
         </is>
       </c>
       <c r="Z58" t="n">
@@ -7704,22 +7718,18 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="inlineStr"/>
       <c r="AH58" t="inlineStr"/>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>PAID</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>PAID</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr"/>
+      <c r="AI58" t="inlineStr"/>
+      <c r="AJ58" t="inlineStr"/>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
       <c r="AL58" t="inlineStr"/>
       <c r="AM58" t="inlineStr"/>
       <c r="AN58" t="inlineStr"/>
@@ -7728,7 +7738,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>WGE 603</t>
+          <t xml:space="preserve"> WGG 02</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -7772,26 +7782,14 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MOHAMMED MANSOOR </t>
-        </is>
-      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>6dbe2287-1a7b-4d83-aa2f-b282509c47eb</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>ACC-10880100006045</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>BARB0CAVELO</t>
-        </is>
-      </c>
+          <t>77e6f575-727f-46f8-bdb4-fc9dc511be2c</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
@@ -7804,19 +7802,17 @@
         </is>
       </c>
       <c r="V59" t="n">
-        <v>6060</v>
+        <v>507962</v>
       </c>
       <c r="W59" t="inlineStr"/>
       <c r="X59" t="inlineStr">
         <is>
-          <t>This payment pertains to hotel expenses incurred during work at ONGC. Food was provided to five Rumjan team workers as well as other workers.
-The payment for these expenses has not yet been made. The attached document includes ₹4,070 towards the food expenses of the Rumjan team workers. It also covers the food expenses of other workers who were working at ONGC , In march  food had to be arranged due to the unavailability of gas and the workers being unable to cook at that time.
- this amount is payable to the hotel. RPA_ID : a3e88170ea</t>
+          <t>ESI REVENU RECOVERY  Rs 1015923, to pay 50 % RPA_ID : 7883eeef8f</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>ONGC IPSHEM</t>
+          <t>KOLKATTA</t>
         </is>
       </c>
       <c r="Z59" t="n">
@@ -7839,18 +7835,14 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>6060</v>
+        <v>507962</v>
       </c>
       <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="inlineStr"/>
       <c r="AH59" t="inlineStr"/>
       <c r="AI59" t="inlineStr"/>
       <c r="AJ59" t="inlineStr"/>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>ONGC IPSHEM</t>
-        </is>
-      </c>
+      <c r="AK59" t="inlineStr"/>
       <c r="AL59" t="inlineStr"/>
       <c r="AM59" t="inlineStr"/>
       <c r="AN59" t="inlineStr"/>
@@ -7859,7 +7851,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>WGE 462</t>
+          <t xml:space="preserve"> WGG 02</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7903,26 +7895,14 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>PRANEET</t>
-        </is>
-      </c>
+      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>e3f9a324-1f65-4e92-bd8b-72090701d1ef</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>ACC-095203100002750</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>SRCB00000095</t>
-        </is>
-      </c>
+          <t>a84cf2d5-e4f1-40cc-a572-547da445aaea</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
@@ -7935,17 +7915,17 @@
         </is>
       </c>
       <c r="V60" t="n">
-        <v>5000</v>
+        <v>290000</v>
       </c>
       <c r="W60" t="inlineStr"/>
       <c r="X60" t="inlineStr">
         <is>
-          <t>ST3 Goa Casual Labour Charge 5 Nos @ 1000 RPA_ID : 06a9c241cd</t>
+          <t>AUGUST PF ARREAR KOCHI AND KONGAN APPROXIMATE RPA_ID : 8c6e0f7d6f</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>ST3 GOA</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="Z60" t="n">
@@ -7968,26 +7948,14 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>5000</v>
+        <v>290000</v>
       </c>
       <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="inlineStr"/>
       <c r="AH60" t="inlineStr"/>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>GOA</t>
-        </is>
-      </c>
+      <c r="AI60" t="inlineStr"/>
+      <c r="AJ60" t="inlineStr"/>
+      <c r="AK60" t="inlineStr"/>
       <c r="AL60" t="inlineStr"/>
       <c r="AM60" t="inlineStr"/>
       <c r="AN60" t="inlineStr"/>
@@ -7996,7 +7964,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>WGE 629</t>
+          <t xml:space="preserve"> WGG 02</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -8022,7 +7990,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>DCR</t>
+          <t>NEFT</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -8040,26 +8008,14 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>MR MOHAMMAD SHAKIL</t>
-        </is>
-      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>9dda6d9d-c078-46b8-855e-7755188066fe</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>ACC-000234001100249</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>IBKL01077BD</t>
-        </is>
-      </c>
+          <t>7f3cced5-e8bf-4e40-95e5-107451fd0953</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
@@ -8072,25 +8028,27 @@
         </is>
       </c>
       <c r="V61" t="n">
-        <v>600</v>
+        <v>76700</v>
       </c>
       <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Food Expense (28/03/2026 to 31/03/2026) @ 150 New Joinee Grinder RPA_ID : 12e387c98e</t>
+          <t>Being rental service for crane(A/C NO:-01692560001256 IFSC :-HDFC0000169) (19-03-2026) RPA_ID : b5b502210f</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>Bellari</t>
-        </is>
-      </c>
-      <c r="Z61" t="n">
-        <v>0</v>
+          <t>ONGC JETTY</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>hrm@westernidc.com</t>
+          <t>procexewestern@gmail.com</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
@@ -8105,18 +8063,14 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>600</v>
+        <v>76700</v>
       </c>
       <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr"/>
       <c r="AI61" t="inlineStr"/>
       <c r="AJ61" t="inlineStr"/>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>BELLARI</t>
-        </is>
-      </c>
+      <c r="AK61" t="inlineStr"/>
       <c r="AL61" t="inlineStr"/>
       <c r="AM61" t="inlineStr"/>
       <c r="AN61" t="inlineStr"/>
@@ -8125,7 +8079,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>WGE 629</t>
+          <t xml:space="preserve"> WGG 02</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -8151,7 +8105,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>DCR</t>
+          <t>NEFT</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -8169,26 +8123,14 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>MR MOHAMMAD ABID</t>
-        </is>
-      </c>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>b3817574-8afc-40fd-8cf2-9fd5aff7d74e</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>ACC-38340700009010</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>PUNB0MBGB06</t>
-        </is>
-      </c>
+          <t>e3e7fdb4-30a7-484c-bade-9a93466d097c</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
@@ -8201,25 +8143,27 @@
         </is>
       </c>
       <c r="V62" t="n">
-        <v>600</v>
+        <v>24741</v>
       </c>
       <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Food Expense (28/03/2026 to 31/03/2026) @ 150 New Joinee Grinder RPA_ID : 1b31a2867e</t>
+          <t>Plesae return the GSTR1  amount to the vendor (19-03-2026) RPA_ID : 39dfb304c1</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>Bellari</t>
-        </is>
-      </c>
-      <c r="Z62" t="n">
-        <v>0</v>
+          <t>BPCL BALLARI</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>hrm@westernidc.com</t>
+          <t>procexewestern@gmail.com</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
@@ -8234,18 +8178,14 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>600</v>
+        <v>24741</v>
       </c>
       <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="inlineStr"/>
       <c r="AJ62" t="inlineStr"/>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>BELLARI</t>
-        </is>
-      </c>
+      <c r="AK62" t="inlineStr"/>
       <c r="AL62" t="inlineStr"/>
       <c r="AM62" t="inlineStr"/>
       <c r="AN62" t="inlineStr"/>
@@ -8301,7 +8241,7 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>77e6f575-727f-46f8-bdb4-fc9dc511be2c</t>
+          <t>c6b456f2-c18c-4dbb-b615-121ba7eddf18</t>
         </is>
       </c>
       <c r="M63" t="inlineStr"/>
@@ -8318,25 +8258,27 @@
         </is>
       </c>
       <c r="V63" t="n">
-        <v>507962</v>
+        <v>60000</v>
       </c>
       <c r="W63" t="inlineStr"/>
       <c r="X63" t="inlineStr">
         <is>
-          <t>ESI REVENU RECOVERY  Rs 1015923, to pay 50 % RPA_ID : 7883eeef8f</t>
+          <t>Being hot work channel welding work (19-03-2026) RPA_ID : b0dada9b8c</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>KOLKATTA</t>
-        </is>
-      </c>
-      <c r="Z63" t="n">
-        <v>0</v>
+          <t>NGOP CHENNAI</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>hrm@westernidc.com</t>
+          <t>procexewestern@gmail.com</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
@@ -8351,7 +8293,7 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>507962</v>
+        <v>60000</v>
       </c>
       <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="inlineStr"/>
@@ -8414,7 +8356,7 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>a84cf2d5-e4f1-40cc-a572-547da445aaea</t>
+          <t>5e2732ab-7d39-44dc-a417-024bfde8d624</t>
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
@@ -8431,25 +8373,27 @@
         </is>
       </c>
       <c r="V64" t="n">
-        <v>290000</v>
+        <v>149877.6</v>
       </c>
       <c r="W64" t="inlineStr"/>
       <c r="X64" t="inlineStr">
         <is>
-          <t>AUGUST PF ARREAR KOCHI AND KONGAN APPROXIMATE RPA_ID : 8c6e0f7d6f</t>
+          <t>Being rent for JCB ,Hydra,Braker and farrana crane( total 324877.6  ,90000 paid on 20-03-2026 balance amount remaining (19-03-2026) RPA_ID : d8615d3eb9</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>Kochi</t>
-        </is>
-      </c>
-      <c r="Z64" t="n">
-        <v>0</v>
+          <t>BPCL BALLARI</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>hrm@westernidc.com</t>
+          <t>procexewestern@gmail.com</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
@@ -8464,7 +8408,7 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>290000</v>
+        <v>149877.6</v>
       </c>
       <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="inlineStr"/>
@@ -8527,7 +8471,7 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>7f3cced5-e8bf-4e40-95e5-107451fd0953</t>
+          <t>9dd7baea-8800-43fb-b37f-6c0e83d42b8f</t>
         </is>
       </c>
       <c r="M65" t="inlineStr"/>
@@ -8544,22 +8488,23 @@
         </is>
       </c>
       <c r="V65" t="n">
-        <v>76700</v>
+        <v>8700</v>
       </c>
       <c r="W65" t="inlineStr"/>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Being rental service for crane(A/C NO:-01692560001256 IFSC :-HDFC0000169) (19-03-2026) RPA_ID : b5b502210f</t>
+          <t>Being supply of WIFI camera to JELIN sir flat (A/C NO:-13160200024922
+IFSC :-FDRL000116) 7300 Paid balance amount remaining RPA_ID : 4e2f90b49c</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>ONGC JETTY</t>
+          <t>Maintenance(Jelin sir)</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>SITE EXPENSES</t>
+          <t>MAINTENANCE</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8579,7 +8524,7 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>76700</v>
+        <v>8700</v>
       </c>
       <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="inlineStr"/>
@@ -8642,7 +8587,7 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>e3e7fdb4-30a7-484c-bade-9a93466d097c</t>
+          <t>871ee27b-d353-4bbb-8ff9-798588551428</t>
         </is>
       </c>
       <c r="M66" t="inlineStr"/>
@@ -8659,17 +8604,18 @@
         </is>
       </c>
       <c r="V66" t="n">
-        <v>24741</v>
+        <v>8100</v>
       </c>
       <c r="W66" t="inlineStr"/>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Plesae return the GSTR1  amount to the vendor (19-03-2026) RPA_ID : 39dfb304c1</t>
+          <t>Being rental of grasscutting machine and petrol expenses (A/C NO:-  32555551936 ,IFSC :- SBIN0001890)
+(23-03-2026) RPA_ID : 6832c4a260</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>BPCL BALLARI</t>
+          <t>HPCL ELATHOOR</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
@@ -8694,14 +8640,18 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>24741</v>
+        <v>8100</v>
       </c>
       <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="inlineStr"/>
       <c r="AH66" t="inlineStr"/>
       <c r="AI66" t="inlineStr"/>
       <c r="AJ66" t="inlineStr"/>
-      <c r="AK66" t="inlineStr"/>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
       <c r="AL66" t="inlineStr"/>
       <c r="AM66" t="inlineStr"/>
       <c r="AN66" t="inlineStr"/>
@@ -8757,7 +8707,7 @@
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>c6b456f2-c18c-4dbb-b615-121ba7eddf18</t>
+          <t>bb5648d6-e914-4c99-9a46-ca103ff400d1</t>
         </is>
       </c>
       <c r="M67" t="inlineStr"/>
@@ -8774,17 +8724,19 @@
         </is>
       </c>
       <c r="V67" t="n">
-        <v>60000</v>
+        <v>4400</v>
       </c>
       <c r="W67" t="inlineStr"/>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Being hot work channel welding work (19-03-2026) RPA_ID : b0dada9b8c</t>
+          <t>3.5 mm nylon grass trimming cord 100 meter -1000
+Grass cutting head -5*500=2500
+Grass cutting blade -3nos=3*300=900 RPA_ID : 7db9ba76e0</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>NGOP CHENNAI</t>
+          <t>HPCL ELATHOOR</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
@@ -8809,14 +8761,18 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>60000</v>
+        <v>4400</v>
       </c>
       <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="inlineStr"/>
       <c r="AH67" t="inlineStr"/>
       <c r="AI67" t="inlineStr"/>
       <c r="AJ67" t="inlineStr"/>
-      <c r="AK67" t="inlineStr"/>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
       <c r="AL67" t="inlineStr"/>
       <c r="AM67" t="inlineStr"/>
       <c r="AN67" t="inlineStr"/>
@@ -8835,7 +8791,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>28-03-2026</t>
+          <t>30-03-2026</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -8872,7 +8828,7 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>5e2732ab-7d39-44dc-a417-024bfde8d624</t>
+          <t>c1d39c64-9dc4-4580-866e-e00f5f738f70</t>
         </is>
       </c>
       <c r="M68" t="inlineStr"/>
@@ -8889,27 +8845,27 @@
         </is>
       </c>
       <c r="V68" t="n">
-        <v>149877.6</v>
+        <v>79930</v>
       </c>
       <c r="W68" t="inlineStr"/>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Being rent for JCB ,Hydra,Braker and farrana crane( total 324877.6  ,90000 paid on 20-03-2026 balance amount remaining (19-03-2026) RPA_ID : d8615d3eb9</t>
+          <t>Pep consultancy pendiing payment RPA_ID : 53e907c24b</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>BPCL BALLARI</t>
+          <t>Cochin</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>SITE EXPENSES</t>
+          <t>PAYMENT</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>procexewestern@gmail.com</t>
+          <t>Payments@westernidc.com</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
@@ -8924,7 +8880,7 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>149877.6</v>
+        <v>79930</v>
       </c>
       <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="inlineStr"/>
@@ -8940,7 +8896,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WGG 02</t>
+          <t>WGE 428</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -8950,7 +8906,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>28-03-2026</t>
+          <t>30-03-2026</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -8984,14 +8940,26 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>NAIJAL driver</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>9dd7baea-8800-43fb-b37f-6c0e83d42b8f</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>025ccb00-b0da-4185-80a7-d5825d1133fb</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>ACC-13962100139241</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>FDRL0001396</t>
+        </is>
+      </c>
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
@@ -9004,28 +8972,25 @@
         </is>
       </c>
       <c r="V69" t="n">
-        <v>8700</v>
+        <v>225</v>
       </c>
       <c r="W69" t="inlineStr"/>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Being supply of WIFI camera to JELIN sir flat (A/C NO:-13160200024922
-IFSC :-FDRL000116) 7300 Paid balance amount remaining RPA_ID : 4e2f90b49c</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>Maintenance(Jelin sir)</t>
-        </is>
+          <t>Akshaya tax follow up and welfare charge RPA_ID : d2b63bf1b5</t>
+        </is>
+      </c>
+      <c r="Y69" t="n">
+        <v>0</v>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>MAINTENANCE</t>
+          <t>REIMBURSEMENT</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>procexewestern@gmail.com</t>
+          <t>pa.mdgoc@gmail.com</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
@@ -9040,7 +9005,7 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>8700</v>
+        <v>225</v>
       </c>
       <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="inlineStr"/>
@@ -9056,7 +9021,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WGG 02</t>
+          <t>WGE 429</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -9066,7 +9031,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>28-03-2026</t>
+          <t>30-03-2026</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -9100,14 +9065,26 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>SAFNA</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>871ee27b-d353-4bbb-8ff9-798588551428</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>afa8ec7b-f86d-4bd2-baf8-5a73686ab097</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>ACC- 111001504967</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>ICIC0001110</t>
+        </is>
+      </c>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
@@ -9120,28 +9097,25 @@
         </is>
       </c>
       <c r="V70" t="n">
-        <v>8100</v>
+        <v>300</v>
       </c>
       <c r="W70" t="inlineStr"/>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Being rental of grasscutting machine and petrol expenses (A/C NO:-  32555551936 ,IFSC :- SBIN0001890)
-(23-03-2026) RPA_ID : 6832c4a260</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>HPCL ELATHOOR</t>
-        </is>
+          <t>Aviator petrol amount need in advance RPA_ID : 21efac9e39</t>
+        </is>
+      </c>
+      <c r="Y70" t="n">
+        <v>0</v>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>SITE EXPENSES</t>
+          <t>REIMBURSEMENT</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>procexewestern@gmail.com</t>
+          <t>pa.mdgoc@gmail.com</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
@@ -9156,18 +9130,14 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>8100</v>
+        <v>300</v>
       </c>
       <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="inlineStr"/>
       <c r="AH70" t="inlineStr"/>
       <c r="AI70" t="inlineStr"/>
       <c r="AJ70" t="inlineStr"/>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>HO</t>
-        </is>
-      </c>
+      <c r="AK70" t="inlineStr"/>
       <c r="AL70" t="inlineStr"/>
       <c r="AM70" t="inlineStr"/>
       <c r="AN70" t="inlineStr"/>
@@ -9176,7 +9146,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WGG 02</t>
+          <t>WGE 322</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -9186,7 +9156,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>28-03-2026</t>
+          <t>30-03-2026</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -9202,7 +9172,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>NEFT</t>
+          <t>DCR</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -9220,14 +9190,26 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>MOHAMMED SARFARAS</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>bb5648d6-e914-4c99-9a46-ca103ff400d1</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>ea869f2c-49cf-4706-929a-4ab308c8ae68</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>ACC-67373357798</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>SBIN0010116</t>
+        </is>
+      </c>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr"/>
@@ -9240,29 +9222,25 @@
         </is>
       </c>
       <c r="V71" t="n">
-        <v>4400</v>
+        <v>3000</v>
       </c>
       <c r="W71" t="inlineStr"/>
       <c r="X71" t="inlineStr">
         <is>
-          <t>3.5 mm nylon grass trimming cord 100 meter -1000
-Grass cutting head -5*500=2500
-Grass cutting blade -3nos=3*300=900 RPA_ID : 7db9ba76e0</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>HPCL ELATHOOR</t>
-        </is>
+          <t>BREEZA PETROL need in advance for next week RPA_ID : 60c7845e9d</t>
+        </is>
+      </c>
+      <c r="Y71" t="n">
+        <v>0</v>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>SITE EXPENSES</t>
+          <t>PAYMENT</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>procexewestern@gmail.com</t>
+          <t>pa.mdgoc@gmail.com</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
@@ -9277,18 +9255,14 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>4400</v>
+        <v>3000</v>
       </c>
       <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="inlineStr"/>
       <c r="AH71" t="inlineStr"/>
       <c r="AI71" t="inlineStr"/>
       <c r="AJ71" t="inlineStr"/>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>HO</t>
-        </is>
-      </c>
+      <c r="AK71" t="inlineStr"/>
       <c r="AL71" t="inlineStr"/>
       <c r="AM71" t="inlineStr"/>
       <c r="AN71" t="inlineStr"/>
@@ -9297,7 +9271,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WGG 02</t>
+          <t>WGE 342</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -9341,13 +9315,21 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>PAUL OFFSHORE PVT</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>c1d39c64-9dc4-4580-866e-e00f5f738f70</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr"/>
+          <t>d675224e-60b9-44ea-a459-f9bb4a9e29e7</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>ACC-7806823928</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
@@ -9361,27 +9343,25 @@
         </is>
       </c>
       <c r="V72" t="n">
-        <v>79930</v>
+        <v>117495</v>
       </c>
       <c r="W72" t="inlineStr"/>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Pep consultancy pendiing payment RPA_ID : 53e907c24b</t>
+          <t>ONGC GOA JAN BILL LABOUR CHARGES - WELDER / FITTER/RIGGER AND FOOD ALLOWANCE Total Amount= 342495/- Paid Rs.75000/- , Paid Rs.100000/- Excel Attendnace Sheet already shared= 167495,paid Rs.50000/-21.03.2026 RPA_ID : 9218a8a92c</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>Cochin</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>PAYMENT</t>
-        </is>
+          <t>ONGC GOA</t>
+        </is>
+      </c>
+      <c r="Z72" t="n">
+        <v>0</v>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>Payments@westernidc.com</t>
+          <t>hrm@westernidc.com</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
@@ -9396,14 +9376,18 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>117495</v>
       </c>
       <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="inlineStr"/>
       <c r="AH72" t="inlineStr"/>
       <c r="AI72" t="inlineStr"/>
       <c r="AJ72" t="inlineStr"/>
-      <c r="AK72" t="inlineStr"/>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
       <c r="AL72" t="inlineStr"/>
       <c r="AM72" t="inlineStr"/>
       <c r="AN72" t="inlineStr"/>
@@ -9412,7 +9396,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WGG 02</t>
+          <t>WGE 192</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -9456,14 +9440,26 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Hafis Bin Haris</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>ff4460b2-d3d1-4b5b-9d17-14d2766cad49</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+          <t>e63a0c63-8129-47bf-9ccc-7d7d2a02ca89</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>ACC-99980105201458</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>FDRL0001143</t>
+        </is>
+      </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr"/>
@@ -9476,27 +9472,25 @@
         </is>
       </c>
       <c r="V73" t="n">
-        <v>50000</v>
+        <v>9597</v>
       </c>
       <c r="W73" t="inlineStr"/>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Payment as per the instraction of Sreekumar Sir RPA_ID : 87ede0554e</t>
+          <t>Salary- January 9597/- Full and Final Settlement Paid December 7423 , Balance 9597  Total = 17020 RPA_ID : 240ce1934f</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>Cochin</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>PAYMENT</t>
-        </is>
+          <t>GOA HUL</t>
+        </is>
+      </c>
+      <c r="Z73" t="n">
+        <v>0</v>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>Payments@westernidc.com</t>
+          <t>hrm@westernidc.com</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
@@ -9511,22 +9505,18 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>9597</v>
       </c>
       <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="inlineStr"/>
       <c r="AH73" t="inlineStr"/>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr"/>
+      <c r="AI73" t="inlineStr"/>
+      <c r="AJ73" t="inlineStr"/>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
       <c r="AL73" t="inlineStr"/>
       <c r="AM73" t="inlineStr"/>
       <c r="AN73" t="inlineStr"/>
@@ -9535,7 +9525,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WGG 02</t>
+          <t>WGE 104</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -9579,14 +9569,26 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>BRAHMADATHAN</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>f77c080c-0117-44f0-97a9-66d41ae23763</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>3c67710a-2a04-4611-9eee-ea5fc2fe5ee1</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>ACC-232001000010098</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>IOBA0002320</t>
+        </is>
+      </c>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>
@@ -9599,27 +9601,25 @@
         </is>
       </c>
       <c r="V74" t="n">
-        <v>200000</v>
+        <v>14379</v>
       </c>
       <c r="W74" t="inlineStr"/>
       <c r="X74" t="inlineStr">
         <is>
-          <t>Cash payment to sreenikethana RPA_ID : 128e610dfc</t>
+          <t>Salary November Full and Final settlement Final Settlement Total 24379 , Rs.10000/- Paid  18.03.2026 Balance to be paid RPA_ID : 91a8ca8f63</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>Mumbai</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>PAYMENT</t>
-        </is>
+          <t>GOA HUL</t>
+        </is>
+      </c>
+      <c r="Z74" t="n">
+        <v>0</v>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>Payments@westernidc.com</t>
+          <t>hrm@westernidc.com</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
@@ -9634,22 +9634,18 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>0</v>
+        <v>14379</v>
       </c>
       <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="inlineStr"/>
       <c r="AH74" t="inlineStr"/>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr"/>
+      <c r="AI74" t="inlineStr"/>
+      <c r="AJ74" t="inlineStr"/>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
       <c r="AL74" t="inlineStr"/>
       <c r="AM74" t="inlineStr"/>
       <c r="AN74" t="inlineStr"/>
@@ -9658,7 +9654,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>WGE 428</t>
+          <t>WGE 452</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -9704,22 +9700,22 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>NAIJAL driver</t>
+          <t>CHANDRAKALA REDDY</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>ea0df8df-bd17-4e72-a957-77a8c6ff82db</t>
+          <t>5113f654-4f39-4784-883c-e4df3004c8bb</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>ACC-13962100139241</t>
+          <t>ACC- 79860100001270</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>FDRL0001396</t>
+          <t>BARB0VASCOD</t>
         </is>
       </c>
       <c r="O75" t="inlineStr"/>
@@ -9734,25 +9730,25 @@
         </is>
       </c>
       <c r="V75" t="n">
-        <v>200</v>
+        <v>15000</v>
       </c>
       <c r="W75" t="inlineStr"/>
       <c r="X75" t="inlineStr">
         <is>
-          <t>Aviator petrol paid by naijal RPA_ID : 4b1bc48b7f</t>
-        </is>
-      </c>
-      <c r="Y75" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>REIMBURSEMENT</t>
-        </is>
+          <t>Hishm sir baleno auto 4th jan 10th jan 7days=10500,Baleno auto 14th jan 29th jan 16days=24000,Swift manual 17th jan 19th jan 3days=3600,Sidharth Dezire 13th feb  to 14th 3days 2400,Sir swift auto 16thfeb 17thfeb 2days 3000 2nd 1500 =45000 (10000 paid) As per Advice from Admin Andriya - No documents provided Rs.10000/- paid,Rs.10000/- paid 18.03.2026,23.023.2026 10000/-paid RPA_ID : 597bc7b10e</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>ONGC IPSHEM</t>
+        </is>
+      </c>
+      <c r="Z75" t="n">
+        <v>0</v>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>pa.mdgoc@gmail.com</t>
+          <t>hrm@westernidc.com</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
@@ -9767,22 +9763,18 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="inlineStr"/>
       <c r="AH75" t="inlineStr"/>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr"/>
+      <c r="AI75" t="inlineStr"/>
+      <c r="AJ75" t="inlineStr"/>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>ONGC IPSHEM</t>
+        </is>
+      </c>
       <c r="AL75" t="inlineStr"/>
       <c r="AM75" t="inlineStr"/>
       <c r="AN75" t="inlineStr"/>
@@ -9791,7 +9783,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>WGE 220</t>
+          <t>WGE 170</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -9837,22 +9829,22 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>ANDRIYA THOMAS</t>
+          <t>VEDANT</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>38c181ec-1154-484f-a8c4-a4808e99f818</t>
+          <t>24ff7668-e6f9-48ca-8ac5-4a93645a66cf</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>ACC-0706101053789</t>
+          <t>ACC-2047172054</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>CNRB0000706</t>
+          <t>KKBK0001429</t>
         </is>
       </c>
       <c r="O76" t="inlineStr"/>
@@ -9867,25 +9859,25 @@
         </is>
       </c>
       <c r="V76" t="n">
-        <v>669</v>
+        <v>6451</v>
       </c>
       <c r="W76" t="inlineStr"/>
       <c r="X76" t="inlineStr">
         <is>
-          <t>smart marine RPA_ID : aab663f0e8</t>
-        </is>
-      </c>
-      <c r="Y76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>REIMBURSEMENT</t>
-        </is>
+          <t>Material Shiftng 8 Days worked (December 5 days , January 3 Days) Basic Pay is Rs.25000/- perday 806.45 RPA_ID : 0d9d98ba3e</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>MDL</t>
+        </is>
+      </c>
+      <c r="Z76" t="n">
+        <v>0</v>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>pa.mdgoc@gmail.com</t>
+          <t>hrm@westernidc.com</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
@@ -9900,21 +9892,13 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>6451</v>
       </c>
       <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="inlineStr"/>
       <c r="AH76" t="inlineStr"/>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
+      <c r="AI76" t="inlineStr"/>
+      <c r="AJ76" t="inlineStr"/>
       <c r="AK76" t="inlineStr"/>
       <c r="AL76" t="inlineStr"/>
       <c r="AM76" t="inlineStr"/>
@@ -9924,7 +9908,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>WGE 428</t>
+          <t>WGE 603</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -9970,22 +9954,22 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>NAIJAL driver</t>
+          <t xml:space="preserve">MOHAMMED MANSOOR </t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>5e972fc0-8da8-4191-9105-61149a8f3f5c</t>
+          <t>2471680a-3858-4c9e-8a43-6e49d0113163</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>ACC-13962100139241</t>
+          <t>ACC-10880100006045</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>FDRL0001396</t>
+          <t>BARB0CAVELO</t>
         </is>
       </c>
       <c r="O77" t="inlineStr"/>
@@ -10000,25 +9984,29 @@
         </is>
       </c>
       <c r="V77" t="n">
-        <v>60</v>
+        <v>6060</v>
       </c>
       <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Biscuts for Hemilda mam and hisham sir RPA_ID : 19a35a6ae6</t>
-        </is>
-      </c>
-      <c r="Y77" t="n">
-        <v>0</v>
+          <t>This payment pertains to hotel expenses incurred during work at ONGC. Food was provided to five Rumjan team workers as well as other workers.
+The payment for these expenses has not yet been made. The attached document includes ₹4,070 towards the food expenses of the Rumjan team workers. It also covers the food expenses of other workers who were working at ONGC , In march  food had to be arranged due to the unavailability of gas and the workers being unable to cook at that time.
+ this amount is payable to the hotel. RPA_ID : 7b75210e15</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>ONGC IPSHEM</t>
+        </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>REIMBURSEMENT</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>pa.mdgoc@gmail.com</t>
+          <t>hrm@westernidc.com</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
@@ -10033,22 +10021,18 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>6060</v>
       </c>
       <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="inlineStr"/>
       <c r="AH77" t="inlineStr"/>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr"/>
+      <c r="AI77" t="inlineStr"/>
+      <c r="AJ77" t="inlineStr"/>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>ONGC IPSHEM</t>
+        </is>
+      </c>
       <c r="AL77" t="inlineStr"/>
       <c r="AM77" t="inlineStr"/>
       <c r="AN77" t="inlineStr"/>
@@ -10057,7 +10041,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>WGE 428</t>
+          <t>WGE 462</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -10103,22 +10087,22 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>NAIJAL driver</t>
+          <t>PRANEET</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>025ccb00-b0da-4185-80a7-d5825d1133fb</t>
+          <t>67981808-cdca-4b03-ac09-2c3ee5f9d29f</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>ACC-13962100139241</t>
+          <t>ACC-095203100002750</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>FDRL0001396</t>
+          <t>SRCB00000095</t>
         </is>
       </c>
       <c r="O78" t="inlineStr"/>
@@ -10133,25 +10117,25 @@
         </is>
       </c>
       <c r="V78" t="n">
-        <v>225</v>
+        <v>5000</v>
       </c>
       <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr">
         <is>
-          <t>Akshaya tax follow up and welfare charge RPA_ID : d2b63bf1b5</t>
-        </is>
-      </c>
-      <c r="Y78" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>REIMBURSEMENT</t>
-        </is>
+          <t>ST3 Goa Casual Labour Charge 5 Nos @ 1000 30.03.2026 RPA_ID : d09d0910da</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>ST3 GOA</t>
+        </is>
+      </c>
+      <c r="Z78" t="n">
+        <v>0</v>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>pa.mdgoc@gmail.com</t>
+          <t>hrm@westernidc.com</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
@@ -10166,14 +10150,18 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="inlineStr"/>
       <c r="AH78" t="inlineStr"/>
       <c r="AI78" t="inlineStr"/>
       <c r="AJ78" t="inlineStr"/>
-      <c r="AK78" t="inlineStr"/>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
       <c r="AL78" t="inlineStr"/>
       <c r="AM78" t="inlineStr"/>
       <c r="AN78" t="inlineStr"/>
@@ -10182,7 +10170,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>WGE 429</t>
+          <t>WGE 340</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -10208,7 +10196,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>NEFT</t>
+          <t>DCR</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -10228,22 +10216,22 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>SAFNA</t>
+          <t>SAMAL KUMAR</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>d4afa87c-166e-4ff4-ab59-1c44bee5e0b8</t>
+          <t>55f823d5-47f5-4922-a065-d8591057adf3</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>ACC- 111001504967</t>
+          <t>ACC-42854727464</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>ICIC0001110</t>
+          <t>SBIN0060181</t>
         </is>
       </c>
       <c r="O79" t="inlineStr"/>
@@ -10258,25 +10246,25 @@
         </is>
       </c>
       <c r="V79" t="n">
-        <v>267</v>
+        <v>8700</v>
       </c>
       <c r="W79" t="inlineStr"/>
       <c r="X79" t="inlineStr">
         <is>
-          <t>GARBAGE FOR KITCHEN ( EXTRALARGE &amp; SMALL) RPA_ID : fe2ad3b5e3</t>
-        </is>
-      </c>
-      <c r="Y79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>PAYMENT</t>
-        </is>
+          <t>Expense for the period 19.03.2026 to 27.03.2026 Dhumka Advance expense till 29.03.2026 RPA_ID : 9f7322036f</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>DHUMKA</t>
+        </is>
+      </c>
+      <c r="Z79" t="n">
+        <v>0</v>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>pa.mdgoc@gmail.com</t>
+          <t>hrm@westernidc.com</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
@@ -10291,21 +10279,13 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>8700</v>
       </c>
       <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="inlineStr"/>
       <c r="AH79" t="inlineStr"/>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
+      <c r="AI79" t="inlineStr"/>
+      <c r="AJ79" t="inlineStr"/>
       <c r="AK79" t="inlineStr"/>
       <c r="AL79" t="inlineStr"/>
       <c r="AM79" t="inlineStr"/>
@@ -10315,7 +10295,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>WGE 429</t>
+          <t xml:space="preserve"> WGG 02</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -10359,26 +10339,14 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>SAFNA</t>
-        </is>
-      </c>
+      <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>afa8ec7b-f86d-4bd2-baf8-5a73686ab097</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>ACC- 111001504967</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>ICIC0001110</t>
-        </is>
-      </c>
+          <t>b2f965a8-1f4d-43ed-a280-423f02d9761d</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr"/>
@@ -10391,25 +10359,25 @@
         </is>
       </c>
       <c r="V80" t="n">
-        <v>300</v>
+        <v>507962</v>
       </c>
       <c r="W80" t="inlineStr"/>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Aviator petrol amount need in advance RPA_ID : 21efac9e39</t>
-        </is>
-      </c>
-      <c r="Y80" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>REIMBURSEMENT</t>
-        </is>
+          <t>ESI REVENU RECOVERY  Rs 1015923, to pay 50 % RPA_ID : c47f2c22f4</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>KOLKATTA</t>
+        </is>
+      </c>
+      <c r="Z80" t="n">
+        <v>0</v>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>pa.mdgoc@gmail.com</t>
+          <t>hrm@westernidc.com</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
@@ -10424,7 +10392,7 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>507962</v>
       </c>
       <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="inlineStr"/>
@@ -10440,7 +10408,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>WGE 428</t>
+          <t xml:space="preserve"> WGG 02</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -10484,26 +10452,14 @@
           <t>32AAAFW8862C1Z9</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>NAIJAL driver</t>
-        </is>
-      </c>
+      <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>9b71aabe-fd11-4568-a401-fd0c67e12910</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>ACC-13962100139241</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>FDRL0001396</t>
-        </is>
-      </c>
+          <t>df1dbe62-d4fa-4d7c-a80d-388fa04b6df6</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr"/>
@@ -10516,25 +10472,25 @@
         </is>
       </c>
       <c r="V81" t="n">
-        <v>28</v>
+        <v>290000</v>
       </c>
       <c r="W81" t="inlineStr"/>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Milk RPA_ID : 2d4d59edd5</t>
-        </is>
-      </c>
-      <c r="Y81" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>REIMBURSEMENT</t>
-        </is>
+          <t>AUGUST PF ARREAR KOCHI AND KONGAN APPROXIMATE RPA_ID : 84bd10b71a</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="Z81" t="n">
+        <v>0</v>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>pa.mdgoc@gmail.com</t>
+          <t>hrm@westernidc.com</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
@@ -10549,21 +10505,13 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>290000</v>
       </c>
       <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="inlineStr"/>
       <c r="AH81" t="inlineStr"/>
-      <c r="AI81" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
+      <c r="AI81" t="inlineStr"/>
+      <c r="AJ81" t="inlineStr"/>
       <c r="AK81" t="inlineStr"/>
       <c r="AL81" t="inlineStr"/>
       <c r="AM81" t="inlineStr"/>
@@ -10573,7 +10521,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>WGE 428</t>
+          <t>WGE 271</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -10619,22 +10567,22 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>NAIJAL driver</t>
+          <t>SHEENA R NAIR</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>a2b17151-cada-4f5b-8f8f-4cfa3eb51e72</t>
+          <t>881d3eb6-d7a2-4557-9bd9-199b75e1a84d</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>ACC-13962100139241</t>
+          <t>ACC-50100161423549</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>FDRL0001396</t>
+          <t>HDFC0000717</t>
         </is>
       </c>
       <c r="O82" t="inlineStr"/>
@@ -10649,25 +10597,25 @@
         </is>
       </c>
       <c r="V82" t="n">
-        <v>147</v>
+        <v>2400</v>
       </c>
       <c r="W82" t="inlineStr"/>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Hisham sir food dated 27.09.26 RPA_ID : 53c5882e7a</t>
-        </is>
-      </c>
-      <c r="Y82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>REIMBURSEMENT</t>
-        </is>
+          <t>Room Stay Sabin Paid Staturday  Rs 2400/- (29.03.026 and 30.03.2026) RPA_ID : 636e9f72f3</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>CHENNAI</t>
+        </is>
+      </c>
+      <c r="Z82" t="n">
+        <v>0</v>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>pa.mdgoc@gmail.com</t>
+          <t>hrm@westernidc.com</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
@@ -10682,21 +10630,13 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="inlineStr"/>
       <c r="AH82" t="inlineStr"/>
-      <c r="AI82" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
+      <c r="AI82" t="inlineStr"/>
+      <c r="AJ82" t="inlineStr"/>
       <c r="AK82" t="inlineStr"/>
       <c r="AL82" t="inlineStr"/>
       <c r="AM82" t="inlineStr"/>
@@ -10706,7 +10646,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>WGE 429</t>
+          <t>WGE 299</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -10732,7 +10672,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>NEFT</t>
+          <t>DCR</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -10752,22 +10692,22 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>SAFNA</t>
+          <t>ARJUN(ONGC) SUPERVISOR</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>d6e34918-a5d3-4389-8c6f-151461231289</t>
+          <t>5d08c05d-fa37-4085-b13f-657fedffb828</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>ACC- 111001504967</t>
+          <t>ACC-67329839060</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>ICIC0001110</t>
+          <t>SBIN0070076</t>
         </is>
       </c>
       <c r="O83" t="inlineStr"/>
@@ -10782,25 +10722,25 @@
         </is>
       </c>
       <c r="V83" t="n">
-        <v>126</v>
+        <v>4800</v>
       </c>
       <c r="W83" t="inlineStr"/>
       <c r="X83" t="inlineStr">
         <is>
-          <t>COFFEE POWDER (BRU instant coffee) 40g need in adance for next week RPA_ID : ea28b03496</t>
-        </is>
-      </c>
-      <c r="Y83" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>PAYMENT</t>
-        </is>
+          <t>Room stay Expense @ 1200 (28.03.2026 to 31.03.2026) RPA_ID : 307429bb90</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="Z83" t="n">
+        <v>0</v>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>pa.mdgoc@gmail.com</t>
+          <t>hrm@westernidc.com</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
@@ -10815,21 +10755,13 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="inlineStr"/>
       <c r="AH83" t="inlineStr"/>
-      <c r="AI83" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
+      <c r="AI83" t="inlineStr"/>
+      <c r="AJ83" t="inlineStr"/>
       <c r="AK83" t="inlineStr"/>
       <c r="AL83" t="inlineStr"/>
       <c r="AM83" t="inlineStr"/>
@@ -10839,7 +10771,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>WGE 322</t>
+          <t>WGE 306</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -10885,22 +10817,22 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>MOHAMMED SARFARAS</t>
+          <t>SABIN V V</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>ea869f2c-49cf-4706-929a-4ab308c8ae68</t>
+          <t>e2dffae2-fb3e-4dfd-9a2a-150f41f07704</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>ACC-67373357798</t>
+          <t>ACC-67274681749</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>SBIN0010116</t>
+          <t>SBIN0070812</t>
         </is>
       </c>
       <c r="O84" t="inlineStr"/>
@@ -10915,25 +10847,25 @@
         </is>
       </c>
       <c r="V84" t="n">
-        <v>3000</v>
+        <v>900</v>
       </c>
       <c r="W84" t="inlineStr"/>
       <c r="X84" t="inlineStr">
         <is>
-          <t>BREEZA PETROL need in advance for next week RPA_ID : 60c7845e9d</t>
-        </is>
-      </c>
-      <c r="Y84" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>PAYMENT</t>
-        </is>
+          <t>RoomStay 31.03.2026 @ 1100 (Advane 200 already paid) RPA_ID : cb5075fd79</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>CHENNAI</t>
+        </is>
+      </c>
+      <c r="Z84" t="n">
+        <v>0</v>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>pa.mdgoc@gmail.com</t>
+          <t>hrm@westernidc.com</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
@@ -10948,7 +10880,7 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="inlineStr"/>
@@ -10964,7 +10896,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>WGE 429</t>
+          <t>WGE 638</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -11010,22 +10942,22 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>SAFNA</t>
+          <t>Vaishali crane hiring service</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>550738ec-439b-4be3-8b9e-c027e0b51e24</t>
+          <t>73a2d361-4e7c-42ab-b682-a4eadbd10494</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>ACC- 111001504967</t>
+          <t>ACC-01692560001256</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>ICIC0001110</t>
+          <t>HDFC0000169</t>
         </is>
       </c>
       <c r="O85" t="inlineStr"/>
@@ -11040,25 +10972,27 @@
         </is>
       </c>
       <c r="V85" t="n">
-        <v>4000</v>
+        <v>76700</v>
       </c>
       <c r="W85" t="inlineStr"/>
       <c r="X85" t="inlineStr">
         <is>
-          <t>Tax renewal pick up need this amount in advance on Monday approx RPA_ID : adbd9978d1</t>
-        </is>
-      </c>
-      <c r="Y85" t="n">
-        <v>0</v>
+          <t>Being rental service for crane(A/C NO:-01692560001256 IFSC :-HDFC0000169) (19-03-2026) RPA_ID : 5420a0196f</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>ONGC JETTY</t>
+        </is>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>PAYMENT</t>
+          <t>SITE EXPENSES</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>pa.mdgoc@gmail.com</t>
+          <t>procexewestern@gmail.com</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
@@ -11073,21 +11007,13 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>76700</v>
       </c>
       <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="inlineStr"/>
       <c r="AH85" t="inlineStr"/>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
+      <c r="AI85" t="inlineStr"/>
+      <c r="AJ85" t="inlineStr"/>
       <c r="AK85" t="inlineStr"/>
       <c r="AL85" t="inlineStr"/>
       <c r="AM85" t="inlineStr"/>
@@ -11097,7 +11023,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>WGE 323</t>
+          <t>WGE 636</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -11143,22 +11069,22 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>VINITHA V NAIR</t>
+          <t>Raj nath yadav</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>22b979be-73c6-4a42-b234-79173a8d1848</t>
+          <t>5d651e6e-9aa8-4a4c-9cbc-3844820d62f1</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>ACC-22020100013715</t>
+          <t>ACC-429502010014495</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>FDRL0002202</t>
+          <t>UBIN0542954</t>
         </is>
       </c>
       <c r="O86" t="inlineStr"/>
@@ -11173,30 +11099,27 @@
         </is>
       </c>
       <c r="V86" t="n">
-        <v>7600</v>
+        <v>60000</v>
       </c>
       <c r="W86" t="inlineStr"/>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Mason 1,300 X 2
-Helper 1,000 X 3
-Additional labour 
-1,000 X 2 RPA_ID : f563483089</t>
+          <t>Being hot work channel welding work (19-03-2026) RPA_ID : 2a5271af26</t>
         </is>
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>Construction of IOCL RO at Pappinisseri</t>
+          <t>NGOP CHENNAI</t>
         </is>
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>LABOUR CHARGES</t>
+          <t>SITE EXPENSES</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>executive.westerntender@gmail.com</t>
+          <t>procexewestern@gmail.com</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
@@ -11211,21 +11134,13 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="inlineStr"/>
       <c r="AH86" t="inlineStr"/>
-      <c r="AI86" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
+      <c r="AI86" t="inlineStr"/>
+      <c r="AJ86" t="inlineStr"/>
       <c r="AK86" t="inlineStr"/>
       <c r="AL86" t="inlineStr"/>
       <c r="AM86" t="inlineStr"/>
@@ -11235,7 +11150,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>WGE 323</t>
+          <t>WGE 635</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -11261,7 +11176,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>NEFT</t>
+          <t>DCR</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -11281,22 +11196,22 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>VINITHA V NAIR</t>
+          <t>S B EARTH MOVERS AND CRANE SERVICES</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>b8a82b53-19df-4abe-89d7-5184e703c9af</t>
+          <t>82239466-52e7-4d59-a12d-754e787d3efb</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>ACC-22020100013715</t>
+          <t>ACC-10120420457</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>FDRL0002202</t>
+          <t>IDFB0081081</t>
         </is>
       </c>
       <c r="O87" t="inlineStr"/>
@@ -11311,29 +11226,27 @@
         </is>
       </c>
       <c r="V87" t="n">
-        <v>252</v>
+        <v>149877.6</v>
       </c>
       <c r="W87" t="inlineStr"/>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Additional labour food
-66x2 = 132 Mrng 
-60x2 = 120 Lunch RPA_ID : ea542f7b59</t>
+          <t>Being rent for JCB ,Hydra,Braker and farrana crane( total 324877.6  ,90000 paid on 20-03-2026 balance amount remaining (19-03-2026) RPA_ID : 2f76ef7a18</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>Construction of IOCL RO at Pappinisseri</t>
+          <t>BPCL BALLARI</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>FOOD CHARGES</t>
+          <t>SITE EXPENSES</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>executive.westerntender@gmail.com</t>
+          <t>procexewestern@gmail.com</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
@@ -11348,21 +11261,13 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>149877.6</v>
       </c>
       <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="inlineStr"/>
       <c r="AH87" t="inlineStr"/>
-      <c r="AI87" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
+      <c r="AI87" t="inlineStr"/>
+      <c r="AJ87" t="inlineStr"/>
       <c r="AK87" t="inlineStr"/>
       <c r="AL87" t="inlineStr"/>
       <c r="AM87" t="inlineStr"/>
@@ -11372,7 +11277,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>WGE 444</t>
+          <t>WGE 527</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -11418,22 +11323,22 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>ADARSH K</t>
+          <t>ELECTRONEX TECHNOLOGIES</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>ef91c6af-4c72-4aef-a3d9-b26ae5017769</t>
+          <t>17234d65-0b19-470e-8899-83bc8ac7d546</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>ACC- 13190100192479</t>
+          <t>ACC-13160200024922</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>FDRL0001319</t>
+          <t>FDRL0001316</t>
         </is>
       </c>
       <c r="O88" t="inlineStr"/>
@@ -11448,33 +11353,28 @@
         </is>
       </c>
       <c r="V88" t="n">
-        <v>11900</v>
+        <v>8700</v>
       </c>
       <c r="W88" t="inlineStr"/>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Ramesh 
-Maison - 1400*2
-Helper - 1100*1
-Company side
-Helper - 1100*5
-Maison -1300*1
-Technician -1200*1 RPA_ID : 977a12e4c6</t>
+          <t>Being supply of WIFI camera to JELIN sir flat (A/C NO:-13160200024922
+IFSC :-FDRL000116) 7300 Paid balance amount remaining RPA_ID : 6185f90bd9</t>
         </is>
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>Construction of IOCL RO at Thiruvaniyoor</t>
+          <t>Maintenance(Jelin sir)</t>
         </is>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>LABOUR CHARGES</t>
+          <t>MAINTENANCE</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>executive.westerntender@gmail.com</t>
+          <t>procexewestern@gmail.com</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
@@ -11489,21 +11389,13 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>8700</v>
       </c>
       <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="inlineStr"/>
       <c r="AH88" t="inlineStr"/>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
+      <c r="AI88" t="inlineStr"/>
+      <c r="AJ88" t="inlineStr"/>
       <c r="AK88" t="inlineStr"/>
       <c r="AL88" t="inlineStr"/>
       <c r="AM88" t="inlineStr"/>
@@ -11513,70 +11405,30 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>WGE 444</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
+          <t>WGE 633</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
           <t>30-03-2026</t>
         </is>
       </c>
-      <c r="D89" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F89" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>NEFT</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>ADARSH K</t>
-        </is>
-      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
-          <t>a5ec90b7-e14a-4165-b2d0-67655562de29</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>ACC- 13190100192479</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>FDRL0001319</t>
-        </is>
-      </c>
+          <t>37928d5c-2918-4547-9899-e8d6241e3393</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr"/>
       <c r="Q89" t="inlineStr"/>
@@ -11589,27 +11441,28 @@
         </is>
       </c>
       <c r="V89" t="n">
-        <v>700</v>
+        <v>8100</v>
       </c>
       <c r="W89" t="inlineStr"/>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Food charges RPA_ID : ce9af50fa2</t>
+          <t>Being rental of grasscutting machine and petrol expenses (A/C NO:-  32555551936 ,IFSC :- SBIN0001890)
+(23-03-2026) RPA_ID : 9852cd6c2b</t>
         </is>
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>Construction of IOCL RO at Thiruvaniyoor</t>
+          <t>HPCL ELATHOOR</t>
         </is>
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>FOOD CHARGES</t>
+          <t>SITE EXPENSES</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>executive.westerntender@gmail.com</t>
+          <t>procexewestern@gmail.com</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
@@ -11624,22 +11477,18 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="inlineStr"/>
       <c r="AH89" t="inlineStr"/>
-      <c r="AI89" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr"/>
+      <c r="AI89" t="inlineStr"/>
+      <c r="AJ89" t="inlineStr"/>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
       <c r="AL89" t="inlineStr"/>
       <c r="AM89" t="inlineStr"/>
       <c r="AN89" t="inlineStr"/>
@@ -11648,7 +11497,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>WGE 444</t>
+          <t>WGE 600</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -11694,22 +11543,22 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>ADARSH K</t>
+          <t>SHARUN EARTH MOVERS</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>d59b4a04-594c-4bf2-8684-18af0c0dcf35</t>
+          <t>c9f56923-eb5e-416a-b795-3fa22642586e</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>ACC- 13190100192479</t>
+          <t>ACC-40422100006913</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>FDRL0001319</t>
+          <t>KLGB0040422</t>
         </is>
       </c>
       <c r="O90" t="inlineStr"/>
@@ -11724,27 +11573,27 @@
         </is>
       </c>
       <c r="V90" t="n">
-        <v>200</v>
+        <v>28960</v>
       </c>
       <c r="W90" t="inlineStr"/>
       <c r="X90" t="inlineStr">
         <is>
-          <t>Petrol charges RPA_ID : 6001de9911</t>
+          <t>Being Rental charges for JCB (A/C NO ;- 40422100006913 ,IFSC KLGB0040422) ( From 1/03/26 to 19/03/26)(25,000 paid on 28/03/26 balance amount remaining) RPA_ID : 0b0e65383b</t>
         </is>
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>Construction of IOCL RO at Thiruvaniyoor</t>
+          <t>IOCL PAPPINISSERI</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>TRAVEL CHARGES</t>
+          <t>SITE EXPENSES</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>executive.westerntender@gmail.com</t>
+          <t>procexewestern@gmail.com</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
@@ -11759,21 +11608,13 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>0</v>
+        <v>28960</v>
       </c>
       <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="inlineStr"/>
       <c r="AH90" t="inlineStr"/>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
+      <c r="AI90" t="inlineStr"/>
+      <c r="AJ90" t="inlineStr"/>
       <c r="AK90" t="inlineStr"/>
       <c r="AL90" t="inlineStr"/>
       <c r="AM90" t="inlineStr"/>
@@ -11783,7 +11624,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>WGE 444</t>
+          <t>WGE 551</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -11829,22 +11670,22 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>ADARSH K</t>
+          <t>PRUDENT GLOBAL SAFETY SOLUTIONS</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>f3e00238-c738-4085-9904-659d38aa1b88</t>
+          <t>8dfe271a-f5ed-4245-8a5f-19e8dfddbe0d</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>ACC- 13190100192479</t>
+          <t>ACC-169105001359</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>FDRL0001319</t>
+          <t>ICIC0001691</t>
         </is>
       </c>
       <c r="O91" t="inlineStr"/>
@@ -11859,27 +11700,27 @@
         </is>
       </c>
       <c r="V91" t="n">
-        <v>350</v>
+        <v>630</v>
       </c>
       <c r="W91" t="inlineStr"/>
       <c r="X91" t="inlineStr">
         <is>
-          <t>Auto charges RPA_ID : 96ee99def3</t>
+          <t>Being purcahsing of safety vest (A/C NO:-169105001359 IFSC:- ICIC0001691) RPA_ID : 412c5dd697</t>
         </is>
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>Construction of IOCL RO at Thiruvaniyoor</t>
+          <t>IOCL THIRUVANIYOOR</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>AUTO CHARGES</t>
+          <t>SITE EXPENSES</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>executive.westerntender@gmail.com</t>
+          <t>procexewestern@gmail.com</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
@@ -11894,21 +11735,13 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>630</v>
       </c>
       <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="inlineStr"/>
       <c r="AH91" t="inlineStr"/>
-      <c r="AI91" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
+      <c r="AI91" t="inlineStr"/>
+      <c r="AJ91" t="inlineStr"/>
       <c r="AK91" t="inlineStr"/>
       <c r="AL91" t="inlineStr"/>
       <c r="AM91" t="inlineStr"/>
@@ -11918,7 +11751,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>WGE 342</t>
+          <t>WGE 551</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -11964,20 +11797,24 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>PAUL OFFSHORE PVT</t>
+          <t>PRUDENT GLOBAL SAFETY SOLUTIONS</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>d675224e-60b9-44ea-a459-f9bb4a9e29e7</t>
+          <t>00e3c24d-f393-4503-9700-d5ab5b15cf18</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>ACC-7806823928</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
+          <t>ACC-169105001359</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>ICIC0001691</t>
+        </is>
+      </c>
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr"/>
@@ -11990,25 +11827,27 @@
         </is>
       </c>
       <c r="V92" t="n">
-        <v>117495</v>
+        <v>5316</v>
       </c>
       <c r="W92" t="inlineStr"/>
       <c r="X92" t="inlineStr">
         <is>
-          <t>ONGC GOA JAN BILL LABOUR CHARGES - WELDER / FITTER/RIGGER AND FOOD ALLOWANCE Total Amount= 342495/- Paid Rs.75000/- , Paid Rs.100000/- Excel Attendnace Sheet already shared= 167495,paid Rs.50000/-21.03.2026 RPA_ID : 9218a8a92c</t>
+          <t>Being purchasing of reflective tape ,barricaution tape(A/C NO:-169105001359 IFSC:- ICIC0001691) RPA_ID : a563936139</t>
         </is>
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>ONGC GOA</t>
-        </is>
-      </c>
-      <c r="Z92" t="n">
-        <v>0</v>
+          <t>IOCL THIRUVANIYOOR</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>hrm@westernidc.com</t>
+          <t>procexewestern@gmail.com</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
@@ -12023,4492 +11862,19 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>0</v>
+        <v>5316</v>
       </c>
       <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="inlineStr"/>
       <c r="AH92" t="inlineStr"/>
       <c r="AI92" t="inlineStr"/>
       <c r="AJ92" t="inlineStr"/>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>GOA</t>
-        </is>
-      </c>
+      <c r="AK92" t="inlineStr"/>
       <c r="AL92" t="inlineStr"/>
       <c r="AM92" t="inlineStr"/>
       <c r="AN92" t="inlineStr"/>
       <c r="AO92" t="inlineStr"/>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>WGE 192</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F93" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>NEFT</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>Hafis Bin Haris</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>e63a0c63-8129-47bf-9ccc-7d7d2a02ca89</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>ACC-99980105201458</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>FDRL0001143</t>
-        </is>
-      </c>
-      <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="inlineStr"/>
-      <c r="S93" t="inlineStr"/>
-      <c r="T93" t="inlineStr"/>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V93" t="n">
-        <v>9597</v>
-      </c>
-      <c r="W93" t="inlineStr"/>
-      <c r="X93" t="inlineStr">
-        <is>
-          <t>Salary- January 9597/- Full and Final Settlement Paid December 7423 , Balance 9597  Total = 17020 RPA_ID : 240ce1934f</t>
-        </is>
-      </c>
-      <c r="Y93" t="inlineStr">
-        <is>
-          <t>GOA HUL</t>
-        </is>
-      </c>
-      <c r="Z93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA93" t="inlineStr">
-        <is>
-          <t>hrm@westernidc.com</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF93" t="inlineStr"/>
-      <c r="AG93" t="inlineStr"/>
-      <c r="AH93" t="inlineStr"/>
-      <c r="AI93" t="inlineStr"/>
-      <c r="AJ93" t="inlineStr"/>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>GOA</t>
-        </is>
-      </c>
-      <c r="AL93" t="inlineStr"/>
-      <c r="AM93" t="inlineStr"/>
-      <c r="AN93" t="inlineStr"/>
-      <c r="AO93" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>WGE 104</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F94" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>NEFT</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>BRAHMADATHAN</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>3c67710a-2a04-4611-9eee-ea5fc2fe5ee1</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>ACC-232001000010098</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>IOBA0002320</t>
-        </is>
-      </c>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
-      <c r="R94" t="inlineStr"/>
-      <c r="S94" t="inlineStr"/>
-      <c r="T94" t="inlineStr"/>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V94" t="n">
-        <v>14379</v>
-      </c>
-      <c r="W94" t="inlineStr"/>
-      <c r="X94" t="inlineStr">
-        <is>
-          <t>Salary November Full and Final settlement Final Settlement Total 24379 , Rs.10000/- Paid  18.03.2026 Balance to be paid RPA_ID : 91a8ca8f63</t>
-        </is>
-      </c>
-      <c r="Y94" t="inlineStr">
-        <is>
-          <t>GOA HUL</t>
-        </is>
-      </c>
-      <c r="Z94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA94" t="inlineStr">
-        <is>
-          <t>hrm@westernidc.com</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF94" t="inlineStr"/>
-      <c r="AG94" t="inlineStr"/>
-      <c r="AH94" t="inlineStr"/>
-      <c r="AI94" t="inlineStr"/>
-      <c r="AJ94" t="inlineStr"/>
-      <c r="AK94" t="inlineStr">
-        <is>
-          <t>GOA</t>
-        </is>
-      </c>
-      <c r="AL94" t="inlineStr"/>
-      <c r="AM94" t="inlineStr"/>
-      <c r="AN94" t="inlineStr"/>
-      <c r="AO94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>WGE 452</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F95" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>NEFT</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA REDDY</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>5113f654-4f39-4784-883c-e4df3004c8bb</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>ACC- 79860100001270</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>BARB0VASCOD</t>
-        </is>
-      </c>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="inlineStr"/>
-      <c r="S95" t="inlineStr"/>
-      <c r="T95" t="inlineStr"/>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V95" t="n">
-        <v>15000</v>
-      </c>
-      <c r="W95" t="inlineStr"/>
-      <c r="X95" t="inlineStr">
-        <is>
-          <t>Hishm sir baleno auto 4th jan 10th jan 7days=10500,Baleno auto 14th jan 29th jan 16days=24000,Swift manual 17th jan 19th jan 3days=3600,Sidharth Dezire 13th feb  to 14th 3days 2400,Sir swift auto 16thfeb 17thfeb 2days 3000 2nd 1500 =45000 (10000 paid) As per Advice from Admin Andriya - No documents provided Rs.10000/- paid,Rs.10000/- paid 18.03.2026,23.023.2026 10000/-paid RPA_ID : 597bc7b10e</t>
-        </is>
-      </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>ONGC IPSHEM</t>
-        </is>
-      </c>
-      <c r="Z95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>hrm@westernidc.com</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF95" t="inlineStr"/>
-      <c r="AG95" t="inlineStr"/>
-      <c r="AH95" t="inlineStr"/>
-      <c r="AI95" t="inlineStr"/>
-      <c r="AJ95" t="inlineStr"/>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>ONGC IPSHEM</t>
-        </is>
-      </c>
-      <c r="AL95" t="inlineStr"/>
-      <c r="AM95" t="inlineStr"/>
-      <c r="AN95" t="inlineStr"/>
-      <c r="AO95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>WGE 170</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F96" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>NEFT</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>VEDANT</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>24ff7668-e6f9-48ca-8ac5-4a93645a66cf</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>ACC-2047172054</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>KKBK0001429</t>
-        </is>
-      </c>
-      <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr"/>
-      <c r="R96" t="inlineStr"/>
-      <c r="S96" t="inlineStr"/>
-      <c r="T96" t="inlineStr"/>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V96" t="n">
-        <v>6451</v>
-      </c>
-      <c r="W96" t="inlineStr"/>
-      <c r="X96" t="inlineStr">
-        <is>
-          <t>Material Shiftng 8 Days worked (December 5 days , January 3 Days) Basic Pay is Rs.25000/- perday 806.45 RPA_ID : 0d9d98ba3e</t>
-        </is>
-      </c>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>MDL</t>
-        </is>
-      </c>
-      <c r="Z96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>hrm@westernidc.com</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF96" t="inlineStr"/>
-      <c r="AG96" t="inlineStr"/>
-      <c r="AH96" t="inlineStr"/>
-      <c r="AI96" t="inlineStr"/>
-      <c r="AJ96" t="inlineStr"/>
-      <c r="AK96" t="inlineStr"/>
-      <c r="AL96" t="inlineStr"/>
-      <c r="AM96" t="inlineStr"/>
-      <c r="AN96" t="inlineStr"/>
-      <c r="AO96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>WGE 603</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F97" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>NEFT</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MOHAMMED MANSOOR </t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>2471680a-3858-4c9e-8a43-6e49d0113163</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>ACC-10880100006045</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>BARB0CAVELO</t>
-        </is>
-      </c>
-      <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr"/>
-      <c r="R97" t="inlineStr"/>
-      <c r="S97" t="inlineStr"/>
-      <c r="T97" t="inlineStr"/>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V97" t="n">
-        <v>6060</v>
-      </c>
-      <c r="W97" t="inlineStr"/>
-      <c r="X97" t="inlineStr">
-        <is>
-          <t>This payment pertains to hotel expenses incurred during work at ONGC. Food was provided to five Rumjan team workers as well as other workers.
-The payment for these expenses has not yet been made. The attached document includes ₹4,070 towards the food expenses of the Rumjan team workers. It also covers the food expenses of other workers who were working at ONGC , In march  food had to be arranged due to the unavailability of gas and the workers being unable to cook at that time.
- this amount is payable to the hotel. RPA_ID : 7b75210e15</t>
-        </is>
-      </c>
-      <c r="Y97" t="inlineStr">
-        <is>
-          <t>ONGC IPSHEM</t>
-        </is>
-      </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>hrm@westernidc.com</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC97" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD97" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE97" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF97" t="inlineStr"/>
-      <c r="AG97" t="inlineStr"/>
-      <c r="AH97" t="inlineStr"/>
-      <c r="AI97" t="inlineStr"/>
-      <c r="AJ97" t="inlineStr"/>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>ONGC IPSHEM</t>
-        </is>
-      </c>
-      <c r="AL97" t="inlineStr"/>
-      <c r="AM97" t="inlineStr"/>
-      <c r="AN97" t="inlineStr"/>
-      <c r="AO97" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>WGE 462</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F98" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>NEFT</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>PRANEET</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>67981808-cdca-4b03-ac09-2c3ee5f9d29f</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>ACC-095203100002750</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>SRCB00000095</t>
-        </is>
-      </c>
-      <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr"/>
-      <c r="R98" t="inlineStr"/>
-      <c r="S98" t="inlineStr"/>
-      <c r="T98" t="inlineStr"/>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V98" t="n">
-        <v>5000</v>
-      </c>
-      <c r="W98" t="inlineStr"/>
-      <c r="X98" t="inlineStr">
-        <is>
-          <t>ST3 Goa Casual Labour Charge 5 Nos @ 1000 30.03.2026 RPA_ID : d09d0910da</t>
-        </is>
-      </c>
-      <c r="Y98" t="inlineStr">
-        <is>
-          <t>ST3 GOA</t>
-        </is>
-      </c>
-      <c r="Z98" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA98" t="inlineStr">
-        <is>
-          <t>hrm@westernidc.com</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC98" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD98" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE98" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF98" t="inlineStr"/>
-      <c r="AG98" t="inlineStr"/>
-      <c r="AH98" t="inlineStr"/>
-      <c r="AI98" t="inlineStr"/>
-      <c r="AJ98" t="inlineStr"/>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>GOA</t>
-        </is>
-      </c>
-      <c r="AL98" t="inlineStr"/>
-      <c r="AM98" t="inlineStr"/>
-      <c r="AN98" t="inlineStr"/>
-      <c r="AO98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>WGE 340</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F99" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>DCR</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>SAMAL KUMAR</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>55f823d5-47f5-4922-a065-d8591057adf3</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>ACC-42854727464</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>SBIN0060181</t>
-        </is>
-      </c>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr"/>
-      <c r="R99" t="inlineStr"/>
-      <c r="S99" t="inlineStr"/>
-      <c r="T99" t="inlineStr"/>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V99" t="n">
-        <v>8700</v>
-      </c>
-      <c r="W99" t="inlineStr"/>
-      <c r="X99" t="inlineStr">
-        <is>
-          <t>Expense for the period 19.03.2026 to 27.03.2026 Dhumka Advance expense till 29.03.2026 RPA_ID : 9f7322036f</t>
-        </is>
-      </c>
-      <c r="Y99" t="inlineStr">
-        <is>
-          <t>DHUMKA</t>
-        </is>
-      </c>
-      <c r="Z99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA99" t="inlineStr">
-        <is>
-          <t>hrm@westernidc.com</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF99" t="inlineStr"/>
-      <c r="AG99" t="inlineStr"/>
-      <c r="AH99" t="inlineStr"/>
-      <c r="AI99" t="inlineStr"/>
-      <c r="AJ99" t="inlineStr"/>
-      <c r="AK99" t="inlineStr"/>
-      <c r="AL99" t="inlineStr"/>
-      <c r="AM99" t="inlineStr"/>
-      <c r="AN99" t="inlineStr"/>
-      <c r="AO99" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> WGG 02</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F100" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>NEFT</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>b2f965a8-1f4d-43ed-a280-423f02d9761d</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="inlineStr"/>
-      <c r="R100" t="inlineStr"/>
-      <c r="S100" t="inlineStr"/>
-      <c r="T100" t="inlineStr"/>
-      <c r="U100" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V100" t="n">
-        <v>507962</v>
-      </c>
-      <c r="W100" t="inlineStr"/>
-      <c r="X100" t="inlineStr">
-        <is>
-          <t>ESI REVENU RECOVERY  Rs 1015923, to pay 50 % RPA_ID : c47f2c22f4</t>
-        </is>
-      </c>
-      <c r="Y100" t="inlineStr">
-        <is>
-          <t>KOLKATTA</t>
-        </is>
-      </c>
-      <c r="Z100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA100" t="inlineStr">
-        <is>
-          <t>hrm@westernidc.com</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF100" t="inlineStr"/>
-      <c r="AG100" t="inlineStr"/>
-      <c r="AH100" t="inlineStr"/>
-      <c r="AI100" t="inlineStr"/>
-      <c r="AJ100" t="inlineStr"/>
-      <c r="AK100" t="inlineStr"/>
-      <c r="AL100" t="inlineStr"/>
-      <c r="AM100" t="inlineStr"/>
-      <c r="AN100" t="inlineStr"/>
-      <c r="AO100" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> WGG 02</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F101" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>NEFT</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>df1dbe62-d4fa-4d7c-a80d-388fa04b6df6</t>
-        </is>
-      </c>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
-      <c r="P101" t="inlineStr"/>
-      <c r="Q101" t="inlineStr"/>
-      <c r="R101" t="inlineStr"/>
-      <c r="S101" t="inlineStr"/>
-      <c r="T101" t="inlineStr"/>
-      <c r="U101" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V101" t="n">
-        <v>290000</v>
-      </c>
-      <c r="W101" t="inlineStr"/>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>AUGUST PF ARREAR KOCHI AND KONGAN APPROXIMATE RPA_ID : 84bd10b71a</t>
-        </is>
-      </c>
-      <c r="Y101" t="inlineStr">
-        <is>
-          <t>Kochi</t>
-        </is>
-      </c>
-      <c r="Z101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA101" t="inlineStr">
-        <is>
-          <t>hrm@westernidc.com</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF101" t="inlineStr"/>
-      <c r="AG101" t="inlineStr"/>
-      <c r="AH101" t="inlineStr"/>
-      <c r="AI101" t="inlineStr"/>
-      <c r="AJ101" t="inlineStr"/>
-      <c r="AK101" t="inlineStr"/>
-      <c r="AL101" t="inlineStr"/>
-      <c r="AM101" t="inlineStr"/>
-      <c r="AN101" t="inlineStr"/>
-      <c r="AO101" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>WGE 271</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F102" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>NEFT</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>SHEENA R NAIR</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>881d3eb6-d7a2-4557-9bd9-199b75e1a84d</t>
-        </is>
-      </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>ACC-50100161423549</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr">
-        <is>
-          <t>HDFC0000717</t>
-        </is>
-      </c>
-      <c r="O102" t="inlineStr"/>
-      <c r="P102" t="inlineStr"/>
-      <c r="Q102" t="inlineStr"/>
-      <c r="R102" t="inlineStr"/>
-      <c r="S102" t="inlineStr"/>
-      <c r="T102" t="inlineStr"/>
-      <c r="U102" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V102" t="n">
-        <v>2400</v>
-      </c>
-      <c r="W102" t="inlineStr"/>
-      <c r="X102" t="inlineStr">
-        <is>
-          <t>Room Stay Sabin Paid Staturday  Rs 2400/- (29.03.026 and 30.03.2026) RPA_ID : 636e9f72f3</t>
-        </is>
-      </c>
-      <c r="Y102" t="inlineStr">
-        <is>
-          <t>CHENNAI</t>
-        </is>
-      </c>
-      <c r="Z102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA102" t="inlineStr">
-        <is>
-          <t>hrm@westernidc.com</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF102" t="inlineStr"/>
-      <c r="AG102" t="inlineStr"/>
-      <c r="AH102" t="inlineStr"/>
-      <c r="AI102" t="inlineStr"/>
-      <c r="AJ102" t="inlineStr"/>
-      <c r="AK102" t="inlineStr"/>
-      <c r="AL102" t="inlineStr"/>
-      <c r="AM102" t="inlineStr"/>
-      <c r="AN102" t="inlineStr"/>
-      <c r="AO102" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>WGE 271</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F103" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>NEFT</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>SHEENA R NAIR</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>4719fbbc-3496-4dfa-9774-06bac71739fd</t>
-        </is>
-      </c>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>ACC-50100161423549</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t>HDFC0000717</t>
-        </is>
-      </c>
-      <c r="O103" t="inlineStr"/>
-      <c r="P103" t="inlineStr"/>
-      <c r="Q103" t="inlineStr"/>
-      <c r="R103" t="inlineStr"/>
-      <c r="S103" t="inlineStr"/>
-      <c r="T103" t="inlineStr"/>
-      <c r="U103" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V103" t="n">
-        <v>500</v>
-      </c>
-      <c r="W103" t="inlineStr"/>
-      <c r="X103" t="inlineStr">
-        <is>
-          <t>Food Expense paid to George for ST3 New joinee labours (27.03.2026 to 29.03.2026) RPA_ID : 263acb56e0</t>
-        </is>
-      </c>
-      <c r="Y103" t="inlineStr">
-        <is>
-          <t>GOA ST3</t>
-        </is>
-      </c>
-      <c r="Z103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA103" t="inlineStr">
-        <is>
-          <t>hrm@westernidc.com</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF103" t="inlineStr"/>
-      <c r="AG103" t="inlineStr"/>
-      <c r="AH103" t="inlineStr"/>
-      <c r="AI103" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>GOA</t>
-        </is>
-      </c>
-      <c r="AL103" t="inlineStr"/>
-      <c r="AM103" t="inlineStr"/>
-      <c r="AN103" t="inlineStr"/>
-      <c r="AO103" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>WGE 299</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F104" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>DCR</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>ARJUN(ONGC) SUPERVISOR</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>9c326a66-ee88-4da8-88a6-ad237ae80c1d</t>
-        </is>
-      </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>ACC-67329839060</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>SBIN0070076</t>
-        </is>
-      </c>
-      <c r="O104" t="inlineStr"/>
-      <c r="P104" t="inlineStr"/>
-      <c r="Q104" t="inlineStr"/>
-      <c r="R104" t="inlineStr"/>
-      <c r="S104" t="inlineStr"/>
-      <c r="T104" t="inlineStr"/>
-      <c r="U104" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V104" t="n">
-        <v>850</v>
-      </c>
-      <c r="W104" t="inlineStr"/>
-      <c r="X104" t="inlineStr">
-        <is>
-          <t>Travel Expense paid up to 19.03.2026 (20.03.2026 to 30.03.2026) @ 80 RPA_ID : 57837a9c0d</t>
-        </is>
-      </c>
-      <c r="Y104" t="inlineStr">
-        <is>
-          <t>ONGC</t>
-        </is>
-      </c>
-      <c r="Z104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA104" t="inlineStr">
-        <is>
-          <t>hrm@westernidc.com</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF104" t="inlineStr"/>
-      <c r="AG104" t="inlineStr"/>
-      <c r="AH104" t="inlineStr"/>
-      <c r="AI104" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr"/>
-      <c r="AL104" t="inlineStr"/>
-      <c r="AM104" t="inlineStr"/>
-      <c r="AN104" t="inlineStr"/>
-      <c r="AO104" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>WGE 299</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F105" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>DCR</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>ARJUN(ONGC) SUPERVISOR</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>5d08c05d-fa37-4085-b13f-657fedffb828</t>
-        </is>
-      </c>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>ACC-67329839060</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>SBIN0070076</t>
-        </is>
-      </c>
-      <c r="O105" t="inlineStr"/>
-      <c r="P105" t="inlineStr"/>
-      <c r="Q105" t="inlineStr"/>
-      <c r="R105" t="inlineStr"/>
-      <c r="S105" t="inlineStr"/>
-      <c r="T105" t="inlineStr"/>
-      <c r="U105" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V105" t="n">
-        <v>4800</v>
-      </c>
-      <c r="W105" t="inlineStr"/>
-      <c r="X105" t="inlineStr">
-        <is>
-          <t>Room stay Expense @ 1200 (28.03.2026 to 31.03.2026) RPA_ID : 307429bb90</t>
-        </is>
-      </c>
-      <c r="Y105" t="inlineStr">
-        <is>
-          <t>ONGC</t>
-        </is>
-      </c>
-      <c r="Z105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA105" t="inlineStr">
-        <is>
-          <t>hrm@westernidc.com</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF105" t="inlineStr"/>
-      <c r="AG105" t="inlineStr"/>
-      <c r="AH105" t="inlineStr"/>
-      <c r="AI105" t="inlineStr"/>
-      <c r="AJ105" t="inlineStr"/>
-      <c r="AK105" t="inlineStr"/>
-      <c r="AL105" t="inlineStr"/>
-      <c r="AM105" t="inlineStr"/>
-      <c r="AN105" t="inlineStr"/>
-      <c r="AO105" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>WGE 306</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F106" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>DCR</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>SABIN V V</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>e2dffae2-fb3e-4dfd-9a2a-150f41f07704</t>
-        </is>
-      </c>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>ACC-67274681749</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>SBIN0070812</t>
-        </is>
-      </c>
-      <c r="O106" t="inlineStr"/>
-      <c r="P106" t="inlineStr"/>
-      <c r="Q106" t="inlineStr"/>
-      <c r="R106" t="inlineStr"/>
-      <c r="S106" t="inlineStr"/>
-      <c r="T106" t="inlineStr"/>
-      <c r="U106" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V106" t="n">
-        <v>900</v>
-      </c>
-      <c r="W106" t="inlineStr"/>
-      <c r="X106" t="inlineStr">
-        <is>
-          <t>RoomStay 31.03.2026 @ 1100 (Advane 200 already paid) RPA_ID : cb5075fd79</t>
-        </is>
-      </c>
-      <c r="Y106" t="inlineStr">
-        <is>
-          <t>CHENNAI</t>
-        </is>
-      </c>
-      <c r="Z106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA106" t="inlineStr">
-        <is>
-          <t>hrm@westernidc.com</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF106" t="inlineStr"/>
-      <c r="AG106" t="inlineStr"/>
-      <c r="AH106" t="inlineStr"/>
-      <c r="AI106" t="inlineStr"/>
-      <c r="AJ106" t="inlineStr"/>
-      <c r="AK106" t="inlineStr"/>
-      <c r="AL106" t="inlineStr"/>
-      <c r="AM106" t="inlineStr"/>
-      <c r="AN106" t="inlineStr"/>
-      <c r="AO106" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>WGE 306</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F107" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>DCR</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>SABIN V V</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>dc487cbb-b765-4abb-b86f-1cbde319f520</t>
-        </is>
-      </c>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>ACC-67274681749</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr">
-        <is>
-          <t>SBIN0070812</t>
-        </is>
-      </c>
-      <c r="O107" t="inlineStr"/>
-      <c r="P107" t="inlineStr"/>
-      <c r="Q107" t="inlineStr"/>
-      <c r="R107" t="inlineStr"/>
-      <c r="S107" t="inlineStr"/>
-      <c r="T107" t="inlineStr"/>
-      <c r="U107" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V107" t="n">
-        <v>160</v>
-      </c>
-      <c r="W107" t="inlineStr"/>
-      <c r="X107" t="inlineStr">
-        <is>
-          <t>Travel Expense 29.03.2026 t0 31.03.2026 @ 80 RPA_ID : d0714dca11</t>
-        </is>
-      </c>
-      <c r="Y107" t="inlineStr">
-        <is>
-          <t>CHENNAI</t>
-        </is>
-      </c>
-      <c r="Z107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA107" t="inlineStr">
-        <is>
-          <t>hrm@westernidc.com</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF107" t="inlineStr"/>
-      <c r="AG107" t="inlineStr"/>
-      <c r="AH107" t="inlineStr"/>
-      <c r="AI107" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr"/>
-      <c r="AL107" t="inlineStr"/>
-      <c r="AM107" t="inlineStr"/>
-      <c r="AN107" t="inlineStr"/>
-      <c r="AO107" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>WGE 306</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F108" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>DCR</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>SABIN V V</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>0cf58cfe-64e4-4e88-9fc7-a19a5ffe2333</t>
-        </is>
-      </c>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>ACC-67274681749</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr">
-        <is>
-          <t>SBIN0070812</t>
-        </is>
-      </c>
-      <c r="O108" t="inlineStr"/>
-      <c r="P108" t="inlineStr"/>
-      <c r="Q108" t="inlineStr"/>
-      <c r="R108" t="inlineStr"/>
-      <c r="S108" t="inlineStr"/>
-      <c r="T108" t="inlineStr"/>
-      <c r="U108" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V108" t="n">
-        <v>500</v>
-      </c>
-      <c r="W108" t="inlineStr"/>
-      <c r="X108" t="inlineStr">
-        <is>
-          <t>Food expense  30.03.2026 to 31.03.2026 @ 250 RPA_ID : c82a088619</t>
-        </is>
-      </c>
-      <c r="Y108" t="inlineStr">
-        <is>
-          <t>CHENNAI</t>
-        </is>
-      </c>
-      <c r="Z108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA108" t="inlineStr">
-        <is>
-          <t>hrm@westernidc.com</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF108" t="inlineStr"/>
-      <c r="AG108" t="inlineStr"/>
-      <c r="AH108" t="inlineStr"/>
-      <c r="AI108" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ108" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AK108" t="inlineStr"/>
-      <c r="AL108" t="inlineStr"/>
-      <c r="AM108" t="inlineStr"/>
-      <c r="AN108" t="inlineStr"/>
-      <c r="AO108" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>WGE 87</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F109" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>DCR</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>Mary Ashna K P</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>0c052109-49d0-46e3-a61e-1bb9eec7533f</t>
-        </is>
-      </c>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>ACC-67216866751</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>SBIN0070150</t>
-        </is>
-      </c>
-      <c r="O109" t="inlineStr"/>
-      <c r="P109" t="inlineStr"/>
-      <c r="Q109" t="inlineStr"/>
-      <c r="R109" t="inlineStr"/>
-      <c r="S109" t="inlineStr"/>
-      <c r="T109" t="inlineStr"/>
-      <c r="U109" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V109" t="n">
-        <v>10802</v>
-      </c>
-      <c r="W109" t="inlineStr"/>
-      <c r="X109" t="inlineStr">
-        <is>
-          <t>Salary for the month of March 2026 RPA_ID : 7f6a5efdfe</t>
-        </is>
-      </c>
-      <c r="Y109" t="inlineStr">
-        <is>
-          <t>HO</t>
-        </is>
-      </c>
-      <c r="Z109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA109" t="inlineStr">
-        <is>
-          <t>hrm@westernidc.com</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF109" t="inlineStr"/>
-      <c r="AG109" t="inlineStr"/>
-      <c r="AH109" t="inlineStr"/>
-      <c r="AI109" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ109" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AK109" t="inlineStr">
-        <is>
-          <t>HO</t>
-        </is>
-      </c>
-      <c r="AL109" t="inlineStr"/>
-      <c r="AM109" t="inlineStr"/>
-      <c r="AN109" t="inlineStr"/>
-      <c r="AO109" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>WGE 132</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F110" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>NEFT</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>United India Insurance</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>9d1ed400-428a-42fd-beb4-0452142c6bd4</t>
-        </is>
-      </c>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>ACC-200999095210100100</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr">
-        <is>
-          <t>INDB0000007</t>
-        </is>
-      </c>
-      <c r="O110" t="inlineStr"/>
-      <c r="P110" t="inlineStr"/>
-      <c r="Q110" t="inlineStr"/>
-      <c r="R110" t="inlineStr"/>
-      <c r="S110" t="inlineStr"/>
-      <c r="T110" t="inlineStr"/>
-      <c r="U110" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V110" t="n">
-        <v>16551</v>
-      </c>
-      <c r="W110" t="inlineStr"/>
-      <c r="X110" t="inlineStr">
-        <is>
-          <t>Wellington Workmen Compensation Policy  (8 Workers) April 2026 to September 2026 RPA_ID : 02666ae70b</t>
-        </is>
-      </c>
-      <c r="Y110" t="inlineStr">
-        <is>
-          <t>IOCL WELLINGTON</t>
-        </is>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>URGENT</t>
-        </is>
-      </c>
-      <c r="AA110" t="inlineStr">
-        <is>
-          <t>hrm@westernidc.com</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF110" t="inlineStr"/>
-      <c r="AG110" t="inlineStr"/>
-      <c r="AH110" t="inlineStr"/>
-      <c r="AI110" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr"/>
-      <c r="AL110" t="inlineStr"/>
-      <c r="AM110" t="inlineStr"/>
-      <c r="AN110" t="inlineStr"/>
-      <c r="AO110" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>WGE 630</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F111" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>NEFT</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>MR MOHAMMAD SHAKIL</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>a5c82d5d-e921-4c4d-8398-0980a0189c8b</t>
-        </is>
-      </c>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>ACC-000234001100249</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr">
-        <is>
-          <t>IBKL01077BD</t>
-        </is>
-      </c>
-      <c r="O111" t="inlineStr"/>
-      <c r="P111" t="inlineStr"/>
-      <c r="Q111" t="inlineStr"/>
-      <c r="R111" t="inlineStr"/>
-      <c r="S111" t="inlineStr"/>
-      <c r="T111" t="inlineStr"/>
-      <c r="U111" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V111" t="n">
-        <v>200</v>
-      </c>
-      <c r="W111" t="inlineStr"/>
-      <c r="X111" t="inlineStr">
-        <is>
-          <t>Food Expense  30.03.2026 to 31.03.2026 @ 100 RPA_ID : 2828da3438</t>
-        </is>
-      </c>
-      <c r="Y111" t="inlineStr">
-        <is>
-          <t>ST3 GOA</t>
-        </is>
-      </c>
-      <c r="Z111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA111" t="inlineStr">
-        <is>
-          <t>hrm@westernidc.com</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF111" t="inlineStr"/>
-      <c r="AG111" t="inlineStr"/>
-      <c r="AH111" t="inlineStr"/>
-      <c r="AI111" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ111" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AK111" t="inlineStr">
-        <is>
-          <t>GOA</t>
-        </is>
-      </c>
-      <c r="AL111" t="inlineStr"/>
-      <c r="AM111" t="inlineStr"/>
-      <c r="AN111" t="inlineStr"/>
-      <c r="AO111" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>WGE 631</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F112" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>NEFT</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>MR MOHAMMAD ABID</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>4360dc33-f94e-4dae-986c-a0ea3a2f00fb</t>
-        </is>
-      </c>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>ACC-38340700009010</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr">
-        <is>
-          <t>PUNB0MBGB06</t>
-        </is>
-      </c>
-      <c r="O112" t="inlineStr"/>
-      <c r="P112" t="inlineStr"/>
-      <c r="Q112" t="inlineStr"/>
-      <c r="R112" t="inlineStr"/>
-      <c r="S112" t="inlineStr"/>
-      <c r="T112" t="inlineStr"/>
-      <c r="U112" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V112" t="n">
-        <v>200</v>
-      </c>
-      <c r="W112" t="inlineStr"/>
-      <c r="X112" t="inlineStr">
-        <is>
-          <t>Food Expense  30.03.2026 to 31.03.2026 @ 100 RPA_ID : 3139fd7baf</t>
-        </is>
-      </c>
-      <c r="Y112" t="inlineStr">
-        <is>
-          <t>ST3 GOA</t>
-        </is>
-      </c>
-      <c r="Z112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA112" t="inlineStr">
-        <is>
-          <t>hrm@westernidc.com</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF112" t="inlineStr"/>
-      <c r="AG112" t="inlineStr"/>
-      <c r="AH112" t="inlineStr"/>
-      <c r="AI112" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>GOA</t>
-        </is>
-      </c>
-      <c r="AL112" t="inlineStr"/>
-      <c r="AM112" t="inlineStr"/>
-      <c r="AN112" t="inlineStr"/>
-      <c r="AO112" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>WGE 236</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F113" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>NEFT</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>vishnu P. G (HULL)</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>3ecdccbb-63fb-4fd8-847d-157b285eb990</t>
-        </is>
-      </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>ACC-40561101027837</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr">
-        <is>
-          <t>KLGB0040561</t>
-        </is>
-      </c>
-      <c r="O113" t="inlineStr"/>
-      <c r="P113" t="inlineStr"/>
-      <c r="Q113" t="inlineStr"/>
-      <c r="R113" t="inlineStr"/>
-      <c r="S113" t="inlineStr"/>
-      <c r="T113" t="inlineStr"/>
-      <c r="U113" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V113" t="n">
-        <v>1950</v>
-      </c>
-      <c r="W113" t="inlineStr"/>
-      <c r="X113" t="inlineStr">
-        <is>
-          <t>GOA HUL GAS EXPENSE RPA_ID : 395394a164</t>
-        </is>
-      </c>
-      <c r="Y113" t="inlineStr">
-        <is>
-          <t>GOA HUL</t>
-        </is>
-      </c>
-      <c r="Z113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA113" t="inlineStr">
-        <is>
-          <t>hrm@westernidc.com</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF113" t="inlineStr"/>
-      <c r="AG113" t="inlineStr"/>
-      <c r="AH113" t="inlineStr"/>
-      <c r="AI113" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>GOA</t>
-        </is>
-      </c>
-      <c r="AL113" t="inlineStr"/>
-      <c r="AM113" t="inlineStr"/>
-      <c r="AN113" t="inlineStr"/>
-      <c r="AO113" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>WGE 461</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F114" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>DCR</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>SUGREEV</t>
-        </is>
-      </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>d261fac1-8361-47ab-be47-85ca6ac48b6c</t>
-        </is>
-      </c>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>ACC-59180985708</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t>IDIB000U511</t>
-        </is>
-      </c>
-      <c r="O114" t="inlineStr"/>
-      <c r="P114" t="inlineStr"/>
-      <c r="Q114" t="inlineStr"/>
-      <c r="R114" t="inlineStr"/>
-      <c r="S114" t="inlineStr"/>
-      <c r="T114" t="inlineStr"/>
-      <c r="U114" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V114" t="n">
-        <v>1950</v>
-      </c>
-      <c r="W114" t="inlineStr"/>
-      <c r="X114" t="inlineStr">
-        <is>
-          <t>GOA HUL GAS EXPENSE RPA_ID : 066ec44df1</t>
-        </is>
-      </c>
-      <c r="Y114" t="inlineStr">
-        <is>
-          <t>ST3 GOA</t>
-        </is>
-      </c>
-      <c r="Z114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA114" t="inlineStr">
-        <is>
-          <t>hrm@westernidc.com</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE114" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF114" t="inlineStr"/>
-      <c r="AG114" t="inlineStr"/>
-      <c r="AH114" t="inlineStr"/>
-      <c r="AI114" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AK114" t="inlineStr">
-        <is>
-          <t>GOA</t>
-        </is>
-      </c>
-      <c r="AL114" t="inlineStr"/>
-      <c r="AM114" t="inlineStr"/>
-      <c r="AN114" t="inlineStr"/>
-      <c r="AO114" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> WGG 02</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F115" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>NEFT</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>0b82e5ef-7c28-4c27-9635-ae4ed8fb41ec</t>
-        </is>
-      </c>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
-      <c r="P115" t="inlineStr"/>
-      <c r="Q115" t="inlineStr"/>
-      <c r="R115" t="inlineStr"/>
-      <c r="S115" t="inlineStr"/>
-      <c r="T115" t="inlineStr"/>
-      <c r="U115" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V115" t="n">
-        <v>4000</v>
-      </c>
-      <c r="W115" t="inlineStr"/>
-      <c r="X115" t="inlineStr">
-        <is>
-          <t>Ticket Expense MP to Bellari (Rigger and Insulator/blaster) RPA_ID : 2b286755fe</t>
-        </is>
-      </c>
-      <c r="Y115" t="inlineStr">
-        <is>
-          <t>BELLARI</t>
-        </is>
-      </c>
-      <c r="Z115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA115" t="inlineStr">
-        <is>
-          <t>hrm@westernidc.com</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF115" t="inlineStr"/>
-      <c r="AG115" t="inlineStr"/>
-      <c r="AH115" t="inlineStr"/>
-      <c r="AI115" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ115" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AK115" t="inlineStr">
-        <is>
-          <t>BELLARI</t>
-        </is>
-      </c>
-      <c r="AL115" t="inlineStr"/>
-      <c r="AM115" t="inlineStr"/>
-      <c r="AN115" t="inlineStr"/>
-      <c r="AO115" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>WGE 638</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F116" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>NEFT</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>Vaishali crane hiring service</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>73a2d361-4e7c-42ab-b682-a4eadbd10494</t>
-        </is>
-      </c>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>ACC-01692560001256</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr">
-        <is>
-          <t>HDFC0000169</t>
-        </is>
-      </c>
-      <c r="O116" t="inlineStr"/>
-      <c r="P116" t="inlineStr"/>
-      <c r="Q116" t="inlineStr"/>
-      <c r="R116" t="inlineStr"/>
-      <c r="S116" t="inlineStr"/>
-      <c r="T116" t="inlineStr"/>
-      <c r="U116" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V116" t="n">
-        <v>76700</v>
-      </c>
-      <c r="W116" t="inlineStr"/>
-      <c r="X116" t="inlineStr">
-        <is>
-          <t>Being rental service for crane(A/C NO:-01692560001256 IFSC :-HDFC0000169) (19-03-2026) RPA_ID : 5420a0196f</t>
-        </is>
-      </c>
-      <c r="Y116" t="inlineStr">
-        <is>
-          <t>ONGC JETTY</t>
-        </is>
-      </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>SITE EXPENSES</t>
-        </is>
-      </c>
-      <c r="AA116" t="inlineStr">
-        <is>
-          <t>procexewestern@gmail.com</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF116" t="inlineStr"/>
-      <c r="AG116" t="inlineStr"/>
-      <c r="AH116" t="inlineStr"/>
-      <c r="AI116" t="inlineStr"/>
-      <c r="AJ116" t="inlineStr"/>
-      <c r="AK116" t="inlineStr"/>
-      <c r="AL116" t="inlineStr"/>
-      <c r="AM116" t="inlineStr"/>
-      <c r="AN116" t="inlineStr"/>
-      <c r="AO116" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>WGE 637</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F117" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>NEFT</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>Vraj corporation</t>
-        </is>
-      </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>977948ba-c231-4605-802a-00739c126d30</t>
-        </is>
-      </c>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>ACC-016505005896</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr">
-        <is>
-          <t>ICIC0000165</t>
-        </is>
-      </c>
-      <c r="O117" t="inlineStr"/>
-      <c r="P117" t="inlineStr"/>
-      <c r="Q117" t="inlineStr"/>
-      <c r="R117" t="inlineStr"/>
-      <c r="S117" t="inlineStr"/>
-      <c r="T117" t="inlineStr"/>
-      <c r="U117" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V117" t="n">
-        <v>24741</v>
-      </c>
-      <c r="W117" t="inlineStr"/>
-      <c r="X117" t="inlineStr">
-        <is>
-          <t>Plesae return the GSTR1  amount to the vendor (19-03-2026) RPA_ID : 26293f6cfa</t>
-        </is>
-      </c>
-      <c r="Y117" t="inlineStr">
-        <is>
-          <t>BPCL BALLARI</t>
-        </is>
-      </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>SITE EXPENSES</t>
-        </is>
-      </c>
-      <c r="AA117" t="inlineStr">
-        <is>
-          <t>procexewestern@gmail.com</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF117" t="inlineStr"/>
-      <c r="AG117" t="inlineStr"/>
-      <c r="AH117" t="inlineStr"/>
-      <c r="AI117" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AK117" t="inlineStr"/>
-      <c r="AL117" t="inlineStr"/>
-      <c r="AM117" t="inlineStr"/>
-      <c r="AN117" t="inlineStr"/>
-      <c r="AO117" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>WGE 636</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F118" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>NEFT</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>Raj nath yadav</t>
-        </is>
-      </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>5d651e6e-9aa8-4a4c-9cbc-3844820d62f1</t>
-        </is>
-      </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>ACC-429502010014495</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr">
-        <is>
-          <t>UBIN0542954</t>
-        </is>
-      </c>
-      <c r="O118" t="inlineStr"/>
-      <c r="P118" t="inlineStr"/>
-      <c r="Q118" t="inlineStr"/>
-      <c r="R118" t="inlineStr"/>
-      <c r="S118" t="inlineStr"/>
-      <c r="T118" t="inlineStr"/>
-      <c r="U118" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V118" t="n">
-        <v>60000</v>
-      </c>
-      <c r="W118" t="inlineStr"/>
-      <c r="X118" t="inlineStr">
-        <is>
-          <t>Being hot work channel welding work (19-03-2026) RPA_ID : 2a5271af26</t>
-        </is>
-      </c>
-      <c r="Y118" t="inlineStr">
-        <is>
-          <t>NGOP CHENNAI</t>
-        </is>
-      </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>SITE EXPENSES</t>
-        </is>
-      </c>
-      <c r="AA118" t="inlineStr">
-        <is>
-          <t>procexewestern@gmail.com</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF118" t="inlineStr"/>
-      <c r="AG118" t="inlineStr"/>
-      <c r="AH118" t="inlineStr"/>
-      <c r="AI118" t="inlineStr"/>
-      <c r="AJ118" t="inlineStr"/>
-      <c r="AK118" t="inlineStr"/>
-      <c r="AL118" t="inlineStr"/>
-      <c r="AM118" t="inlineStr"/>
-      <c r="AN118" t="inlineStr"/>
-      <c r="AO118" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>WGE 635</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F119" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>DCR</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>S B EARTH MOVERS AND CRANE SERVICES</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>82239466-52e7-4d59-a12d-754e787d3efb</t>
-        </is>
-      </c>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>ACC-10120420457</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr">
-        <is>
-          <t>IDFB0081081</t>
-        </is>
-      </c>
-      <c r="O119" t="inlineStr"/>
-      <c r="P119" t="inlineStr"/>
-      <c r="Q119" t="inlineStr"/>
-      <c r="R119" t="inlineStr"/>
-      <c r="S119" t="inlineStr"/>
-      <c r="T119" t="inlineStr"/>
-      <c r="U119" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V119" t="n">
-        <v>149877.6</v>
-      </c>
-      <c r="W119" t="inlineStr"/>
-      <c r="X119" t="inlineStr">
-        <is>
-          <t>Being rent for JCB ,Hydra,Braker and farrana crane( total 324877.6  ,90000 paid on 20-03-2026 balance amount remaining (19-03-2026) RPA_ID : 2f76ef7a18</t>
-        </is>
-      </c>
-      <c r="Y119" t="inlineStr">
-        <is>
-          <t>BPCL BALLARI</t>
-        </is>
-      </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>SITE EXPENSES</t>
-        </is>
-      </c>
-      <c r="AA119" t="inlineStr">
-        <is>
-          <t>procexewestern@gmail.com</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF119" t="inlineStr"/>
-      <c r="AG119" t="inlineStr"/>
-      <c r="AH119" t="inlineStr"/>
-      <c r="AI119" t="inlineStr"/>
-      <c r="AJ119" t="inlineStr"/>
-      <c r="AK119" t="inlineStr"/>
-      <c r="AL119" t="inlineStr"/>
-      <c r="AM119" t="inlineStr"/>
-      <c r="AN119" t="inlineStr"/>
-      <c r="AO119" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>WGE 527</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F120" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>NEFT</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>ELECTRONEX TECHNOLOGIES</t>
-        </is>
-      </c>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>17234d65-0b19-470e-8899-83bc8ac7d546</t>
-        </is>
-      </c>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>ACC-13160200024922</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr">
-        <is>
-          <t>FDRL0001316</t>
-        </is>
-      </c>
-      <c r="O120" t="inlineStr"/>
-      <c r="P120" t="inlineStr"/>
-      <c r="Q120" t="inlineStr"/>
-      <c r="R120" t="inlineStr"/>
-      <c r="S120" t="inlineStr"/>
-      <c r="T120" t="inlineStr"/>
-      <c r="U120" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V120" t="n">
-        <v>8700</v>
-      </c>
-      <c r="W120" t="inlineStr"/>
-      <c r="X120" t="inlineStr">
-        <is>
-          <t>Being supply of WIFI camera to JELIN sir flat (A/C NO:-13160200024922
-IFSC :-FDRL000116) 7300 Paid balance amount remaining RPA_ID : 6185f90bd9</t>
-        </is>
-      </c>
-      <c r="Y120" t="inlineStr">
-        <is>
-          <t>Maintenance(Jelin sir)</t>
-        </is>
-      </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>MAINTENANCE</t>
-        </is>
-      </c>
-      <c r="AA120" t="inlineStr">
-        <is>
-          <t>procexewestern@gmail.com</t>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF120" t="inlineStr"/>
-      <c r="AG120" t="inlineStr"/>
-      <c r="AH120" t="inlineStr"/>
-      <c r="AI120" t="inlineStr"/>
-      <c r="AJ120" t="inlineStr"/>
-      <c r="AK120" t="inlineStr"/>
-      <c r="AL120" t="inlineStr"/>
-      <c r="AM120" t="inlineStr"/>
-      <c r="AN120" t="inlineStr"/>
-      <c r="AO120" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>WGE 633</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr"/>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>37928d5c-2918-4547-9899-e8d6241e3393</t>
-        </is>
-      </c>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr"/>
-      <c r="P121" t="inlineStr"/>
-      <c r="Q121" t="inlineStr"/>
-      <c r="R121" t="inlineStr"/>
-      <c r="S121" t="inlineStr"/>
-      <c r="T121" t="inlineStr"/>
-      <c r="U121" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V121" t="n">
-        <v>8100</v>
-      </c>
-      <c r="W121" t="inlineStr"/>
-      <c r="X121" t="inlineStr">
-        <is>
-          <t>Being rental of grasscutting machine and petrol expenses (A/C NO:-  32555551936 ,IFSC :- SBIN0001890)
-(23-03-2026) RPA_ID : 9852cd6c2b</t>
-        </is>
-      </c>
-      <c r="Y121" t="inlineStr">
-        <is>
-          <t>HPCL ELATHOOR</t>
-        </is>
-      </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>SITE EXPENSES</t>
-        </is>
-      </c>
-      <c r="AA121" t="inlineStr">
-        <is>
-          <t>procexewestern@gmail.com</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF121" t="inlineStr"/>
-      <c r="AG121" t="inlineStr"/>
-      <c r="AH121" t="inlineStr"/>
-      <c r="AI121" t="inlineStr"/>
-      <c r="AJ121" t="inlineStr"/>
-      <c r="AK121" t="inlineStr">
-        <is>
-          <t>HO</t>
-        </is>
-      </c>
-      <c r="AL121" t="inlineStr"/>
-      <c r="AM121" t="inlineStr"/>
-      <c r="AN121" t="inlineStr"/>
-      <c r="AO121" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>WGE 600</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F122" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>NEFT</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>SHARUN EARTH MOVERS</t>
-        </is>
-      </c>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t>c9f56923-eb5e-416a-b795-3fa22642586e</t>
-        </is>
-      </c>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>ACC-40422100006913</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr">
-        <is>
-          <t>KLGB0040422</t>
-        </is>
-      </c>
-      <c r="O122" t="inlineStr"/>
-      <c r="P122" t="inlineStr"/>
-      <c r="Q122" t="inlineStr"/>
-      <c r="R122" t="inlineStr"/>
-      <c r="S122" t="inlineStr"/>
-      <c r="T122" t="inlineStr"/>
-      <c r="U122" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V122" t="n">
-        <v>28960</v>
-      </c>
-      <c r="W122" t="inlineStr"/>
-      <c r="X122" t="inlineStr">
-        <is>
-          <t>Being Rental charges for JCB (A/C NO ;- 40422100006913 ,IFSC KLGB0040422) ( From 1/03/26 to 19/03/26)(25,000 paid on 28/03/26 balance amount remaining) RPA_ID : 0b0e65383b</t>
-        </is>
-      </c>
-      <c r="Y122" t="inlineStr">
-        <is>
-          <t>IOCL PAPPINISSERI</t>
-        </is>
-      </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>SITE EXPENSES</t>
-        </is>
-      </c>
-      <c r="AA122" t="inlineStr">
-        <is>
-          <t>procexewestern@gmail.com</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF122" t="inlineStr"/>
-      <c r="AG122" t="inlineStr"/>
-      <c r="AH122" t="inlineStr"/>
-      <c r="AI122" t="inlineStr"/>
-      <c r="AJ122" t="inlineStr"/>
-      <c r="AK122" t="inlineStr"/>
-      <c r="AL122" t="inlineStr"/>
-      <c r="AM122" t="inlineStr"/>
-      <c r="AN122" t="inlineStr"/>
-      <c r="AO122" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>WGE 633</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr"/>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>d99b7e21-a3cf-4434-b3ce-f719d8a4452e</t>
-        </is>
-      </c>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
-      <c r="P123" t="inlineStr"/>
-      <c r="Q123" t="inlineStr"/>
-      <c r="R123" t="inlineStr"/>
-      <c r="S123" t="inlineStr"/>
-      <c r="T123" t="inlineStr"/>
-      <c r="U123" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V123" t="n">
-        <v>4400</v>
-      </c>
-      <c r="W123" t="inlineStr"/>
-      <c r="X123" t="inlineStr">
-        <is>
-          <t>3.5 mm nylon grass trimming cord 100 meter -1000
-Grass cutting head -5*500=2500
-Grass cutting blade -3nos=3*300=900 RPA_ID : 774842dc47</t>
-        </is>
-      </c>
-      <c r="Y123" t="inlineStr">
-        <is>
-          <t>HPCL ELATHOOR</t>
-        </is>
-      </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>SITE EXPENSES</t>
-        </is>
-      </c>
-      <c r="AA123" t="inlineStr">
-        <is>
-          <t>procexewestern@gmail.com</t>
-        </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF123" t="inlineStr"/>
-      <c r="AG123" t="inlineStr"/>
-      <c r="AH123" t="inlineStr"/>
-      <c r="AI123" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ123" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AK123" t="inlineStr">
-        <is>
-          <t>HO</t>
-        </is>
-      </c>
-      <c r="AL123" t="inlineStr"/>
-      <c r="AM123" t="inlineStr"/>
-      <c r="AN123" t="inlineStr"/>
-      <c r="AO123" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>WGE 592</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F124" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>NEFT</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>FINE HARDWARE</t>
-        </is>
-      </c>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>3b2d2527-bfa2-4840-9d16-65338ea8ba22</t>
-        </is>
-      </c>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>ACC-3878002100002069</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr">
-        <is>
-          <t>PUNB0387800</t>
-        </is>
-      </c>
-      <c r="O124" t="inlineStr"/>
-      <c r="P124" t="inlineStr"/>
-      <c r="Q124" t="inlineStr"/>
-      <c r="R124" t="inlineStr"/>
-      <c r="S124" t="inlineStr"/>
-      <c r="T124" t="inlineStr"/>
-      <c r="U124" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V124" t="n">
-        <v>16690</v>
-      </c>
-      <c r="W124" t="inlineStr"/>
-      <c r="X124" t="inlineStr">
-        <is>
-          <t>Being purchasing of chicken mesh,washer and nails (A/C NO:- 3878002100002069 ,IFSC :-PUNB0387800) RPA_ID : b0197c3d1a</t>
-        </is>
-      </c>
-      <c r="Y124" t="inlineStr">
-        <is>
-          <t>IOCL PAPPINISSERI</t>
-        </is>
-      </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>SITE EXPENSES</t>
-        </is>
-      </c>
-      <c r="AA124" t="inlineStr">
-        <is>
-          <t>procexewestern@gmail.com</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF124" t="inlineStr"/>
-      <c r="AG124" t="inlineStr"/>
-      <c r="AH124" t="inlineStr"/>
-      <c r="AI124" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ124" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AK124" t="inlineStr"/>
-      <c r="AL124" t="inlineStr"/>
-      <c r="AM124" t="inlineStr"/>
-      <c r="AN124" t="inlineStr"/>
-      <c r="AO124" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>WGE 551</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F125" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>NEFT</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>PRUDENT GLOBAL SAFETY SOLUTIONS</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>8dfe271a-f5ed-4245-8a5f-19e8dfddbe0d</t>
-        </is>
-      </c>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>ACC-169105001359</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr">
-        <is>
-          <t>ICIC0001691</t>
-        </is>
-      </c>
-      <c r="O125" t="inlineStr"/>
-      <c r="P125" t="inlineStr"/>
-      <c r="Q125" t="inlineStr"/>
-      <c r="R125" t="inlineStr"/>
-      <c r="S125" t="inlineStr"/>
-      <c r="T125" t="inlineStr"/>
-      <c r="U125" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V125" t="n">
-        <v>630</v>
-      </c>
-      <c r="W125" t="inlineStr"/>
-      <c r="X125" t="inlineStr">
-        <is>
-          <t>Being purcahsing of safety vest (A/C NO:-169105001359 IFSC:- ICIC0001691) RPA_ID : 412c5dd697</t>
-        </is>
-      </c>
-      <c r="Y125" t="inlineStr">
-        <is>
-          <t>IOCL THIRUVANIYOOR</t>
-        </is>
-      </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>SITE EXPENSES</t>
-        </is>
-      </c>
-      <c r="AA125" t="inlineStr">
-        <is>
-          <t>procexewestern@gmail.com</t>
-        </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF125" t="inlineStr"/>
-      <c r="AG125" t="inlineStr"/>
-      <c r="AH125" t="inlineStr"/>
-      <c r="AI125" t="inlineStr"/>
-      <c r="AJ125" t="inlineStr"/>
-      <c r="AK125" t="inlineStr"/>
-      <c r="AL125" t="inlineStr"/>
-      <c r="AM125" t="inlineStr"/>
-      <c r="AN125" t="inlineStr"/>
-      <c r="AO125" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>WGE 639</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F126" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>NEFT</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>BOMBAY SAFETY</t>
-        </is>
-      </c>
-      <c r="L126" t="inlineStr">
-        <is>
-          <t>33b271ac-a121-473f-9220-c46621a5c8ea</t>
-        </is>
-      </c>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>ACC-920020067784355</t>
-        </is>
-      </c>
-      <c r="N126" t="inlineStr">
-        <is>
-          <t>UTIB0001469</t>
-        </is>
-      </c>
-      <c r="O126" t="inlineStr"/>
-      <c r="P126" t="inlineStr"/>
-      <c r="Q126" t="inlineStr"/>
-      <c r="R126" t="inlineStr"/>
-      <c r="S126" t="inlineStr"/>
-      <c r="T126" t="inlineStr"/>
-      <c r="U126" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V126" t="n">
-        <v>11151</v>
-      </c>
-      <c r="W126" t="inlineStr"/>
-      <c r="X126" t="inlineStr">
-        <is>
-          <t>Being purcahsing of boiler suit and safety shoes (A/C NO:-920020067784355 IFSC :-UTIB0001469) RPA_ID : 22c9786d36</t>
-        </is>
-      </c>
-      <c r="Y126" t="inlineStr">
-        <is>
-          <t>HPCL Mumbai</t>
-        </is>
-      </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>SITE EXPENSES</t>
-        </is>
-      </c>
-      <c r="AA126" t="inlineStr">
-        <is>
-          <t>procexewestern@gmail.com</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF126" t="inlineStr"/>
-      <c r="AG126" t="inlineStr"/>
-      <c r="AH126" t="inlineStr"/>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AJ126" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="AK126" t="inlineStr"/>
-      <c r="AL126" t="inlineStr"/>
-      <c r="AM126" t="inlineStr"/>
-      <c r="AN126" t="inlineStr"/>
-      <c r="AO126" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>WGE 551</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>286962</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>Western Interior Designers &amp; Marine Contractors</t>
-        </is>
-      </c>
-      <c r="F127" t="n">
-        <v>34413429360</v>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>NEFT</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>SBIN0003229</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>AAAFW8862C</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>32AAAFW8862C1Z9</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>PRUDENT GLOBAL SAFETY SOLUTIONS</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>00e3c24d-f393-4503-9700-d5ab5b15cf18</t>
-        </is>
-      </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>ACC-169105001359</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr">
-        <is>
-          <t>ICIC0001691</t>
-        </is>
-      </c>
-      <c r="O127" t="inlineStr"/>
-      <c r="P127" t="inlineStr"/>
-      <c r="Q127" t="inlineStr"/>
-      <c r="R127" t="inlineStr"/>
-      <c r="S127" t="inlineStr"/>
-      <c r="T127" t="inlineStr"/>
-      <c r="U127" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="V127" t="n">
-        <v>5316</v>
-      </c>
-      <c r="W127" t="inlineStr"/>
-      <c r="X127" t="inlineStr">
-        <is>
-          <t>Being purchasing of reflective tape ,barricaution tape(A/C NO:-169105001359 IFSC:- ICIC0001691) RPA_ID : a563936139</t>
-        </is>
-      </c>
-      <c r="Y127" t="inlineStr">
-        <is>
-          <t>IOCL THIRUVANIYOOR</t>
-        </is>
-      </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>SITE EXPENSES</t>
-        </is>
-      </c>
-      <c r="AA127" t="inlineStr">
-        <is>
-          <t>procexewestern@gmail.com</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>ESTIMATION NOT MATCHED</t>
-        </is>
-      </c>
-      <c r="AC127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF127" t="inlineStr"/>
-      <c r="AG127" t="inlineStr"/>
-      <c r="AH127" t="inlineStr"/>
-      <c r="AI127" t="inlineStr"/>
-      <c r="AJ127" t="inlineStr"/>
-      <c r="AK127" t="inlineStr"/>
-      <c r="AL127" t="inlineStr"/>
-      <c r="AM127" t="inlineStr"/>
-      <c r="AN127" t="inlineStr"/>
-      <c r="AO127" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PENDING_APPROVAL_SHEET.xlsx
+++ b/PENDING_APPROVAL_SHEET.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO220"/>
+  <dimension ref="A1:AO243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -744,12 +744,12 @@
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr"/>
@@ -873,8 +873,16 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr"/>
@@ -986,8 +994,16 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
@@ -1109,8 +1125,16 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
@@ -1232,8 +1256,16 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
@@ -1355,8 +1387,16 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
@@ -1478,8 +1518,16 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
@@ -1601,8 +1649,16 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
@@ -1724,8 +1780,16 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="inlineStr"/>
@@ -1847,8 +1911,16 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr"/>
       <c r="AM11" t="inlineStr"/>
@@ -1970,8 +2042,16 @@
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
-      <c r="AJ12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr"/>
       <c r="AM12" t="inlineStr"/>
@@ -2093,8 +2173,16 @@
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="inlineStr"/>
       <c r="AM13" t="inlineStr"/>
@@ -2216,8 +2304,16 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="inlineStr"/>
       <c r="AM14" t="inlineStr"/>
@@ -2339,8 +2435,16 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr"/>
-      <c r="AJ15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="inlineStr"/>
       <c r="AM15" t="inlineStr"/>
@@ -2462,8 +2566,16 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr"/>
-      <c r="AJ16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK16" t="inlineStr"/>
       <c r="AL16" t="inlineStr"/>
       <c r="AM16" t="inlineStr"/>
@@ -2589,8 +2701,16 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
-      <c r="AJ17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="inlineStr"/>
       <c r="AM17" t="inlineStr"/>
@@ -2714,8 +2834,16 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
-      <c r="AJ18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="inlineStr"/>
       <c r="AM18" t="inlineStr"/>
@@ -2837,8 +2965,16 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr"/>
-      <c r="AJ19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK19" t="inlineStr">
         <is>
           <t>HO</t>
@@ -2964,8 +3100,16 @@
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="inlineStr"/>
-      <c r="AJ20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK20" t="inlineStr">
         <is>
           <t>HO</t>
@@ -3091,8 +3235,16 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr"/>
-      <c r="AJ21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK21" t="inlineStr">
         <is>
           <t>HO</t>
@@ -3218,8 +3370,16 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr"/>
-      <c r="AI22" t="inlineStr"/>
-      <c r="AJ22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK22" t="inlineStr">
         <is>
           <t>HO</t>
@@ -3345,8 +3505,16 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="inlineStr"/>
-      <c r="AJ23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK23" t="inlineStr">
         <is>
           <t>HO</t>
@@ -3472,8 +3640,16 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="inlineStr"/>
-      <c r="AI24" t="inlineStr"/>
-      <c r="AJ24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK24" t="inlineStr">
         <is>
           <t>HO</t>
@@ -3599,8 +3775,16 @@
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr"/>
-      <c r="AI25" t="inlineStr"/>
-      <c r="AJ25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK25" t="inlineStr">
         <is>
           <t>HO</t>
@@ -3728,8 +3912,16 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr"/>
-      <c r="AI26" t="inlineStr"/>
-      <c r="AJ26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK26" t="inlineStr">
         <is>
           <t>ONGC ELECTRICAL</t>
@@ -3857,8 +4049,16 @@
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr"/>
-      <c r="AI27" t="inlineStr"/>
-      <c r="AJ27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK27" t="inlineStr"/>
       <c r="AL27" t="inlineStr"/>
       <c r="AM27" t="inlineStr"/>
@@ -3982,8 +4182,16 @@
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="inlineStr"/>
-      <c r="AI28" t="inlineStr"/>
-      <c r="AJ28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK28" t="inlineStr">
         <is>
           <t>ONGC ELECTRICAL</t>
@@ -4111,8 +4319,16 @@
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="inlineStr"/>
-      <c r="AI29" t="inlineStr"/>
-      <c r="AJ29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK29" t="inlineStr">
         <is>
           <t>ONGC IPSHEM</t>
@@ -4240,8 +4456,16 @@
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="inlineStr"/>
-      <c r="AI30" t="inlineStr"/>
-      <c r="AJ30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK30" t="inlineStr"/>
       <c r="AL30" t="inlineStr"/>
       <c r="AM30" t="inlineStr"/>
@@ -4365,8 +4589,16 @@
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr"/>
-      <c r="AI31" t="inlineStr"/>
-      <c r="AJ31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK31" t="inlineStr"/>
       <c r="AL31" t="inlineStr"/>
       <c r="AM31" t="inlineStr"/>
@@ -4490,8 +4722,16 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr"/>
-      <c r="AI32" t="inlineStr"/>
-      <c r="AJ32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK32" t="inlineStr"/>
       <c r="AL32" t="inlineStr"/>
       <c r="AM32" t="inlineStr"/>
@@ -4615,8 +4855,16 @@
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr"/>
-      <c r="AI33" t="inlineStr"/>
-      <c r="AJ33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK33" t="inlineStr"/>
       <c r="AL33" t="inlineStr"/>
       <c r="AM33" t="inlineStr"/>
@@ -4741,8 +4989,16 @@
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr"/>
-      <c r="AI34" t="inlineStr"/>
-      <c r="AJ34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK34" t="inlineStr"/>
       <c r="AL34" t="inlineStr"/>
       <c r="AM34" t="inlineStr"/>
@@ -4868,8 +5124,16 @@
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="inlineStr"/>
-      <c r="AI35" t="inlineStr"/>
-      <c r="AJ35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK35" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -4998,8 +5262,16 @@
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="inlineStr"/>
-      <c r="AI36" t="inlineStr"/>
-      <c r="AJ36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK36" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -5128,8 +5400,16 @@
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="inlineStr"/>
-      <c r="AI37" t="inlineStr"/>
-      <c r="AJ37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK37" t="inlineStr">
         <is>
           <t>HO</t>
@@ -5257,8 +5537,16 @@
       <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="inlineStr"/>
-      <c r="AI38" t="inlineStr"/>
-      <c r="AJ38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK38" t="inlineStr"/>
       <c r="AL38" t="inlineStr"/>
       <c r="AM38" t="inlineStr"/>
@@ -5382,8 +5670,16 @@
       <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="inlineStr"/>
       <c r="AH39" t="inlineStr"/>
-      <c r="AI39" t="inlineStr"/>
-      <c r="AJ39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK39" t="inlineStr"/>
       <c r="AL39" t="inlineStr"/>
       <c r="AM39" t="inlineStr"/>
@@ -5507,8 +5803,16 @@
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="inlineStr"/>
       <c r="AH40" t="inlineStr"/>
-      <c r="AI40" t="inlineStr"/>
-      <c r="AJ40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK40" t="inlineStr"/>
       <c r="AL40" t="inlineStr"/>
       <c r="AM40" t="inlineStr"/>
@@ -5632,8 +5936,16 @@
       <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="inlineStr"/>
-      <c r="AI41" t="inlineStr"/>
-      <c r="AJ41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK41" t="inlineStr"/>
       <c r="AL41" t="inlineStr"/>
       <c r="AM41" t="inlineStr"/>
@@ -5757,8 +6069,16 @@
       <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="inlineStr"/>
       <c r="AH42" t="inlineStr"/>
-      <c r="AI42" t="inlineStr"/>
-      <c r="AJ42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK42" t="inlineStr"/>
       <c r="AL42" t="inlineStr"/>
       <c r="AM42" t="inlineStr"/>
@@ -5878,8 +6198,16 @@
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="inlineStr"/>
       <c r="AH43" t="inlineStr"/>
-      <c r="AI43" t="inlineStr"/>
-      <c r="AJ43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK43" t="inlineStr"/>
       <c r="AL43" t="inlineStr"/>
       <c r="AM43" t="inlineStr"/>
@@ -6003,8 +6331,16 @@
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="inlineStr"/>
-      <c r="AI44" t="inlineStr"/>
-      <c r="AJ44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK44" t="inlineStr"/>
       <c r="AL44" t="inlineStr"/>
       <c r="AM44" t="inlineStr"/>
@@ -6120,8 +6456,16 @@
       <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="inlineStr"/>
       <c r="AH45" t="inlineStr"/>
-      <c r="AI45" t="inlineStr"/>
-      <c r="AJ45" t="inlineStr"/>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK45" t="inlineStr"/>
       <c r="AL45" t="inlineStr"/>
       <c r="AM45" t="inlineStr"/>
@@ -6245,8 +6589,16 @@
       <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="inlineStr"/>
       <c r="AH46" t="inlineStr"/>
-      <c r="AI46" t="inlineStr"/>
-      <c r="AJ46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK46" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -6374,8 +6726,16 @@
       <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="inlineStr"/>
       <c r="AH47" t="inlineStr"/>
-      <c r="AI47" t="inlineStr"/>
-      <c r="AJ47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK47" t="inlineStr"/>
       <c r="AL47" t="inlineStr"/>
       <c r="AM47" t="inlineStr"/>
@@ -6500,8 +6860,16 @@
       <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="inlineStr"/>
       <c r="AH48" t="inlineStr"/>
-      <c r="AI48" t="inlineStr"/>
-      <c r="AJ48" t="inlineStr"/>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK48" t="inlineStr">
         <is>
           <t>ONGC IPSHEM</t>
@@ -6629,8 +6997,16 @@
       <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="inlineStr"/>
       <c r="AH49" t="inlineStr"/>
-      <c r="AI49" t="inlineStr"/>
-      <c r="AJ49" t="inlineStr"/>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK49" t="inlineStr"/>
       <c r="AL49" t="inlineStr"/>
       <c r="AM49" t="inlineStr"/>
@@ -6758,8 +7134,16 @@
       <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="inlineStr"/>
       <c r="AH50" t="inlineStr"/>
-      <c r="AI50" t="inlineStr"/>
-      <c r="AJ50" t="inlineStr"/>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK50" t="inlineStr"/>
       <c r="AL50" t="inlineStr"/>
       <c r="AM50" t="inlineStr"/>
@@ -6884,8 +7268,16 @@
       <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="inlineStr"/>
       <c r="AH51" t="inlineStr"/>
-      <c r="AI51" t="inlineStr"/>
-      <c r="AJ51" t="inlineStr"/>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK51" t="inlineStr"/>
       <c r="AL51" t="inlineStr"/>
       <c r="AM51" t="inlineStr"/>
@@ -7013,8 +7405,16 @@
       <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="inlineStr"/>
       <c r="AH52" t="inlineStr"/>
-      <c r="AI52" t="inlineStr"/>
-      <c r="AJ52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK52" t="inlineStr"/>
       <c r="AL52" t="inlineStr"/>
       <c r="AM52" t="inlineStr"/>
@@ -7138,8 +7538,16 @@
       <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="inlineStr"/>
       <c r="AH53" t="inlineStr"/>
-      <c r="AI53" t="inlineStr"/>
-      <c r="AJ53" t="inlineStr"/>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK53" t="inlineStr"/>
       <c r="AL53" t="inlineStr"/>
       <c r="AM53" t="inlineStr"/>
@@ -7263,8 +7671,16 @@
       <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="inlineStr"/>
       <c r="AH54" t="inlineStr"/>
-      <c r="AI54" t="inlineStr"/>
-      <c r="AJ54" t="inlineStr"/>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK54" t="inlineStr"/>
       <c r="AL54" t="inlineStr"/>
       <c r="AM54" t="inlineStr"/>
@@ -7382,8 +7798,16 @@
       <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="inlineStr"/>
       <c r="AH55" t="inlineStr"/>
-      <c r="AI55" t="inlineStr"/>
-      <c r="AJ55" t="inlineStr"/>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK55" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -7509,8 +7933,16 @@
       <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="inlineStr"/>
       <c r="AH56" t="inlineStr"/>
-      <c r="AI56" t="inlineStr"/>
-      <c r="AJ56" t="inlineStr"/>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK56" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -7636,8 +8068,16 @@
       <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="inlineStr"/>
       <c r="AH57" t="inlineStr"/>
-      <c r="AI57" t="inlineStr"/>
-      <c r="AJ57" t="inlineStr"/>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK57" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -7763,8 +8203,16 @@
       <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="inlineStr"/>
       <c r="AH58" t="inlineStr"/>
-      <c r="AI58" t="inlineStr"/>
-      <c r="AJ58" t="inlineStr"/>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK58" t="inlineStr">
         <is>
           <t>ONGC IPSHEM</t>
@@ -7890,8 +8338,16 @@
       <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="inlineStr"/>
       <c r="AH59" t="inlineStr"/>
-      <c r="AI59" t="inlineStr"/>
-      <c r="AJ59" t="inlineStr"/>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK59" t="inlineStr"/>
       <c r="AL59" t="inlineStr"/>
       <c r="AM59" t="inlineStr"/>
@@ -8017,8 +8473,16 @@
       <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="inlineStr"/>
       <c r="AH60" t="inlineStr"/>
-      <c r="AI60" t="inlineStr"/>
-      <c r="AJ60" t="inlineStr"/>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK60" t="inlineStr">
         <is>
           <t>ONGC IPSHEM</t>
@@ -8136,8 +8600,16 @@
       <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr"/>
-      <c r="AI61" t="inlineStr"/>
-      <c r="AJ61" t="inlineStr"/>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK61" t="inlineStr"/>
       <c r="AL61" t="inlineStr"/>
       <c r="AM61" t="inlineStr"/>
@@ -8251,8 +8723,16 @@
       <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr"/>
-      <c r="AI62" t="inlineStr"/>
-      <c r="AJ62" t="inlineStr"/>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK62" t="inlineStr"/>
       <c r="AL62" t="inlineStr"/>
       <c r="AM62" t="inlineStr"/>
@@ -8374,8 +8854,16 @@
       <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="inlineStr"/>
       <c r="AH63" t="inlineStr"/>
-      <c r="AI63" t="inlineStr"/>
-      <c r="AJ63" t="inlineStr"/>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK63" t="inlineStr"/>
       <c r="AL63" t="inlineStr"/>
       <c r="AM63" t="inlineStr"/>
@@ -8497,8 +8985,16 @@
       <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="inlineStr"/>
       <c r="AH64" t="inlineStr"/>
-      <c r="AI64" t="inlineStr"/>
-      <c r="AJ64" t="inlineStr"/>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK64" t="inlineStr"/>
       <c r="AL64" t="inlineStr"/>
       <c r="AM64" t="inlineStr"/>
@@ -8620,8 +9116,16 @@
       <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="inlineStr"/>
       <c r="AH65" t="inlineStr"/>
-      <c r="AI65" t="inlineStr"/>
-      <c r="AJ65" t="inlineStr"/>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK65" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -8747,8 +9251,16 @@
       <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="inlineStr"/>
       <c r="AH66" t="inlineStr"/>
-      <c r="AI66" t="inlineStr"/>
-      <c r="AJ66" t="inlineStr"/>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK66" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -8874,8 +9386,16 @@
       <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="inlineStr"/>
       <c r="AH67" t="inlineStr"/>
-      <c r="AI67" t="inlineStr"/>
-      <c r="AJ67" t="inlineStr"/>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK67" t="inlineStr">
         <is>
           <t>ONGC IPSHEM</t>
@@ -9001,8 +9521,16 @@
       <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="inlineStr"/>
       <c r="AH68" t="inlineStr"/>
-      <c r="AI68" t="inlineStr"/>
-      <c r="AJ68" t="inlineStr"/>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK68" t="inlineStr">
         <is>
           <t>ONGC ELECTRICAL</t>
@@ -9128,8 +9656,16 @@
       <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="inlineStr"/>
       <c r="AH69" t="inlineStr"/>
-      <c r="AI69" t="inlineStr"/>
-      <c r="AJ69" t="inlineStr"/>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK69" t="inlineStr">
         <is>
           <t>ONGC IPSHEM</t>
@@ -9255,8 +9791,16 @@
       <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="inlineStr"/>
       <c r="AH70" t="inlineStr"/>
-      <c r="AI70" t="inlineStr"/>
-      <c r="AJ70" t="inlineStr"/>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK70" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -9382,8 +9926,16 @@
       <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="inlineStr"/>
       <c r="AH71" t="inlineStr"/>
-      <c r="AI71" t="inlineStr"/>
-      <c r="AJ71" t="inlineStr"/>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK71" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -9509,8 +10061,16 @@
       <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="inlineStr"/>
       <c r="AH72" t="inlineStr"/>
-      <c r="AI72" t="inlineStr"/>
-      <c r="AJ72" t="inlineStr"/>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK72" t="inlineStr">
         <is>
           <t>BELLARI</t>
@@ -9636,8 +10196,16 @@
       <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="inlineStr"/>
       <c r="AH73" t="inlineStr"/>
-      <c r="AI73" t="inlineStr"/>
-      <c r="AJ73" t="inlineStr"/>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK73" t="inlineStr"/>
       <c r="AL73" t="inlineStr"/>
       <c r="AM73" t="inlineStr"/>
@@ -9759,8 +10327,16 @@
       <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="inlineStr"/>
       <c r="AH74" t="inlineStr"/>
-      <c r="AI74" t="inlineStr"/>
-      <c r="AJ74" t="inlineStr"/>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK74" t="inlineStr"/>
       <c r="AL74" t="inlineStr"/>
       <c r="AM74" t="inlineStr"/>
@@ -9882,8 +10458,16 @@
       <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="inlineStr"/>
       <c r="AH75" t="inlineStr"/>
-      <c r="AI75" t="inlineStr"/>
-      <c r="AJ75" t="inlineStr"/>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK75" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -10009,8 +10593,16 @@
       <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="inlineStr"/>
       <c r="AH76" t="inlineStr"/>
-      <c r="AI76" t="inlineStr"/>
-      <c r="AJ76" t="inlineStr"/>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK76" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -10136,8 +10728,16 @@
       <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="inlineStr"/>
       <c r="AH77" t="inlineStr"/>
-      <c r="AI77" t="inlineStr"/>
-      <c r="AJ77" t="inlineStr"/>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK77" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -10259,8 +10859,16 @@
       <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="inlineStr"/>
       <c r="AH78" t="inlineStr"/>
-      <c r="AI78" t="inlineStr"/>
-      <c r="AJ78" t="inlineStr"/>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK78" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -10386,8 +10994,16 @@
       <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="inlineStr"/>
       <c r="AH79" t="inlineStr"/>
-      <c r="AI79" t="inlineStr"/>
-      <c r="AJ79" t="inlineStr"/>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK79" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -10513,8 +11129,16 @@
       <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="inlineStr"/>
       <c r="AH80" t="inlineStr"/>
-      <c r="AI80" t="inlineStr"/>
-      <c r="AJ80" t="inlineStr"/>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK80" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -10640,8 +11264,16 @@
       <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="inlineStr"/>
       <c r="AH81" t="inlineStr"/>
-      <c r="AI81" t="inlineStr"/>
-      <c r="AJ81" t="inlineStr"/>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK81" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -10767,8 +11399,16 @@
       <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="inlineStr"/>
       <c r="AH82" t="inlineStr"/>
-      <c r="AI82" t="inlineStr"/>
-      <c r="AJ82" t="inlineStr"/>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK82" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -10894,8 +11534,16 @@
       <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="inlineStr"/>
       <c r="AH83" t="inlineStr"/>
-      <c r="AI83" t="inlineStr"/>
-      <c r="AJ83" t="inlineStr"/>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK83" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -11021,8 +11669,16 @@
       <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="inlineStr"/>
       <c r="AH84" t="inlineStr"/>
-      <c r="AI84" t="inlineStr"/>
-      <c r="AJ84" t="inlineStr"/>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK84" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -11148,8 +11804,16 @@
       <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="inlineStr"/>
       <c r="AH85" t="inlineStr"/>
-      <c r="AI85" t="inlineStr"/>
-      <c r="AJ85" t="inlineStr"/>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK85" t="inlineStr"/>
       <c r="AL85" t="inlineStr"/>
       <c r="AM85" t="inlineStr"/>
@@ -11271,8 +11935,16 @@
       <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="inlineStr"/>
       <c r="AH86" t="inlineStr"/>
-      <c r="AI86" t="inlineStr"/>
-      <c r="AJ86" t="inlineStr"/>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK86" t="inlineStr"/>
       <c r="AL86" t="inlineStr"/>
       <c r="AM86" t="inlineStr"/>
@@ -11394,8 +12066,16 @@
       <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="inlineStr"/>
       <c r="AH87" t="inlineStr"/>
-      <c r="AI87" t="inlineStr"/>
-      <c r="AJ87" t="inlineStr"/>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK87" t="inlineStr">
         <is>
           <t>BELLARI</t>
@@ -11521,8 +12201,16 @@
       <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="inlineStr"/>
       <c r="AH88" t="inlineStr"/>
-      <c r="AI88" t="inlineStr"/>
-      <c r="AJ88" t="inlineStr"/>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK88" t="inlineStr">
         <is>
           <t>BELLARI</t>
@@ -11648,8 +12336,16 @@
       <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="inlineStr"/>
       <c r="AH89" t="inlineStr"/>
-      <c r="AI89" t="inlineStr"/>
-      <c r="AJ89" t="inlineStr"/>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK89" t="inlineStr">
         <is>
           <t>BELLARI</t>
@@ -11775,8 +12471,16 @@
       <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="inlineStr"/>
       <c r="AH90" t="inlineStr"/>
-      <c r="AI90" t="inlineStr"/>
-      <c r="AJ90" t="inlineStr"/>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK90" t="inlineStr">
         <is>
           <t>BELLARI</t>
@@ -11902,8 +12606,16 @@
       <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="inlineStr"/>
       <c r="AH91" t="inlineStr"/>
-      <c r="AI91" t="inlineStr"/>
-      <c r="AJ91" t="inlineStr"/>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK91" t="inlineStr">
         <is>
           <t>BELLARI</t>
@@ -12029,8 +12741,16 @@
       <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="inlineStr"/>
       <c r="AH92" t="inlineStr"/>
-      <c r="AI92" t="inlineStr"/>
-      <c r="AJ92" t="inlineStr"/>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK92" t="inlineStr">
         <is>
           <t>BELLARI</t>
@@ -12156,8 +12876,16 @@
       <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="inlineStr"/>
       <c r="AH93" t="inlineStr"/>
-      <c r="AI93" t="inlineStr"/>
-      <c r="AJ93" t="inlineStr"/>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK93" t="inlineStr">
         <is>
           <t>BELLARI</t>
@@ -12283,8 +13011,16 @@
       <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="inlineStr"/>
       <c r="AH94" t="inlineStr"/>
-      <c r="AI94" t="inlineStr"/>
-      <c r="AJ94" t="inlineStr"/>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK94" t="inlineStr">
         <is>
           <t>BELLARI</t>
@@ -12410,8 +13146,16 @@
       <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="inlineStr"/>
       <c r="AH95" t="inlineStr"/>
-      <c r="AI95" t="inlineStr"/>
-      <c r="AJ95" t="inlineStr"/>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK95" t="inlineStr">
         <is>
           <t>BELLARI</t>
@@ -12537,8 +13281,16 @@
       <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="inlineStr"/>
       <c r="AH96" t="inlineStr"/>
-      <c r="AI96" t="inlineStr"/>
-      <c r="AJ96" t="inlineStr"/>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK96" t="inlineStr">
         <is>
           <t>BELLARI</t>
@@ -12664,8 +13416,16 @@
       <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="inlineStr"/>
       <c r="AH97" t="inlineStr"/>
-      <c r="AI97" t="inlineStr"/>
-      <c r="AJ97" t="inlineStr"/>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK97" t="inlineStr">
         <is>
           <t>BELLARI</t>
@@ -12792,8 +13552,16 @@
       <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="inlineStr"/>
       <c r="AH98" t="inlineStr"/>
-      <c r="AI98" t="inlineStr"/>
-      <c r="AJ98" t="inlineStr"/>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK98" t="inlineStr">
         <is>
           <t>BELLARI</t>
@@ -12919,8 +13687,16 @@
       <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="inlineStr"/>
       <c r="AH99" t="inlineStr"/>
-      <c r="AI99" t="inlineStr"/>
-      <c r="AJ99" t="inlineStr"/>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK99" t="inlineStr"/>
       <c r="AL99" t="inlineStr"/>
       <c r="AM99" t="inlineStr"/>
@@ -13042,8 +13818,16 @@
       <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="inlineStr"/>
       <c r="AH100" t="inlineStr"/>
-      <c r="AI100" t="inlineStr"/>
-      <c r="AJ100" t="inlineStr"/>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK100" t="inlineStr"/>
       <c r="AL100" t="inlineStr"/>
       <c r="AM100" t="inlineStr"/>
@@ -13165,8 +13949,16 @@
       <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="inlineStr"/>
       <c r="AH101" t="inlineStr"/>
-      <c r="AI101" t="inlineStr"/>
-      <c r="AJ101" t="inlineStr"/>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK101" t="inlineStr"/>
       <c r="AL101" t="inlineStr"/>
       <c r="AM101" t="inlineStr"/>
@@ -13288,8 +14080,16 @@
       <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="inlineStr"/>
       <c r="AH102" t="inlineStr"/>
-      <c r="AI102" t="inlineStr"/>
-      <c r="AJ102" t="inlineStr"/>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK102" t="inlineStr">
         <is>
           <t>IOCL STATE OFFICE</t>
@@ -13415,8 +14215,16 @@
       <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="inlineStr"/>
       <c r="AH103" t="inlineStr"/>
-      <c r="AI103" t="inlineStr"/>
-      <c r="AJ103" t="inlineStr"/>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK103" t="inlineStr">
         <is>
           <t>IOCL STATE OFFICE</t>
@@ -13542,8 +14350,16 @@
       <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="inlineStr"/>
       <c r="AH104" t="inlineStr"/>
-      <c r="AI104" t="inlineStr"/>
-      <c r="AJ104" t="inlineStr"/>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK104" t="inlineStr">
         <is>
           <t>IOCL STATE OFFICE</t>
@@ -13669,8 +14485,16 @@
       <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="inlineStr"/>
       <c r="AH105" t="inlineStr"/>
-      <c r="AI105" t="inlineStr"/>
-      <c r="AJ105" t="inlineStr"/>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK105" t="inlineStr">
         <is>
           <t>IOCL STATE OFFICE</t>
@@ -13796,8 +14620,16 @@
       <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="inlineStr"/>
       <c r="AH106" t="inlineStr"/>
-      <c r="AI106" t="inlineStr"/>
-      <c r="AJ106" t="inlineStr"/>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK106" t="inlineStr">
         <is>
           <t>IOCL STATE OFFICE</t>
@@ -13931,8 +14763,16 @@
       <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="inlineStr"/>
       <c r="AH107" t="inlineStr"/>
-      <c r="AI107" t="inlineStr"/>
-      <c r="AJ107" t="inlineStr"/>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK107" t="inlineStr">
         <is>
           <t>IOCL STATE OFFICE</t>
@@ -14058,8 +14898,16 @@
       <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="inlineStr"/>
       <c r="AH108" t="inlineStr"/>
-      <c r="AI108" t="inlineStr"/>
-      <c r="AJ108" t="inlineStr"/>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK108" t="inlineStr">
         <is>
           <t>IOCL STATE OFFICE</t>
@@ -14185,8 +15033,16 @@
       <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="inlineStr"/>
       <c r="AH109" t="inlineStr"/>
-      <c r="AI109" t="inlineStr"/>
-      <c r="AJ109" t="inlineStr"/>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK109" t="inlineStr">
         <is>
           <t>IOCL STATE OFFICE</t>
@@ -14312,8 +15168,16 @@
       <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="inlineStr"/>
       <c r="AH110" t="inlineStr"/>
-      <c r="AI110" t="inlineStr"/>
-      <c r="AJ110" t="inlineStr"/>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK110" t="inlineStr">
         <is>
           <t>IOCL STATE OFFICE</t>
@@ -14439,8 +15303,16 @@
       <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="inlineStr"/>
       <c r="AH111" t="inlineStr"/>
-      <c r="AI111" t="inlineStr"/>
-      <c r="AJ111" t="inlineStr"/>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK111" t="inlineStr">
         <is>
           <t>IOCL STATE OFFICE</t>
@@ -14566,8 +15438,16 @@
       <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="inlineStr"/>
       <c r="AH112" t="inlineStr"/>
-      <c r="AI112" t="inlineStr"/>
-      <c r="AJ112" t="inlineStr"/>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK112" t="inlineStr">
         <is>
           <t>IOCL STATE OFFICE</t>
@@ -14693,8 +15573,16 @@
       <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="inlineStr"/>
       <c r="AH113" t="inlineStr"/>
-      <c r="AI113" t="inlineStr"/>
-      <c r="AJ113" t="inlineStr"/>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK113" t="inlineStr">
         <is>
           <t>IOCL STATE OFFICE</t>
@@ -14820,8 +15708,16 @@
       <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="inlineStr"/>
       <c r="AH114" t="inlineStr"/>
-      <c r="AI114" t="inlineStr"/>
-      <c r="AJ114" t="inlineStr"/>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK114" t="inlineStr">
         <is>
           <t>IOCL STATE OFFICE</t>
@@ -14947,8 +15843,16 @@
       <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="inlineStr"/>
       <c r="AH115" t="inlineStr"/>
-      <c r="AI115" t="inlineStr"/>
-      <c r="AJ115" t="inlineStr"/>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK115" t="inlineStr">
         <is>
           <t>IOCL GARDEN</t>
@@ -15074,8 +15978,16 @@
       <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="inlineStr"/>
       <c r="AH116" t="inlineStr"/>
-      <c r="AI116" t="inlineStr"/>
-      <c r="AJ116" t="inlineStr"/>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK116" t="inlineStr">
         <is>
           <t>IOCL GARDEN</t>
@@ -15201,8 +16113,16 @@
       <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="inlineStr"/>
       <c r="AH117" t="inlineStr"/>
-      <c r="AI117" t="inlineStr"/>
-      <c r="AJ117" t="inlineStr"/>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK117" t="inlineStr">
         <is>
           <t>IOCL STATE OFFICE</t>
@@ -15328,8 +16248,16 @@
       <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="inlineStr"/>
       <c r="AH118" t="inlineStr"/>
-      <c r="AI118" t="inlineStr"/>
-      <c r="AJ118" t="inlineStr"/>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK118" t="inlineStr">
         <is>
           <t>IOCL STATE OFFICE</t>
@@ -15455,8 +16383,16 @@
       <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="inlineStr"/>
       <c r="AH119" t="inlineStr"/>
-      <c r="AI119" t="inlineStr"/>
-      <c r="AJ119" t="inlineStr"/>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK119" t="inlineStr">
         <is>
           <t>IOCL STATE OFFICE</t>
@@ -15582,8 +16518,16 @@
       <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="inlineStr"/>
       <c r="AH120" t="inlineStr"/>
-      <c r="AI120" t="inlineStr"/>
-      <c r="AJ120" t="inlineStr"/>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK120" t="inlineStr">
         <is>
           <t>IOCL STATE OFFICE</t>
@@ -15709,8 +16653,16 @@
       <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="inlineStr"/>
       <c r="AH121" t="inlineStr"/>
-      <c r="AI121" t="inlineStr"/>
-      <c r="AJ121" t="inlineStr"/>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK121" t="inlineStr">
         <is>
           <t>IOCL STATE OFFICE</t>
@@ -15836,8 +16788,16 @@
       <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="inlineStr"/>
       <c r="AH122" t="inlineStr"/>
-      <c r="AI122" t="inlineStr"/>
-      <c r="AJ122" t="inlineStr"/>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK122" t="inlineStr"/>
       <c r="AL122" t="inlineStr"/>
       <c r="AM122" t="inlineStr"/>
@@ -15959,8 +16919,16 @@
       <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="inlineStr"/>
       <c r="AH123" t="inlineStr"/>
-      <c r="AI123" t="inlineStr"/>
-      <c r="AJ123" t="inlineStr"/>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK123" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -16086,8 +17054,16 @@
       <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="inlineStr"/>
       <c r="AH124" t="inlineStr"/>
-      <c r="AI124" t="inlineStr"/>
-      <c r="AJ124" t="inlineStr"/>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK124" t="inlineStr">
         <is>
           <t>HO</t>
@@ -16215,8 +17191,16 @@
       <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="inlineStr"/>
       <c r="AH125" t="inlineStr"/>
-      <c r="AI125" t="inlineStr"/>
-      <c r="AJ125" t="inlineStr"/>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK125" t="inlineStr"/>
       <c r="AL125" t="inlineStr"/>
       <c r="AM125" t="inlineStr"/>
@@ -16340,8 +17324,16 @@
       <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="inlineStr"/>
       <c r="AH126" t="inlineStr"/>
-      <c r="AI126" t="inlineStr"/>
-      <c r="AJ126" t="inlineStr"/>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK126" t="inlineStr"/>
       <c r="AL126" t="inlineStr"/>
       <c r="AM126" t="inlineStr"/>
@@ -16465,8 +17457,16 @@
       <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="inlineStr"/>
       <c r="AH127" t="inlineStr"/>
-      <c r="AI127" t="inlineStr"/>
-      <c r="AJ127" t="inlineStr"/>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK127" t="inlineStr"/>
       <c r="AL127" t="inlineStr"/>
       <c r="AM127" t="inlineStr"/>
@@ -16582,8 +17582,16 @@
       <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="inlineStr"/>
       <c r="AH128" t="inlineStr"/>
-      <c r="AI128" t="inlineStr"/>
-      <c r="AJ128" t="inlineStr"/>
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK128" t="inlineStr"/>
       <c r="AL128" t="inlineStr"/>
       <c r="AM128" t="inlineStr"/>
@@ -16699,8 +17707,16 @@
       <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="inlineStr"/>
       <c r="AH129" t="inlineStr"/>
-      <c r="AI129" t="inlineStr"/>
-      <c r="AJ129" t="inlineStr"/>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK129" t="inlineStr"/>
       <c r="AL129" t="inlineStr"/>
       <c r="AM129" t="inlineStr"/>
@@ -16816,8 +17832,16 @@
       <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="inlineStr"/>
       <c r="AH130" t="inlineStr"/>
-      <c r="AI130" t="inlineStr"/>
-      <c r="AJ130" t="inlineStr"/>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK130" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -16937,8 +17961,16 @@
       <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="inlineStr"/>
       <c r="AH131" t="inlineStr"/>
-      <c r="AI131" t="inlineStr"/>
-      <c r="AJ131" t="inlineStr"/>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK131" t="inlineStr"/>
       <c r="AL131" t="inlineStr"/>
       <c r="AM131" t="inlineStr"/>
@@ -17054,8 +18086,16 @@
       <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="inlineStr"/>
       <c r="AH132" t="inlineStr"/>
-      <c r="AI132" t="inlineStr"/>
-      <c r="AJ132" t="inlineStr"/>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK132" t="inlineStr"/>
       <c r="AL132" t="inlineStr"/>
       <c r="AM132" t="inlineStr"/>
@@ -17171,8 +18211,16 @@
       <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="inlineStr"/>
       <c r="AH133" t="inlineStr"/>
-      <c r="AI133" t="inlineStr"/>
-      <c r="AJ133" t="inlineStr"/>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK133" t="inlineStr"/>
       <c r="AL133" t="inlineStr"/>
       <c r="AM133" t="inlineStr"/>
@@ -17288,8 +18336,16 @@
       <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="inlineStr"/>
       <c r="AH134" t="inlineStr"/>
-      <c r="AI134" t="inlineStr"/>
-      <c r="AJ134" t="inlineStr"/>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK134" t="inlineStr"/>
       <c r="AL134" t="inlineStr"/>
       <c r="AM134" t="inlineStr"/>
@@ -17405,8 +18461,16 @@
       <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="inlineStr"/>
       <c r="AH135" t="inlineStr"/>
-      <c r="AI135" t="inlineStr"/>
-      <c r="AJ135" t="inlineStr"/>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK135" t="inlineStr"/>
       <c r="AL135" t="inlineStr"/>
       <c r="AM135" t="inlineStr"/>
@@ -17533,8 +18597,16 @@
       <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="inlineStr"/>
       <c r="AH136" t="inlineStr"/>
-      <c r="AI136" t="inlineStr"/>
-      <c r="AJ136" t="inlineStr"/>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK136" t="inlineStr"/>
       <c r="AL136" t="inlineStr"/>
       <c r="AM136" t="inlineStr"/>
@@ -17658,8 +18730,16 @@
       <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="inlineStr"/>
       <c r="AH137" t="inlineStr"/>
-      <c r="AI137" t="inlineStr"/>
-      <c r="AJ137" t="inlineStr"/>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK137" t="inlineStr"/>
       <c r="AL137" t="inlineStr"/>
       <c r="AM137" t="inlineStr"/>
@@ -17786,8 +18866,16 @@
       <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="inlineStr"/>
       <c r="AH138" t="inlineStr"/>
-      <c r="AI138" t="inlineStr"/>
-      <c r="AJ138" t="inlineStr"/>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ138" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK138" t="inlineStr"/>
       <c r="AL138" t="inlineStr"/>
       <c r="AM138" t="inlineStr"/>
@@ -17911,8 +18999,16 @@
       <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="inlineStr"/>
       <c r="AH139" t="inlineStr"/>
-      <c r="AI139" t="inlineStr"/>
-      <c r="AJ139" t="inlineStr"/>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK139" t="inlineStr"/>
       <c r="AL139" t="inlineStr"/>
       <c r="AM139" t="inlineStr"/>
@@ -18036,8 +19132,16 @@
       <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="inlineStr"/>
       <c r="AH140" t="inlineStr"/>
-      <c r="AI140" t="inlineStr"/>
-      <c r="AJ140" t="inlineStr"/>
+      <c r="AI140" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK140" t="inlineStr"/>
       <c r="AL140" t="inlineStr"/>
       <c r="AM140" t="inlineStr"/>
@@ -18159,8 +19263,16 @@
       <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="inlineStr"/>
       <c r="AH141" t="inlineStr"/>
-      <c r="AI141" t="inlineStr"/>
-      <c r="AJ141" t="inlineStr"/>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK141" t="inlineStr"/>
       <c r="AL141" t="inlineStr"/>
       <c r="AM141" t="inlineStr"/>
@@ -18282,8 +19394,16 @@
       <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="inlineStr"/>
       <c r="AH142" t="inlineStr"/>
-      <c r="AI142" t="inlineStr"/>
-      <c r="AJ142" t="inlineStr"/>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK142" t="inlineStr"/>
       <c r="AL142" t="inlineStr"/>
       <c r="AM142" t="inlineStr"/>
@@ -18395,8 +19515,16 @@
       <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="inlineStr"/>
       <c r="AH143" t="inlineStr"/>
-      <c r="AI143" t="inlineStr"/>
-      <c r="AJ143" t="inlineStr"/>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK143" t="inlineStr"/>
       <c r="AL143" t="inlineStr"/>
       <c r="AM143" t="inlineStr"/>
@@ -18518,8 +19646,16 @@
       <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="inlineStr"/>
       <c r="AH144" t="inlineStr"/>
-      <c r="AI144" t="inlineStr"/>
-      <c r="AJ144" t="inlineStr"/>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK144" t="inlineStr"/>
       <c r="AL144" t="inlineStr"/>
       <c r="AM144" t="inlineStr"/>
@@ -18641,8 +19777,16 @@
       <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="inlineStr"/>
       <c r="AH145" t="inlineStr"/>
-      <c r="AI145" t="inlineStr"/>
-      <c r="AJ145" t="inlineStr"/>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK145" t="inlineStr"/>
       <c r="AL145" t="inlineStr"/>
       <c r="AM145" t="inlineStr"/>
@@ -18764,8 +19908,16 @@
       <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="inlineStr"/>
       <c r="AH146" t="inlineStr"/>
-      <c r="AI146" t="inlineStr"/>
-      <c r="AJ146" t="inlineStr"/>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK146" t="inlineStr"/>
       <c r="AL146" t="inlineStr"/>
       <c r="AM146" t="inlineStr"/>
@@ -18887,8 +20039,16 @@
       <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="inlineStr"/>
       <c r="AH147" t="inlineStr"/>
-      <c r="AI147" t="inlineStr"/>
-      <c r="AJ147" t="inlineStr"/>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK147" t="inlineStr"/>
       <c r="AL147" t="inlineStr"/>
       <c r="AM147" t="inlineStr"/>
@@ -19010,8 +20170,16 @@
       <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="inlineStr"/>
       <c r="AH148" t="inlineStr"/>
-      <c r="AI148" t="inlineStr"/>
-      <c r="AJ148" t="inlineStr"/>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK148" t="inlineStr"/>
       <c r="AL148" t="inlineStr"/>
       <c r="AM148" t="inlineStr"/>
@@ -19133,8 +20301,16 @@
       <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="inlineStr"/>
       <c r="AH149" t="inlineStr"/>
-      <c r="AI149" t="inlineStr"/>
-      <c r="AJ149" t="inlineStr"/>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK149" t="inlineStr"/>
       <c r="AL149" t="inlineStr"/>
       <c r="AM149" t="inlineStr"/>
@@ -19256,8 +20432,16 @@
       <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="inlineStr"/>
       <c r="AH150" t="inlineStr"/>
-      <c r="AI150" t="inlineStr"/>
-      <c r="AJ150" t="inlineStr"/>
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK150" t="inlineStr"/>
       <c r="AL150" t="inlineStr"/>
       <c r="AM150" t="inlineStr"/>
@@ -19379,8 +20563,16 @@
       <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="inlineStr"/>
       <c r="AH151" t="inlineStr"/>
-      <c r="AI151" t="inlineStr"/>
-      <c r="AJ151" t="inlineStr"/>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK151" t="inlineStr"/>
       <c r="AL151" t="inlineStr"/>
       <c r="AM151" t="inlineStr"/>
@@ -19502,8 +20694,16 @@
       <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="inlineStr"/>
       <c r="AH152" t="inlineStr"/>
-      <c r="AI152" t="inlineStr"/>
-      <c r="AJ152" t="inlineStr"/>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK152" t="inlineStr"/>
       <c r="AL152" t="inlineStr"/>
       <c r="AM152" t="inlineStr"/>
@@ -19625,8 +20825,16 @@
       <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="inlineStr"/>
       <c r="AH153" t="inlineStr"/>
-      <c r="AI153" t="inlineStr"/>
-      <c r="AJ153" t="inlineStr"/>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK153" t="inlineStr"/>
       <c r="AL153" t="inlineStr"/>
       <c r="AM153" t="inlineStr"/>
@@ -19748,8 +20956,16 @@
       <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="inlineStr"/>
       <c r="AH154" t="inlineStr"/>
-      <c r="AI154" t="inlineStr"/>
-      <c r="AJ154" t="inlineStr"/>
+      <c r="AI154" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ154" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK154" t="inlineStr"/>
       <c r="AL154" t="inlineStr"/>
       <c r="AM154" t="inlineStr"/>
@@ -19871,8 +21087,16 @@
       <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="inlineStr"/>
       <c r="AH155" t="inlineStr"/>
-      <c r="AI155" t="inlineStr"/>
-      <c r="AJ155" t="inlineStr"/>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK155" t="inlineStr"/>
       <c r="AL155" t="inlineStr"/>
       <c r="AM155" t="inlineStr"/>
@@ -19994,8 +21218,16 @@
       <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="inlineStr"/>
       <c r="AH156" t="inlineStr"/>
-      <c r="AI156" t="inlineStr"/>
-      <c r="AJ156" t="inlineStr"/>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK156" t="inlineStr"/>
       <c r="AL156" t="inlineStr"/>
       <c r="AM156" t="inlineStr"/>
@@ -20117,8 +21349,16 @@
       <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="inlineStr"/>
       <c r="AH157" t="inlineStr"/>
-      <c r="AI157" t="inlineStr"/>
-      <c r="AJ157" t="inlineStr"/>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK157" t="inlineStr"/>
       <c r="AL157" t="inlineStr"/>
       <c r="AM157" t="inlineStr"/>
@@ -20240,8 +21480,16 @@
       <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="inlineStr"/>
       <c r="AH158" t="inlineStr"/>
-      <c r="AI158" t="inlineStr"/>
-      <c r="AJ158" t="inlineStr"/>
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ158" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK158" t="inlineStr"/>
       <c r="AL158" t="inlineStr"/>
       <c r="AM158" t="inlineStr"/>
@@ -20363,8 +21611,16 @@
       <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="inlineStr"/>
       <c r="AH159" t="inlineStr"/>
-      <c r="AI159" t="inlineStr"/>
-      <c r="AJ159" t="inlineStr"/>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK159" t="inlineStr"/>
       <c r="AL159" t="inlineStr"/>
       <c r="AM159" t="inlineStr"/>
@@ -20486,8 +21742,16 @@
       <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="inlineStr"/>
       <c r="AH160" t="inlineStr"/>
-      <c r="AI160" t="inlineStr"/>
-      <c r="AJ160" t="inlineStr"/>
+      <c r="AI160" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ160" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK160" t="inlineStr"/>
       <c r="AL160" t="inlineStr"/>
       <c r="AM160" t="inlineStr"/>
@@ -20609,8 +21873,16 @@
       <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="inlineStr"/>
       <c r="AH161" t="inlineStr"/>
-      <c r="AI161" t="inlineStr"/>
-      <c r="AJ161" t="inlineStr"/>
+      <c r="AI161" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK161" t="inlineStr"/>
       <c r="AL161" t="inlineStr"/>
       <c r="AM161" t="inlineStr"/>
@@ -20732,8 +22004,16 @@
       <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="inlineStr"/>
       <c r="AH162" t="inlineStr"/>
-      <c r="AI162" t="inlineStr"/>
-      <c r="AJ162" t="inlineStr"/>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK162" t="inlineStr"/>
       <c r="AL162" t="inlineStr"/>
       <c r="AM162" t="inlineStr"/>
@@ -20855,8 +22135,16 @@
       <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="inlineStr"/>
       <c r="AH163" t="inlineStr"/>
-      <c r="AI163" t="inlineStr"/>
-      <c r="AJ163" t="inlineStr"/>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK163" t="inlineStr"/>
       <c r="AL163" t="inlineStr"/>
       <c r="AM163" t="inlineStr"/>
@@ -20974,8 +22262,16 @@
       <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="inlineStr"/>
       <c r="AH164" t="inlineStr"/>
-      <c r="AI164" t="inlineStr"/>
-      <c r="AJ164" t="inlineStr"/>
+      <c r="AI164" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK164" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -21101,8 +22397,16 @@
       <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="inlineStr"/>
       <c r="AH165" t="inlineStr"/>
-      <c r="AI165" t="inlineStr"/>
-      <c r="AJ165" t="inlineStr"/>
+      <c r="AI165" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK165" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -21228,8 +22532,16 @@
       <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="inlineStr"/>
       <c r="AH166" t="inlineStr"/>
-      <c r="AI166" t="inlineStr"/>
-      <c r="AJ166" t="inlineStr"/>
+      <c r="AI166" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ166" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK166" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -21355,8 +22667,16 @@
       <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="inlineStr"/>
       <c r="AH167" t="inlineStr"/>
-      <c r="AI167" t="inlineStr"/>
-      <c r="AJ167" t="inlineStr"/>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK167" t="inlineStr">
         <is>
           <t>ONGC IPSHEM</t>
@@ -21482,8 +22802,16 @@
       <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="inlineStr"/>
       <c r="AH168" t="inlineStr"/>
-      <c r="AI168" t="inlineStr"/>
-      <c r="AJ168" t="inlineStr"/>
+      <c r="AI168" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ168" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK168" t="inlineStr"/>
       <c r="AL168" t="inlineStr"/>
       <c r="AM168" t="inlineStr"/>
@@ -21609,8 +22937,16 @@
       <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="inlineStr"/>
       <c r="AH169" t="inlineStr"/>
-      <c r="AI169" t="inlineStr"/>
-      <c r="AJ169" t="inlineStr"/>
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK169" t="inlineStr">
         <is>
           <t>ONGC IPSHEM</t>
@@ -21728,8 +23064,16 @@
       <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="inlineStr"/>
       <c r="AH170" t="inlineStr"/>
-      <c r="AI170" t="inlineStr"/>
-      <c r="AJ170" t="inlineStr"/>
+      <c r="AI170" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK170" t="inlineStr"/>
       <c r="AL170" t="inlineStr"/>
       <c r="AM170" t="inlineStr"/>
@@ -21843,8 +23187,16 @@
       <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="inlineStr"/>
       <c r="AH171" t="inlineStr"/>
-      <c r="AI171" t="inlineStr"/>
-      <c r="AJ171" t="inlineStr"/>
+      <c r="AI171" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ171" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK171" t="inlineStr"/>
       <c r="AL171" t="inlineStr"/>
       <c r="AM171" t="inlineStr"/>
@@ -21966,8 +23318,16 @@
       <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="inlineStr"/>
       <c r="AH172" t="inlineStr"/>
-      <c r="AI172" t="inlineStr"/>
-      <c r="AJ172" t="inlineStr"/>
+      <c r="AI172" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ172" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK172" t="inlineStr"/>
       <c r="AL172" t="inlineStr"/>
       <c r="AM172" t="inlineStr"/>
@@ -22089,8 +23449,16 @@
       <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="inlineStr"/>
       <c r="AH173" t="inlineStr"/>
-      <c r="AI173" t="inlineStr"/>
-      <c r="AJ173" t="inlineStr"/>
+      <c r="AI173" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ173" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK173" t="inlineStr"/>
       <c r="AL173" t="inlineStr"/>
       <c r="AM173" t="inlineStr"/>
@@ -22212,8 +23580,16 @@
       <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="inlineStr"/>
       <c r="AH174" t="inlineStr"/>
-      <c r="AI174" t="inlineStr"/>
-      <c r="AJ174" t="inlineStr"/>
+      <c r="AI174" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ174" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK174" t="inlineStr">
         <is>
           <t>BELLARI</t>
@@ -22339,8 +23715,16 @@
       <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="inlineStr"/>
       <c r="AH175" t="inlineStr"/>
-      <c r="AI175" t="inlineStr"/>
-      <c r="AJ175" t="inlineStr"/>
+      <c r="AI175" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ175" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK175" t="inlineStr">
         <is>
           <t>BELLARI</t>
@@ -22466,8 +23850,16 @@
       <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="inlineStr"/>
       <c r="AH176" t="inlineStr"/>
-      <c r="AI176" t="inlineStr"/>
-      <c r="AJ176" t="inlineStr"/>
+      <c r="AI176" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ176" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK176" t="inlineStr"/>
       <c r="AL176" t="inlineStr"/>
       <c r="AM176" t="inlineStr"/>
@@ -22589,8 +23981,16 @@
       <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="inlineStr"/>
       <c r="AH177" t="inlineStr"/>
-      <c r="AI177" t="inlineStr"/>
-      <c r="AJ177" t="inlineStr"/>
+      <c r="AI177" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ177" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK177" t="inlineStr"/>
       <c r="AL177" t="inlineStr"/>
       <c r="AM177" t="inlineStr"/>
@@ -22712,8 +24112,16 @@
       <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="inlineStr"/>
       <c r="AH178" t="inlineStr"/>
-      <c r="AI178" t="inlineStr"/>
-      <c r="AJ178" t="inlineStr"/>
+      <c r="AI178" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ178" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK178" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -22839,8 +24247,16 @@
       <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="inlineStr"/>
       <c r="AH179" t="inlineStr"/>
-      <c r="AI179" t="inlineStr"/>
-      <c r="AJ179" t="inlineStr"/>
+      <c r="AI179" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ179" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK179" t="inlineStr"/>
       <c r="AL179" t="inlineStr"/>
       <c r="AM179" t="inlineStr"/>
@@ -22962,8 +24378,16 @@
       <c r="AF180" t="inlineStr"/>
       <c r="AG180" t="inlineStr"/>
       <c r="AH180" t="inlineStr"/>
-      <c r="AI180" t="inlineStr"/>
-      <c r="AJ180" t="inlineStr"/>
+      <c r="AI180" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ180" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK180" t="inlineStr"/>
       <c r="AL180" t="inlineStr"/>
       <c r="AM180" t="inlineStr"/>
@@ -23085,8 +24509,16 @@
       <c r="AF181" t="inlineStr"/>
       <c r="AG181" t="inlineStr"/>
       <c r="AH181" t="inlineStr"/>
-      <c r="AI181" t="inlineStr"/>
-      <c r="AJ181" t="inlineStr"/>
+      <c r="AI181" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ181" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK181" t="inlineStr"/>
       <c r="AL181" t="inlineStr"/>
       <c r="AM181" t="inlineStr"/>
@@ -23208,8 +24640,16 @@
       <c r="AF182" t="inlineStr"/>
       <c r="AG182" t="inlineStr"/>
       <c r="AH182" t="inlineStr"/>
-      <c r="AI182" t="inlineStr"/>
-      <c r="AJ182" t="inlineStr"/>
+      <c r="AI182" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ182" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK182" t="inlineStr"/>
       <c r="AL182" t="inlineStr"/>
       <c r="AM182" t="inlineStr"/>
@@ -23331,8 +24771,16 @@
       <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="inlineStr"/>
       <c r="AH183" t="inlineStr"/>
-      <c r="AI183" t="inlineStr"/>
-      <c r="AJ183" t="inlineStr"/>
+      <c r="AI183" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ183" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK183" t="inlineStr"/>
       <c r="AL183" t="inlineStr"/>
       <c r="AM183" t="inlineStr"/>
@@ -23454,8 +24902,16 @@
       <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="inlineStr"/>
       <c r="AH184" t="inlineStr"/>
-      <c r="AI184" t="inlineStr"/>
-      <c r="AJ184" t="inlineStr"/>
+      <c r="AI184" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ184" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK184" t="inlineStr"/>
       <c r="AL184" t="inlineStr"/>
       <c r="AM184" t="inlineStr"/>
@@ -23577,8 +25033,16 @@
       <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="inlineStr"/>
       <c r="AH185" t="inlineStr"/>
-      <c r="AI185" t="inlineStr"/>
-      <c r="AJ185" t="inlineStr"/>
+      <c r="AI185" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ185" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK185" t="inlineStr"/>
       <c r="AL185" t="inlineStr"/>
       <c r="AM185" t="inlineStr"/>
@@ -23700,8 +25164,16 @@
       <c r="AF186" t="inlineStr"/>
       <c r="AG186" t="inlineStr"/>
       <c r="AH186" t="inlineStr"/>
-      <c r="AI186" t="inlineStr"/>
-      <c r="AJ186" t="inlineStr"/>
+      <c r="AI186" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ186" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK186" t="inlineStr"/>
       <c r="AL186" t="inlineStr"/>
       <c r="AM186" t="inlineStr"/>
@@ -23823,8 +25295,16 @@
       <c r="AF187" t="inlineStr"/>
       <c r="AG187" t="inlineStr"/>
       <c r="AH187" t="inlineStr"/>
-      <c r="AI187" t="inlineStr"/>
-      <c r="AJ187" t="inlineStr"/>
+      <c r="AI187" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ187" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK187" t="inlineStr"/>
       <c r="AL187" t="inlineStr"/>
       <c r="AM187" t="inlineStr"/>
@@ -23946,8 +25426,16 @@
       <c r="AF188" t="inlineStr"/>
       <c r="AG188" t="inlineStr"/>
       <c r="AH188" t="inlineStr"/>
-      <c r="AI188" t="inlineStr"/>
-      <c r="AJ188" t="inlineStr"/>
+      <c r="AI188" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ188" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK188" t="inlineStr"/>
       <c r="AL188" t="inlineStr"/>
       <c r="AM188" t="inlineStr"/>
@@ -24069,8 +25557,16 @@
       <c r="AF189" t="inlineStr"/>
       <c r="AG189" t="inlineStr"/>
       <c r="AH189" t="inlineStr"/>
-      <c r="AI189" t="inlineStr"/>
-      <c r="AJ189" t="inlineStr"/>
+      <c r="AI189" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ189" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK189" t="inlineStr"/>
       <c r="AL189" t="inlineStr"/>
       <c r="AM189" t="inlineStr"/>
@@ -24192,8 +25688,16 @@
       <c r="AF190" t="inlineStr"/>
       <c r="AG190" t="inlineStr"/>
       <c r="AH190" t="inlineStr"/>
-      <c r="AI190" t="inlineStr"/>
-      <c r="AJ190" t="inlineStr"/>
+      <c r="AI190" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ190" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK190" t="inlineStr">
         <is>
           <t>KOLKATA</t>
@@ -24319,8 +25823,16 @@
       <c r="AF191" t="inlineStr"/>
       <c r="AG191" t="inlineStr"/>
       <c r="AH191" t="inlineStr"/>
-      <c r="AI191" t="inlineStr"/>
-      <c r="AJ191" t="inlineStr"/>
+      <c r="AI191" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ191" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK191" t="inlineStr">
         <is>
           <t>BELLARI</t>
@@ -24446,8 +25958,16 @@
       <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="inlineStr"/>
       <c r="AH192" t="inlineStr"/>
-      <c r="AI192" t="inlineStr"/>
-      <c r="AJ192" t="inlineStr"/>
+      <c r="AI192" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ192" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK192" t="inlineStr"/>
       <c r="AL192" t="inlineStr"/>
       <c r="AM192" t="inlineStr"/>
@@ -24569,8 +26089,16 @@
       <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="inlineStr"/>
       <c r="AH193" t="inlineStr"/>
-      <c r="AI193" t="inlineStr"/>
-      <c r="AJ193" t="inlineStr"/>
+      <c r="AI193" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ193" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK193" t="inlineStr"/>
       <c r="AL193" t="inlineStr"/>
       <c r="AM193" t="inlineStr"/>
@@ -24694,8 +26222,16 @@
       <c r="AF194" t="inlineStr"/>
       <c r="AG194" t="inlineStr"/>
       <c r="AH194" t="inlineStr"/>
-      <c r="AI194" t="inlineStr"/>
-      <c r="AJ194" t="inlineStr"/>
+      <c r="AI194" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ194" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK194" t="inlineStr">
         <is>
           <t>ONGC ELECTRICAL</t>
@@ -24823,8 +26359,16 @@
       <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="inlineStr"/>
       <c r="AH195" t="inlineStr"/>
-      <c r="AI195" t="inlineStr"/>
-      <c r="AJ195" t="inlineStr"/>
+      <c r="AI195" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ195" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK195" t="inlineStr"/>
       <c r="AL195" t="inlineStr"/>
       <c r="AM195" t="inlineStr"/>
@@ -24948,8 +26492,16 @@
       <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="inlineStr"/>
       <c r="AH196" t="inlineStr"/>
-      <c r="AI196" t="inlineStr"/>
-      <c r="AJ196" t="inlineStr"/>
+      <c r="AI196" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ196" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK196" t="inlineStr">
         <is>
           <t>ONGC ELECTRICAL</t>
@@ -25077,8 +26629,16 @@
       <c r="AF197" t="inlineStr"/>
       <c r="AG197" t="inlineStr"/>
       <c r="AH197" t="inlineStr"/>
-      <c r="AI197" t="inlineStr"/>
-      <c r="AJ197" t="inlineStr"/>
+      <c r="AI197" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ197" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK197" t="inlineStr">
         <is>
           <t>ONGC IPSHEM</t>
@@ -25206,8 +26766,16 @@
       <c r="AF198" t="inlineStr"/>
       <c r="AG198" t="inlineStr"/>
       <c r="AH198" t="inlineStr"/>
-      <c r="AI198" t="inlineStr"/>
-      <c r="AJ198" t="inlineStr"/>
+      <c r="AI198" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ198" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK198" t="inlineStr"/>
       <c r="AL198" t="inlineStr"/>
       <c r="AM198" t="inlineStr"/>
@@ -25331,8 +26899,16 @@
       <c r="AF199" t="inlineStr"/>
       <c r="AG199" t="inlineStr"/>
       <c r="AH199" t="inlineStr"/>
-      <c r="AI199" t="inlineStr"/>
-      <c r="AJ199" t="inlineStr"/>
+      <c r="AI199" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ199" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK199" t="inlineStr"/>
       <c r="AL199" t="inlineStr"/>
       <c r="AM199" t="inlineStr"/>
@@ -25456,8 +27032,16 @@
       <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="inlineStr"/>
       <c r="AH200" t="inlineStr"/>
-      <c r="AI200" t="inlineStr"/>
-      <c r="AJ200" t="inlineStr"/>
+      <c r="AI200" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ200" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK200" t="inlineStr"/>
       <c r="AL200" t="inlineStr"/>
       <c r="AM200" t="inlineStr"/>
@@ -25581,8 +27165,16 @@
       <c r="AF201" t="inlineStr"/>
       <c r="AG201" t="inlineStr"/>
       <c r="AH201" t="inlineStr"/>
-      <c r="AI201" t="inlineStr"/>
-      <c r="AJ201" t="inlineStr"/>
+      <c r="AI201" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ201" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK201" t="inlineStr"/>
       <c r="AL201" t="inlineStr"/>
       <c r="AM201" t="inlineStr"/>
@@ -25707,8 +27299,16 @@
       <c r="AF202" t="inlineStr"/>
       <c r="AG202" t="inlineStr"/>
       <c r="AH202" t="inlineStr"/>
-      <c r="AI202" t="inlineStr"/>
-      <c r="AJ202" t="inlineStr"/>
+      <c r="AI202" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ202" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK202" t="inlineStr"/>
       <c r="AL202" t="inlineStr"/>
       <c r="AM202" t="inlineStr"/>
@@ -25834,8 +27434,16 @@
       <c r="AF203" t="inlineStr"/>
       <c r="AG203" t="inlineStr"/>
       <c r="AH203" t="inlineStr"/>
-      <c r="AI203" t="inlineStr"/>
-      <c r="AJ203" t="inlineStr"/>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ203" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK203" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -25964,8 +27572,16 @@
       <c r="AF204" t="inlineStr"/>
       <c r="AG204" t="inlineStr"/>
       <c r="AH204" t="inlineStr"/>
-      <c r="AI204" t="inlineStr"/>
-      <c r="AJ204" t="inlineStr"/>
+      <c r="AI204" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ204" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK204" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -26094,8 +27710,16 @@
       <c r="AF205" t="inlineStr"/>
       <c r="AG205" t="inlineStr"/>
       <c r="AH205" t="inlineStr"/>
-      <c r="AI205" t="inlineStr"/>
-      <c r="AJ205" t="inlineStr"/>
+      <c r="AI205" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ205" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK205" t="inlineStr">
         <is>
           <t>HO</t>
@@ -26223,8 +27847,16 @@
       <c r="AF206" t="inlineStr"/>
       <c r="AG206" t="inlineStr"/>
       <c r="AH206" t="inlineStr"/>
-      <c r="AI206" t="inlineStr"/>
-      <c r="AJ206" t="inlineStr"/>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ206" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK206" t="inlineStr"/>
       <c r="AL206" t="inlineStr"/>
       <c r="AM206" t="inlineStr"/>
@@ -26348,8 +27980,16 @@
       <c r="AF207" t="inlineStr"/>
       <c r="AG207" t="inlineStr"/>
       <c r="AH207" t="inlineStr"/>
-      <c r="AI207" t="inlineStr"/>
-      <c r="AJ207" t="inlineStr"/>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ207" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK207" t="inlineStr"/>
       <c r="AL207" t="inlineStr"/>
       <c r="AM207" t="inlineStr"/>
@@ -26473,8 +28113,16 @@
       <c r="AF208" t="inlineStr"/>
       <c r="AG208" t="inlineStr"/>
       <c r="AH208" t="inlineStr"/>
-      <c r="AI208" t="inlineStr"/>
-      <c r="AJ208" t="inlineStr"/>
+      <c r="AI208" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ208" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK208" t="inlineStr"/>
       <c r="AL208" t="inlineStr"/>
       <c r="AM208" t="inlineStr"/>
@@ -26598,8 +28246,16 @@
       <c r="AF209" t="inlineStr"/>
       <c r="AG209" t="inlineStr"/>
       <c r="AH209" t="inlineStr"/>
-      <c r="AI209" t="inlineStr"/>
-      <c r="AJ209" t="inlineStr"/>
+      <c r="AI209" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ209" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK209" t="inlineStr"/>
       <c r="AL209" t="inlineStr"/>
       <c r="AM209" t="inlineStr"/>
@@ -26723,8 +28379,16 @@
       <c r="AF210" t="inlineStr"/>
       <c r="AG210" t="inlineStr"/>
       <c r="AH210" t="inlineStr"/>
-      <c r="AI210" t="inlineStr"/>
-      <c r="AJ210" t="inlineStr"/>
+      <c r="AI210" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ210" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK210" t="inlineStr"/>
       <c r="AL210" t="inlineStr"/>
       <c r="AM210" t="inlineStr"/>
@@ -26848,8 +28512,16 @@
       <c r="AF211" t="inlineStr"/>
       <c r="AG211" t="inlineStr"/>
       <c r="AH211" t="inlineStr"/>
-      <c r="AI211" t="inlineStr"/>
-      <c r="AJ211" t="inlineStr"/>
+      <c r="AI211" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ211" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK211" t="inlineStr"/>
       <c r="AL211" t="inlineStr"/>
       <c r="AM211" t="inlineStr"/>
@@ -26973,8 +28645,16 @@
       <c r="AF212" t="inlineStr"/>
       <c r="AG212" t="inlineStr"/>
       <c r="AH212" t="inlineStr"/>
-      <c r="AI212" t="inlineStr"/>
-      <c r="AJ212" t="inlineStr"/>
+      <c r="AI212" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ212" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK212" t="inlineStr"/>
       <c r="AL212" t="inlineStr"/>
       <c r="AM212" t="inlineStr"/>
@@ -27098,8 +28778,16 @@
       <c r="AF213" t="inlineStr"/>
       <c r="AG213" t="inlineStr"/>
       <c r="AH213" t="inlineStr"/>
-      <c r="AI213" t="inlineStr"/>
-      <c r="AJ213" t="inlineStr"/>
+      <c r="AI213" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ213" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK213" t="inlineStr"/>
       <c r="AL213" t="inlineStr"/>
       <c r="AM213" t="inlineStr"/>
@@ -27219,8 +28907,16 @@
       <c r="AF214" t="inlineStr"/>
       <c r="AG214" t="inlineStr"/>
       <c r="AH214" t="inlineStr"/>
-      <c r="AI214" t="inlineStr"/>
-      <c r="AJ214" t="inlineStr"/>
+      <c r="AI214" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ214" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK214" t="inlineStr"/>
       <c r="AL214" t="inlineStr"/>
       <c r="AM214" t="inlineStr"/>
@@ -27344,8 +29040,16 @@
       <c r="AF215" t="inlineStr"/>
       <c r="AG215" t="inlineStr"/>
       <c r="AH215" t="inlineStr"/>
-      <c r="AI215" t="inlineStr"/>
-      <c r="AJ215" t="inlineStr"/>
+      <c r="AI215" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ215" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK215" t="inlineStr">
         <is>
           <t>HO</t>
@@ -27473,8 +29177,16 @@
       <c r="AF216" t="inlineStr"/>
       <c r="AG216" t="inlineStr"/>
       <c r="AH216" t="inlineStr"/>
-      <c r="AI216" t="inlineStr"/>
-      <c r="AJ216" t="inlineStr"/>
+      <c r="AI216" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ216" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK216" t="inlineStr"/>
       <c r="AL216" t="inlineStr"/>
       <c r="AM216" t="inlineStr"/>
@@ -27598,8 +29310,16 @@
       <c r="AF217" t="inlineStr"/>
       <c r="AG217" t="inlineStr"/>
       <c r="AH217" t="inlineStr"/>
-      <c r="AI217" t="inlineStr"/>
-      <c r="AJ217" t="inlineStr"/>
+      <c r="AI217" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ217" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK217" t="inlineStr"/>
       <c r="AL217" t="inlineStr"/>
       <c r="AM217" t="inlineStr"/>
@@ -27723,8 +29443,16 @@
       <c r="AF218" t="inlineStr"/>
       <c r="AG218" t="inlineStr"/>
       <c r="AH218" t="inlineStr"/>
-      <c r="AI218" t="inlineStr"/>
-      <c r="AJ218" t="inlineStr"/>
+      <c r="AI218" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ218" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK218" t="inlineStr"/>
       <c r="AL218" t="inlineStr"/>
       <c r="AM218" t="inlineStr"/>
@@ -27848,8 +29576,16 @@
       <c r="AF219" t="inlineStr"/>
       <c r="AG219" t="inlineStr"/>
       <c r="AH219" t="inlineStr"/>
-      <c r="AI219" t="inlineStr"/>
-      <c r="AJ219" t="inlineStr"/>
+      <c r="AI219" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ219" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK219" t="inlineStr"/>
       <c r="AL219" t="inlineStr"/>
       <c r="AM219" t="inlineStr"/>
@@ -27973,8 +29709,16 @@
       <c r="AF220" t="inlineStr"/>
       <c r="AG220" t="inlineStr"/>
       <c r="AH220" t="inlineStr"/>
-      <c r="AI220" t="inlineStr"/>
-      <c r="AJ220" t="inlineStr"/>
+      <c r="AI220" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ220" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK220" t="inlineStr">
         <is>
           <t>ONGC ELECTRICAL</t>
@@ -27985,6 +29729,2956 @@
       <c r="AN220" t="inlineStr"/>
       <c r="AO220" t="inlineStr"/>
     </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>WGE 342</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C221" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D221" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F221" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>PAUL OFFSHORE PVT</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>1fd21fab-0b2b-476d-b8d1-76460cedb3d1</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>ACC-7806823928</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr"/>
+      <c r="O221" t="inlineStr"/>
+      <c r="P221" t="inlineStr"/>
+      <c r="Q221" t="inlineStr"/>
+      <c r="R221" t="inlineStr"/>
+      <c r="S221" t="inlineStr"/>
+      <c r="T221" t="inlineStr"/>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V221" t="n">
+        <v>117495</v>
+      </c>
+      <c r="W221" t="inlineStr"/>
+      <c r="X221" t="inlineStr">
+        <is>
+          <t>ONGC GOA JAN BILL LABOUR CHARGES - WELDER / FITTER/RIGGER AND FOOD ALLOWANCE Total Amount= 342495/- Paid Rs.75000/- , Paid Rs.100000/- Excel Attendnace Sheet already shared= 167495,paid Rs.50000/-21.03.2026 RPA_ID : 544f378466</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>ONGC GOA</t>
+        </is>
+      </c>
+      <c r="Z221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB221" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF221" t="inlineStr"/>
+      <c r="AG221" t="inlineStr"/>
+      <c r="AH221" t="inlineStr"/>
+      <c r="AI221" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ221" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK221" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL221" t="inlineStr"/>
+      <c r="AM221" t="inlineStr"/>
+      <c r="AN221" t="inlineStr"/>
+      <c r="AO221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>WGE 192</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C222" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D222" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F222" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Hafis Bin Haris</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>c72b1d12-acb5-4c21-84b6-b87f066e87c5</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>ACC-99980105201458</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>FDRL0001143</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr"/>
+      <c r="P222" t="inlineStr"/>
+      <c r="Q222" t="inlineStr"/>
+      <c r="R222" t="inlineStr"/>
+      <c r="S222" t="inlineStr"/>
+      <c r="T222" t="inlineStr"/>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V222" t="n">
+        <v>9597</v>
+      </c>
+      <c r="W222" t="inlineStr"/>
+      <c r="X222" t="inlineStr">
+        <is>
+          <t>Salary- January 9597/- Full and Final Settlement Paid December 7423 , Balance 9597  Total = 17020 RPA_ID : 0e88b09653</t>
+        </is>
+      </c>
+      <c r="Y222" t="inlineStr">
+        <is>
+          <t>GOA HUL</t>
+        </is>
+      </c>
+      <c r="Z222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB222" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF222" t="inlineStr"/>
+      <c r="AG222" t="inlineStr"/>
+      <c r="AH222" t="inlineStr"/>
+      <c r="AI222" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ222" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK222" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL222" t="inlineStr"/>
+      <c r="AM222" t="inlineStr"/>
+      <c r="AN222" t="inlineStr"/>
+      <c r="AO222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>WGE 104</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C223" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D223" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F223" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>BRAHMADATHAN</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>193f1ab1-dd3a-4f8d-93b3-ec85512e1c0b</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>ACC-232001000010098</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>IOBA0002320</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr"/>
+      <c r="P223" t="inlineStr"/>
+      <c r="Q223" t="inlineStr"/>
+      <c r="R223" t="inlineStr"/>
+      <c r="S223" t="inlineStr"/>
+      <c r="T223" t="inlineStr"/>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V223" t="n">
+        <v>14379</v>
+      </c>
+      <c r="W223" t="inlineStr"/>
+      <c r="X223" t="inlineStr">
+        <is>
+          <t>Salary November Full and Final settlement Final Settlement Total 24379 , Rs.10000/- Paid  18.03.2026 Balance to be paid RPA_ID : 9d860f87fa</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>GOA HUL</t>
+        </is>
+      </c>
+      <c r="Z223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB223" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF223" t="inlineStr"/>
+      <c r="AG223" t="inlineStr"/>
+      <c r="AH223" t="inlineStr"/>
+      <c r="AI223" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ223" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK223" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL223" t="inlineStr"/>
+      <c r="AM223" t="inlineStr"/>
+      <c r="AN223" t="inlineStr"/>
+      <c r="AO223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>WGE 452</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C224" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D224" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F224" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA REDDY</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>175f6c3c-cc4f-4dba-8032-4855a66b4040</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>ACC- 79860100001270</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>BARB0VASCOD</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr"/>
+      <c r="P224" t="inlineStr"/>
+      <c r="Q224" t="inlineStr"/>
+      <c r="R224" t="inlineStr"/>
+      <c r="S224" t="inlineStr"/>
+      <c r="T224" t="inlineStr"/>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V224" t="n">
+        <v>15000</v>
+      </c>
+      <c r="W224" t="inlineStr"/>
+      <c r="X224" t="inlineStr">
+        <is>
+          <t>Hishm sir baleno auto 4th jan 10th jan 7days=10500,Baleno auto 14th jan 29th jan 16days=24000,Swift manual 17th jan 19th jan 3days=3600,Sidharth Dezire 13th feb  to 14th 3days 2400,Sir swift auto 16thfeb 17thfeb 2days 3000 2nd 1500 =45000 (10000 paid) As per Advice from Admin Andriya - No documents provided Rs.10000/- paid,Rs.10000/- paid 18.03.2026,23.023.2026 10000/-paid RPA_ID : 19b7073ac5</t>
+        </is>
+      </c>
+      <c r="Y224" t="inlineStr">
+        <is>
+          <t>ONGC IPSHEM</t>
+        </is>
+      </c>
+      <c r="Z224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB224" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF224" t="inlineStr"/>
+      <c r="AG224" t="inlineStr"/>
+      <c r="AH224" t="inlineStr"/>
+      <c r="AI224" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ224" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK224" t="inlineStr">
+        <is>
+          <t>ONGC IPSHEM</t>
+        </is>
+      </c>
+      <c r="AL224" t="inlineStr"/>
+      <c r="AM224" t="inlineStr"/>
+      <c r="AN224" t="inlineStr"/>
+      <c r="AO224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>WGE 170</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C225" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D225" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F225" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>VEDANT</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>7a65e8d7-dfe6-4389-bd47-416063ac4ae5</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>ACC-2047172054</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>KKBK0001429</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr"/>
+      <c r="P225" t="inlineStr"/>
+      <c r="Q225" t="inlineStr"/>
+      <c r="R225" t="inlineStr"/>
+      <c r="S225" t="inlineStr"/>
+      <c r="T225" t="inlineStr"/>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V225" t="n">
+        <v>6451</v>
+      </c>
+      <c r="W225" t="inlineStr"/>
+      <c r="X225" t="inlineStr">
+        <is>
+          <t>Material Shiftng 8 Days worked (December 5 days , January 3 Days) Basic Pay is Rs.25000/- perday 806.45 RPA_ID : 205c86dc07</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>MDL</t>
+        </is>
+      </c>
+      <c r="Z225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB225" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF225" t="inlineStr"/>
+      <c r="AG225" t="inlineStr"/>
+      <c r="AH225" t="inlineStr"/>
+      <c r="AI225" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ225" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK225" t="inlineStr"/>
+      <c r="AL225" t="inlineStr"/>
+      <c r="AM225" t="inlineStr"/>
+      <c r="AN225" t="inlineStr"/>
+      <c r="AO225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>WGE 603</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C226" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D226" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F226" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOHAMMED MANSOOR </t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>b73dedd7-9c7e-44b2-b618-77b6c2e856ed</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>ACC-10880100006045</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>BARB0CAVELO</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr"/>
+      <c r="P226" t="inlineStr"/>
+      <c r="Q226" t="inlineStr"/>
+      <c r="R226" t="inlineStr"/>
+      <c r="S226" t="inlineStr"/>
+      <c r="T226" t="inlineStr"/>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V226" t="n">
+        <v>6060</v>
+      </c>
+      <c r="W226" t="inlineStr"/>
+      <c r="X226" t="inlineStr">
+        <is>
+          <t>This payment pertains to hotel expenses incurred during work at ONGC. Food was provided to five Rumjan team workers as well as other workers.
+The payment for these expenses has not yet been made. The attached document includes ₹4,070 towards the food expenses of the Rumjan team workers. It also covers the food expenses of other workers who were working at ONGC , In march  food had to be arranged due to the unavailability of gas and the workers being unable to cook at that time.
+ this amount is payable to the hotel. RPA_ID : 2a9c3b46af</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>ONGC IPSHEM</t>
+        </is>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB226" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF226" t="inlineStr"/>
+      <c r="AG226" t="inlineStr"/>
+      <c r="AH226" t="inlineStr"/>
+      <c r="AI226" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ226" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK226" t="inlineStr">
+        <is>
+          <t>ONGC IPSHEM</t>
+        </is>
+      </c>
+      <c r="AL226" t="inlineStr"/>
+      <c r="AM226" t="inlineStr"/>
+      <c r="AN226" t="inlineStr"/>
+      <c r="AO226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> WGG 02</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C227" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D227" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F227" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>06d8cdd5-9168-43dc-9c10-c72dd748fa97</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr"/>
+      <c r="N227" t="inlineStr"/>
+      <c r="O227" t="inlineStr"/>
+      <c r="P227" t="inlineStr"/>
+      <c r="Q227" t="inlineStr"/>
+      <c r="R227" t="inlineStr"/>
+      <c r="S227" t="inlineStr"/>
+      <c r="T227" t="inlineStr"/>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V227" t="n">
+        <v>507962</v>
+      </c>
+      <c r="W227" t="inlineStr"/>
+      <c r="X227" t="inlineStr">
+        <is>
+          <t>ESI REVENU RECOVERY  Rs 1015923, to pay 50 % RPA_ID : e64c2fefbe</t>
+        </is>
+      </c>
+      <c r="Y227" t="inlineStr">
+        <is>
+          <t>KOLKATTA</t>
+        </is>
+      </c>
+      <c r="Z227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB227" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF227" t="inlineStr"/>
+      <c r="AG227" t="inlineStr"/>
+      <c r="AH227" t="inlineStr"/>
+      <c r="AI227" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ227" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK227" t="inlineStr"/>
+      <c r="AL227" t="inlineStr"/>
+      <c r="AM227" t="inlineStr"/>
+      <c r="AN227" t="inlineStr"/>
+      <c r="AO227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> WGG 02</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C228" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D228" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F228" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>8a75c211-0c1a-40ff-a848-7a1d542816c4</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr"/>
+      <c r="N228" t="inlineStr"/>
+      <c r="O228" t="inlineStr"/>
+      <c r="P228" t="inlineStr"/>
+      <c r="Q228" t="inlineStr"/>
+      <c r="R228" t="inlineStr"/>
+      <c r="S228" t="inlineStr"/>
+      <c r="T228" t="inlineStr"/>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V228" t="n">
+        <v>290000</v>
+      </c>
+      <c r="W228" t="inlineStr"/>
+      <c r="X228" t="inlineStr">
+        <is>
+          <t>AUGUST PF ARREAR KOCHI AND KONGAN APPROXIMATE RPA_ID : 4286a85cfa</t>
+        </is>
+      </c>
+      <c r="Y228" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="Z228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB228" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF228" t="inlineStr"/>
+      <c r="AG228" t="inlineStr"/>
+      <c r="AH228" t="inlineStr"/>
+      <c r="AI228" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ228" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK228" t="inlineStr"/>
+      <c r="AL228" t="inlineStr"/>
+      <c r="AM228" t="inlineStr"/>
+      <c r="AN228" t="inlineStr"/>
+      <c r="AO228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>WGE 73</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C229" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D229" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F229" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>DCR</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>NITHIN P</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>bd5de4a0-a3bc-43e0-9adf-7cc13fc64252</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>ACC-32555551936</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>SBIN0001890</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr"/>
+      <c r="P229" t="inlineStr"/>
+      <c r="Q229" t="inlineStr"/>
+      <c r="R229" t="inlineStr"/>
+      <c r="S229" t="inlineStr"/>
+      <c r="T229" t="inlineStr"/>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V229" t="n">
+        <v>3000</v>
+      </c>
+      <c r="W229" t="inlineStr"/>
+      <c r="X229" t="inlineStr">
+        <is>
+          <t>Casual Payment 31.03.2026 (2000), 01.04.2026(1000) Leave Nishanth RPA_ID : 2210bad376</t>
+        </is>
+      </c>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>HPCL ELATHOOR</t>
+        </is>
+      </c>
+      <c r="Z229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB229" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF229" t="inlineStr"/>
+      <c r="AG229" t="inlineStr"/>
+      <c r="AH229" t="inlineStr"/>
+      <c r="AI229" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ229" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK229" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="AL229" t="inlineStr"/>
+      <c r="AM229" t="inlineStr"/>
+      <c r="AN229" t="inlineStr"/>
+      <c r="AO229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>WGE 02</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C230" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D230" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F230" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>DCR</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>SAFAL SOJAN</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>4063becd-9fac-4dac-b889-e77b4a5e9cee</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>ACC-67268241138</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>SBIN0070435</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr"/>
+      <c r="P230" t="inlineStr"/>
+      <c r="Q230" t="inlineStr"/>
+      <c r="R230" t="inlineStr"/>
+      <c r="S230" t="inlineStr"/>
+      <c r="T230" t="inlineStr"/>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V230" t="n">
+        <v>2000</v>
+      </c>
+      <c r="W230" t="inlineStr"/>
+      <c r="X230" t="inlineStr">
+        <is>
+          <t>Horse Fiting Charges 19.03.2026 RPA_ID : e998a8abc6</t>
+        </is>
+      </c>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>IOCL WELLINGDON</t>
+        </is>
+      </c>
+      <c r="Z230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB230" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF230" t="inlineStr"/>
+      <c r="AG230" t="inlineStr"/>
+      <c r="AH230" t="inlineStr"/>
+      <c r="AI230" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ230" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK230" t="inlineStr"/>
+      <c r="AL230" t="inlineStr"/>
+      <c r="AM230" t="inlineStr"/>
+      <c r="AN230" t="inlineStr"/>
+      <c r="AO230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>WGE 323</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C231" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D231" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F231" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>VINITHA V NAIR</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>cfc954e6-eba5-4bf3-80ff-bc093e7d0019</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>ACC-22020100013715</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>FDRL0002202</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr"/>
+      <c r="P231" t="inlineStr"/>
+      <c r="Q231" t="inlineStr"/>
+      <c r="R231" t="inlineStr"/>
+      <c r="S231" t="inlineStr"/>
+      <c r="T231" t="inlineStr"/>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V231" t="n">
+        <v>14500</v>
+      </c>
+      <c r="W231" t="inlineStr"/>
+      <c r="X231" t="inlineStr">
+        <is>
+          <t>Prabeesh labours
+5 - mason x 1300 : 6500
+8 - helpers x 1000 : 8000 RPA_ID : e926eccabf</t>
+        </is>
+      </c>
+      <c r="Y231" t="inlineStr">
+        <is>
+          <t>Construction of IOCL RO at Pappinisseri</t>
+        </is>
+      </c>
+      <c r="Z231" t="inlineStr">
+        <is>
+          <t>LABOUR CHARGES</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>commercial@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB231" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF231" t="inlineStr"/>
+      <c r="AG231" t="inlineStr"/>
+      <c r="AH231" t="inlineStr"/>
+      <c r="AI231" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ231" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK231" t="inlineStr"/>
+      <c r="AL231" t="inlineStr"/>
+      <c r="AM231" t="inlineStr"/>
+      <c r="AN231" t="inlineStr"/>
+      <c r="AO231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>WGE 323</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C232" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D232" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F232" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>VINITHA V NAIR</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>8be0bc1c-33b7-4a60-861b-097ea4a8e318</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>ACC-22020100013715</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>FDRL0002202</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr"/>
+      <c r="P232" t="inlineStr"/>
+      <c r="Q232" t="inlineStr"/>
+      <c r="R232" t="inlineStr"/>
+      <c r="S232" t="inlineStr"/>
+      <c r="T232" t="inlineStr"/>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V232" t="n">
+        <v>1300</v>
+      </c>
+      <c r="W232" t="inlineStr"/>
+      <c r="X232" t="inlineStr">
+        <is>
+          <t>additional labours 
+1-mason : 1300/- RPA_ID : ec31986722</t>
+        </is>
+      </c>
+      <c r="Y232" t="inlineStr">
+        <is>
+          <t>Construction of IOCL RO at Pappinisseri</t>
+        </is>
+      </c>
+      <c r="Z232" t="inlineStr">
+        <is>
+          <t>LABOUR CHARGES</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>commercial@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB232" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF232" t="inlineStr"/>
+      <c r="AG232" t="inlineStr"/>
+      <c r="AH232" t="inlineStr"/>
+      <c r="AI232" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ232" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK232" t="inlineStr"/>
+      <c r="AL232" t="inlineStr"/>
+      <c r="AM232" t="inlineStr"/>
+      <c r="AN232" t="inlineStr"/>
+      <c r="AO232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>WGE 323</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C233" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D233" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F233" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>VINITHA V NAIR</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>7a73622f-b536-481c-9a95-9d15c8657adc</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>ACC-22020100013715</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>FDRL0002202</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr"/>
+      <c r="P233" t="inlineStr"/>
+      <c r="Q233" t="inlineStr"/>
+      <c r="R233" t="inlineStr"/>
+      <c r="S233" t="inlineStr"/>
+      <c r="T233" t="inlineStr"/>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V233" t="n">
+        <v>540</v>
+      </c>
+      <c r="W233" t="inlineStr"/>
+      <c r="X233" t="inlineStr">
+        <is>
+          <t>food : 540/- RPA_ID : 5a8d847443</t>
+        </is>
+      </c>
+      <c r="Y233" t="inlineStr">
+        <is>
+          <t>Construction of IOCL RO at Pappinisseri</t>
+        </is>
+      </c>
+      <c r="Z233" t="inlineStr">
+        <is>
+          <t>FOOD CHARGES</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>commercial@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB233" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF233" t="inlineStr"/>
+      <c r="AG233" t="inlineStr"/>
+      <c r="AH233" t="inlineStr"/>
+      <c r="AI233" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ233" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK233" t="inlineStr"/>
+      <c r="AL233" t="inlineStr"/>
+      <c r="AM233" t="inlineStr"/>
+      <c r="AN233" t="inlineStr"/>
+      <c r="AO233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> WGG 02</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C234" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D234" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F234" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>72665bc0-0b9d-420c-8179-2ab0ee38a2e7</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr"/>
+      <c r="N234" t="inlineStr"/>
+      <c r="O234" t="inlineStr"/>
+      <c r="P234" t="inlineStr"/>
+      <c r="Q234" t="inlineStr"/>
+      <c r="R234" t="inlineStr"/>
+      <c r="S234" t="inlineStr"/>
+      <c r="T234" t="inlineStr"/>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V234" t="n">
+        <v>30525</v>
+      </c>
+      <c r="W234" t="inlineStr"/>
+      <c r="X234" t="inlineStr">
+        <is>
+          <t>SALARY MARCH 2026 RPA_ID : 88e12e6fa4</t>
+        </is>
+      </c>
+      <c r="Y234" t="inlineStr">
+        <is>
+          <t>SMART MARINE</t>
+        </is>
+      </c>
+      <c r="Z234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB234" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF234" t="inlineStr"/>
+      <c r="AG234" t="inlineStr"/>
+      <c r="AH234" t="inlineStr"/>
+      <c r="AI234" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ234" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK234" t="inlineStr"/>
+      <c r="AL234" t="inlineStr"/>
+      <c r="AM234" t="inlineStr"/>
+      <c r="AN234" t="inlineStr"/>
+      <c r="AO234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> WGG 02</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C235" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D235" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F235" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>d9442071-6fee-4ffb-a9f4-3843245275b8</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr"/>
+      <c r="N235" t="inlineStr"/>
+      <c r="O235" t="inlineStr"/>
+      <c r="P235" t="inlineStr"/>
+      <c r="Q235" t="inlineStr"/>
+      <c r="R235" t="inlineStr"/>
+      <c r="S235" t="inlineStr"/>
+      <c r="T235" t="inlineStr"/>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V235" t="n">
+        <v>21134</v>
+      </c>
+      <c r="W235" t="inlineStr"/>
+      <c r="X235" t="inlineStr">
+        <is>
+          <t>SALARY MARCH 2026 RPA_ID : 2163ea0e5e</t>
+        </is>
+      </c>
+      <c r="Y235" t="inlineStr">
+        <is>
+          <t>SMART MARINE</t>
+        </is>
+      </c>
+      <c r="Z235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB235" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF235" t="inlineStr"/>
+      <c r="AG235" t="inlineStr"/>
+      <c r="AH235" t="inlineStr"/>
+      <c r="AI235" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ235" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK235" t="inlineStr"/>
+      <c r="AL235" t="inlineStr"/>
+      <c r="AM235" t="inlineStr"/>
+      <c r="AN235" t="inlineStr"/>
+      <c r="AO235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> WGG 02</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C236" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D236" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F236" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>4dfe9822-6d6d-4654-94a0-8525f434bdce</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr"/>
+      <c r="N236" t="inlineStr"/>
+      <c r="O236" t="inlineStr"/>
+      <c r="P236" t="inlineStr"/>
+      <c r="Q236" t="inlineStr"/>
+      <c r="R236" t="inlineStr"/>
+      <c r="S236" t="inlineStr"/>
+      <c r="T236" t="inlineStr"/>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V236" t="n">
+        <v>32634</v>
+      </c>
+      <c r="W236" t="inlineStr"/>
+      <c r="X236" t="inlineStr">
+        <is>
+          <t>SALARY MARCH 2026 RPA_ID : ec287a70f9</t>
+        </is>
+      </c>
+      <c r="Y236" t="inlineStr">
+        <is>
+          <t>SMART MARINE</t>
+        </is>
+      </c>
+      <c r="Z236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB236" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF236" t="inlineStr"/>
+      <c r="AG236" t="inlineStr"/>
+      <c r="AH236" t="inlineStr"/>
+      <c r="AI236" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ236" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK236" t="inlineStr"/>
+      <c r="AL236" t="inlineStr"/>
+      <c r="AM236" t="inlineStr"/>
+      <c r="AN236" t="inlineStr"/>
+      <c r="AO236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> WGG 02</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C237" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D237" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F237" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>3d424875-3c02-4be1-8cad-bd689401d4ed</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr"/>
+      <c r="N237" t="inlineStr"/>
+      <c r="O237" t="inlineStr"/>
+      <c r="P237" t="inlineStr"/>
+      <c r="Q237" t="inlineStr"/>
+      <c r="R237" t="inlineStr"/>
+      <c r="S237" t="inlineStr"/>
+      <c r="T237" t="inlineStr"/>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V237" t="n">
+        <v>33262</v>
+      </c>
+      <c r="W237" t="inlineStr"/>
+      <c r="X237" t="inlineStr">
+        <is>
+          <t>SALARY MARCH 2026 RPA_ID : df90b7faa5</t>
+        </is>
+      </c>
+      <c r="Y237" t="inlineStr">
+        <is>
+          <t>SMART MARINE</t>
+        </is>
+      </c>
+      <c r="Z237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB237" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF237" t="inlineStr"/>
+      <c r="AG237" t="inlineStr"/>
+      <c r="AH237" t="inlineStr"/>
+      <c r="AI237" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ237" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK237" t="inlineStr"/>
+      <c r="AL237" t="inlineStr"/>
+      <c r="AM237" t="inlineStr"/>
+      <c r="AN237" t="inlineStr"/>
+      <c r="AO237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> WGG 02</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C238" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D238" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F238" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>6257aaa1-9f79-4227-80d1-545d4f4f5e94</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr"/>
+      <c r="N238" t="inlineStr"/>
+      <c r="O238" t="inlineStr"/>
+      <c r="P238" t="inlineStr"/>
+      <c r="Q238" t="inlineStr"/>
+      <c r="R238" t="inlineStr"/>
+      <c r="S238" t="inlineStr"/>
+      <c r="T238" t="inlineStr"/>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V238" t="n">
+        <v>33262</v>
+      </c>
+      <c r="W238" t="inlineStr"/>
+      <c r="X238" t="inlineStr">
+        <is>
+          <t>SALARY MARCH 2026 RPA_ID : 6a38b5f660</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>SMART MARINE</t>
+        </is>
+      </c>
+      <c r="Z238" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB238" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC238" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD238" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE238" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF238" t="inlineStr"/>
+      <c r="AG238" t="inlineStr"/>
+      <c r="AH238" t="inlineStr"/>
+      <c r="AI238" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ238" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK238" t="inlineStr"/>
+      <c r="AL238" t="inlineStr"/>
+      <c r="AM238" t="inlineStr"/>
+      <c r="AN238" t="inlineStr"/>
+      <c r="AO238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> WGG 02</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C239" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D239" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F239" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>7edd8fa2-2708-4e5c-893b-5423bfb3aed0</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr"/>
+      <c r="N239" t="inlineStr"/>
+      <c r="O239" t="inlineStr"/>
+      <c r="P239" t="inlineStr"/>
+      <c r="Q239" t="inlineStr"/>
+      <c r="R239" t="inlineStr"/>
+      <c r="S239" t="inlineStr"/>
+      <c r="T239" t="inlineStr"/>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V239" t="n">
+        <v>37400</v>
+      </c>
+      <c r="W239" t="inlineStr"/>
+      <c r="X239" t="inlineStr">
+        <is>
+          <t>SALARY MARCH 2026 RPA_ID : 8823b70286</t>
+        </is>
+      </c>
+      <c r="Y239" t="inlineStr">
+        <is>
+          <t>SMART MARINE</t>
+        </is>
+      </c>
+      <c r="Z239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB239" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF239" t="inlineStr"/>
+      <c r="AG239" t="inlineStr"/>
+      <c r="AH239" t="inlineStr"/>
+      <c r="AI239" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ239" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK239" t="inlineStr"/>
+      <c r="AL239" t="inlineStr"/>
+      <c r="AM239" t="inlineStr"/>
+      <c r="AN239" t="inlineStr"/>
+      <c r="AO239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> WGG 02</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C240" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D240" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F240" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>754afcd3-21db-44e1-9326-50d25c1c075b</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr"/>
+      <c r="N240" t="inlineStr"/>
+      <c r="O240" t="inlineStr"/>
+      <c r="P240" t="inlineStr"/>
+      <c r="Q240" t="inlineStr"/>
+      <c r="R240" t="inlineStr"/>
+      <c r="S240" t="inlineStr"/>
+      <c r="T240" t="inlineStr"/>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V240" t="n">
+        <v>37400</v>
+      </c>
+      <c r="W240" t="inlineStr"/>
+      <c r="X240" t="inlineStr">
+        <is>
+          <t>SALARY MARCH 2026 RPA_ID : 1a7bd4958e</t>
+        </is>
+      </c>
+      <c r="Y240" t="inlineStr">
+        <is>
+          <t>SMART MARINE</t>
+        </is>
+      </c>
+      <c r="Z240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB240" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF240" t="inlineStr"/>
+      <c r="AG240" t="inlineStr"/>
+      <c r="AH240" t="inlineStr"/>
+      <c r="AI240" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ240" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK240" t="inlineStr"/>
+      <c r="AL240" t="inlineStr"/>
+      <c r="AM240" t="inlineStr"/>
+      <c r="AN240" t="inlineStr"/>
+      <c r="AO240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> WGG 02</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C241" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D241" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F241" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>76f3c17f-fd23-4033-8958-d4c6885e74cf</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr"/>
+      <c r="N241" t="inlineStr"/>
+      <c r="O241" t="inlineStr"/>
+      <c r="P241" t="inlineStr"/>
+      <c r="Q241" t="inlineStr"/>
+      <c r="R241" t="inlineStr"/>
+      <c r="S241" t="inlineStr"/>
+      <c r="T241" t="inlineStr"/>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V241" t="n">
+        <v>38400</v>
+      </c>
+      <c r="W241" t="inlineStr"/>
+      <c r="X241" t="inlineStr">
+        <is>
+          <t>SALARY MARCH 2026 RPA_ID : 051ea02e19</t>
+        </is>
+      </c>
+      <c r="Y241" t="inlineStr">
+        <is>
+          <t>SMART MARINE</t>
+        </is>
+      </c>
+      <c r="Z241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB241" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF241" t="inlineStr"/>
+      <c r="AG241" t="inlineStr"/>
+      <c r="AH241" t="inlineStr"/>
+      <c r="AI241" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ241" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK241" t="inlineStr"/>
+      <c r="AL241" t="inlineStr"/>
+      <c r="AM241" t="inlineStr"/>
+      <c r="AN241" t="inlineStr"/>
+      <c r="AO241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> WGG 02</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C242" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D242" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F242" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>57cab3e7-744f-41f7-af2c-be88338cb885</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr"/>
+      <c r="N242" t="inlineStr"/>
+      <c r="O242" t="inlineStr"/>
+      <c r="P242" t="inlineStr"/>
+      <c r="Q242" t="inlineStr"/>
+      <c r="R242" t="inlineStr"/>
+      <c r="S242" t="inlineStr"/>
+      <c r="T242" t="inlineStr"/>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V242" t="n">
+        <v>37518</v>
+      </c>
+      <c r="W242" t="inlineStr"/>
+      <c r="X242" t="inlineStr">
+        <is>
+          <t>SALARY MARCH 2026 RPA_ID : 145c7ce0f6</t>
+        </is>
+      </c>
+      <c r="Y242" t="inlineStr">
+        <is>
+          <t>SMART MARINE</t>
+        </is>
+      </c>
+      <c r="Z242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB242" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF242" t="inlineStr"/>
+      <c r="AG242" t="inlineStr"/>
+      <c r="AH242" t="inlineStr"/>
+      <c r="AI242" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ242" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK242" t="inlineStr"/>
+      <c r="AL242" t="inlineStr"/>
+      <c r="AM242" t="inlineStr"/>
+      <c r="AN242" t="inlineStr"/>
+      <c r="AO242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> WGG 02</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C243" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D243" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F243" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>18bdc386-f5dc-4b63-8c2b-5a588cbc7b94</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr"/>
+      <c r="N243" t="inlineStr"/>
+      <c r="O243" t="inlineStr"/>
+      <c r="P243" t="inlineStr"/>
+      <c r="Q243" t="inlineStr"/>
+      <c r="R243" t="inlineStr"/>
+      <c r="S243" t="inlineStr"/>
+      <c r="T243" t="inlineStr"/>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V243" t="n">
+        <v>37900</v>
+      </c>
+      <c r="W243" t="inlineStr"/>
+      <c r="X243" t="inlineStr">
+        <is>
+          <t>SALARY MARCH 2026 RPA_ID : 0722fccdfa</t>
+        </is>
+      </c>
+      <c r="Y243" t="inlineStr">
+        <is>
+          <t>SMART MARINE</t>
+        </is>
+      </c>
+      <c r="Z243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB243" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF243" t="inlineStr"/>
+      <c r="AG243" t="inlineStr"/>
+      <c r="AH243" t="inlineStr"/>
+      <c r="AI243" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ243" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK243" t="inlineStr"/>
+      <c r="AL243" t="inlineStr"/>
+      <c r="AM243" t="inlineStr"/>
+      <c r="AN243" t="inlineStr"/>
+      <c r="AO243" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PENDING_APPROVAL_SHEET.xlsx
+++ b/PENDING_APPROVAL_SHEET.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO243"/>
+  <dimension ref="A1:AO311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32679,6 +32679,9076 @@
       <c r="AN243" t="inlineStr"/>
       <c r="AO243" t="inlineStr"/>
     </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>WGE 511</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C244" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D244" t="n">
+        <v>286964</v>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F244" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>DCR</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Johny P A</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>f1a7fac7-41a7-4f63-9197-a41fce79697d</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>ACC-57067358784</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>SBIN0070855</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr"/>
+      <c r="P244" t="inlineStr"/>
+      <c r="Q244" t="inlineStr"/>
+      <c r="R244" t="inlineStr"/>
+      <c r="S244" t="inlineStr"/>
+      <c r="T244" t="inlineStr"/>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V244" t="n">
+        <v>3700</v>
+      </c>
+      <c r="W244" t="inlineStr"/>
+      <c r="X244" t="inlineStr">
+        <is>
+          <t>JAY JAY PRINTING(SMART MARINE LETTER HEAD &amp; COVER LETTER) RPA_ID : f7dd130351</t>
+        </is>
+      </c>
+      <c r="Y244" t="inlineStr">
+        <is>
+          <t>SMART MARINE</t>
+        </is>
+      </c>
+      <c r="Z244" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
+      </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>misexecutivewgc@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB244" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF244" t="inlineStr"/>
+      <c r="AG244" t="inlineStr"/>
+      <c r="AH244" t="inlineStr"/>
+      <c r="AI244" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ244" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK244" t="inlineStr"/>
+      <c r="AL244" t="inlineStr"/>
+      <c r="AM244" t="inlineStr"/>
+      <c r="AN244" t="inlineStr"/>
+      <c r="AO244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>WGE 513</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C245" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D245" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F245" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>TRAVEL DESIGNERS HUB</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>f71def9a-c4ea-4cd3-ac2a-5d5bcf4a530f</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>ACC-10030200033897</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>FDRL0001003</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr"/>
+      <c r="P245" t="inlineStr"/>
+      <c r="Q245" t="inlineStr"/>
+      <c r="R245" t="inlineStr"/>
+      <c r="S245" t="inlineStr"/>
+      <c r="T245" t="inlineStr"/>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V245" t="n">
+        <v>55950</v>
+      </c>
+      <c r="W245" t="inlineStr"/>
+      <c r="X245" t="inlineStr">
+        <is>
+          <t>SONIYA FLIGHT TICKET BOOKING (HISHAM SIR &amp; HIJAS SIR GOA-KOCHI -IPSHEM -14200,PATEL SUBHASHBHAI -SURAT TO GOA IPSHEM -15950,RAMESH KUMAR &amp;KRISHNA KUMAR - PATNA TO HUBLI BELLARI - 25800 RPA_ID : 39c0919144</t>
+        </is>
+      </c>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
+      </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>misexecutivewgc@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB245" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC245" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD245" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE245" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF245" t="inlineStr"/>
+      <c r="AG245" t="inlineStr"/>
+      <c r="AH245" t="inlineStr"/>
+      <c r="AI245" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ245" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK245" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="AL245" t="inlineStr"/>
+      <c r="AM245" t="inlineStr"/>
+      <c r="AN245" t="inlineStr"/>
+      <c r="AO245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>WGE 220</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C246" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D246" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F246" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>ANDRIYA THOMAS</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>2ec119c7-a08f-42dd-bdd7-21f16f1fbaac</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>ACC-0706101053789</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>CNRB0000706</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr"/>
+      <c r="P246" t="inlineStr"/>
+      <c r="Q246" t="inlineStr"/>
+      <c r="R246" t="inlineStr"/>
+      <c r="S246" t="inlineStr"/>
+      <c r="T246" t="inlineStr"/>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V246" t="n">
+        <v>100</v>
+      </c>
+      <c r="W246" t="inlineStr"/>
+      <c r="X246" t="inlineStr">
+        <is>
+          <t>(SMART MARINE) - PETROL (31-03-2026) &amp; (01-04-2026) RPA_ID : 00cdc6d4dc</t>
+        </is>
+      </c>
+      <c r="Y246" t="inlineStr">
+        <is>
+          <t>SMART MARINE</t>
+        </is>
+      </c>
+      <c r="Z246" t="inlineStr">
+        <is>
+          <t>REIMBURSEMENT</t>
+        </is>
+      </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>misexecutivewgc@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB246" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF246" t="inlineStr"/>
+      <c r="AG246" t="inlineStr"/>
+      <c r="AH246" t="inlineStr"/>
+      <c r="AI246" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ246" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK246" t="inlineStr"/>
+      <c r="AL246" t="inlineStr"/>
+      <c r="AM246" t="inlineStr"/>
+      <c r="AN246" t="inlineStr"/>
+      <c r="AO246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>WGE 477</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C247" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D247" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F247" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Techmate Solutions ( NEW)</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>f8d0ac1f-208e-4f10-a716-35a454158d57</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>ACC-30810400000070</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>BARB0VYTILA</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr"/>
+      <c r="P247" t="inlineStr"/>
+      <c r="Q247" t="inlineStr"/>
+      <c r="R247" t="inlineStr"/>
+      <c r="S247" t="inlineStr"/>
+      <c r="T247" t="inlineStr"/>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V247" t="n">
+        <v>2336</v>
+      </c>
+      <c r="W247" t="inlineStr"/>
+      <c r="X247" t="inlineStr">
+        <is>
+          <t>TP-LINK WIFI RANGE EXTENDER (18-03-2026) RPA_ID : 0f0ccb5697</t>
+        </is>
+      </c>
+      <c r="Y247" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="Z247" t="inlineStr">
+        <is>
+          <t>REIMBURSEMENT</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>misexecutivewgc@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB247" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC247" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD247" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE247" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF247" t="inlineStr"/>
+      <c r="AG247" t="inlineStr"/>
+      <c r="AH247" t="inlineStr"/>
+      <c r="AI247" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ247" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK247" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="AL247" t="inlineStr"/>
+      <c r="AM247" t="inlineStr"/>
+      <c r="AN247" t="inlineStr"/>
+      <c r="AO247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>WGE 477</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C248" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D248" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F248" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Techmate Solutions ( NEW)</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>6bc3e036-d8fb-4ccb-a47c-8f557ea3328a</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>ACC-30810400000070</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>BARB0VYTILA</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr"/>
+      <c r="P248" t="inlineStr"/>
+      <c r="Q248" t="inlineStr"/>
+      <c r="R248" t="inlineStr"/>
+      <c r="S248" t="inlineStr"/>
+      <c r="T248" t="inlineStr"/>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V248" t="n">
+        <v>1121</v>
+      </c>
+      <c r="W248" t="inlineStr"/>
+      <c r="X248" t="inlineStr">
+        <is>
+          <t>VENTION HDMI CABLE 5 METER RPA_ID : 774a1ed64a</t>
+        </is>
+      </c>
+      <c r="Y248" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="Z248" t="inlineStr">
+        <is>
+          <t>REIMBURSEMENT</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>misexecutivewgc@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB248" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC248" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD248" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE248" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF248" t="inlineStr"/>
+      <c r="AG248" t="inlineStr"/>
+      <c r="AH248" t="inlineStr"/>
+      <c r="AI248" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ248" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK248" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="AL248" t="inlineStr"/>
+      <c r="AM248" t="inlineStr"/>
+      <c r="AN248" t="inlineStr"/>
+      <c r="AO248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>WGE 429</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C249" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D249" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F249" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>SAFNA</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>b5f16dbc-e311-484c-b23a-331c24cc415c</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>ACC- 111001504967</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>ICIC0001110</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr"/>
+      <c r="P249" t="inlineStr"/>
+      <c r="Q249" t="inlineStr"/>
+      <c r="R249" t="inlineStr"/>
+      <c r="S249" t="inlineStr"/>
+      <c r="T249" t="inlineStr"/>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V249" t="n">
+        <v>47</v>
+      </c>
+      <c r="W249" t="inlineStr"/>
+      <c r="X249" t="inlineStr">
+        <is>
+          <t>BISCUIT (SIR) RPA_ID : 83d54c1048</t>
+        </is>
+      </c>
+      <c r="Y249" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="Z249" t="inlineStr">
+        <is>
+          <t>REIMBURSEMENT</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>misexecutivewgc@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB249" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF249" t="inlineStr"/>
+      <c r="AG249" t="inlineStr"/>
+      <c r="AH249" t="inlineStr"/>
+      <c r="AI249" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ249" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK249" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="AL249" t="inlineStr"/>
+      <c r="AM249" t="inlineStr"/>
+      <c r="AN249" t="inlineStr"/>
+      <c r="AO249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>WGE 428</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C250" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D250" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F250" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>NAIJAL driver</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>6a852f93-5669-4529-8f3e-665ec910e0b5</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>ACC-13962100139241</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>FDRL0001396</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr"/>
+      <c r="P250" t="inlineStr"/>
+      <c r="Q250" t="inlineStr"/>
+      <c r="R250" t="inlineStr"/>
+      <c r="S250" t="inlineStr"/>
+      <c r="T250" t="inlineStr"/>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V250" t="n">
+        <v>56</v>
+      </c>
+      <c r="W250" t="inlineStr"/>
+      <c r="X250" t="inlineStr">
+        <is>
+          <t>MILK (2NOS) RPA_ID : ef32ae5a01</t>
+        </is>
+      </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="Z250" t="inlineStr">
+        <is>
+          <t>REIMBURSEMENT</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>misexecutivewgc@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB250" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC250" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD250" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE250" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF250" t="inlineStr"/>
+      <c r="AG250" t="inlineStr"/>
+      <c r="AH250" t="inlineStr"/>
+      <c r="AI250" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ250" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK250" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="AL250" t="inlineStr"/>
+      <c r="AM250" t="inlineStr"/>
+      <c r="AN250" t="inlineStr"/>
+      <c r="AO250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>WGE 457</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C251" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D251" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F251" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>AKHIL HO</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>b67b02d9-5a58-411f-a275-913c5b6f30ab</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>ACC-10120100459191</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>FDRL0001012</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr"/>
+      <c r="P251" t="inlineStr"/>
+      <c r="Q251" t="inlineStr"/>
+      <c r="R251" t="inlineStr"/>
+      <c r="S251" t="inlineStr"/>
+      <c r="T251" t="inlineStr"/>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V251" t="n">
+        <v>100</v>
+      </c>
+      <c r="W251" t="inlineStr"/>
+      <c r="X251" t="inlineStr">
+        <is>
+          <t>BATTERY PURCHASE RPA_ID : 139ca4cbed</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="Z251" t="inlineStr">
+        <is>
+          <t>REIMBURSEMENT</t>
+        </is>
+      </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>misexecutivewgc@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB251" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC251" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD251" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE251" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF251" t="inlineStr"/>
+      <c r="AG251" t="inlineStr"/>
+      <c r="AH251" t="inlineStr"/>
+      <c r="AI251" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ251" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK251" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="AL251" t="inlineStr"/>
+      <c r="AM251" t="inlineStr"/>
+      <c r="AN251" t="inlineStr"/>
+      <c r="AO251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>WGE 429</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C252" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D252" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F252" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>SAFNA</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>57d3b7de-1255-4270-8773-4d993d914a19</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>ACC- 111001504967</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>ICIC0001110</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr"/>
+      <c r="P252" t="inlineStr"/>
+      <c r="Q252" t="inlineStr"/>
+      <c r="R252" t="inlineStr"/>
+      <c r="S252" t="inlineStr"/>
+      <c r="T252" t="inlineStr"/>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V252" t="n">
+        <v>10100</v>
+      </c>
+      <c r="W252" t="inlineStr"/>
+      <c r="X252" t="inlineStr">
+        <is>
+          <t>(HIJAS SIR  WIFE )        FEES VTH std - 5120 &amp; IIIRD std - 4980 RPA_ID : b57c3b674e</t>
+        </is>
+      </c>
+      <c r="Y252" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="Z252" t="inlineStr">
+        <is>
+          <t>REIMBURSEMENT</t>
+        </is>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>misexecutivewgc@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB252" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC252" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD252" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE252" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF252" t="inlineStr"/>
+      <c r="AG252" t="inlineStr"/>
+      <c r="AH252" t="inlineStr"/>
+      <c r="AI252" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ252" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK252" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="AL252" t="inlineStr"/>
+      <c r="AM252" t="inlineStr"/>
+      <c r="AN252" t="inlineStr"/>
+      <c r="AO252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>WGE 90</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C253" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D253" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F253" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Roslin Neenu</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>66c8b74a-cca1-4854-a713-c3098aa971b9</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>ACC-520291000298651</t>
+        </is>
+      </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>UBIN0919748</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr"/>
+      <c r="P253" t="inlineStr"/>
+      <c r="Q253" t="inlineStr"/>
+      <c r="R253" t="inlineStr"/>
+      <c r="S253" t="inlineStr"/>
+      <c r="T253" t="inlineStr"/>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V253" t="n">
+        <v>420</v>
+      </c>
+      <c r="W253" t="inlineStr"/>
+      <c r="X253" t="inlineStr">
+        <is>
+          <t>MILK(MONDAY TO SATURDAY) - EXCLUDE  FRIDAY RPA_ID : a23eb06541</t>
+        </is>
+      </c>
+      <c r="Y253" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="Z253" t="inlineStr">
+        <is>
+          <t>REIMBURSEMENT</t>
+        </is>
+      </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>misexecutivewgc@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB253" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC253" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD253" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE253" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF253" t="inlineStr"/>
+      <c r="AG253" t="inlineStr"/>
+      <c r="AH253" t="inlineStr"/>
+      <c r="AI253" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ253" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK253" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="AL253" t="inlineStr"/>
+      <c r="AM253" t="inlineStr"/>
+      <c r="AN253" t="inlineStr"/>
+      <c r="AO253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>WGE 497</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C254" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D254" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F254" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Madhu John</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>dd5ae3ec-0c9c-4a95-848d-dd5267b99cc2</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>ACC-13160100106860</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>FDRL0001316</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr"/>
+      <c r="P254" t="inlineStr"/>
+      <c r="Q254" t="inlineStr"/>
+      <c r="R254" t="inlineStr"/>
+      <c r="S254" t="inlineStr"/>
+      <c r="T254" t="inlineStr"/>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V254" t="n">
+        <v>4200</v>
+      </c>
+      <c r="W254" t="inlineStr"/>
+      <c r="X254" t="inlineStr">
+        <is>
+          <t>FOOD DELIVERY RPA_ID : 49b7803a4b</t>
+        </is>
+      </c>
+      <c r="Y254" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="Z254" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>misexecutivewgc@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB254" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC254" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD254" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE254" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF254" t="inlineStr"/>
+      <c r="AG254" t="inlineStr"/>
+      <c r="AH254" t="inlineStr"/>
+      <c r="AI254" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ254" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK254" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="AL254" t="inlineStr"/>
+      <c r="AM254" t="inlineStr"/>
+      <c r="AN254" t="inlineStr"/>
+      <c r="AO254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>WGE 220</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C255" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D255" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F255" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>ANDRIYA THOMAS</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>fc2e512e-9c12-45ef-a471-9dfbcd560796</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>ACC-0706101053789</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>CNRB0000706</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr"/>
+      <c r="P255" t="inlineStr"/>
+      <c r="Q255" t="inlineStr"/>
+      <c r="R255" t="inlineStr"/>
+      <c r="S255" t="inlineStr"/>
+      <c r="T255" t="inlineStr"/>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V255" t="n">
+        <v>50</v>
+      </c>
+      <c r="W255" t="inlineStr"/>
+      <c r="X255" t="inlineStr">
+        <is>
+          <t>Travel Expense : kadavantra to vadakekotta ,petta to kadavantra RPA_ID : f08e2329a6</t>
+        </is>
+      </c>
+      <c r="Y255" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="Z255" t="inlineStr">
+        <is>
+          <t>REIMBURSEMENT</t>
+        </is>
+      </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>misexecutivewgc@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB255" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF255" t="inlineStr"/>
+      <c r="AG255" t="inlineStr"/>
+      <c r="AH255" t="inlineStr"/>
+      <c r="AI255" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ255" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK255" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="AL255" t="inlineStr"/>
+      <c r="AM255" t="inlineStr"/>
+      <c r="AN255" t="inlineStr"/>
+      <c r="AO255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>WGE 220</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C256" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D256" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F256" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>ANDRIYA THOMAS</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>55becf37-a5ce-40f8-b264-b508e60fc21d</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>ACC-0706101053789</t>
+        </is>
+      </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>CNRB0000706</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr"/>
+      <c r="P256" t="inlineStr"/>
+      <c r="Q256" t="inlineStr"/>
+      <c r="R256" t="inlineStr"/>
+      <c r="S256" t="inlineStr"/>
+      <c r="T256" t="inlineStr"/>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V256" t="n">
+        <v>669</v>
+      </c>
+      <c r="W256" t="inlineStr"/>
+      <c r="X256" t="inlineStr">
+        <is>
+          <t>Mobile Service Charge: 300 ,Bus Fare / Travel Expense: ₹70 ,Smart marine mobile recharge 299/- RPA_ID : e245317f79</t>
+        </is>
+      </c>
+      <c r="Y256" t="inlineStr">
+        <is>
+          <t>SMART MARINE</t>
+        </is>
+      </c>
+      <c r="Z256" t="inlineStr">
+        <is>
+          <t>REIMBURSEMENT</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>misexecutivewgc@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB256" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF256" t="inlineStr"/>
+      <c r="AG256" t="inlineStr"/>
+      <c r="AH256" t="inlineStr"/>
+      <c r="AI256" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ256" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK256" t="inlineStr"/>
+      <c r="AL256" t="inlineStr"/>
+      <c r="AM256" t="inlineStr"/>
+      <c r="AN256" t="inlineStr"/>
+      <c r="AO256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>WGE 543</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C257" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D257" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F257" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>DCR</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>GAYATHRI ELECTRICALS</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>8b91a5af-6333-4697-a416-e627439f7106</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>ACC-39177475703</t>
+        </is>
+      </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>SBIN0000512</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr"/>
+      <c r="P257" t="inlineStr"/>
+      <c r="Q257" t="inlineStr"/>
+      <c r="R257" t="inlineStr"/>
+      <c r="S257" t="inlineStr"/>
+      <c r="T257" t="inlineStr"/>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V257" t="n">
+        <v>360870</v>
+      </c>
+      <c r="W257" t="inlineStr"/>
+      <c r="X257" t="inlineStr">
+        <is>
+          <t>Being material purchase (50000 paid on 20-03-2026,70000 paid on 02-04-26 remaining pending) RPA_ID : 021dc4773a</t>
+        </is>
+      </c>
+      <c r="Y257" t="inlineStr">
+        <is>
+          <t>ONGC Electrical</t>
+        </is>
+      </c>
+      <c r="Z257" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>procexewestern@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB257" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC257" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD257" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE257" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF257" t="inlineStr"/>
+      <c r="AG257" t="inlineStr"/>
+      <c r="AH257" t="inlineStr"/>
+      <c r="AI257" t="inlineStr"/>
+      <c r="AJ257" t="inlineStr"/>
+      <c r="AK257" t="inlineStr">
+        <is>
+          <t>ONGC ELECTRICAL</t>
+        </is>
+      </c>
+      <c r="AL257" t="inlineStr"/>
+      <c r="AM257" t="inlineStr"/>
+      <c r="AN257" t="inlineStr"/>
+      <c r="AO257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>WGE 570</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C258" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D258" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F258" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>DCR</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>SURANA MARKETING</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>223de75c-d40e-4ec5-bbf6-23ac9ce100f5</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>ACC-4211805706</t>
+        </is>
+      </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>KKBK0008655</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr"/>
+      <c r="P258" t="inlineStr"/>
+      <c r="Q258" t="inlineStr"/>
+      <c r="R258" t="inlineStr"/>
+      <c r="S258" t="inlineStr"/>
+      <c r="T258" t="inlineStr"/>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V258" t="n">
+        <v>410433</v>
+      </c>
+      <c r="W258" t="inlineStr"/>
+      <c r="X258" t="inlineStr">
+        <is>
+          <t>Being purchase electrical consumable  ( 50000 paid on 20-03-2026 balance amount remaining) RPA_ID : 5efe49eff0</t>
+        </is>
+      </c>
+      <c r="Y258" t="inlineStr">
+        <is>
+          <t>BPCL PKD</t>
+        </is>
+      </c>
+      <c r="Z258" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>procexewestern@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB258" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC258" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD258" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE258" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF258" t="inlineStr"/>
+      <c r="AG258" t="inlineStr"/>
+      <c r="AH258" t="inlineStr"/>
+      <c r="AI258" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ258" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK258" t="inlineStr"/>
+      <c r="AL258" t="inlineStr"/>
+      <c r="AM258" t="inlineStr"/>
+      <c r="AN258" t="inlineStr"/>
+      <c r="AO258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>WGE 262</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C259" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D259" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F259" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>GAURAV ELECTRICAL</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>31ae88b4-2d99-434b-b67c-776c7160556d</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>ACC-15960500004640</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>BARB0INDVAT</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr"/>
+      <c r="P259" t="inlineStr"/>
+      <c r="Q259" t="inlineStr"/>
+      <c r="R259" t="inlineStr"/>
+      <c r="S259" t="inlineStr"/>
+      <c r="T259" t="inlineStr"/>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V259" t="n">
+        <v>383100</v>
+      </c>
+      <c r="W259" t="inlineStr"/>
+      <c r="X259" t="inlineStr">
+        <is>
+          <t>Being balance payment(500000 paid on 20-03-2026 remaining pending) RPA_ID : b57c196cdd</t>
+        </is>
+      </c>
+      <c r="Y259" t="inlineStr">
+        <is>
+          <t>ONGC Electrical</t>
+        </is>
+      </c>
+      <c r="Z259" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>procexewestern@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB259" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC259" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD259" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE259" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF259" t="inlineStr"/>
+      <c r="AG259" t="inlineStr"/>
+      <c r="AH259" t="inlineStr"/>
+      <c r="AI259" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ259" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK259" t="inlineStr">
+        <is>
+          <t>ONGC ELECTRICAL</t>
+        </is>
+      </c>
+      <c r="AL259" t="inlineStr"/>
+      <c r="AM259" t="inlineStr"/>
+      <c r="AN259" t="inlineStr"/>
+      <c r="AO259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>WGE 556</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C260" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D260" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F260" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>INTWAY INSPECTION TECHNOLOGY AND NDT PVT LTD</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>62d7d1f5-b885-49d2-bb15-343299143952</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>ACC-50200037365080</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>HDFC0001218</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr"/>
+      <c r="P260" t="inlineStr"/>
+      <c r="Q260" t="inlineStr"/>
+      <c r="R260" t="inlineStr"/>
+      <c r="S260" t="inlineStr"/>
+      <c r="T260" t="inlineStr"/>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V260" t="n">
+        <v>184380</v>
+      </c>
+      <c r="W260" t="inlineStr"/>
+      <c r="X260" t="inlineStr">
+        <is>
+          <t>Being UTI machine payment RPA_ID : cb7e78e9ef</t>
+        </is>
+      </c>
+      <c r="Y260" t="inlineStr">
+        <is>
+          <t>ONGC IPSHEM</t>
+        </is>
+      </c>
+      <c r="Z260" t="inlineStr">
+        <is>
+          <t>ASSET</t>
+        </is>
+      </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>procexewestern@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB260" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC260" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD260" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE260" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF260" t="inlineStr"/>
+      <c r="AG260" t="inlineStr"/>
+      <c r="AH260" t="inlineStr"/>
+      <c r="AI260" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ260" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK260" t="inlineStr">
+        <is>
+          <t>ONGC IPSHEM</t>
+        </is>
+      </c>
+      <c r="AL260" t="inlineStr"/>
+      <c r="AM260" t="inlineStr"/>
+      <c r="AN260" t="inlineStr"/>
+      <c r="AO260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>WGE 638</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C261" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D261" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F261" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Vaishali crane hiring service</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>a120f3c6-352d-4e5b-a42c-62530ccac160</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>ACC-01692560001256</t>
+        </is>
+      </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>HDFC0000169</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr"/>
+      <c r="P261" t="inlineStr"/>
+      <c r="Q261" t="inlineStr"/>
+      <c r="R261" t="inlineStr"/>
+      <c r="S261" t="inlineStr"/>
+      <c r="T261" t="inlineStr"/>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V261" t="n">
+        <v>76700</v>
+      </c>
+      <c r="W261" t="inlineStr"/>
+      <c r="X261" t="inlineStr">
+        <is>
+          <t>Being rental service for crane(A/C NO:-01692560001256 IFSC :-HDFC0000169) (19-03-2026) RPA_ID : cb1ecb5c64</t>
+        </is>
+      </c>
+      <c r="Y261" t="inlineStr">
+        <is>
+          <t>ONGC JETTY</t>
+        </is>
+      </c>
+      <c r="Z261" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>procexewestern@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB261" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF261" t="inlineStr"/>
+      <c r="AG261" t="inlineStr"/>
+      <c r="AH261" t="inlineStr"/>
+      <c r="AI261" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ261" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK261" t="inlineStr"/>
+      <c r="AL261" t="inlineStr"/>
+      <c r="AM261" t="inlineStr"/>
+      <c r="AN261" t="inlineStr"/>
+      <c r="AO261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>WGE 637</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C262" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D262" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F262" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Vraj corporation</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>7a61bdfb-3985-477c-95d5-40b5fd294d1c</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>ACC-016505005896</t>
+        </is>
+      </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>ICIC0000165</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr"/>
+      <c r="P262" t="inlineStr"/>
+      <c r="Q262" t="inlineStr"/>
+      <c r="R262" t="inlineStr"/>
+      <c r="S262" t="inlineStr"/>
+      <c r="T262" t="inlineStr"/>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V262" t="n">
+        <v>9436</v>
+      </c>
+      <c r="W262" t="inlineStr"/>
+      <c r="X262" t="inlineStr">
+        <is>
+          <t>Plesae return the GSTR1  amount to the vendor (19-03-2026) RPA_ID : 8bc73b16a8</t>
+        </is>
+      </c>
+      <c r="Y262" t="inlineStr">
+        <is>
+          <t>BPCL BALLARI</t>
+        </is>
+      </c>
+      <c r="Z262" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>procexewestern@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB262" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF262" t="inlineStr"/>
+      <c r="AG262" t="inlineStr"/>
+      <c r="AH262" t="inlineStr"/>
+      <c r="AI262" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ262" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK262" t="inlineStr"/>
+      <c r="AL262" t="inlineStr"/>
+      <c r="AM262" t="inlineStr"/>
+      <c r="AN262" t="inlineStr"/>
+      <c r="AO262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>WGE 636</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C263" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D263" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F263" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Raj nath yadav</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>bb310bab-e570-4977-9437-24879090f276</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>ACC-429502010014495</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>UBIN0542954</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr"/>
+      <c r="P263" t="inlineStr"/>
+      <c r="Q263" t="inlineStr"/>
+      <c r="R263" t="inlineStr"/>
+      <c r="S263" t="inlineStr"/>
+      <c r="T263" t="inlineStr"/>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V263" t="n">
+        <v>60000</v>
+      </c>
+      <c r="W263" t="inlineStr"/>
+      <c r="X263" t="inlineStr">
+        <is>
+          <t>Being hot work channel welding work (19-03-2026) RPA_ID : 3156c5188b</t>
+        </is>
+      </c>
+      <c r="Y263" t="inlineStr">
+        <is>
+          <t>NGOP CHENNAI</t>
+        </is>
+      </c>
+      <c r="Z263" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>procexewestern@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB263" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF263" t="inlineStr"/>
+      <c r="AG263" t="inlineStr"/>
+      <c r="AH263" t="inlineStr"/>
+      <c r="AI263" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ263" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK263" t="inlineStr"/>
+      <c r="AL263" t="inlineStr"/>
+      <c r="AM263" t="inlineStr"/>
+      <c r="AN263" t="inlineStr"/>
+      <c r="AO263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>WGE 635</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C264" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D264" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F264" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>DCR</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>S B EARTH MOVERS AND CRANE SERVICES</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>4ed5e4ca-6b57-442a-9b74-7077b7ffbd9b</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>ACC-10120420457</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>IDFB0081081</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr"/>
+      <c r="P264" t="inlineStr"/>
+      <c r="Q264" t="inlineStr"/>
+      <c r="R264" t="inlineStr"/>
+      <c r="S264" t="inlineStr"/>
+      <c r="T264" t="inlineStr"/>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V264" t="n">
+        <v>149877.6</v>
+      </c>
+      <c r="W264" t="inlineStr"/>
+      <c r="X264" t="inlineStr">
+        <is>
+          <t>Being rent for JCB ,Hydra,Braker and farrana crane( total 324877.6  ,90000 paid on 20-03-2026 balance amount remaining (19-03-2026) RPA_ID : 1a548900f7</t>
+        </is>
+      </c>
+      <c r="Y264" t="inlineStr">
+        <is>
+          <t>BPCL BALLARI</t>
+        </is>
+      </c>
+      <c r="Z264" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>procexewestern@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB264" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF264" t="inlineStr"/>
+      <c r="AG264" t="inlineStr"/>
+      <c r="AH264" t="inlineStr"/>
+      <c r="AI264" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ264" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK264" t="inlineStr"/>
+      <c r="AL264" t="inlineStr"/>
+      <c r="AM264" t="inlineStr"/>
+      <c r="AN264" t="inlineStr"/>
+      <c r="AO264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>WGE 487</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C265" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D265" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F265" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>GOA PAINTS &amp; ALLIED PRODUCTS PVT.LTD</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>ea8c51f7-06fc-4982-94f0-4a7910bb1f92</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>ACC-592320003684</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>HDFC0000059</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr"/>
+      <c r="P265" t="inlineStr"/>
+      <c r="Q265" t="inlineStr"/>
+      <c r="R265" t="inlineStr"/>
+      <c r="S265" t="inlineStr"/>
+      <c r="T265" t="inlineStr"/>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V265" t="n">
+        <v>39178</v>
+      </c>
+      <c r="W265" t="inlineStr"/>
+      <c r="X265" t="inlineStr">
+        <is>
+          <t>GXY EPOXY MASTIC 6606 AL.GREY-20  AND EPOXY THINNER-20 (A/C NO:- 00592320003684 ,IFSC HDFC0000059)
+(PO NO:-WIDMC-PO-2025-26-176 (20-01-2026) (40,000 paid on 24/03/2026) Balance Amount 39,178
+(21-03-2026) RPA_ID : c55cda70c7</t>
+        </is>
+      </c>
+      <c r="Y265" t="inlineStr">
+        <is>
+          <t>ONGC GOA</t>
+        </is>
+      </c>
+      <c r="Z265" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>procexewestern@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB265" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF265" t="inlineStr"/>
+      <c r="AG265" t="inlineStr"/>
+      <c r="AH265" t="inlineStr"/>
+      <c r="AI265" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ265" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK265" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL265" t="inlineStr"/>
+      <c r="AM265" t="inlineStr"/>
+      <c r="AN265" t="inlineStr"/>
+      <c r="AO265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>WGE 569</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C266" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D266" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F266" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>DCR</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>MAA CRANE</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>a27d26e8-15f9-447f-ab0e-8cab33d34adc</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>ACC-50200034984564</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>HDFC0000169</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr"/>
+      <c r="P266" t="inlineStr"/>
+      <c r="Q266" t="inlineStr"/>
+      <c r="R266" t="inlineStr"/>
+      <c r="S266" t="inlineStr"/>
+      <c r="T266" t="inlineStr"/>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V266" t="n">
+        <v>477153.72</v>
+      </c>
+      <c r="W266" t="inlineStr"/>
+      <c r="X266" t="inlineStr">
+        <is>
+          <t>Being rent for crane service in ONGC GOA (A/C NO:- 50200034984564 IFSC :- HDFC0000169) 
+Total bill amount 3513041.72 ,paid amount :- 3035888, balance remaining (21-03-2026) RPA_ID : 41ba7fca89</t>
+        </is>
+      </c>
+      <c r="Y266" t="inlineStr">
+        <is>
+          <t>ONGC GOA</t>
+        </is>
+      </c>
+      <c r="Z266" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>procexewestern@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB266" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF266" t="inlineStr"/>
+      <c r="AG266" t="inlineStr"/>
+      <c r="AH266" t="inlineStr"/>
+      <c r="AI266" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ266" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK266" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL266" t="inlineStr"/>
+      <c r="AM266" t="inlineStr"/>
+      <c r="AN266" t="inlineStr"/>
+      <c r="AO266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>WGE 633</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C267" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D267" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F267" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Aria Fresca System</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>68bc4a36-048e-4e47-8d33-30ff781baac6</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>ACC-1503280000000253</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>KVBL0001503</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr"/>
+      <c r="P267" t="inlineStr"/>
+      <c r="Q267" t="inlineStr"/>
+      <c r="R267" t="inlineStr"/>
+      <c r="S267" t="inlineStr"/>
+      <c r="T267" t="inlineStr"/>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V267" t="n">
+        <v>6000</v>
+      </c>
+      <c r="W267" t="inlineStr"/>
+      <c r="X267" t="inlineStr">
+        <is>
+          <t>Being petrol expenses (A/C NO:-  32555551936 ,IFSC :- SBIN0001890)
+(23-03-2026) RPA_ID : 55bf7cb92b</t>
+        </is>
+      </c>
+      <c r="Y267" t="inlineStr">
+        <is>
+          <t>HPCL ELATHOOR</t>
+        </is>
+      </c>
+      <c r="Z267" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>procexewestern@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB267" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF267" t="inlineStr"/>
+      <c r="AG267" t="inlineStr"/>
+      <c r="AH267" t="inlineStr"/>
+      <c r="AI267" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ267" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK267" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="AL267" t="inlineStr"/>
+      <c r="AM267" t="inlineStr"/>
+      <c r="AN267" t="inlineStr"/>
+      <c r="AO267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>WGE 642</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C268" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D268" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F268" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>VEDANTA POLYMERS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>80b13509-f7f5-4102-b7e0-43a9db77d764</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>ACC-8282200000004435</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>DBSS0IN0820</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr"/>
+      <c r="P268" t="inlineStr"/>
+      <c r="Q268" t="inlineStr"/>
+      <c r="R268" t="inlineStr"/>
+      <c r="S268" t="inlineStr"/>
+      <c r="T268" t="inlineStr"/>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V268" t="n">
+        <v>101472</v>
+      </c>
+      <c r="W268" t="inlineStr"/>
+      <c r="X268" t="inlineStr">
+        <is>
+          <t>Being purchasing of HDPE PLB duct coupler 40mm,40mm end plug (A/C NO:- 8282200000004435 IFSC :- DBSS0IN0820) RPA_ID : a50e5d6caa</t>
+        </is>
+      </c>
+      <c r="Y268" t="inlineStr">
+        <is>
+          <t>BPCL BALLARI</t>
+        </is>
+      </c>
+      <c r="Z268" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>procexewestern@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB268" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF268" t="inlineStr"/>
+      <c r="AG268" t="inlineStr"/>
+      <c r="AH268" t="inlineStr"/>
+      <c r="AI268" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ268" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK268" t="inlineStr"/>
+      <c r="AL268" t="inlineStr"/>
+      <c r="AM268" t="inlineStr"/>
+      <c r="AN268" t="inlineStr"/>
+      <c r="AO268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>WGE 643</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C269" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D269" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F269" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>RAJESHWAR ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>b6c746b2-1a5f-4b2e-82c4-65116de1bde9</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>ACC-378405070000102</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>UBIN0537845</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr"/>
+      <c r="P269" t="inlineStr"/>
+      <c r="Q269" t="inlineStr"/>
+      <c r="R269" t="inlineStr"/>
+      <c r="S269" t="inlineStr"/>
+      <c r="T269" t="inlineStr"/>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V269" t="n">
+        <v>96951</v>
+      </c>
+      <c r="W269" t="inlineStr"/>
+      <c r="X269" t="inlineStr">
+        <is>
+          <t>Being purchasing of welding rod ,paper wheel,HSS drill bit (A/C NO:-378405070000102 IFSC:-UBIN0537845) RPA_ID : 09863cddee</t>
+        </is>
+      </c>
+      <c r="Y269" t="inlineStr">
+        <is>
+          <t>ONGC JETTY</t>
+        </is>
+      </c>
+      <c r="Z269" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>procexewestern@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB269" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF269" t="inlineStr"/>
+      <c r="AG269" t="inlineStr"/>
+      <c r="AH269" t="inlineStr"/>
+      <c r="AI269" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ269" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK269" t="inlineStr"/>
+      <c r="AL269" t="inlineStr"/>
+      <c r="AM269" t="inlineStr"/>
+      <c r="AN269" t="inlineStr"/>
+      <c r="AO269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>WGE 638</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C270" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D270" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F270" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Vaishali crane hiring service</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>e2598643-830f-4130-a5df-bd7f29f65f81</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>ACC-01692560001256</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>HDFC0000169</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr"/>
+      <c r="P270" t="inlineStr"/>
+      <c r="Q270" t="inlineStr"/>
+      <c r="R270" t="inlineStr"/>
+      <c r="S270" t="inlineStr"/>
+      <c r="T270" t="inlineStr"/>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V270" t="n">
+        <v>100000</v>
+      </c>
+      <c r="W270" t="inlineStr"/>
+      <c r="X270" t="inlineStr">
+        <is>
+          <t>Being charges for 60ton crane (from 10/01/26 to23/01/26)and mobilization and demoblization charge(A/C NO:-01692560001256 IFSC:-HDFC0000169) RPA_ID : 6763e0c5e8</t>
+        </is>
+      </c>
+      <c r="Y270" t="inlineStr">
+        <is>
+          <t>ONGC JETTY</t>
+        </is>
+      </c>
+      <c r="Z270" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>procexewestern@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB270" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF270" t="inlineStr"/>
+      <c r="AG270" t="inlineStr"/>
+      <c r="AH270" t="inlineStr"/>
+      <c r="AI270" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ270" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK270" t="inlineStr"/>
+      <c r="AL270" t="inlineStr"/>
+      <c r="AM270" t="inlineStr"/>
+      <c r="AN270" t="inlineStr"/>
+      <c r="AO270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>WGE 604</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C271" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D271" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F271" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>DCR</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Asian trade links</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>67f62447-3c9c-428c-b16c-79a51d4dbc3b</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>ACC-044707300000089</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>SIBL0000484</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr"/>
+      <c r="P271" t="inlineStr"/>
+      <c r="Q271" t="inlineStr"/>
+      <c r="R271" t="inlineStr"/>
+      <c r="S271" t="inlineStr"/>
+      <c r="T271" t="inlineStr"/>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V271" t="n">
+        <v>17892</v>
+      </c>
+      <c r="W271" t="inlineStr"/>
+      <c r="X271" t="inlineStr">
+        <is>
+          <t>Being purchasing of Shalimastic HD (A/C NO:- 0447073000000389 RPA_ID : 985be440b2</t>
+        </is>
+      </c>
+      <c r="Y271" t="inlineStr">
+        <is>
+          <t>IOCLTHIRUVANIYOOR</t>
+        </is>
+      </c>
+      <c r="Z271" t="inlineStr">
+        <is>
+          <t>SITE EXPENSES</t>
+        </is>
+      </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>procexewestern@gmail.com</t>
+        </is>
+      </c>
+      <c r="AB271" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF271" t="inlineStr"/>
+      <c r="AG271" t="inlineStr"/>
+      <c r="AH271" t="inlineStr"/>
+      <c r="AI271" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ271" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK271" t="inlineStr"/>
+      <c r="AL271" t="inlineStr"/>
+      <c r="AM271" t="inlineStr"/>
+      <c r="AN271" t="inlineStr"/>
+      <c r="AO271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>WGE 342</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C272" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D272" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F272" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>PAUL OFFSHORE PVT</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>76a5dcd2-3792-4713-92ad-7b1ead307898</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>ACC-7806823928</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr"/>
+      <c r="O272" t="inlineStr"/>
+      <c r="P272" t="inlineStr"/>
+      <c r="Q272" t="inlineStr"/>
+      <c r="R272" t="inlineStr"/>
+      <c r="S272" t="inlineStr"/>
+      <c r="T272" t="inlineStr"/>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V272" t="n">
+        <v>50000</v>
+      </c>
+      <c r="W272" t="inlineStr"/>
+      <c r="X272" t="inlineStr">
+        <is>
+          <t>ONGC GOA JAN BILL LABOUR CHARGES - WELDER / FITTER/RIGGER AND FOOD ALLOWANCE Total Amount= 342495/- Paid Rs.75000/- , Paid Rs.100000/- Excel Attendnace Sheet already shared= 167495,paid Rs.50000/-21.03.2026 RPA_ID : 3ee0425bb4</t>
+        </is>
+      </c>
+      <c r="Y272" t="inlineStr">
+        <is>
+          <t>ONGC GOA</t>
+        </is>
+      </c>
+      <c r="Z272" t="inlineStr">
+        <is>
+          <t>URGENT</t>
+        </is>
+      </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB272" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF272" t="inlineStr"/>
+      <c r="AG272" t="inlineStr"/>
+      <c r="AH272" t="inlineStr"/>
+      <c r="AI272" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ272" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK272" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL272" t="inlineStr"/>
+      <c r="AM272" t="inlineStr"/>
+      <c r="AN272" t="inlineStr"/>
+      <c r="AO272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>WGE 192</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C273" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D273" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F273" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Hafis Bin Haris</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>3fe659d5-c26c-466b-a1fc-5b623c43adc5</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>ACC-99980105201458</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>FDRL0001143</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr"/>
+      <c r="P273" t="inlineStr"/>
+      <c r="Q273" t="inlineStr"/>
+      <c r="R273" t="inlineStr"/>
+      <c r="S273" t="inlineStr"/>
+      <c r="T273" t="inlineStr"/>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V273" t="n">
+        <v>9597</v>
+      </c>
+      <c r="W273" t="inlineStr"/>
+      <c r="X273" t="inlineStr">
+        <is>
+          <t>Salary- January 9597/- Full and Final Settlement Paid December 7423 , Balance 9597  Total = 17020 RPA_ID : 77496ae382</t>
+        </is>
+      </c>
+      <c r="Y273" t="inlineStr">
+        <is>
+          <t>GOA HUL</t>
+        </is>
+      </c>
+      <c r="Z273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB273" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF273" t="inlineStr"/>
+      <c r="AG273" t="inlineStr"/>
+      <c r="AH273" t="inlineStr"/>
+      <c r="AI273" t="inlineStr"/>
+      <c r="AJ273" t="inlineStr"/>
+      <c r="AK273" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL273" t="inlineStr"/>
+      <c r="AM273" t="inlineStr"/>
+      <c r="AN273" t="inlineStr"/>
+      <c r="AO273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>WGE 104</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C274" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D274" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F274" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>BRAHMADATHAN</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>a2c297da-bd4e-4007-aabc-c9329c0e8bec</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>ACC-232001000010098</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>IOBA0002320</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr"/>
+      <c r="P274" t="inlineStr"/>
+      <c r="Q274" t="inlineStr"/>
+      <c r="R274" t="inlineStr"/>
+      <c r="S274" t="inlineStr"/>
+      <c r="T274" t="inlineStr"/>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V274" t="n">
+        <v>14379</v>
+      </c>
+      <c r="W274" t="inlineStr"/>
+      <c r="X274" t="inlineStr">
+        <is>
+          <t>Salary November Full and Final settlement Final Settlement Total 24379 , Rs.10000/- Paid  18.03.2026 Balance to be paid RPA_ID : 7c6e0eb35b</t>
+        </is>
+      </c>
+      <c r="Y274" t="inlineStr">
+        <is>
+          <t>GOA HUL</t>
+        </is>
+      </c>
+      <c r="Z274" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB274" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC274" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD274" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE274" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF274" t="inlineStr"/>
+      <c r="AG274" t="inlineStr"/>
+      <c r="AH274" t="inlineStr"/>
+      <c r="AI274" t="inlineStr"/>
+      <c r="AJ274" t="inlineStr"/>
+      <c r="AK274" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL274" t="inlineStr"/>
+      <c r="AM274" t="inlineStr"/>
+      <c r="AN274" t="inlineStr"/>
+      <c r="AO274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>WGE 452</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C275" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D275" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F275" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA REDDY</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>50bb4f10-5748-47d9-8af8-3876d85a2c33</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>ACC- 79860100001270</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>BARB0VASCOD</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr"/>
+      <c r="P275" t="inlineStr"/>
+      <c r="Q275" t="inlineStr"/>
+      <c r="R275" t="inlineStr"/>
+      <c r="S275" t="inlineStr"/>
+      <c r="T275" t="inlineStr"/>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V275" t="n">
+        <v>15000</v>
+      </c>
+      <c r="W275" t="inlineStr"/>
+      <c r="X275" t="inlineStr">
+        <is>
+          <t>Hishm sir baleno auto 4th jan 10th jan 7days=10500,Baleno auto 14th jan 29th jan 16days=24000,Swift manual 17th jan 19th jan 3days=3600,Sidharth Dezire 13th feb  to 14th 3days 2400,Sir swift auto 16thfeb 17thfeb 2days 3000 2nd 1500 =45000 (10000 paid) As per Advice from Admin Andriya - No documents provided Rs.10000/- paid,Rs.10000/- paid 18.03.2026,23.023.2026 10000/-paid RPA_ID : db78b79a82</t>
+        </is>
+      </c>
+      <c r="Y275" t="inlineStr">
+        <is>
+          <t>ONGC IPSHEM</t>
+        </is>
+      </c>
+      <c r="Z275" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB275" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC275" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD275" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE275" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF275" t="inlineStr"/>
+      <c r="AG275" t="inlineStr"/>
+      <c r="AH275" t="inlineStr"/>
+      <c r="AI275" t="inlineStr"/>
+      <c r="AJ275" t="inlineStr"/>
+      <c r="AK275" t="inlineStr">
+        <is>
+          <t>ONGC IPSHEM</t>
+        </is>
+      </c>
+      <c r="AL275" t="inlineStr"/>
+      <c r="AM275" t="inlineStr"/>
+      <c r="AN275" t="inlineStr"/>
+      <c r="AO275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>WGE 170</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C276" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D276" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F276" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>VEDANT</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>692a50b0-8125-4456-8a02-834162f6d902</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>ACC-2047172054</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>KKBK0001429</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr"/>
+      <c r="P276" t="inlineStr"/>
+      <c r="Q276" t="inlineStr"/>
+      <c r="R276" t="inlineStr"/>
+      <c r="S276" t="inlineStr"/>
+      <c r="T276" t="inlineStr"/>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V276" t="n">
+        <v>6451</v>
+      </c>
+      <c r="W276" t="inlineStr"/>
+      <c r="X276" t="inlineStr">
+        <is>
+          <t>Material Shiftng 8 Days worked (December 5 days , January 3 Days) Basic Pay is Rs.25000/- perday 806.45 RPA_ID : da0d9de850</t>
+        </is>
+      </c>
+      <c r="Y276" t="inlineStr">
+        <is>
+          <t>MDL</t>
+        </is>
+      </c>
+      <c r="Z276" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB276" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC276" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD276" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE276" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF276" t="inlineStr"/>
+      <c r="AG276" t="inlineStr"/>
+      <c r="AH276" t="inlineStr"/>
+      <c r="AI276" t="inlineStr"/>
+      <c r="AJ276" t="inlineStr"/>
+      <c r="AK276" t="inlineStr"/>
+      <c r="AL276" t="inlineStr"/>
+      <c r="AM276" t="inlineStr"/>
+      <c r="AN276" t="inlineStr"/>
+      <c r="AO276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>WGE 603</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C277" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D277" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F277" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOHAMMED MANSOOR </t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>d4d77078-6021-4589-a5b0-dc8cde616b55</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>ACC-10880100006045</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>BARB0CAVELO</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr"/>
+      <c r="P277" t="inlineStr"/>
+      <c r="Q277" t="inlineStr"/>
+      <c r="R277" t="inlineStr"/>
+      <c r="S277" t="inlineStr"/>
+      <c r="T277" t="inlineStr"/>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V277" t="n">
+        <v>6060</v>
+      </c>
+      <c r="W277" t="inlineStr"/>
+      <c r="X277" t="inlineStr">
+        <is>
+          <t>This payment pertains to hotel expenses incurred during work at ONGC. Food was provided to five Rumjan team workers as well as other workers.
+The payment for these expenses has not yet been made. The attached document includes ₹4,070 towards the food expenses of the Rumjan team workers. It also covers the food expenses of other workers who were working at ONGC , In march  food had to be arranged due to the unavailability of gas and the workers being unable to cook at that time.
+ this amount is payable to the hotel. RPA_ID : 8b32c17cff</t>
+        </is>
+      </c>
+      <c r="Y277" t="inlineStr">
+        <is>
+          <t>ONGC IPSHEM</t>
+        </is>
+      </c>
+      <c r="Z277" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB277" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC277" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD277" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE277" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF277" t="inlineStr"/>
+      <c r="AG277" t="inlineStr"/>
+      <c r="AH277" t="inlineStr"/>
+      <c r="AI277" t="inlineStr"/>
+      <c r="AJ277" t="inlineStr"/>
+      <c r="AK277" t="inlineStr">
+        <is>
+          <t>ONGC IPSHEM</t>
+        </is>
+      </c>
+      <c r="AL277" t="inlineStr"/>
+      <c r="AM277" t="inlineStr"/>
+      <c r="AN277" t="inlineStr"/>
+      <c r="AO277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> WGG 02</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C278" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D278" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F278" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>ebbedd9d-69c3-423b-92bb-2df12a1d18db</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr"/>
+      <c r="N278" t="inlineStr"/>
+      <c r="O278" t="inlineStr"/>
+      <c r="P278" t="inlineStr"/>
+      <c r="Q278" t="inlineStr"/>
+      <c r="R278" t="inlineStr"/>
+      <c r="S278" t="inlineStr"/>
+      <c r="T278" t="inlineStr"/>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V278" t="n">
+        <v>507962</v>
+      </c>
+      <c r="W278" t="inlineStr"/>
+      <c r="X278" t="inlineStr">
+        <is>
+          <t>ESI REVENU RECOVERY  Rs 1015923, to pay 50 % RPA_ID : a5a9b79963</t>
+        </is>
+      </c>
+      <c r="Y278" t="inlineStr">
+        <is>
+          <t>KOLKATTA</t>
+        </is>
+      </c>
+      <c r="Z278" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB278" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC278" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD278" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE278" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF278" t="inlineStr"/>
+      <c r="AG278" t="inlineStr"/>
+      <c r="AH278" t="inlineStr"/>
+      <c r="AI278" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ278" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK278" t="inlineStr"/>
+      <c r="AL278" t="inlineStr"/>
+      <c r="AM278" t="inlineStr"/>
+      <c r="AN278" t="inlineStr"/>
+      <c r="AO278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> WGG 02</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C279" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D279" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F279" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>6cf7b190-51a1-4881-bcd5-5940af38e6fd</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr"/>
+      <c r="N279" t="inlineStr"/>
+      <c r="O279" t="inlineStr"/>
+      <c r="P279" t="inlineStr"/>
+      <c r="Q279" t="inlineStr"/>
+      <c r="R279" t="inlineStr"/>
+      <c r="S279" t="inlineStr"/>
+      <c r="T279" t="inlineStr"/>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V279" t="n">
+        <v>290000</v>
+      </c>
+      <c r="W279" t="inlineStr"/>
+      <c r="X279" t="inlineStr">
+        <is>
+          <t>AUGUST PF ARREAR KOCHI AND KONGAN APPROXIMATE RPA_ID : 02f697f63c</t>
+        </is>
+      </c>
+      <c r="Y279" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="Z279" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB279" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC279" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD279" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE279" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF279" t="inlineStr"/>
+      <c r="AG279" t="inlineStr"/>
+      <c r="AH279" t="inlineStr"/>
+      <c r="AI279" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ279" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK279" t="inlineStr"/>
+      <c r="AL279" t="inlineStr"/>
+      <c r="AM279" t="inlineStr"/>
+      <c r="AN279" t="inlineStr"/>
+      <c r="AO279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>WGE 659</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C280" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D280" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F280" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>United India Insurance Company Ltd</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>1e2d0b67-855d-475d-8d11-2e7110020acf</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>ACC-ZUIICL120502WESTERN</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>INDB0000007</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr"/>
+      <c r="P280" t="inlineStr"/>
+      <c r="Q280" t="inlineStr"/>
+      <c r="R280" t="inlineStr"/>
+      <c r="S280" t="inlineStr"/>
+      <c r="T280" t="inlineStr"/>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V280" t="n">
+        <v>153000</v>
+      </c>
+      <c r="W280" t="inlineStr"/>
+      <c r="X280" t="inlineStr">
+        <is>
+          <t>Policy of Floating Pontoon is due for renewal on 06/04/2026. RPA_ID : 58b2a92a96</t>
+        </is>
+      </c>
+      <c r="Y280" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="Z280" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB280" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC280" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD280" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE280" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF280" t="inlineStr"/>
+      <c r="AG280" t="inlineStr"/>
+      <c r="AH280" t="inlineStr"/>
+      <c r="AI280" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ280" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK280" t="inlineStr"/>
+      <c r="AL280" t="inlineStr"/>
+      <c r="AM280" t="inlineStr"/>
+      <c r="AN280" t="inlineStr"/>
+      <c r="AO280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>WGE 299</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C281" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D281" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F281" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>DCR</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>ARJUN(ONGC) SUPERVISOR</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>aa819db6-095e-4f8c-b4b4-a9d755bd7e43</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>ACC-67329839060</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>SBIN0070076</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr"/>
+      <c r="P281" t="inlineStr"/>
+      <c r="Q281" t="inlineStr"/>
+      <c r="R281" t="inlineStr"/>
+      <c r="S281" t="inlineStr"/>
+      <c r="T281" t="inlineStr"/>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V281" t="n">
+        <v>4800</v>
+      </c>
+      <c r="W281" t="inlineStr"/>
+      <c r="X281" t="inlineStr">
+        <is>
+          <t>Room stay Expense @ 1200 (01.04.2026 to 04.04.2026) RPA_ID : fd639e19ad</t>
+        </is>
+      </c>
+      <c r="Y281" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="Z281" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB281" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC281" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD281" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE281" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF281" t="inlineStr"/>
+      <c r="AG281" t="inlineStr"/>
+      <c r="AH281" t="inlineStr"/>
+      <c r="AI281" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ281" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AK281" t="inlineStr"/>
+      <c r="AL281" t="inlineStr"/>
+      <c r="AM281" t="inlineStr"/>
+      <c r="AN281" t="inlineStr"/>
+      <c r="AO281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>WGE 236</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C282" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D282" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F282" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>vishnu P. G (HULL)</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>0f182e17-49e1-40a8-98ea-ed2f806cf492</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>ACC-40561101027837</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>KLGB0040561</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr"/>
+      <c r="P282" t="inlineStr"/>
+      <c r="Q282" t="inlineStr"/>
+      <c r="R282" t="inlineStr"/>
+      <c r="S282" t="inlineStr"/>
+      <c r="T282" t="inlineStr"/>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V282" t="n">
+        <v>8120</v>
+      </c>
+      <c r="W282" t="inlineStr"/>
+      <c r="X282" t="inlineStr">
+        <is>
+          <t>Weekly Salary (March 28 to 03April 2026) RPA_ID : 0c7cc0cbcd</t>
+        </is>
+      </c>
+      <c r="Y282" t="inlineStr">
+        <is>
+          <t>GOA HUL</t>
+        </is>
+      </c>
+      <c r="Z282" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB282" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC282" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD282" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE282" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF282" t="inlineStr"/>
+      <c r="AG282" t="inlineStr"/>
+      <c r="AH282" t="inlineStr"/>
+      <c r="AI282" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ282" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK282" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL282" t="inlineStr"/>
+      <c r="AM282" t="inlineStr"/>
+      <c r="AN282" t="inlineStr"/>
+      <c r="AO282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>WGE 332</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C283" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D283" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F283" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>CLEETUS PETER ( ONGC)</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>b25fc073-3f47-4eea-b8e8-15ab30727b81</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>ACC-40062610000123</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>CNRB0014006</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr"/>
+      <c r="P283" t="inlineStr"/>
+      <c r="Q283" t="inlineStr"/>
+      <c r="R283" t="inlineStr"/>
+      <c r="S283" t="inlineStr"/>
+      <c r="T283" t="inlineStr"/>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V283" t="n">
+        <v>4442</v>
+      </c>
+      <c r="W283" t="inlineStr"/>
+      <c r="X283" t="inlineStr">
+        <is>
+          <t>Weekly Salary (March 28 to 03April 2026) RPA_ID : d7ba1b7b6e</t>
+        </is>
+      </c>
+      <c r="Y283" t="inlineStr">
+        <is>
+          <t>GOA HUL</t>
+        </is>
+      </c>
+      <c r="Z283" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB283" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC283" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD283" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE283" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF283" t="inlineStr"/>
+      <c r="AG283" t="inlineStr"/>
+      <c r="AH283" t="inlineStr"/>
+      <c r="AI283" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ283" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK283" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL283" t="inlineStr"/>
+      <c r="AM283" t="inlineStr"/>
+      <c r="AN283" t="inlineStr"/>
+      <c r="AO283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>WGE 221</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C284" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D284" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F284" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>GLADWIN JESTIN</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>b5a34ae7-822b-40e8-9004-74d7feb2096b</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>ACC-609053000010959</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>SIBL0000609</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr"/>
+      <c r="P284" t="inlineStr"/>
+      <c r="Q284" t="inlineStr"/>
+      <c r="R284" t="inlineStr"/>
+      <c r="S284" t="inlineStr"/>
+      <c r="T284" t="inlineStr"/>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V284" t="n">
+        <v>1006</v>
+      </c>
+      <c r="W284" t="inlineStr"/>
+      <c r="X284" t="inlineStr">
+        <is>
+          <t>Weekly Salary (March 28 to 03April 2026) RPA_ID : 04926905e4</t>
+        </is>
+      </c>
+      <c r="Y284" t="inlineStr">
+        <is>
+          <t>GOA HUL</t>
+        </is>
+      </c>
+      <c r="Z284" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB284" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC284" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD284" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE284" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF284" t="inlineStr"/>
+      <c r="AG284" t="inlineStr"/>
+      <c r="AH284" t="inlineStr"/>
+      <c r="AI284" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ284" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK284" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL284" t="inlineStr"/>
+      <c r="AM284" t="inlineStr"/>
+      <c r="AN284" t="inlineStr"/>
+      <c r="AO284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>WGE 416</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C285" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D285" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F285" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>SREEJITH P R</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>988c424b-89b7-4328-bfcb-d8c39b064ce7</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>ACC-110020773907</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr"/>
+      <c r="O285" t="inlineStr"/>
+      <c r="P285" t="inlineStr"/>
+      <c r="Q285" t="inlineStr"/>
+      <c r="R285" t="inlineStr"/>
+      <c r="S285" t="inlineStr"/>
+      <c r="T285" t="inlineStr"/>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V285" t="n">
+        <v>5459</v>
+      </c>
+      <c r="W285" t="inlineStr"/>
+      <c r="X285" t="inlineStr">
+        <is>
+          <t>Weekly Salary (March 28 to 03April 2026) RPA_ID : 3a4a84b83e</t>
+        </is>
+      </c>
+      <c r="Y285" t="inlineStr">
+        <is>
+          <t>GOA HUL</t>
+        </is>
+      </c>
+      <c r="Z285" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB285" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC285" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD285" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE285" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF285" t="inlineStr"/>
+      <c r="AG285" t="inlineStr"/>
+      <c r="AH285" t="inlineStr"/>
+      <c r="AI285" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ285" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK285" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL285" t="inlineStr"/>
+      <c r="AM285" t="inlineStr"/>
+      <c r="AN285" t="inlineStr"/>
+      <c r="AO285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>WGE 298</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C286" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D286" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F286" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>NAKUL(ONGC)</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>7ce98f4b-ac7b-49ed-b80c-032463323f5d</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>ACC-054801000019038</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>IOBA0000548</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr"/>
+      <c r="P286" t="inlineStr"/>
+      <c r="Q286" t="inlineStr"/>
+      <c r="R286" t="inlineStr"/>
+      <c r="S286" t="inlineStr"/>
+      <c r="T286" t="inlineStr"/>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V286" t="n">
+        <v>5641</v>
+      </c>
+      <c r="W286" t="inlineStr"/>
+      <c r="X286" t="inlineStr">
+        <is>
+          <t>Weekly Salary (March 28 to 03April 2026) RPA_ID : 5855e673f9</t>
+        </is>
+      </c>
+      <c r="Y286" t="inlineStr">
+        <is>
+          <t>GOA HUL</t>
+        </is>
+      </c>
+      <c r="Z286" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB286" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC286" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD286" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE286" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF286" t="inlineStr"/>
+      <c r="AG286" t="inlineStr"/>
+      <c r="AH286" t="inlineStr"/>
+      <c r="AI286" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ286" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK286" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL286" t="inlineStr"/>
+      <c r="AM286" t="inlineStr"/>
+      <c r="AN286" t="inlineStr"/>
+      <c r="AO286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>WGE 309</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C287" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D287" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F287" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>DCR</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Harvin(ongc )</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>8be31b3b-ebd4-4240-84fd-43965475045f</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>ACC-20533170557</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>SBIN0007617</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr"/>
+      <c r="P287" t="inlineStr"/>
+      <c r="Q287" t="inlineStr"/>
+      <c r="R287" t="inlineStr"/>
+      <c r="S287" t="inlineStr"/>
+      <c r="T287" t="inlineStr"/>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V287" t="n">
+        <v>3866</v>
+      </c>
+      <c r="W287" t="inlineStr"/>
+      <c r="X287" t="inlineStr">
+        <is>
+          <t>Weekly Salary (March 28 to 03April 2026) RPA_ID : b4d40b34c2</t>
+        </is>
+      </c>
+      <c r="Y287" t="inlineStr">
+        <is>
+          <t>GOA HUL</t>
+        </is>
+      </c>
+      <c r="Z287" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB287" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC287" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD287" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE287" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF287" t="inlineStr"/>
+      <c r="AG287" t="inlineStr"/>
+      <c r="AH287" t="inlineStr"/>
+      <c r="AI287" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ287" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK287" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL287" t="inlineStr"/>
+      <c r="AM287" t="inlineStr"/>
+      <c r="AN287" t="inlineStr"/>
+      <c r="AO287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>WGE 446</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C288" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D288" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F288" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>ANIMON</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>fa2dde78-4685-4ccc-840e-d744f15d78bf</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>ACC- 0985053000002319</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>SIBL0000985</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr"/>
+      <c r="P288" t="inlineStr"/>
+      <c r="Q288" t="inlineStr"/>
+      <c r="R288" t="inlineStr"/>
+      <c r="S288" t="inlineStr"/>
+      <c r="T288" t="inlineStr"/>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V288" t="n">
+        <v>7266</v>
+      </c>
+      <c r="W288" t="inlineStr"/>
+      <c r="X288" t="inlineStr">
+        <is>
+          <t>Weekly Salary (March 28 to 03April 2026) RPA_ID : af5da15805</t>
+        </is>
+      </c>
+      <c r="Y288" t="inlineStr">
+        <is>
+          <t>GOA HUL</t>
+        </is>
+      </c>
+      <c r="Z288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB288" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF288" t="inlineStr"/>
+      <c r="AG288" t="inlineStr"/>
+      <c r="AH288" t="inlineStr"/>
+      <c r="AI288" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ288" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK288" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL288" t="inlineStr"/>
+      <c r="AM288" t="inlineStr"/>
+      <c r="AN288" t="inlineStr"/>
+      <c r="AO288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>WGE 334</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C289" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D289" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F289" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>RAJU YADAV ( KHALASI)</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>b760416e-d98f-42b5-a4ed-684f7672b9f1</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>ACC-7452654471</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>IDIB000B005</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr"/>
+      <c r="P289" t="inlineStr"/>
+      <c r="Q289" t="inlineStr"/>
+      <c r="R289" t="inlineStr"/>
+      <c r="S289" t="inlineStr"/>
+      <c r="T289" t="inlineStr"/>
+      <c r="U289" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V289" t="n">
+        <v>14250</v>
+      </c>
+      <c r="W289" t="inlineStr"/>
+      <c r="X289" t="inlineStr">
+        <is>
+          <t>Weekly Salary (March 28 to 03April 2026) RPA_ID : 6b58905430</t>
+        </is>
+      </c>
+      <c r="Y289" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="Z289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA289" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB289" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF289" t="inlineStr"/>
+      <c r="AG289" t="inlineStr"/>
+      <c r="AH289" t="inlineStr"/>
+      <c r="AI289" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ289" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK289" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="AL289" t="inlineStr"/>
+      <c r="AM289" t="inlineStr"/>
+      <c r="AN289" t="inlineStr"/>
+      <c r="AO289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>WGE 362</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C290" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D290" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F290" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Ramjathan</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>f066338c-2320-4df2-9f71-269d78732da5</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>ACC-501051125288</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>NSPB0000002</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr"/>
+      <c r="P290" t="inlineStr"/>
+      <c r="Q290" t="inlineStr"/>
+      <c r="R290" t="inlineStr"/>
+      <c r="S290" t="inlineStr"/>
+      <c r="T290" t="inlineStr"/>
+      <c r="U290" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V290" t="n">
+        <v>8500</v>
+      </c>
+      <c r="W290" t="inlineStr"/>
+      <c r="X290" t="inlineStr">
+        <is>
+          <t>Weekly Salary (March 28 to 03April 2026) RPA_ID : c58efd63cc</t>
+        </is>
+      </c>
+      <c r="Y290" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="Z290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA290" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB290" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF290" t="inlineStr"/>
+      <c r="AG290" t="inlineStr"/>
+      <c r="AH290" t="inlineStr"/>
+      <c r="AI290" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ290" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK290" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="AL290" t="inlineStr"/>
+      <c r="AM290" t="inlineStr"/>
+      <c r="AN290" t="inlineStr"/>
+      <c r="AO290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>WGE 363</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C291" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D291" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F291" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Pramod Kumar</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>1d2f85bf-5b73-4cc5-98c1-68eaa9b74b89</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>ACC-694402010010832</t>
+        </is>
+      </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>UBIN0569445</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr"/>
+      <c r="P291" t="inlineStr"/>
+      <c r="Q291" t="inlineStr"/>
+      <c r="R291" t="inlineStr"/>
+      <c r="S291" t="inlineStr"/>
+      <c r="T291" t="inlineStr"/>
+      <c r="U291" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V291" t="n">
+        <v>8500</v>
+      </c>
+      <c r="W291" t="inlineStr"/>
+      <c r="X291" t="inlineStr">
+        <is>
+          <t>Weekly Salary (March 28 to 03April 2026) RPA_ID : b405b2adbb</t>
+        </is>
+      </c>
+      <c r="Y291" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="Z291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA291" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB291" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF291" t="inlineStr"/>
+      <c r="AG291" t="inlineStr"/>
+      <c r="AH291" t="inlineStr"/>
+      <c r="AI291" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ291" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK291" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="AL291" t="inlineStr"/>
+      <c r="AM291" t="inlineStr"/>
+      <c r="AN291" t="inlineStr"/>
+      <c r="AO291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>WGE 364</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C292" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D292" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F292" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Manmohan Yadahv</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>f0be880c-c6db-4b29-b123-f62aed45042e</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>ACC-791510110002741</t>
+        </is>
+      </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>BKID0007915</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr"/>
+      <c r="P292" t="inlineStr"/>
+      <c r="Q292" t="inlineStr"/>
+      <c r="R292" t="inlineStr"/>
+      <c r="S292" t="inlineStr"/>
+      <c r="T292" t="inlineStr"/>
+      <c r="U292" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V292" t="n">
+        <v>9500</v>
+      </c>
+      <c r="W292" t="inlineStr"/>
+      <c r="X292" t="inlineStr">
+        <is>
+          <t>Weekly Salary (March 28 to 03April 2026) RPA_ID : a43bb5cc45</t>
+        </is>
+      </c>
+      <c r="Y292" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="Z292" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA292" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB292" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC292" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD292" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE292" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF292" t="inlineStr"/>
+      <c r="AG292" t="inlineStr"/>
+      <c r="AH292" t="inlineStr"/>
+      <c r="AI292" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ292" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK292" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="AL292" t="inlineStr"/>
+      <c r="AM292" t="inlineStr"/>
+      <c r="AN292" t="inlineStr"/>
+      <c r="AO292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>WGE 333</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C293" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D293" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F293" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>DCR</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>LAKHI CHAND SAHANI</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>7aa9804d-34ac-4ef6-b39a-83d1eb928b25</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>ACC-041215193811</t>
+        </is>
+      </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>SBIN0008326</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr"/>
+      <c r="P293" t="inlineStr"/>
+      <c r="Q293" t="inlineStr"/>
+      <c r="R293" t="inlineStr"/>
+      <c r="S293" t="inlineStr"/>
+      <c r="T293" t="inlineStr"/>
+      <c r="U293" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V293" t="n">
+        <v>12750</v>
+      </c>
+      <c r="W293" t="inlineStr"/>
+      <c r="X293" t="inlineStr">
+        <is>
+          <t>Weekly Salary (March 28 to 03April 2026) RPA_ID : 6748e9d452</t>
+        </is>
+      </c>
+      <c r="Y293" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="Z293" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA293" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB293" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC293" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD293" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE293" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF293" t="inlineStr"/>
+      <c r="AG293" t="inlineStr"/>
+      <c r="AH293" t="inlineStr"/>
+      <c r="AI293" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ293" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK293" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="AL293" t="inlineStr"/>
+      <c r="AM293" t="inlineStr"/>
+      <c r="AN293" t="inlineStr"/>
+      <c r="AO293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>WGE 628</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C294" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D294" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F294" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>KRISHNA KUMAR ( grinder)</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>1de6b8e7-599d-4c9d-a2b0-3a6bb469f3c9</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>ACC-52930100001708</t>
+        </is>
+      </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>BARB0BALTHI</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr"/>
+      <c r="P294" t="inlineStr"/>
+      <c r="Q294" t="inlineStr"/>
+      <c r="R294" t="inlineStr"/>
+      <c r="S294" t="inlineStr"/>
+      <c r="T294" t="inlineStr"/>
+      <c r="U294" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V294" t="n">
+        <v>6184</v>
+      </c>
+      <c r="W294" t="inlineStr"/>
+      <c r="X294" t="inlineStr">
+        <is>
+          <t>Weekly Salary (March 28 to 03April 2026) RPA_ID : 36d31902f3</t>
+        </is>
+      </c>
+      <c r="Y294" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="Z294" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA294" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB294" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC294" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD294" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE294" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF294" t="inlineStr"/>
+      <c r="AG294" t="inlineStr"/>
+      <c r="AH294" t="inlineStr"/>
+      <c r="AI294" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ294" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK294" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="AL294" t="inlineStr"/>
+      <c r="AM294" t="inlineStr"/>
+      <c r="AN294" t="inlineStr"/>
+      <c r="AO294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>WGE 629</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C295" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D295" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F295" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>RAMESH KUMAR (grinder)</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>f741d665-0c61-4b2c-9f51-5be71895e404</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>ACC-50100499111780</t>
+        </is>
+      </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>HDFC0000645</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr"/>
+      <c r="P295" t="inlineStr"/>
+      <c r="Q295" t="inlineStr"/>
+      <c r="R295" t="inlineStr"/>
+      <c r="S295" t="inlineStr"/>
+      <c r="T295" t="inlineStr"/>
+      <c r="U295" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V295" t="n">
+        <v>6184</v>
+      </c>
+      <c r="W295" t="inlineStr"/>
+      <c r="X295" t="inlineStr">
+        <is>
+          <t>Weekly Salary (March 28 to 03April 2026) RPA_ID : 92a465838b</t>
+        </is>
+      </c>
+      <c r="Y295" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="Z295" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA295" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB295" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC295" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD295" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE295" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF295" t="inlineStr"/>
+      <c r="AG295" t="inlineStr"/>
+      <c r="AH295" t="inlineStr"/>
+      <c r="AI295" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ295" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK295" t="inlineStr">
+        <is>
+          <t>BELLARI</t>
+        </is>
+      </c>
+      <c r="AL295" t="inlineStr"/>
+      <c r="AM295" t="inlineStr"/>
+      <c r="AN295" t="inlineStr"/>
+      <c r="AO295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>WGE 462</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C296" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D296" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F296" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>PRANEET</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>49610a57-27ff-411d-8c0e-a7968821e3d6</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>ACC-095203100002750</t>
+        </is>
+      </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>SRCB0000095</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr"/>
+      <c r="P296" t="inlineStr"/>
+      <c r="Q296" t="inlineStr"/>
+      <c r="R296" t="inlineStr"/>
+      <c r="S296" t="inlineStr"/>
+      <c r="T296" t="inlineStr"/>
+      <c r="U296" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V296" t="n">
+        <v>5000</v>
+      </c>
+      <c r="W296" t="inlineStr"/>
+      <c r="X296" t="inlineStr">
+        <is>
+          <t>Casual Labour Charge 5 Nos @1000 RPA_ID : c5bb91869c</t>
+        </is>
+      </c>
+      <c r="Y296" t="inlineStr">
+        <is>
+          <t>ST3 GOA</t>
+        </is>
+      </c>
+      <c r="Z296" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA296" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB296" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC296" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD296" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE296" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF296" t="inlineStr"/>
+      <c r="AG296" t="inlineStr"/>
+      <c r="AH296" t="inlineStr"/>
+      <c r="AI296" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ296" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK296" t="inlineStr">
+        <is>
+          <t>GOA</t>
+        </is>
+      </c>
+      <c r="AL296" t="inlineStr"/>
+      <c r="AM296" t="inlineStr"/>
+      <c r="AN296" t="inlineStr"/>
+      <c r="AO296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>WGE 302</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C297" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D297" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F297" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>George Ben</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>74fb0077-a1d5-48a9-95dd-09d54890d7a1</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>ACC-6099033889</t>
+        </is>
+      </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>IDIB000T021</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr"/>
+      <c r="P297" t="inlineStr"/>
+      <c r="Q297" t="inlineStr"/>
+      <c r="R297" t="inlineStr"/>
+      <c r="S297" t="inlineStr"/>
+      <c r="T297" t="inlineStr"/>
+      <c r="U297" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V297" t="n">
+        <v>3000</v>
+      </c>
+      <c r="W297" t="inlineStr"/>
+      <c r="X297" t="inlineStr">
+        <is>
+          <t>Travel Expense  and Food Expense RPA_ID : d1378a6c47</t>
+        </is>
+      </c>
+      <c r="Y297" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="Z297" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA297" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB297" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC297" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD297" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE297" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF297" t="inlineStr"/>
+      <c r="AG297" t="inlineStr"/>
+      <c r="AH297" t="inlineStr"/>
+      <c r="AI297" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ297" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK297" t="inlineStr">
+        <is>
+          <t>HO</t>
+        </is>
+      </c>
+      <c r="AL297" t="inlineStr"/>
+      <c r="AM297" t="inlineStr"/>
+      <c r="AN297" t="inlineStr"/>
+      <c r="AO297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>WGE 08</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C298" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D298" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F298" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>ANISH MOHANAN</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>e91b5dda-cf32-44db-8245-cc3bfe3306d0</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>ACC-110197237190</t>
+        </is>
+      </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>CNRB0000703</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr"/>
+      <c r="P298" t="inlineStr"/>
+      <c r="Q298" t="inlineStr"/>
+      <c r="R298" t="inlineStr"/>
+      <c r="S298" t="inlineStr"/>
+      <c r="T298" t="inlineStr"/>
+      <c r="U298" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V298" t="n">
+        <v>32300</v>
+      </c>
+      <c r="W298" t="inlineStr"/>
+      <c r="X298" t="inlineStr">
+        <is>
+          <t>Salary March 2026 RPA_ID : 21313ecb1a</t>
+        </is>
+      </c>
+      <c r="Y298" t="inlineStr">
+        <is>
+          <t>IOCL WILLINGTON</t>
+        </is>
+      </c>
+      <c r="Z298" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA298" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB298" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC298" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD298" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE298" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF298" t="inlineStr"/>
+      <c r="AG298" t="inlineStr"/>
+      <c r="AH298" t="inlineStr"/>
+      <c r="AI298" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ298" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK298" t="inlineStr">
+        <is>
+          <t>IOCL WILLINGTON</t>
+        </is>
+      </c>
+      <c r="AL298" t="inlineStr"/>
+      <c r="AM298" t="inlineStr"/>
+      <c r="AN298" t="inlineStr"/>
+      <c r="AO298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>WGE 04</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C299" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D299" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F299" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>UDAYAN T K</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>9b4be9b7-db35-4a85-9cf1-1e16d44645cd</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>ACC-43152200021937</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>CNRB0014315</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr"/>
+      <c r="P299" t="inlineStr"/>
+      <c r="Q299" t="inlineStr"/>
+      <c r="R299" t="inlineStr"/>
+      <c r="S299" t="inlineStr"/>
+      <c r="T299" t="inlineStr"/>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V299" t="n">
+        <v>35513</v>
+      </c>
+      <c r="W299" t="inlineStr"/>
+      <c r="X299" t="inlineStr">
+        <is>
+          <t>Salary March 2026 RPA_ID : aa18f65a61</t>
+        </is>
+      </c>
+      <c r="Y299" t="inlineStr">
+        <is>
+          <t>IOCL WILLINGTON</t>
+        </is>
+      </c>
+      <c r="Z299" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA299" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB299" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC299" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD299" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE299" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF299" t="inlineStr"/>
+      <c r="AG299" t="inlineStr"/>
+      <c r="AH299" t="inlineStr"/>
+      <c r="AI299" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ299" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK299" t="inlineStr">
+        <is>
+          <t>IOCL WILLINGTON</t>
+        </is>
+      </c>
+      <c r="AL299" t="inlineStr"/>
+      <c r="AM299" t="inlineStr"/>
+      <c r="AN299" t="inlineStr"/>
+      <c r="AO299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>WGE 07</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C300" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D300" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F300" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>ANUDAS A M</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>c4be2a72-3121-4d0e-a6ef-65c7b43501c9</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>ACC- 110283704650</t>
+        </is>
+      </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>CNRB0014315</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr"/>
+      <c r="P300" t="inlineStr"/>
+      <c r="Q300" t="inlineStr"/>
+      <c r="R300" t="inlineStr"/>
+      <c r="S300" t="inlineStr"/>
+      <c r="T300" t="inlineStr"/>
+      <c r="U300" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V300" t="n">
+        <v>44685</v>
+      </c>
+      <c r="W300" t="inlineStr"/>
+      <c r="X300" t="inlineStr">
+        <is>
+          <t>Salary March 2026 RPA_ID : 25a060ddcb</t>
+        </is>
+      </c>
+      <c r="Y300" t="inlineStr">
+        <is>
+          <t>IOCL WILLINGTON</t>
+        </is>
+      </c>
+      <c r="Z300" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA300" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB300" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC300" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD300" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE300" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF300" t="inlineStr"/>
+      <c r="AG300" t="inlineStr"/>
+      <c r="AH300" t="inlineStr"/>
+      <c r="AI300" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ300" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK300" t="inlineStr">
+        <is>
+          <t>IOCL WILLINGTON</t>
+        </is>
+      </c>
+      <c r="AL300" t="inlineStr"/>
+      <c r="AM300" t="inlineStr"/>
+      <c r="AN300" t="inlineStr"/>
+      <c r="AO300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>WGE 01</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C301" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D301" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F301" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>BENNY P A</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>c996f0dc-0d95-4982-a4f5-008571aa0c1c</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>ACC-43152200012062</t>
+        </is>
+      </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>CNRB0014315</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr"/>
+      <c r="P301" t="inlineStr"/>
+      <c r="Q301" t="inlineStr"/>
+      <c r="R301" t="inlineStr"/>
+      <c r="S301" t="inlineStr"/>
+      <c r="T301" t="inlineStr"/>
+      <c r="U301" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V301" t="n">
+        <v>47212</v>
+      </c>
+      <c r="W301" t="inlineStr"/>
+      <c r="X301" t="inlineStr">
+        <is>
+          <t>Salary March 2026 RPA_ID : 40239dc01d</t>
+        </is>
+      </c>
+      <c r="Y301" t="inlineStr">
+        <is>
+          <t>IOCL WILLINGTON</t>
+        </is>
+      </c>
+      <c r="Z301" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA301" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB301" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC301" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD301" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE301" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF301" t="inlineStr"/>
+      <c r="AG301" t="inlineStr"/>
+      <c r="AH301" t="inlineStr"/>
+      <c r="AI301" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ301" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK301" t="inlineStr">
+        <is>
+          <t>IOCL WILLINGTON</t>
+        </is>
+      </c>
+      <c r="AL301" t="inlineStr"/>
+      <c r="AM301" t="inlineStr"/>
+      <c r="AN301" t="inlineStr"/>
+      <c r="AO301" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>WGE 06</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C302" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D302" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F302" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>DCR</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>SUDHEER K N</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>874b63d8-81e7-47d5-920e-b14e4a505106</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>ACC-32474466361</t>
+        </is>
+      </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>SBIN0006367</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr"/>
+      <c r="P302" t="inlineStr"/>
+      <c r="Q302" t="inlineStr"/>
+      <c r="R302" t="inlineStr"/>
+      <c r="S302" t="inlineStr"/>
+      <c r="T302" t="inlineStr"/>
+      <c r="U302" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V302" t="n">
+        <v>41375</v>
+      </c>
+      <c r="W302" t="inlineStr"/>
+      <c r="X302" t="inlineStr">
+        <is>
+          <t>Salary March 2026 RPA_ID : 2f1eb03faa</t>
+        </is>
+      </c>
+      <c r="Y302" t="inlineStr">
+        <is>
+          <t>IOCL WILLINGTON</t>
+        </is>
+      </c>
+      <c r="Z302" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA302" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB302" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC302" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD302" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE302" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF302" t="inlineStr"/>
+      <c r="AG302" t="inlineStr"/>
+      <c r="AH302" t="inlineStr"/>
+      <c r="AI302" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ302" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK302" t="inlineStr">
+        <is>
+          <t>IOCL WILLINGTON</t>
+        </is>
+      </c>
+      <c r="AL302" t="inlineStr"/>
+      <c r="AM302" t="inlineStr"/>
+      <c r="AN302" t="inlineStr"/>
+      <c r="AO302" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>WGE 05</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C303" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D303" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F303" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>ANEESH V A</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>0f54d41c-0b7c-47fa-91d9-93cfb62af8d4</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>ACC-43152200021811</t>
+        </is>
+      </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>CNRB0014315</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr"/>
+      <c r="P303" t="inlineStr"/>
+      <c r="Q303" t="inlineStr"/>
+      <c r="R303" t="inlineStr"/>
+      <c r="S303" t="inlineStr"/>
+      <c r="T303" t="inlineStr"/>
+      <c r="U303" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V303" t="n">
+        <v>19557</v>
+      </c>
+      <c r="W303" t="inlineStr"/>
+      <c r="X303" t="inlineStr">
+        <is>
+          <t>Salary March 2026 RPA_ID : 65ca218f4f</t>
+        </is>
+      </c>
+      <c r="Y303" t="inlineStr">
+        <is>
+          <t>IOCL WILLINGTON</t>
+        </is>
+      </c>
+      <c r="Z303" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA303" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB303" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC303" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD303" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE303" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF303" t="inlineStr"/>
+      <c r="AG303" t="inlineStr"/>
+      <c r="AH303" t="inlineStr"/>
+      <c r="AI303" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ303" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK303" t="inlineStr">
+        <is>
+          <t>IOCL WILLINGTON</t>
+        </is>
+      </c>
+      <c r="AL303" t="inlineStr"/>
+      <c r="AM303" t="inlineStr"/>
+      <c r="AN303" t="inlineStr"/>
+      <c r="AO303" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>WGE 02</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C304" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D304" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F304" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>DCR</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>SAFAL SOJAN</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>4b835743-7558-4387-971c-3e0754597853</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>ACC-67268241138</t>
+        </is>
+      </c>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>SBIN0070435</t>
+        </is>
+      </c>
+      <c r="O304" t="inlineStr"/>
+      <c r="P304" t="inlineStr"/>
+      <c r="Q304" t="inlineStr"/>
+      <c r="R304" t="inlineStr"/>
+      <c r="S304" t="inlineStr"/>
+      <c r="T304" t="inlineStr"/>
+      <c r="U304" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V304" t="n">
+        <v>33757</v>
+      </c>
+      <c r="W304" t="inlineStr"/>
+      <c r="X304" t="inlineStr">
+        <is>
+          <t>Salary March 2026 RPA_ID : 6a0f99356f</t>
+        </is>
+      </c>
+      <c r="Y304" t="inlineStr">
+        <is>
+          <t>IOCL WILLINGTON</t>
+        </is>
+      </c>
+      <c r="Z304" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA304" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB304" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC304" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD304" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE304" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF304" t="inlineStr"/>
+      <c r="AG304" t="inlineStr"/>
+      <c r="AH304" t="inlineStr"/>
+      <c r="AI304" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ304" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK304" t="inlineStr">
+        <is>
+          <t>IOCL WILLINGTON</t>
+        </is>
+      </c>
+      <c r="AL304" t="inlineStr"/>
+      <c r="AM304" t="inlineStr"/>
+      <c r="AN304" t="inlineStr"/>
+      <c r="AO304" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>WGE 03</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C305" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D305" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F305" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>VINOD K S</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>4308aff2-411a-4af6-ae71-bb5ab1b1893a</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>ACC-110002216145</t>
+        </is>
+      </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>CNRB0014315</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr"/>
+      <c r="P305" t="inlineStr"/>
+      <c r="Q305" t="inlineStr"/>
+      <c r="R305" t="inlineStr"/>
+      <c r="S305" t="inlineStr"/>
+      <c r="T305" t="inlineStr"/>
+      <c r="U305" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V305" t="n">
+        <v>33173</v>
+      </c>
+      <c r="W305" t="inlineStr"/>
+      <c r="X305" t="inlineStr">
+        <is>
+          <t>Salary March 2026 RPA_ID : 7c5840dc23</t>
+        </is>
+      </c>
+      <c r="Y305" t="inlineStr">
+        <is>
+          <t>IOCL WILLINGTON</t>
+        </is>
+      </c>
+      <c r="Z305" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA305" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB305" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC305" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD305" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE305" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF305" t="inlineStr"/>
+      <c r="AG305" t="inlineStr"/>
+      <c r="AH305" t="inlineStr"/>
+      <c r="AI305" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ305" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK305" t="inlineStr">
+        <is>
+          <t>IOCL WILLINGTON</t>
+        </is>
+      </c>
+      <c r="AL305" t="inlineStr"/>
+      <c r="AM305" t="inlineStr"/>
+      <c r="AN305" t="inlineStr"/>
+      <c r="AO305" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>WGE 09</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C306" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D306" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F306" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>SMITHA</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>5f4f4466-19a8-4a10-b8f7-8023efd9edef</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>ACC-741302010009203</t>
+        </is>
+      </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>UBIN0574139</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr"/>
+      <c r="P306" t="inlineStr"/>
+      <c r="Q306" t="inlineStr"/>
+      <c r="R306" t="inlineStr"/>
+      <c r="S306" t="inlineStr"/>
+      <c r="T306" t="inlineStr"/>
+      <c r="U306" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V306" t="n">
+        <v>13300</v>
+      </c>
+      <c r="W306" t="inlineStr"/>
+      <c r="X306" t="inlineStr">
+        <is>
+          <t>Salary March 2026 RPA_ID : 1f2fbd5a27</t>
+        </is>
+      </c>
+      <c r="Y306" t="inlineStr">
+        <is>
+          <t>IOCL WILLINGTON</t>
+        </is>
+      </c>
+      <c r="Z306" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA306" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB306" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC306" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD306" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE306" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF306" t="inlineStr"/>
+      <c r="AG306" t="inlineStr"/>
+      <c r="AH306" t="inlineStr"/>
+      <c r="AI306" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ306" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK306" t="inlineStr">
+        <is>
+          <t>IOCL WILLINGTON</t>
+        </is>
+      </c>
+      <c r="AL306" t="inlineStr"/>
+      <c r="AM306" t="inlineStr"/>
+      <c r="AN306" t="inlineStr"/>
+      <c r="AO306" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>WGE 194</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C307" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D307" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F307" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Sujata Chakraborty</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>77d03cb3-9261-476e-920b-402e1b05de79</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>ACC-17900100005528</t>
+        </is>
+      </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>UCBA0001790</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr"/>
+      <c r="P307" t="inlineStr"/>
+      <c r="Q307" t="inlineStr"/>
+      <c r="R307" t="inlineStr"/>
+      <c r="S307" t="inlineStr"/>
+      <c r="T307" t="inlineStr"/>
+      <c r="U307" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V307" t="n">
+        <v>6000</v>
+      </c>
+      <c r="W307" t="inlineStr"/>
+      <c r="X307" t="inlineStr">
+        <is>
+          <t>Salary Advance  Rs.5000/- Sagar Rs.1000/0 RPA_ID : 92959c4bab</t>
+        </is>
+      </c>
+      <c r="Y307" t="inlineStr">
+        <is>
+          <t>KOLKATTA</t>
+        </is>
+      </c>
+      <c r="Z307" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA307" t="inlineStr">
+        <is>
+          <t>hrm@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB307" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC307" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD307" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE307" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF307" t="inlineStr"/>
+      <c r="AG307" t="inlineStr"/>
+      <c r="AH307" t="inlineStr"/>
+      <c r="AI307" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ307" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK307" t="inlineStr"/>
+      <c r="AL307" t="inlineStr"/>
+      <c r="AM307" t="inlineStr"/>
+      <c r="AN307" t="inlineStr"/>
+      <c r="AO307" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> WGG 02</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C308" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D308" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F308" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>78fc5f6d-9311-4c93-9a38-84876d6e9695</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr"/>
+      <c r="N308" t="inlineStr"/>
+      <c r="O308" t="inlineStr"/>
+      <c r="P308" t="inlineStr"/>
+      <c r="Q308" t="inlineStr"/>
+      <c r="R308" t="inlineStr"/>
+      <c r="S308" t="inlineStr"/>
+      <c r="T308" t="inlineStr"/>
+      <c r="U308" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V308" t="n">
+        <v>75796</v>
+      </c>
+      <c r="W308" t="inlineStr"/>
+      <c r="X308" t="inlineStr">
+        <is>
+          <t>EMI auto debit from current account RPA_ID : 09aed72cd6</t>
+        </is>
+      </c>
+      <c r="Y308" t="inlineStr">
+        <is>
+          <t>Cochin</t>
+        </is>
+      </c>
+      <c r="Z308" t="inlineStr">
+        <is>
+          <t>PAYMENTS</t>
+        </is>
+      </c>
+      <c r="AA308" t="inlineStr">
+        <is>
+          <t>Payments@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB308" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC308" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD308" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE308" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF308" t="inlineStr"/>
+      <c r="AG308" t="inlineStr"/>
+      <c r="AH308" t="inlineStr"/>
+      <c r="AI308" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ308" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK308" t="inlineStr"/>
+      <c r="AL308" t="inlineStr"/>
+      <c r="AM308" t="inlineStr"/>
+      <c r="AN308" t="inlineStr"/>
+      <c r="AO308" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> WGG 02</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C309" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D309" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F309" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>a842bb6f-a3f7-4265-b90e-c8f118d13317</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr"/>
+      <c r="N309" t="inlineStr"/>
+      <c r="O309" t="inlineStr"/>
+      <c r="P309" t="inlineStr"/>
+      <c r="Q309" t="inlineStr"/>
+      <c r="R309" t="inlineStr"/>
+      <c r="S309" t="inlineStr"/>
+      <c r="T309" t="inlineStr"/>
+      <c r="U309" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V309" t="n">
+        <v>89272</v>
+      </c>
+      <c r="W309" t="inlineStr"/>
+      <c r="X309" t="inlineStr">
+        <is>
+          <t>EMI auto debit from current account RPA_ID : 8f92b4e3a6</t>
+        </is>
+      </c>
+      <c r="Y309" t="inlineStr">
+        <is>
+          <t>Cochin</t>
+        </is>
+      </c>
+      <c r="Z309" t="inlineStr">
+        <is>
+          <t>PAYMENTS</t>
+        </is>
+      </c>
+      <c r="AA309" t="inlineStr">
+        <is>
+          <t>Payments@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB309" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC309" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD309" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE309" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF309" t="inlineStr"/>
+      <c r="AG309" t="inlineStr"/>
+      <c r="AH309" t="inlineStr"/>
+      <c r="AI309" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ309" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK309" t="inlineStr"/>
+      <c r="AL309" t="inlineStr"/>
+      <c r="AM309" t="inlineStr"/>
+      <c r="AN309" t="inlineStr"/>
+      <c r="AO309" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> WGG 02</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C310" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D310" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F310" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>b18fca2a-786c-4db4-aa84-c2f8c6ac5670</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr"/>
+      <c r="N310" t="inlineStr"/>
+      <c r="O310" t="inlineStr"/>
+      <c r="P310" t="inlineStr"/>
+      <c r="Q310" t="inlineStr"/>
+      <c r="R310" t="inlineStr"/>
+      <c r="S310" t="inlineStr"/>
+      <c r="T310" t="inlineStr"/>
+      <c r="U310" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V310" t="n">
+        <v>100333</v>
+      </c>
+      <c r="W310" t="inlineStr"/>
+      <c r="X310" t="inlineStr">
+        <is>
+          <t>EMI auto debit from current account RPA_ID : 76591c2392</t>
+        </is>
+      </c>
+      <c r="Y310" t="inlineStr">
+        <is>
+          <t>Cochin</t>
+        </is>
+      </c>
+      <c r="Z310" t="inlineStr">
+        <is>
+          <t>PAYMENTS</t>
+        </is>
+      </c>
+      <c r="AA310" t="inlineStr">
+        <is>
+          <t>Payments@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB310" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC310" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD310" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE310" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF310" t="inlineStr"/>
+      <c r="AG310" t="inlineStr"/>
+      <c r="AH310" t="inlineStr"/>
+      <c r="AI310" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ310" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK310" t="inlineStr"/>
+      <c r="AL310" t="inlineStr"/>
+      <c r="AM310" t="inlineStr"/>
+      <c r="AN310" t="inlineStr"/>
+      <c r="AO310" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>WGE 425</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="C311" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D311" t="n">
+        <v>286962</v>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Western Interior Designers &amp; Marine Contractors</t>
+        </is>
+      </c>
+      <c r="F311" t="n">
+        <v>34413429360</v>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>SBIN0003229</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>AAAFW8862C</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>32AAAFW8862C1Z9</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>SHANIBA BEEVI</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>e6ec0700-1294-4587-913b-769507b4631e</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>ACC-0572053000003124</t>
+        </is>
+      </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>SIBL0000572</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr"/>
+      <c r="P311" t="inlineStr"/>
+      <c r="Q311" t="inlineStr"/>
+      <c r="R311" t="inlineStr"/>
+      <c r="S311" t="inlineStr"/>
+      <c r="T311" t="inlineStr"/>
+      <c r="U311" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="V311" t="n">
+        <v>10000</v>
+      </c>
+      <c r="W311" t="inlineStr"/>
+      <c r="X311" t="inlineStr">
+        <is>
+          <t>Salary 5th RPA_ID : 171f74d9f4</t>
+        </is>
+      </c>
+      <c r="Y311" t="inlineStr">
+        <is>
+          <t>Cochin</t>
+        </is>
+      </c>
+      <c r="Z311" t="inlineStr">
+        <is>
+          <t>PAYMENTS</t>
+        </is>
+      </c>
+      <c r="AA311" t="inlineStr">
+        <is>
+          <t>Payments@westernidc.com</t>
+        </is>
+      </c>
+      <c r="AB311" t="inlineStr">
+        <is>
+          <t>ESTIMATION NOT MATCHED</t>
+        </is>
+      </c>
+      <c r="AC311" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD311" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE311" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF311" t="inlineStr"/>
+      <c r="AG311" t="inlineStr"/>
+      <c r="AH311" t="inlineStr"/>
+      <c r="AI311" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ311" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AK311" t="inlineStr"/>
+      <c r="AL311" t="inlineStr"/>
+      <c r="AM311" t="inlineStr"/>
+      <c r="AN311" t="inlineStr"/>
+      <c r="AO311" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PENDING_APPROVAL_SHEET.xlsx
+++ b/PENDING_APPROVAL_SHEET.xlsx
@@ -2051,8 +2051,16 @@
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
-      <c r="AJ12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr"/>
       <c r="AM12" t="inlineStr"/>
@@ -23812,8 +23820,16 @@
       <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="inlineStr"/>
       <c r="AH185" t="inlineStr"/>
-      <c r="AI185" t="inlineStr"/>
-      <c r="AJ185" t="inlineStr"/>
+      <c r="AI185" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ185" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
       <c r="AK185" t="inlineStr">
         <is>
           <t>GOA</t>

--- a/PENDING_APPROVAL_SHEET.xlsx
+++ b/PENDING_APPROVAL_SHEET.xlsx
@@ -1548,8 +1548,16 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>

--- a/PENDING_APPROVAL_SHEET.xlsx
+++ b/PENDING_APPROVAL_SHEET.xlsx
@@ -1550,12 +1550,12 @@
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>ACCEPTED</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>ACCEPTED</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr"/>
@@ -1673,8 +1673,16 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK9" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -1804,8 +1812,16 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="inlineStr"/>
@@ -1929,8 +1945,16 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr"/>
       <c r="AM11" t="inlineStr"/>
@@ -2061,12 +2085,12 @@
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>ACCEPTED</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>ACCEPTED</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr"/>
@@ -2192,8 +2216,16 @@
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="inlineStr"/>
       <c r="AM13" t="inlineStr"/>
@@ -2317,8 +2349,16 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="inlineStr"/>
       <c r="AM14" t="inlineStr"/>
@@ -2442,8 +2482,16 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr"/>
-      <c r="AJ15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="inlineStr"/>
       <c r="AM15" t="inlineStr"/>
@@ -2567,8 +2615,16 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr"/>
-      <c r="AJ16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK16" t="inlineStr">
         <is>
           <t>HO</t>
@@ -2696,8 +2752,16 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
-      <c r="AJ17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="inlineStr"/>
       <c r="AM17" t="inlineStr"/>
@@ -2821,8 +2885,16 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
-      <c r="AJ18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK18" t="inlineStr">
         <is>
           <t>HO</t>
@@ -2950,8 +3022,16 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr"/>
-      <c r="AJ19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK19" t="inlineStr">
         <is>
           <t>HO</t>
@@ -3079,8 +3159,16 @@
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="inlineStr"/>
-      <c r="AJ20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK20" t="inlineStr"/>
       <c r="AL20" t="inlineStr"/>
       <c r="AM20" t="inlineStr"/>
@@ -3204,8 +3292,16 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr"/>
-      <c r="AJ21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK21" t="inlineStr">
         <is>
           <t>HO</t>
@@ -3333,8 +3429,16 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr"/>
-      <c r="AI22" t="inlineStr"/>
-      <c r="AJ22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK22" t="inlineStr">
         <is>
           <t>HO</t>
@@ -3462,8 +3566,16 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="inlineStr"/>
-      <c r="AJ23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK23" t="inlineStr">
         <is>
           <t>HO</t>
@@ -3591,8 +3703,16 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="inlineStr"/>
-      <c r="AI24" t="inlineStr"/>
-      <c r="AJ24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK24" t="inlineStr">
         <is>
           <t>HO</t>
@@ -3720,8 +3840,16 @@
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr"/>
-      <c r="AI25" t="inlineStr"/>
-      <c r="AJ25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK25" t="inlineStr">
         <is>
           <t>HO</t>
@@ -3849,8 +3977,16 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr"/>
-      <c r="AI26" t="inlineStr"/>
-      <c r="AJ26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK26" t="inlineStr">
         <is>
           <t>HO</t>
@@ -3970,8 +4106,16 @@
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr"/>
-      <c r="AI27" t="inlineStr"/>
-      <c r="AJ27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK27" t="inlineStr"/>
       <c r="AL27" t="inlineStr"/>
       <c r="AM27" t="inlineStr"/>
@@ -4087,8 +4231,16 @@
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="inlineStr"/>
-      <c r="AI28" t="inlineStr"/>
-      <c r="AJ28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK28" t="inlineStr"/>
       <c r="AL28" t="inlineStr"/>
       <c r="AM28" t="inlineStr"/>
@@ -4210,8 +4362,16 @@
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="inlineStr"/>
-      <c r="AI29" t="inlineStr"/>
-      <c r="AJ29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK29" t="inlineStr">
         <is>
           <t>ONGC ELECTRICAL</t>
@@ -4337,8 +4497,16 @@
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="inlineStr"/>
-      <c r="AI30" t="inlineStr"/>
-      <c r="AJ30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK30" t="inlineStr">
         <is>
           <t>ONGC ELECTRICAL</t>
@@ -4464,8 +4632,16 @@
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr"/>
-      <c r="AI31" t="inlineStr"/>
-      <c r="AJ31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK31" t="inlineStr">
         <is>
           <t>ONGC ELECTRICAL</t>
@@ -4591,8 +4767,16 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr"/>
-      <c r="AI32" t="inlineStr"/>
-      <c r="AJ32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK32" t="inlineStr">
         <is>
           <t>ONGC ELECTRICAL</t>
@@ -4718,8 +4902,16 @@
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr"/>
-      <c r="AI33" t="inlineStr"/>
-      <c r="AJ33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK33" t="inlineStr">
         <is>
           <t>ONGC ELECTRICAL</t>
@@ -4845,8 +5037,16 @@
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr"/>
-      <c r="AI34" t="inlineStr"/>
-      <c r="AJ34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK34" t="inlineStr">
         <is>
           <t>ONGC ELECTRICAL</t>
@@ -4972,8 +5172,16 @@
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="inlineStr"/>
-      <c r="AI35" t="inlineStr"/>
-      <c r="AJ35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK35" t="inlineStr">
         <is>
           <t>ONGC ELECTRICAL</t>
@@ -5099,8 +5307,16 @@
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="inlineStr"/>
-      <c r="AI36" t="inlineStr"/>
-      <c r="AJ36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK36" t="inlineStr">
         <is>
           <t>ONGC ELECTRICAL</t>
@@ -5226,8 +5442,16 @@
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="inlineStr"/>
-      <c r="AI37" t="inlineStr"/>
-      <c r="AJ37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK37" t="inlineStr">
         <is>
           <t>ONGC ELECTRICAL</t>
@@ -5353,8 +5577,16 @@
       <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="inlineStr"/>
-      <c r="AI38" t="inlineStr"/>
-      <c r="AJ38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK38" t="inlineStr">
         <is>
           <t>ONGC ELECTRICAL</t>
@@ -5480,8 +5712,16 @@
       <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="inlineStr"/>
       <c r="AH39" t="inlineStr"/>
-      <c r="AI39" t="inlineStr"/>
-      <c r="AJ39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK39" t="inlineStr">
         <is>
           <t>ONGC ELECTRICAL</t>
@@ -5607,8 +5847,16 @@
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="inlineStr"/>
       <c r="AH40" t="inlineStr"/>
-      <c r="AI40" t="inlineStr"/>
-      <c r="AJ40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK40" t="inlineStr">
         <is>
           <t>ONGC ELECTRICAL</t>
@@ -5734,8 +5982,16 @@
       <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="inlineStr"/>
-      <c r="AI41" t="inlineStr"/>
-      <c r="AJ41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK41" t="inlineStr">
         <is>
           <t>ONGC ELECTRICAL</t>
@@ -5861,8 +6117,16 @@
       <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="inlineStr"/>
       <c r="AH42" t="inlineStr"/>
-      <c r="AI42" t="inlineStr"/>
-      <c r="AJ42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK42" t="inlineStr">
         <is>
           <t>ONGC ELECTRICAL</t>
@@ -5988,8 +6252,16 @@
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="inlineStr"/>
       <c r="AH43" t="inlineStr"/>
-      <c r="AI43" t="inlineStr"/>
-      <c r="AJ43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK43" t="inlineStr">
         <is>
           <t>ONGC ELECTRICAL</t>
@@ -6115,8 +6387,16 @@
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="inlineStr"/>
-      <c r="AI44" t="inlineStr"/>
-      <c r="AJ44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK44" t="inlineStr">
         <is>
           <t>ONGC ELECTRICAL</t>
@@ -6242,8 +6522,16 @@
       <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="inlineStr"/>
       <c r="AH45" t="inlineStr"/>
-      <c r="AI45" t="inlineStr"/>
-      <c r="AJ45" t="inlineStr"/>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK45" t="inlineStr">
         <is>
           <t>IOCL FEROKE</t>
@@ -6369,8 +6657,16 @@
       <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="inlineStr"/>
       <c r="AH46" t="inlineStr"/>
-      <c r="AI46" t="inlineStr"/>
-      <c r="AJ46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK46" t="inlineStr">
         <is>
           <t>IOCL FEROKE</t>
@@ -6496,8 +6792,16 @@
       <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="inlineStr"/>
       <c r="AH47" t="inlineStr"/>
-      <c r="AI47" t="inlineStr"/>
-      <c r="AJ47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK47" t="inlineStr">
         <is>
           <t>IOCL FEROKE</t>
@@ -6623,8 +6927,16 @@
       <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="inlineStr"/>
       <c r="AH48" t="inlineStr"/>
-      <c r="AI48" t="inlineStr"/>
-      <c r="AJ48" t="inlineStr"/>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK48" t="inlineStr">
         <is>
           <t>IOCL FEROKE</t>
@@ -6750,8 +7062,16 @@
       <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="inlineStr"/>
       <c r="AH49" t="inlineStr"/>
-      <c r="AI49" t="inlineStr"/>
-      <c r="AJ49" t="inlineStr"/>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK49" t="inlineStr">
         <is>
           <t>IOCL FEROKE</t>
@@ -6877,8 +7197,16 @@
       <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="inlineStr"/>
       <c r="AH50" t="inlineStr"/>
-      <c r="AI50" t="inlineStr"/>
-      <c r="AJ50" t="inlineStr"/>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK50" t="inlineStr">
         <is>
           <t>IOCL FEROKE</t>
@@ -7004,8 +7332,16 @@
       <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="inlineStr"/>
       <c r="AH51" t="inlineStr"/>
-      <c r="AI51" t="inlineStr"/>
-      <c r="AJ51" t="inlineStr"/>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK51" t="inlineStr">
         <is>
           <t>IOCL FEROKE</t>
@@ -7131,8 +7467,16 @@
       <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="inlineStr"/>
       <c r="AH52" t="inlineStr"/>
-      <c r="AI52" t="inlineStr"/>
-      <c r="AJ52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK52" t="inlineStr">
         <is>
           <t>IOCL FEROKE</t>
@@ -7258,8 +7602,16 @@
       <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="inlineStr"/>
       <c r="AH53" t="inlineStr"/>
-      <c r="AI53" t="inlineStr"/>
-      <c r="AJ53" t="inlineStr"/>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK53" t="inlineStr">
         <is>
           <t>IOCL FEROKE</t>
@@ -7385,8 +7737,16 @@
       <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="inlineStr"/>
       <c r="AH54" t="inlineStr"/>
-      <c r="AI54" t="inlineStr"/>
-      <c r="AJ54" t="inlineStr"/>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK54" t="inlineStr">
         <is>
           <t>IOCL FEROKE</t>
@@ -7512,8 +7872,16 @@
       <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="inlineStr"/>
       <c r="AH55" t="inlineStr"/>
-      <c r="AI55" t="inlineStr"/>
-      <c r="AJ55" t="inlineStr"/>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK55" t="inlineStr">
         <is>
           <t>IOCL FEROKE</t>
@@ -7639,8 +8007,16 @@
       <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="inlineStr"/>
       <c r="AH56" t="inlineStr"/>
-      <c r="AI56" t="inlineStr"/>
-      <c r="AJ56" t="inlineStr"/>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK56" t="inlineStr">
         <is>
           <t>IOCL FEROKE</t>
@@ -7766,8 +8142,16 @@
       <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="inlineStr"/>
       <c r="AH57" t="inlineStr"/>
-      <c r="AI57" t="inlineStr"/>
-      <c r="AJ57" t="inlineStr"/>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK57" t="inlineStr">
         <is>
           <t>IOCL FEROKE</t>
@@ -7893,8 +8277,16 @@
       <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="inlineStr"/>
       <c r="AH58" t="inlineStr"/>
-      <c r="AI58" t="inlineStr"/>
-      <c r="AJ58" t="inlineStr"/>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK58" t="inlineStr">
         <is>
           <t>IOCL FEROKE</t>
@@ -8020,8 +8412,16 @@
       <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="inlineStr"/>
       <c r="AH59" t="inlineStr"/>
-      <c r="AI59" t="inlineStr"/>
-      <c r="AJ59" t="inlineStr"/>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK59" t="inlineStr">
         <is>
           <t>IOCL FEROKE</t>
@@ -8147,8 +8547,16 @@
       <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="inlineStr"/>
       <c r="AH60" t="inlineStr"/>
-      <c r="AI60" t="inlineStr"/>
-      <c r="AJ60" t="inlineStr"/>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK60" t="inlineStr">
         <is>
           <t>IOCL FEROKE</t>
@@ -8274,8 +8682,16 @@
       <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr"/>
-      <c r="AI61" t="inlineStr"/>
-      <c r="AJ61" t="inlineStr"/>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK61" t="inlineStr">
         <is>
           <t>IOCL FEROKE</t>
@@ -8401,8 +8817,16 @@
       <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr"/>
-      <c r="AI62" t="inlineStr"/>
-      <c r="AJ62" t="inlineStr"/>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK62" t="inlineStr">
         <is>
           <t>IOCL FEROKE</t>
@@ -8528,8 +8952,16 @@
       <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="inlineStr"/>
       <c r="AH63" t="inlineStr"/>
-      <c r="AI63" t="inlineStr"/>
-      <c r="AJ63" t="inlineStr"/>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK63" t="inlineStr">
         <is>
           <t>IOCL FEROKE</t>
@@ -8655,8 +9087,16 @@
       <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="inlineStr"/>
       <c r="AH64" t="inlineStr"/>
-      <c r="AI64" t="inlineStr"/>
-      <c r="AJ64" t="inlineStr"/>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK64" t="inlineStr">
         <is>
           <t>IOCL FEROKE</t>
@@ -8782,8 +9222,16 @@
       <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="inlineStr"/>
       <c r="AH65" t="inlineStr"/>
-      <c r="AI65" t="inlineStr"/>
-      <c r="AJ65" t="inlineStr"/>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK65" t="inlineStr">
         <is>
           <t>IOCL FEROKE</t>
@@ -8909,8 +9357,16 @@
       <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="inlineStr"/>
       <c r="AH66" t="inlineStr"/>
-      <c r="AI66" t="inlineStr"/>
-      <c r="AJ66" t="inlineStr"/>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK66" t="inlineStr">
         <is>
           <t>IOCL FEROKE</t>
@@ -9036,8 +9492,16 @@
       <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="inlineStr"/>
       <c r="AH67" t="inlineStr"/>
-      <c r="AI67" t="inlineStr"/>
-      <c r="AJ67" t="inlineStr"/>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK67" t="inlineStr">
         <is>
           <t>IOCL FEROKE</t>
@@ -9163,8 +9627,16 @@
       <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="inlineStr"/>
       <c r="AH68" t="inlineStr"/>
-      <c r="AI68" t="inlineStr"/>
-      <c r="AJ68" t="inlineStr"/>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK68" t="inlineStr">
         <is>
           <t>IOCL FEROKE</t>
@@ -9290,8 +9762,16 @@
       <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="inlineStr"/>
       <c r="AH69" t="inlineStr"/>
-      <c r="AI69" t="inlineStr"/>
-      <c r="AJ69" t="inlineStr"/>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK69" t="inlineStr">
         <is>
           <t>IOCL FEROKE</t>
@@ -9417,8 +9897,16 @@
       <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="inlineStr"/>
       <c r="AH70" t="inlineStr"/>
-      <c r="AI70" t="inlineStr"/>
-      <c r="AJ70" t="inlineStr"/>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK70" t="inlineStr">
         <is>
           <t>HPCL THIRUNELVELI</t>
@@ -9544,8 +10032,16 @@
       <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="inlineStr"/>
       <c r="AH71" t="inlineStr"/>
-      <c r="AI71" t="inlineStr"/>
-      <c r="AJ71" t="inlineStr"/>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK71" t="inlineStr">
         <is>
           <t>HPCL THIRUNELVELI</t>
@@ -9671,8 +10167,16 @@
       <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="inlineStr"/>
       <c r="AH72" t="inlineStr"/>
-      <c r="AI72" t="inlineStr"/>
-      <c r="AJ72" t="inlineStr"/>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK72" t="inlineStr">
         <is>
           <t>HPCL THIRUNELVELI</t>
@@ -9798,8 +10302,16 @@
       <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="inlineStr"/>
       <c r="AH73" t="inlineStr"/>
-      <c r="AI73" t="inlineStr"/>
-      <c r="AJ73" t="inlineStr"/>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK73" t="inlineStr">
         <is>
           <t>HPCL THIRUNELVELI</t>
@@ -9925,8 +10437,16 @@
       <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="inlineStr"/>
       <c r="AH74" t="inlineStr"/>
-      <c r="AI74" t="inlineStr"/>
-      <c r="AJ74" t="inlineStr"/>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK74" t="inlineStr">
         <is>
           <t>HPCL THIRUNELVELI</t>
@@ -10052,8 +10572,16 @@
       <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="inlineStr"/>
       <c r="AH75" t="inlineStr"/>
-      <c r="AI75" t="inlineStr"/>
-      <c r="AJ75" t="inlineStr"/>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK75" t="inlineStr">
         <is>
           <t>HPCL THIRUNELVELI</t>
@@ -10179,8 +10707,16 @@
       <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="inlineStr"/>
       <c r="AH76" t="inlineStr"/>
-      <c r="AI76" t="inlineStr"/>
-      <c r="AJ76" t="inlineStr"/>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK76" t="inlineStr">
         <is>
           <t>HPCL THIRUNELVELI</t>
@@ -10306,8 +10842,16 @@
       <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="inlineStr"/>
       <c r="AH77" t="inlineStr"/>
-      <c r="AI77" t="inlineStr"/>
-      <c r="AJ77" t="inlineStr"/>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK77" t="inlineStr"/>
       <c r="AL77" t="inlineStr"/>
       <c r="AM77" t="inlineStr"/>
@@ -10429,8 +10973,16 @@
       <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="inlineStr"/>
       <c r="AH78" t="inlineStr"/>
-      <c r="AI78" t="inlineStr"/>
-      <c r="AJ78" t="inlineStr"/>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK78" t="inlineStr"/>
       <c r="AL78" t="inlineStr"/>
       <c r="AM78" t="inlineStr"/>
@@ -10552,8 +11104,16 @@
       <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="inlineStr"/>
       <c r="AH79" t="inlineStr"/>
-      <c r="AI79" t="inlineStr"/>
-      <c r="AJ79" t="inlineStr"/>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK79" t="inlineStr"/>
       <c r="AL79" t="inlineStr"/>
       <c r="AM79" t="inlineStr"/>
@@ -10675,8 +11235,16 @@
       <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="inlineStr"/>
       <c r="AH80" t="inlineStr"/>
-      <c r="AI80" t="inlineStr"/>
-      <c r="AJ80" t="inlineStr"/>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK80" t="inlineStr"/>
       <c r="AL80" t="inlineStr"/>
       <c r="AM80" t="inlineStr"/>
@@ -10798,8 +11366,16 @@
       <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="inlineStr"/>
       <c r="AH81" t="inlineStr"/>
-      <c r="AI81" t="inlineStr"/>
-      <c r="AJ81" t="inlineStr"/>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK81" t="inlineStr"/>
       <c r="AL81" t="inlineStr"/>
       <c r="AM81" t="inlineStr"/>
@@ -10921,8 +11497,16 @@
       <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="inlineStr"/>
       <c r="AH82" t="inlineStr"/>
-      <c r="AI82" t="inlineStr"/>
-      <c r="AJ82" t="inlineStr"/>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK82" t="inlineStr"/>
       <c r="AL82" t="inlineStr"/>
       <c r="AM82" t="inlineStr"/>
@@ -11044,8 +11628,16 @@
       <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="inlineStr"/>
       <c r="AH83" t="inlineStr"/>
-      <c r="AI83" t="inlineStr"/>
-      <c r="AJ83" t="inlineStr"/>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK83" t="inlineStr">
         <is>
           <t>ONGC IPSHEM</t>
@@ -11171,8 +11763,16 @@
       <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="inlineStr"/>
       <c r="AH84" t="inlineStr"/>
-      <c r="AI84" t="inlineStr"/>
-      <c r="AJ84" t="inlineStr"/>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK84" t="inlineStr">
         <is>
           <t>ONGC IPSHEM</t>
@@ -11298,8 +11898,16 @@
       <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="inlineStr"/>
       <c r="AH85" t="inlineStr"/>
-      <c r="AI85" t="inlineStr"/>
-      <c r="AJ85" t="inlineStr"/>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK85" t="inlineStr">
         <is>
           <t>ONGC IPSHEM</t>
@@ -11425,8 +12033,16 @@
       <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="inlineStr"/>
       <c r="AH86" t="inlineStr"/>
-      <c r="AI86" t="inlineStr"/>
-      <c r="AJ86" t="inlineStr"/>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK86" t="inlineStr"/>
       <c r="AL86" t="inlineStr"/>
       <c r="AM86" t="inlineStr"/>
@@ -11550,8 +12166,16 @@
       <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="inlineStr"/>
       <c r="AH87" t="inlineStr"/>
-      <c r="AI87" t="inlineStr"/>
-      <c r="AJ87" t="inlineStr"/>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK87" t="inlineStr">
         <is>
           <t>BELLARI</t>
@@ -11679,8 +12303,16 @@
       <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="inlineStr"/>
       <c r="AH88" t="inlineStr"/>
-      <c r="AI88" t="inlineStr"/>
-      <c r="AJ88" t="inlineStr"/>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK88" t="inlineStr">
         <is>
           <t>BELLARI</t>
@@ -11806,8 +12438,16 @@
       <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="inlineStr"/>
       <c r="AH89" t="inlineStr"/>
-      <c r="AI89" t="inlineStr"/>
-      <c r="AJ89" t="inlineStr"/>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK89" t="inlineStr">
         <is>
           <t>BELLARI</t>
@@ -11933,8 +12573,16 @@
       <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="inlineStr"/>
       <c r="AH90" t="inlineStr"/>
-      <c r="AI90" t="inlineStr"/>
-      <c r="AJ90" t="inlineStr"/>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK90" t="inlineStr">
         <is>
           <t>BELLARI</t>
@@ -12060,8 +12708,16 @@
       <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="inlineStr"/>
       <c r="AH91" t="inlineStr"/>
-      <c r="AI91" t="inlineStr"/>
-      <c r="AJ91" t="inlineStr"/>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK91" t="inlineStr">
         <is>
           <t>BELLARI</t>
@@ -12187,8 +12843,16 @@
       <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="inlineStr"/>
       <c r="AH92" t="inlineStr"/>
-      <c r="AI92" t="inlineStr"/>
-      <c r="AJ92" t="inlineStr"/>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK92" t="inlineStr">
         <is>
           <t>BELLARI</t>
@@ -12314,8 +12978,16 @@
       <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="inlineStr"/>
       <c r="AH93" t="inlineStr"/>
-      <c r="AI93" t="inlineStr"/>
-      <c r="AJ93" t="inlineStr"/>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK93" t="inlineStr">
         <is>
           <t>BELLARI</t>
@@ -12441,8 +13113,16 @@
       <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="inlineStr"/>
       <c r="AH94" t="inlineStr"/>
-      <c r="AI94" t="inlineStr"/>
-      <c r="AJ94" t="inlineStr"/>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK94" t="inlineStr">
         <is>
           <t>BELLARI</t>
@@ -12568,8 +13248,16 @@
       <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="inlineStr"/>
       <c r="AH95" t="inlineStr"/>
-      <c r="AI95" t="inlineStr"/>
-      <c r="AJ95" t="inlineStr"/>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK95" t="inlineStr">
         <is>
           <t>BELLARI</t>
@@ -12695,8 +13383,16 @@
       <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="inlineStr"/>
       <c r="AH96" t="inlineStr"/>
-      <c r="AI96" t="inlineStr"/>
-      <c r="AJ96" t="inlineStr"/>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK96" t="inlineStr"/>
       <c r="AL96" t="inlineStr"/>
       <c r="AM96" t="inlineStr"/>
@@ -12818,8 +13514,16 @@
       <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="inlineStr"/>
       <c r="AH97" t="inlineStr"/>
-      <c r="AI97" t="inlineStr"/>
-      <c r="AJ97" t="inlineStr"/>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK97" t="inlineStr"/>
       <c r="AL97" t="inlineStr"/>
       <c r="AM97" t="inlineStr"/>
@@ -12941,8 +13645,16 @@
       <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="inlineStr"/>
       <c r="AH98" t="inlineStr"/>
-      <c r="AI98" t="inlineStr"/>
-      <c r="AJ98" t="inlineStr"/>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK98" t="inlineStr"/>
       <c r="AL98" t="inlineStr"/>
       <c r="AM98" t="inlineStr"/>
@@ -13064,8 +13776,16 @@
       <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="inlineStr"/>
       <c r="AH99" t="inlineStr"/>
-      <c r="AI99" t="inlineStr"/>
-      <c r="AJ99" t="inlineStr"/>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK99" t="inlineStr"/>
       <c r="AL99" t="inlineStr"/>
       <c r="AM99" t="inlineStr"/>
@@ -13187,8 +13907,16 @@
       <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="inlineStr"/>
       <c r="AH100" t="inlineStr"/>
-      <c r="AI100" t="inlineStr"/>
-      <c r="AJ100" t="inlineStr"/>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK100" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -13314,8 +14042,16 @@
       <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="inlineStr"/>
       <c r="AH101" t="inlineStr"/>
-      <c r="AI101" t="inlineStr"/>
-      <c r="AJ101" t="inlineStr"/>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK101" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -13441,8 +14177,16 @@
       <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="inlineStr"/>
       <c r="AH102" t="inlineStr"/>
-      <c r="AI102" t="inlineStr"/>
-      <c r="AJ102" t="inlineStr"/>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK102" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -13568,8 +14312,16 @@
       <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="inlineStr"/>
       <c r="AH103" t="inlineStr"/>
-      <c r="AI103" t="inlineStr"/>
-      <c r="AJ103" t="inlineStr"/>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK103" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -13695,8 +14447,16 @@
       <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="inlineStr"/>
       <c r="AH104" t="inlineStr"/>
-      <c r="AI104" t="inlineStr"/>
-      <c r="AJ104" t="inlineStr"/>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK104" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -13822,8 +14582,16 @@
       <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="inlineStr"/>
       <c r="AH105" t="inlineStr"/>
-      <c r="AI105" t="inlineStr"/>
-      <c r="AJ105" t="inlineStr"/>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK105" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -13949,8 +14717,16 @@
       <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="inlineStr"/>
       <c r="AH106" t="inlineStr"/>
-      <c r="AI106" t="inlineStr"/>
-      <c r="AJ106" t="inlineStr"/>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK106" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -14076,8 +14852,16 @@
       <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="inlineStr"/>
       <c r="AH107" t="inlineStr"/>
-      <c r="AI107" t="inlineStr"/>
-      <c r="AJ107" t="inlineStr"/>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK107" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -14203,8 +14987,16 @@
       <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="inlineStr"/>
       <c r="AH108" t="inlineStr"/>
-      <c r="AI108" t="inlineStr"/>
-      <c r="AJ108" t="inlineStr"/>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK108" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -14330,8 +15122,16 @@
       <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="inlineStr"/>
       <c r="AH109" t="inlineStr"/>
-      <c r="AI109" t="inlineStr"/>
-      <c r="AJ109" t="inlineStr"/>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK109" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -14457,8 +15257,16 @@
       <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="inlineStr"/>
       <c r="AH110" t="inlineStr"/>
-      <c r="AI110" t="inlineStr"/>
-      <c r="AJ110" t="inlineStr"/>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK110" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -14584,8 +15392,16 @@
       <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="inlineStr"/>
       <c r="AH111" t="inlineStr"/>
-      <c r="AI111" t="inlineStr"/>
-      <c r="AJ111" t="inlineStr"/>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK111" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -14711,8 +15527,16 @@
       <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="inlineStr"/>
       <c r="AH112" t="inlineStr"/>
-      <c r="AI112" t="inlineStr"/>
-      <c r="AJ112" t="inlineStr"/>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK112" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -14838,8 +15662,16 @@
       <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="inlineStr"/>
       <c r="AH113" t="inlineStr"/>
-      <c r="AI113" t="inlineStr"/>
-      <c r="AJ113" t="inlineStr"/>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK113" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -14965,8 +15797,16 @@
       <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="inlineStr"/>
       <c r="AH114" t="inlineStr"/>
-      <c r="AI114" t="inlineStr"/>
-      <c r="AJ114" t="inlineStr"/>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK114" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -15092,8 +15932,16 @@
       <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="inlineStr"/>
       <c r="AH115" t="inlineStr"/>
-      <c r="AI115" t="inlineStr"/>
-      <c r="AJ115" t="inlineStr"/>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK115" t="inlineStr"/>
       <c r="AL115" t="inlineStr"/>
       <c r="AM115" t="inlineStr"/>
@@ -15215,8 +16063,16 @@
       <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="inlineStr"/>
       <c r="AH116" t="inlineStr"/>
-      <c r="AI116" t="inlineStr"/>
-      <c r="AJ116" t="inlineStr"/>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK116" t="inlineStr"/>
       <c r="AL116" t="inlineStr"/>
       <c r="AM116" t="inlineStr"/>
@@ -15338,8 +16194,16 @@
       <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="inlineStr"/>
       <c r="AH117" t="inlineStr"/>
-      <c r="AI117" t="inlineStr"/>
-      <c r="AJ117" t="inlineStr"/>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK117" t="inlineStr"/>
       <c r="AL117" t="inlineStr"/>
       <c r="AM117" t="inlineStr"/>
@@ -15461,8 +16325,16 @@
       <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="inlineStr"/>
       <c r="AH118" t="inlineStr"/>
-      <c r="AI118" t="inlineStr"/>
-      <c r="AJ118" t="inlineStr"/>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK118" t="inlineStr">
         <is>
           <t>HPCL LUBE</t>
@@ -15588,8 +16460,16 @@
       <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="inlineStr"/>
       <c r="AH119" t="inlineStr"/>
-      <c r="AI119" t="inlineStr"/>
-      <c r="AJ119" t="inlineStr"/>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK119" t="inlineStr">
         <is>
           <t>HPCL LUBE</t>
@@ -15715,8 +16595,16 @@
       <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="inlineStr"/>
       <c r="AH120" t="inlineStr"/>
-      <c r="AI120" t="inlineStr"/>
-      <c r="AJ120" t="inlineStr"/>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK120" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -15842,8 +16730,16 @@
       <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="inlineStr"/>
       <c r="AH121" t="inlineStr"/>
-      <c r="AI121" t="inlineStr"/>
-      <c r="AJ121" t="inlineStr"/>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK121" t="inlineStr"/>
       <c r="AL121" t="inlineStr"/>
       <c r="AM121" t="inlineStr"/>
@@ -15965,8 +16861,16 @@
       <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="inlineStr"/>
       <c r="AH122" t="inlineStr"/>
-      <c r="AI122" t="inlineStr"/>
-      <c r="AJ122" t="inlineStr"/>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK122" t="inlineStr"/>
       <c r="AL122" t="inlineStr"/>
       <c r="AM122" t="inlineStr"/>
@@ -16088,8 +16992,16 @@
       <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="inlineStr"/>
       <c r="AH123" t="inlineStr"/>
-      <c r="AI123" t="inlineStr"/>
-      <c r="AJ123" t="inlineStr"/>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK123" t="inlineStr"/>
       <c r="AL123" t="inlineStr"/>
       <c r="AM123" t="inlineStr"/>
@@ -16211,8 +17123,16 @@
       <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="inlineStr"/>
       <c r="AH124" t="inlineStr"/>
-      <c r="AI124" t="inlineStr"/>
-      <c r="AJ124" t="inlineStr"/>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK124" t="inlineStr"/>
       <c r="AL124" t="inlineStr"/>
       <c r="AM124" t="inlineStr"/>
@@ -16334,8 +17254,16 @@
       <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="inlineStr"/>
       <c r="AH125" t="inlineStr"/>
-      <c r="AI125" t="inlineStr"/>
-      <c r="AJ125" t="inlineStr"/>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK125" t="inlineStr"/>
       <c r="AL125" t="inlineStr"/>
       <c r="AM125" t="inlineStr"/>
@@ -16457,8 +17385,16 @@
       <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="inlineStr"/>
       <c r="AH126" t="inlineStr"/>
-      <c r="AI126" t="inlineStr"/>
-      <c r="AJ126" t="inlineStr"/>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK126" t="inlineStr">
         <is>
           <t>IOCL FEROKE</t>
@@ -16584,8 +17520,16 @@
       <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="inlineStr"/>
       <c r="AH127" t="inlineStr"/>
-      <c r="AI127" t="inlineStr"/>
-      <c r="AJ127" t="inlineStr"/>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK127" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -16711,8 +17655,16 @@
       <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="inlineStr"/>
       <c r="AH128" t="inlineStr"/>
-      <c r="AI128" t="inlineStr"/>
-      <c r="AJ128" t="inlineStr"/>
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK128" t="inlineStr">
         <is>
           <t>HO</t>
@@ -16838,8 +17790,16 @@
       <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="inlineStr"/>
       <c r="AH129" t="inlineStr"/>
-      <c r="AI129" t="inlineStr"/>
-      <c r="AJ129" t="inlineStr"/>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK129" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -16965,8 +17925,16 @@
       <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="inlineStr"/>
       <c r="AH130" t="inlineStr"/>
-      <c r="AI130" t="inlineStr"/>
-      <c r="AJ130" t="inlineStr"/>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK130" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -17092,8 +18060,16 @@
       <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="inlineStr"/>
       <c r="AH131" t="inlineStr"/>
-      <c r="AI131" t="inlineStr"/>
-      <c r="AJ131" t="inlineStr"/>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK131" t="inlineStr">
         <is>
           <t>IOCL FEROKE</t>
@@ -17219,8 +18195,16 @@
       <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="inlineStr"/>
       <c r="AH132" t="inlineStr"/>
-      <c r="AI132" t="inlineStr"/>
-      <c r="AJ132" t="inlineStr"/>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK132" t="inlineStr"/>
       <c r="AL132" t="inlineStr"/>
       <c r="AM132" t="inlineStr"/>
@@ -17342,8 +18326,16 @@
       <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="inlineStr"/>
       <c r="AH133" t="inlineStr"/>
-      <c r="AI133" t="inlineStr"/>
-      <c r="AJ133" t="inlineStr"/>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK133" t="inlineStr">
         <is>
           <t>IOCL FEROKE</t>
@@ -17469,8 +18461,16 @@
       <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="inlineStr"/>
       <c r="AH134" t="inlineStr"/>
-      <c r="AI134" t="inlineStr"/>
-      <c r="AJ134" t="inlineStr"/>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK134" t="inlineStr"/>
       <c r="AL134" t="inlineStr"/>
       <c r="AM134" t="inlineStr"/>
@@ -17592,8 +18592,16 @@
       <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="inlineStr"/>
       <c r="AH135" t="inlineStr"/>
-      <c r="AI135" t="inlineStr"/>
-      <c r="AJ135" t="inlineStr"/>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK135" t="inlineStr"/>
       <c r="AL135" t="inlineStr"/>
       <c r="AM135" t="inlineStr"/>
@@ -17715,8 +18723,16 @@
       <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="inlineStr"/>
       <c r="AH136" t="inlineStr"/>
-      <c r="AI136" t="inlineStr"/>
-      <c r="AJ136" t="inlineStr"/>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK136" t="inlineStr"/>
       <c r="AL136" t="inlineStr"/>
       <c r="AM136" t="inlineStr"/>
@@ -17838,8 +18854,16 @@
       <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="inlineStr"/>
       <c r="AH137" t="inlineStr"/>
-      <c r="AI137" t="inlineStr"/>
-      <c r="AJ137" t="inlineStr"/>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK137" t="inlineStr"/>
       <c r="AL137" t="inlineStr"/>
       <c r="AM137" t="inlineStr"/>
@@ -17961,8 +18985,16 @@
       <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="inlineStr"/>
       <c r="AH138" t="inlineStr"/>
-      <c r="AI138" t="inlineStr"/>
-      <c r="AJ138" t="inlineStr"/>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ138" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK138" t="inlineStr"/>
       <c r="AL138" t="inlineStr"/>
       <c r="AM138" t="inlineStr"/>
@@ -18084,8 +19116,16 @@
       <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="inlineStr"/>
       <c r="AH139" t="inlineStr"/>
-      <c r="AI139" t="inlineStr"/>
-      <c r="AJ139" t="inlineStr"/>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK139" t="inlineStr"/>
       <c r="AL139" t="inlineStr"/>
       <c r="AM139" t="inlineStr"/>
@@ -18207,8 +19247,16 @@
       <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="inlineStr"/>
       <c r="AH140" t="inlineStr"/>
-      <c r="AI140" t="inlineStr"/>
-      <c r="AJ140" t="inlineStr"/>
+      <c r="AI140" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK140" t="inlineStr"/>
       <c r="AL140" t="inlineStr"/>
       <c r="AM140" t="inlineStr"/>
@@ -18330,8 +19378,16 @@
       <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="inlineStr"/>
       <c r="AH141" t="inlineStr"/>
-      <c r="AI141" t="inlineStr"/>
-      <c r="AJ141" t="inlineStr"/>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK141" t="inlineStr"/>
       <c r="AL141" t="inlineStr"/>
       <c r="AM141" t="inlineStr"/>
@@ -18453,8 +19509,16 @@
       <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="inlineStr"/>
       <c r="AH142" t="inlineStr"/>
-      <c r="AI142" t="inlineStr"/>
-      <c r="AJ142" t="inlineStr"/>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK142" t="inlineStr"/>
       <c r="AL142" t="inlineStr"/>
       <c r="AM142" t="inlineStr"/>
@@ -18577,8 +19641,16 @@
       <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="inlineStr"/>
       <c r="AH143" t="inlineStr"/>
-      <c r="AI143" t="inlineStr"/>
-      <c r="AJ143" t="inlineStr"/>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK143" t="inlineStr"/>
       <c r="AL143" t="inlineStr"/>
       <c r="AM143" t="inlineStr"/>
@@ -18700,8 +19772,16 @@
       <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="inlineStr"/>
       <c r="AH144" t="inlineStr"/>
-      <c r="AI144" t="inlineStr"/>
-      <c r="AJ144" t="inlineStr"/>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK144" t="inlineStr"/>
       <c r="AL144" t="inlineStr"/>
       <c r="AM144" t="inlineStr"/>
@@ -18823,8 +19903,16 @@
       <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="inlineStr"/>
       <c r="AH145" t="inlineStr"/>
-      <c r="AI145" t="inlineStr"/>
-      <c r="AJ145" t="inlineStr"/>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK145" t="inlineStr"/>
       <c r="AL145" t="inlineStr"/>
       <c r="AM145" t="inlineStr"/>
@@ -18946,8 +20034,16 @@
       <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="inlineStr"/>
       <c r="AH146" t="inlineStr"/>
-      <c r="AI146" t="inlineStr"/>
-      <c r="AJ146" t="inlineStr"/>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK146" t="inlineStr"/>
       <c r="AL146" t="inlineStr"/>
       <c r="AM146" t="inlineStr"/>
@@ -19069,8 +20165,16 @@
       <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="inlineStr"/>
       <c r="AH147" t="inlineStr"/>
-      <c r="AI147" t="inlineStr"/>
-      <c r="AJ147" t="inlineStr"/>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK147" t="inlineStr"/>
       <c r="AL147" t="inlineStr"/>
       <c r="AM147" t="inlineStr"/>
@@ -19192,8 +20296,16 @@
       <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="inlineStr"/>
       <c r="AH148" t="inlineStr"/>
-      <c r="AI148" t="inlineStr"/>
-      <c r="AJ148" t="inlineStr"/>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK148" t="inlineStr"/>
       <c r="AL148" t="inlineStr"/>
       <c r="AM148" t="inlineStr"/>
@@ -19315,8 +20427,16 @@
       <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="inlineStr"/>
       <c r="AH149" t="inlineStr"/>
-      <c r="AI149" t="inlineStr"/>
-      <c r="AJ149" t="inlineStr"/>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK149" t="inlineStr"/>
       <c r="AL149" t="inlineStr"/>
       <c r="AM149" t="inlineStr"/>
@@ -19438,8 +20558,16 @@
       <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="inlineStr"/>
       <c r="AH150" t="inlineStr"/>
-      <c r="AI150" t="inlineStr"/>
-      <c r="AJ150" t="inlineStr"/>
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK150" t="inlineStr"/>
       <c r="AL150" t="inlineStr"/>
       <c r="AM150" t="inlineStr"/>
@@ -19561,8 +20689,16 @@
       <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="inlineStr"/>
       <c r="AH151" t="inlineStr"/>
-      <c r="AI151" t="inlineStr"/>
-      <c r="AJ151" t="inlineStr"/>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK151" t="inlineStr"/>
       <c r="AL151" t="inlineStr"/>
       <c r="AM151" t="inlineStr"/>
@@ -19684,8 +20820,16 @@
       <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="inlineStr"/>
       <c r="AH152" t="inlineStr"/>
-      <c r="AI152" t="inlineStr"/>
-      <c r="AJ152" t="inlineStr"/>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK152" t="inlineStr"/>
       <c r="AL152" t="inlineStr"/>
       <c r="AM152" t="inlineStr"/>
@@ -19807,8 +20951,16 @@
       <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="inlineStr"/>
       <c r="AH153" t="inlineStr"/>
-      <c r="AI153" t="inlineStr"/>
-      <c r="AJ153" t="inlineStr"/>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK153" t="inlineStr"/>
       <c r="AL153" t="inlineStr"/>
       <c r="AM153" t="inlineStr"/>
@@ -19930,8 +21082,16 @@
       <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="inlineStr"/>
       <c r="AH154" t="inlineStr"/>
-      <c r="AI154" t="inlineStr"/>
-      <c r="AJ154" t="inlineStr"/>
+      <c r="AI154" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ154" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK154" t="inlineStr"/>
       <c r="AL154" t="inlineStr"/>
       <c r="AM154" t="inlineStr"/>
@@ -20053,8 +21213,16 @@
       <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="inlineStr"/>
       <c r="AH155" t="inlineStr"/>
-      <c r="AI155" t="inlineStr"/>
-      <c r="AJ155" t="inlineStr"/>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK155" t="inlineStr"/>
       <c r="AL155" t="inlineStr"/>
       <c r="AM155" t="inlineStr"/>
@@ -20176,8 +21344,16 @@
       <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="inlineStr"/>
       <c r="AH156" t="inlineStr"/>
-      <c r="AI156" t="inlineStr"/>
-      <c r="AJ156" t="inlineStr"/>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK156" t="inlineStr"/>
       <c r="AL156" t="inlineStr"/>
       <c r="AM156" t="inlineStr"/>
@@ -20297,8 +21473,16 @@
       <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="inlineStr"/>
       <c r="AH157" t="inlineStr"/>
-      <c r="AI157" t="inlineStr"/>
-      <c r="AJ157" t="inlineStr"/>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK157" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -20424,8 +21608,16 @@
       <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="inlineStr"/>
       <c r="AH158" t="inlineStr"/>
-      <c r="AI158" t="inlineStr"/>
-      <c r="AJ158" t="inlineStr"/>
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ158" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK158" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -20551,8 +21743,16 @@
       <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="inlineStr"/>
       <c r="AH159" t="inlineStr"/>
-      <c r="AI159" t="inlineStr"/>
-      <c r="AJ159" t="inlineStr"/>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK159" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -20678,8 +21878,16 @@
       <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="inlineStr"/>
       <c r="AH160" t="inlineStr"/>
-      <c r="AI160" t="inlineStr"/>
-      <c r="AJ160" t="inlineStr"/>
+      <c r="AI160" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ160" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK160" t="inlineStr">
         <is>
           <t>ONGC IPSHEM</t>
@@ -20805,8 +22013,16 @@
       <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="inlineStr"/>
       <c r="AH161" t="inlineStr"/>
-      <c r="AI161" t="inlineStr"/>
-      <c r="AJ161" t="inlineStr"/>
+      <c r="AI161" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK161" t="inlineStr"/>
       <c r="AL161" t="inlineStr"/>
       <c r="AM161" t="inlineStr"/>
@@ -20932,8 +22148,16 @@
       <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="inlineStr"/>
       <c r="AH162" t="inlineStr"/>
-      <c r="AI162" t="inlineStr"/>
-      <c r="AJ162" t="inlineStr"/>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK162" t="inlineStr">
         <is>
           <t>ONGC IPSHEM</t>
@@ -21059,8 +22283,16 @@
       <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="inlineStr"/>
       <c r="AH163" t="inlineStr"/>
-      <c r="AI163" t="inlineStr"/>
-      <c r="AJ163" t="inlineStr"/>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK163" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -21178,8 +22410,16 @@
       <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="inlineStr"/>
       <c r="AH164" t="inlineStr"/>
-      <c r="AI164" t="inlineStr"/>
-      <c r="AJ164" t="inlineStr"/>
+      <c r="AI164" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK164" t="inlineStr"/>
       <c r="AL164" t="inlineStr"/>
       <c r="AM164" t="inlineStr"/>
@@ -21293,8 +22533,16 @@
       <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="inlineStr"/>
       <c r="AH165" t="inlineStr"/>
-      <c r="AI165" t="inlineStr"/>
-      <c r="AJ165" t="inlineStr"/>
+      <c r="AI165" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK165" t="inlineStr"/>
       <c r="AL165" t="inlineStr"/>
       <c r="AM165" t="inlineStr"/>
@@ -21418,8 +22666,16 @@
       <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="inlineStr"/>
       <c r="AH166" t="inlineStr"/>
-      <c r="AI166" t="inlineStr"/>
-      <c r="AJ166" t="inlineStr"/>
+      <c r="AI166" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ166" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK166" t="inlineStr">
         <is>
           <t>ONGC ELECTRICAL</t>
@@ -21547,8 +22803,16 @@
       <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="inlineStr"/>
       <c r="AH167" t="inlineStr"/>
-      <c r="AI167" t="inlineStr"/>
-      <c r="AJ167" t="inlineStr"/>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK167" t="inlineStr"/>
       <c r="AL167" t="inlineStr"/>
       <c r="AM167" t="inlineStr"/>
@@ -21672,8 +22936,16 @@
       <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="inlineStr"/>
       <c r="AH168" t="inlineStr"/>
-      <c r="AI168" t="inlineStr"/>
-      <c r="AJ168" t="inlineStr"/>
+      <c r="AI168" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ168" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK168" t="inlineStr">
         <is>
           <t>ONGC ELECTRICAL</t>
@@ -21801,8 +23073,16 @@
       <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="inlineStr"/>
       <c r="AH169" t="inlineStr"/>
-      <c r="AI169" t="inlineStr"/>
-      <c r="AJ169" t="inlineStr"/>
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK169" t="inlineStr"/>
       <c r="AL169" t="inlineStr"/>
       <c r="AM169" t="inlineStr"/>
@@ -21926,8 +23206,16 @@
       <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="inlineStr"/>
       <c r="AH170" t="inlineStr"/>
-      <c r="AI170" t="inlineStr"/>
-      <c r="AJ170" t="inlineStr"/>
+      <c r="AI170" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK170" t="inlineStr"/>
       <c r="AL170" t="inlineStr"/>
       <c r="AM170" t="inlineStr"/>
@@ -22051,8 +23339,16 @@
       <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="inlineStr"/>
       <c r="AH171" t="inlineStr"/>
-      <c r="AI171" t="inlineStr"/>
-      <c r="AJ171" t="inlineStr"/>
+      <c r="AI171" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ171" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK171" t="inlineStr"/>
       <c r="AL171" t="inlineStr"/>
       <c r="AM171" t="inlineStr"/>
@@ -22178,8 +23474,16 @@
       <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="inlineStr"/>
       <c r="AH172" t="inlineStr"/>
-      <c r="AI172" t="inlineStr"/>
-      <c r="AJ172" t="inlineStr"/>
+      <c r="AI172" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ172" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK172" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -22308,8 +23612,16 @@
       <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="inlineStr"/>
       <c r="AH173" t="inlineStr"/>
-      <c r="AI173" t="inlineStr"/>
-      <c r="AJ173" t="inlineStr"/>
+      <c r="AI173" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ173" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK173" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -22437,8 +23749,16 @@
       <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="inlineStr"/>
       <c r="AH174" t="inlineStr"/>
-      <c r="AI174" t="inlineStr"/>
-      <c r="AJ174" t="inlineStr"/>
+      <c r="AI174" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ174" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK174" t="inlineStr"/>
       <c r="AL174" t="inlineStr"/>
       <c r="AM174" t="inlineStr"/>
@@ -22562,8 +23882,16 @@
       <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="inlineStr"/>
       <c r="AH175" t="inlineStr"/>
-      <c r="AI175" t="inlineStr"/>
-      <c r="AJ175" t="inlineStr"/>
+      <c r="AI175" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ175" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK175" t="inlineStr"/>
       <c r="AL175" t="inlineStr"/>
       <c r="AM175" t="inlineStr"/>
@@ -22687,8 +24015,16 @@
       <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="inlineStr"/>
       <c r="AH176" t="inlineStr"/>
-      <c r="AI176" t="inlineStr"/>
-      <c r="AJ176" t="inlineStr"/>
+      <c r="AI176" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ176" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK176" t="inlineStr">
         <is>
           <t>ONGC IPSHEM</t>
@@ -22816,8 +24152,16 @@
       <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="inlineStr"/>
       <c r="AH177" t="inlineStr"/>
-      <c r="AI177" t="inlineStr"/>
-      <c r="AJ177" t="inlineStr"/>
+      <c r="AI177" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ177" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK177" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -22945,8 +24289,16 @@
       <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="inlineStr"/>
       <c r="AH178" t="inlineStr"/>
-      <c r="AI178" t="inlineStr"/>
-      <c r="AJ178" t="inlineStr"/>
+      <c r="AI178" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ178" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK178" t="inlineStr">
         <is>
           <t>ONGC IPSHEM</t>
@@ -23074,8 +24426,16 @@
       <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="inlineStr"/>
       <c r="AH179" t="inlineStr"/>
-      <c r="AI179" t="inlineStr"/>
-      <c r="AJ179" t="inlineStr"/>
+      <c r="AI179" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ179" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK179" t="inlineStr"/>
       <c r="AL179" t="inlineStr"/>
       <c r="AM179" t="inlineStr"/>
@@ -23199,8 +24559,16 @@
       <c r="AF180" t="inlineStr"/>
       <c r="AG180" t="inlineStr"/>
       <c r="AH180" t="inlineStr"/>
-      <c r="AI180" t="inlineStr"/>
-      <c r="AJ180" t="inlineStr"/>
+      <c r="AI180" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ180" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK180" t="inlineStr"/>
       <c r="AL180" t="inlineStr"/>
       <c r="AM180" t="inlineStr"/>
@@ -23324,8 +24692,16 @@
       <c r="AF181" t="inlineStr"/>
       <c r="AG181" t="inlineStr"/>
       <c r="AH181" t="inlineStr"/>
-      <c r="AI181" t="inlineStr"/>
-      <c r="AJ181" t="inlineStr"/>
+      <c r="AI181" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ181" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK181" t="inlineStr"/>
       <c r="AL181" t="inlineStr"/>
       <c r="AM181" t="inlineStr"/>
@@ -23449,8 +24825,16 @@
       <c r="AF182" t="inlineStr"/>
       <c r="AG182" t="inlineStr"/>
       <c r="AH182" t="inlineStr"/>
-      <c r="AI182" t="inlineStr"/>
-      <c r="AJ182" t="inlineStr"/>
+      <c r="AI182" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ182" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK182" t="inlineStr">
         <is>
           <t>ONGC ELECTRICAL</t>
@@ -23578,8 +24962,16 @@
       <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="inlineStr"/>
       <c r="AH183" t="inlineStr"/>
-      <c r="AI183" t="inlineStr"/>
-      <c r="AJ183" t="inlineStr"/>
+      <c r="AI183" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ183" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK183" t="inlineStr"/>
       <c r="AL183" t="inlineStr"/>
       <c r="AM183" t="inlineStr"/>
@@ -23703,8 +25095,16 @@
       <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="inlineStr"/>
       <c r="AH184" t="inlineStr"/>
-      <c r="AI184" t="inlineStr"/>
-      <c r="AJ184" t="inlineStr"/>
+      <c r="AI184" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ184" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK184" t="inlineStr"/>
       <c r="AL184" t="inlineStr"/>
       <c r="AM184" t="inlineStr"/>
@@ -23830,12 +25230,12 @@
       <c r="AH185" t="inlineStr"/>
       <c r="AI185" t="inlineStr">
         <is>
-          <t>ACCEPTED</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>ACCEPTED</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -23965,8 +25365,16 @@
       <c r="AF186" t="inlineStr"/>
       <c r="AG186" t="inlineStr"/>
       <c r="AH186" t="inlineStr"/>
-      <c r="AI186" t="inlineStr"/>
-      <c r="AJ186" t="inlineStr"/>
+      <c r="AI186" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ186" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK186" t="inlineStr"/>
       <c r="AL186" t="inlineStr"/>
       <c r="AM186" t="inlineStr"/>
@@ -24090,8 +25498,16 @@
       <c r="AF187" t="inlineStr"/>
       <c r="AG187" t="inlineStr"/>
       <c r="AH187" t="inlineStr"/>
-      <c r="AI187" t="inlineStr"/>
-      <c r="AJ187" t="inlineStr"/>
+      <c r="AI187" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ187" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK187" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -24223,8 +25639,16 @@
       <c r="AF188" t="inlineStr"/>
       <c r="AG188" t="inlineStr"/>
       <c r="AH188" t="inlineStr"/>
-      <c r="AI188" t="inlineStr"/>
-      <c r="AJ188" t="inlineStr"/>
+      <c r="AI188" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ188" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK188" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -24356,8 +25780,16 @@
       <c r="AF189" t="inlineStr"/>
       <c r="AG189" t="inlineStr"/>
       <c r="AH189" t="inlineStr"/>
-      <c r="AI189" t="inlineStr"/>
-      <c r="AJ189" t="inlineStr"/>
+      <c r="AI189" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ189" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK189" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -24489,8 +25921,16 @@
       <c r="AF190" t="inlineStr"/>
       <c r="AG190" t="inlineStr"/>
       <c r="AH190" t="inlineStr"/>
-      <c r="AI190" t="inlineStr"/>
-      <c r="AJ190" t="inlineStr"/>
+      <c r="AI190" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ190" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK190" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -24622,8 +26062,16 @@
       <c r="AF191" t="inlineStr"/>
       <c r="AG191" t="inlineStr"/>
       <c r="AH191" t="inlineStr"/>
-      <c r="AI191" t="inlineStr"/>
-      <c r="AJ191" t="inlineStr"/>
+      <c r="AI191" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ191" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK191" t="inlineStr">
         <is>
           <t>GOA</t>
@@ -24755,8 +26203,16 @@
       <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="inlineStr"/>
       <c r="AH192" t="inlineStr"/>
-      <c r="AI192" t="inlineStr"/>
-      <c r="AJ192" t="inlineStr"/>
+      <c r="AI192" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AJ192" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
       <c r="AK192" t="inlineStr">
         <is>
           <t>GOA</t>
